--- a/file/table/DAPC_AIALayerName.xlsx
+++ b/file/table/DAPC_AIALayerName.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29022"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BC6C27-4B04-47E8-BBC7-E04589CB08BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B201D16-2648-4405-877B-7945B2388F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="819" activeTab="4" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
+    <workbookView xWindow="5100" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="4" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
   </bookViews>
   <sheets>
     <sheet name="Level1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6195" uniqueCount="3802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6084" uniqueCount="3808">
   <si>
     <t>A</t>
   </si>
@@ -11514,6 +11514,24 @@
   </si>
   <si>
     <t>Layer - name</t>
+  </si>
+  <si>
+    <t>cyan</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>Magenta</t>
+  </si>
+  <si>
+    <t>HIDDEN2</t>
   </si>
 </sst>
 </file>
@@ -15169,8 +15187,8 @@
     <col min="1" max="1" width="8.33203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="19.1328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="69.3984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.86328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="69.3984375" style="1" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11.1328125" style="11" customWidth="1"/>
     <col min="7" max="7" width="14.06640625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.06640625" style="11" bestFit="1" customWidth="1"/>
@@ -15227,7 +15245,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -15241,7 +15259,7 @@
         <v>162</v>
       </c>
       <c r="E3" s="1" t="str">
-        <f>_xlfn.CONCAT(B3," (",C3," - ",D3,")")</f>
+        <f t="shared" ref="E3:E66" si="0">_xlfn.CONCAT(B3," (",C3," - ",D3,")")</f>
         <v>A-AREA (Arquitectura - Área)</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -15251,7 +15269,7 @@
         <v>3799</v>
       </c>
       <c r="H3" s="11">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="I3" s="11">
         <v>0</v>
@@ -15280,7 +15298,7 @@
         <v>727</v>
       </c>
       <c r="E4" s="1" t="str">
-        <f>_xlfn.CONCAT(B4," (",C4," - ",D4,")")</f>
+        <f t="shared" si="0"/>
         <v>A-AREA-OCCP (Arquitectura - Área: nombres de ocupantes o empleados)</v>
       </c>
       <c r="I4" s="11">
@@ -15310,7 +15328,7 @@
         <v>168</v>
       </c>
       <c r="E5" s="1" t="str">
-        <f>_xlfn.CONCAT(B5," (",C5," - ",D5,")")</f>
+        <f t="shared" si="0"/>
         <v>A-BARR (Arquitectura - Barrera)</v>
       </c>
       <c r="I5" s="11">
@@ -15340,7 +15358,7 @@
         <v>731</v>
       </c>
       <c r="E6" s="1" t="str">
-        <f>_xlfn.CONCAT(B6," (",C6," - ",D6,")")</f>
+        <f t="shared" si="0"/>
         <v>A-BARR-AIR~ (Arquitectura - Barrera: aire)</v>
       </c>
       <c r="I6" s="11">
@@ -15356,7 +15374,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A7" s="9">
         <v>1</v>
       </c>
@@ -15370,15 +15388,18 @@
         <v>234</v>
       </c>
       <c r="E7" s="1" t="str">
-        <f>_xlfn.CONCAT(B7," (",C7," - ",D7,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG (Arquitectura - Techo)</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>3800</v>
+      <c r="F7" s="11">
+        <v>226</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H7" s="11">
+        <v>0.25</v>
+      </c>
       <c r="I7" s="11">
         <v>0</v>
       </c>
@@ -15406,7 +15427,7 @@
         <v>735</v>
       </c>
       <c r="E8" s="1" t="str">
-        <f>_xlfn.CONCAT(B8," (",C8," - ",D8,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG-ACCS (Arquitectura - Techo: acceso)</v>
       </c>
       <c r="I8" s="11">
@@ -15436,7 +15457,7 @@
         <v>738</v>
       </c>
       <c r="E9" s="1" t="str">
-        <f>_xlfn.CONCAT(B9," (",C9," - ",D9,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG-GRID (Arquitectura - Techo: rejilla)</v>
       </c>
       <c r="I9" s="11">
@@ -15466,7 +15487,7 @@
         <v>741</v>
       </c>
       <c r="E10" s="1" t="str">
-        <f>_xlfn.CONCAT(B10," (",C10," - ",D10,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG-OPNG (Arquitectura - Techo: aberturas)</v>
       </c>
       <c r="I10" s="11">
@@ -15496,7 +15517,7 @@
         <v>744</v>
       </c>
       <c r="E11" s="1" t="str">
-        <f>_xlfn.CONCAT(B11," (",C11," - ",D11,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG-SUSP (Arquitectura - Techo: elementos suspendidos)</v>
       </c>
       <c r="I11" s="11">
@@ -15526,7 +15547,7 @@
         <v>747</v>
       </c>
       <c r="E12" s="1" t="str">
-        <f>_xlfn.CONCAT(B12," (",C12," - ",D12,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CLNG-TEES (Arquitectura - Techo: tes principales)</v>
       </c>
       <c r="I12" s="11">
@@ -15542,7 +15563,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A13" s="9">
         <v>1</v>
       </c>
@@ -15556,17 +15577,17 @@
         <v>255</v>
       </c>
       <c r="E13" s="1" t="str">
-        <f>_xlfn.CONCAT(B13," (",C13," - ",D13,")")</f>
+        <f t="shared" si="0"/>
         <v>A-COLS (Arquitectura - Columnas)</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>3800</v>
+        <v>3803</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>3799</v>
       </c>
       <c r="H13" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
@@ -15595,7 +15616,7 @@
         <v>264</v>
       </c>
       <c r="E14" s="1" t="str">
-        <f>_xlfn.CONCAT(B14," (",C14," - ",D14,")")</f>
+        <f t="shared" si="0"/>
         <v>A-CONV (Arquitectura - Sistemas de transporte)</v>
       </c>
       <c r="I14" s="11">
@@ -15611,7 +15632,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A15" s="9">
         <v>1</v>
       </c>
@@ -15625,15 +15646,18 @@
         <v>300</v>
       </c>
       <c r="E15" s="1" t="str">
-        <f>_xlfn.CONCAT(B15," (",C15," - ",D15,")")</f>
+        <f t="shared" si="0"/>
         <v>A-DOOR (Arquitectura - Puertas)</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>3800</v>
+      <c r="F15" s="11">
+        <v>251</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H15" s="11">
+        <v>0.18</v>
+      </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
@@ -15661,7 +15685,7 @@
         <v>753</v>
       </c>
       <c r="E16" s="1" t="str">
-        <f>_xlfn.CONCAT(B16," (",C16," - ",D16,")")</f>
+        <f t="shared" si="0"/>
         <v>A-DOOR-FULL (Arquitectura - Puertas: altura completa (batientes y de hoja))</v>
       </c>
       <c r="I16" s="11">
@@ -15691,7 +15715,7 @@
         <v>756</v>
       </c>
       <c r="E17" s="1" t="str">
-        <f>_xlfn.CONCAT(B17," (",C17," - ",D17,")")</f>
+        <f t="shared" si="0"/>
         <v>A-DOOR-PRHT (Arquitectura - Puertas: altura parcial (batientes y de hoja))</v>
       </c>
       <c r="I17" s="11">
@@ -15707,7 +15731,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <v>1</v>
       </c>
@@ -15721,15 +15745,18 @@
         <v>332</v>
       </c>
       <c r="E18" s="1" t="str">
-        <f>_xlfn.CONCAT(B18," (",C18," - ",D18,")")</f>
+        <f t="shared" si="0"/>
         <v>A-EQPM (Arquitectura - Equipo)</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>3800</v>
+      <c r="F18" s="11">
+        <v>46</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H18" s="11">
+        <v>0.18</v>
+      </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
@@ -15757,7 +15784,7 @@
         <v>760</v>
       </c>
       <c r="E19" s="1" t="str">
-        <f>_xlfn.CONCAT(B19," (",C19," - ",D19,")")</f>
+        <f t="shared" si="0"/>
         <v>A-EQPM-ACCS (Arquitectura - Equipo: acceso)</v>
       </c>
       <c r="I19" s="11">
@@ -15787,7 +15814,7 @@
         <v>763</v>
       </c>
       <c r="E20" s="1" t="str">
-        <f>_xlfn.CONCAT(B20," (",C20," - ",D20,")")</f>
+        <f t="shared" si="0"/>
         <v>A-EQPM-FIXD (Arquitectura - Equipo: fijo)</v>
       </c>
       <c r="I20" s="11">
@@ -15817,7 +15844,7 @@
         <v>766</v>
       </c>
       <c r="E21" s="1" t="str">
-        <f>_xlfn.CONCAT(B21," (",C21," - ",D21,")")</f>
+        <f t="shared" si="0"/>
         <v>A-EQPM-OVHD (Arquitectura - Equipo: suspendido)</v>
       </c>
       <c r="I21" s="11">
@@ -15833,7 +15860,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <v>1</v>
       </c>
@@ -15847,15 +15874,18 @@
         <v>355</v>
       </c>
       <c r="E22" s="1" t="str">
-        <f>_xlfn.CONCAT(B22," (",C22," - ",D22,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR (Arquitectura - Piso)</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>3800</v>
+      <c r="F22" s="11">
+        <v>252</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H22" s="11">
+        <v>0.35</v>
+      </c>
       <c r="I22" s="11">
         <v>0</v>
       </c>
@@ -15883,7 +15913,7 @@
         <v>770</v>
       </c>
       <c r="E23" s="1" t="str">
-        <f>_xlfn.CONCAT(B23," (",C23," - ",D23,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-CSWK (Arquitectura - Piso: carpintería)</v>
       </c>
       <c r="I23" s="11">
@@ -15913,7 +15943,7 @@
         <v>773</v>
       </c>
       <c r="E24" s="1" t="str">
-        <f>_xlfn.CONCAT(B24," (",C24," - ",D24,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-EVTR (Arquitectura - Piso: cabinas y equipo de ascensor)</v>
       </c>
       <c r="I24" s="11">
@@ -15943,7 +15973,7 @@
         <v>776</v>
       </c>
       <c r="E25" s="1" t="str">
-        <f>_xlfn.CONCAT(B25," (",C25," - ",D25,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-FIXT (Arquitectura - Piso: accesorios (fontanería))</v>
       </c>
       <c r="I25" s="11">
@@ -15973,7 +16003,7 @@
         <v>779</v>
       </c>
       <c r="E26" s="1" t="str">
-        <f>_xlfn.CONCAT(B26," (",C26," - ",D26,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-HRAL (Arquitectura - Piso: pasamanos/barandillas)</v>
       </c>
       <c r="I26" s="11">
@@ -15991,7 +16021,7 @@
     </row>
     <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>2955</v>
@@ -16003,8 +16033,17 @@
         <v>782</v>
       </c>
       <c r="E27" s="1" t="str">
-        <f>_xlfn.CONCAT(B27," (",C27," - ",D27,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-LEVL (Arquitectura - Piso: cambios de nivel (rampas, fosos, depresiones))</v>
+      </c>
+      <c r="F27" s="11">
+        <v>145</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>3799</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.18</v>
       </c>
       <c r="I27" s="11">
         <v>0</v>
@@ -16033,7 +16072,7 @@
         <v>785</v>
       </c>
       <c r="E28" s="1" t="str">
-        <f>_xlfn.CONCAT(B28," (",C28," - ",D28,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-OTLN (Arquitectura - Piso: contorno)</v>
       </c>
       <c r="I28" s="11">
@@ -16063,7 +16102,7 @@
         <v>788</v>
       </c>
       <c r="E29" s="1" t="str">
-        <f>_xlfn.CONCAT(B29," (",C29," - ",D29,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-OVHD (Arquitectura - Piso: suspendido)</v>
       </c>
       <c r="I29" s="11">
@@ -16093,7 +16132,7 @@
         <v>791</v>
       </c>
       <c r="E30" s="1" t="str">
-        <f>_xlfn.CONCAT(B30," (",C30," - ",D30,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-RAIS (Arquitectura - Piso: elevado)</v>
       </c>
       <c r="I30" s="11">
@@ -16123,7 +16162,7 @@
         <v>794</v>
       </c>
       <c r="E31" s="1" t="str">
-        <f>_xlfn.CONCAT(B31," (",C31," - ",D31,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-RISR (Arquitectura - Piso: contrahuellas)</v>
       </c>
       <c r="I31" s="11">
@@ -16153,7 +16192,7 @@
         <v>797</v>
       </c>
       <c r="E32" s="1" t="str">
-        <f>_xlfn.CONCAT(B32," (",C32," - ",D32,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-SIGN (Arquitectura - Piso: señalización)</v>
       </c>
       <c r="I32" s="11">
@@ -16183,7 +16222,7 @@
         <v>800</v>
       </c>
       <c r="E33" s="1" t="str">
-        <f>_xlfn.CONCAT(B33," (",C33," - ",D33,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-SPCL (Arquitectura - Piso: artículos especiales (accesorios para baños, vitrinas))</v>
       </c>
       <c r="I33" s="11">
@@ -16213,7 +16252,7 @@
         <v>803</v>
       </c>
       <c r="E34" s="1" t="str">
-        <f>_xlfn.CONCAT(B34," (",C34," - ",D34,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-STRS (Arquitectura - Piso: escalones de escaleras (escaleras mecánicas, escaleras de mano))</v>
       </c>
       <c r="I34" s="11">
@@ -16243,7 +16282,7 @@
         <v>806</v>
       </c>
       <c r="E35" s="1" t="str">
-        <f>_xlfn.CONCAT(B35," (",C35," - ",D35,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-TPTN (Arquitectura - Suelo: mamparas de baño)</v>
       </c>
       <c r="I35" s="11">
@@ -16273,7 +16312,7 @@
         <v>809</v>
       </c>
       <c r="E36" s="1" t="str">
-        <f>_xlfn.CONCAT(B36," (",C36," - ",D36,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FLOR-WDWK (Arquitectura - Suelo: carpintería arquitectónica)</v>
       </c>
       <c r="I36" s="11">
@@ -16289,7 +16328,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A37" s="9">
         <v>1</v>
       </c>
@@ -16303,15 +16342,18 @@
         <v>376</v>
       </c>
       <c r="E37" s="1" t="str">
-        <f>_xlfn.CONCAT(B37," (",C37," - ",D37,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN (Arquitectura - Mobiliario)</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>3800</v>
+      <c r="F37" s="11">
+        <v>46</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H37" s="11">
+        <v>0.18</v>
+      </c>
       <c r="I37" s="11">
         <v>0</v>
       </c>
@@ -16339,7 +16381,7 @@
         <v>813</v>
       </c>
       <c r="E38" s="1" t="str">
-        <f>_xlfn.CONCAT(B38," (",C38," - ",D38,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-FILE (Arquitectura - Mobiliario: archivadores)</v>
       </c>
       <c r="I38" s="11">
@@ -16369,7 +16411,7 @@
         <v>816</v>
       </c>
       <c r="E39" s="1" t="str">
-        <f>_xlfn.CONCAT(B39," (",C39," - ",D39,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-FIXD (Arquitectura - Mobiliario: fijo)</v>
       </c>
       <c r="I39" s="11">
@@ -16399,7 +16441,7 @@
         <v>819</v>
       </c>
       <c r="E40" s="1" t="str">
-        <f>_xlfn.CONCAT(B40," (",C40," - ",D40,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-FREE (Arquitectura - Mobiliario: independiente)</v>
       </c>
       <c r="I40" s="11">
@@ -16429,7 +16471,7 @@
         <v>822</v>
       </c>
       <c r="E41" s="1" t="str">
-        <f>_xlfn.CONCAT(B41," (",C41," - ",D41,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-PLNT (Arquitectura - Mobiliario: plantas)</v>
       </c>
       <c r="I41" s="11">
@@ -16459,7 +16501,7 @@
         <v>825</v>
       </c>
       <c r="E42" s="1" t="str">
-        <f>_xlfn.CONCAT(B42," (",C42," - ",D42,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-PNLS (Arquitectura - Mobiliario: paneles de sistema)</v>
       </c>
       <c r="I42" s="11">
@@ -16489,7 +16531,7 @@
         <v>828</v>
       </c>
       <c r="E43" s="1" t="str">
-        <f>_xlfn.CONCAT(B43," (",C43," - ",D43,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-SEAT (Arquitectura - Mobiliario: asientos)</v>
       </c>
       <c r="I43" s="11">
@@ -16519,7 +16561,7 @@
         <v>831</v>
       </c>
       <c r="E44" s="1" t="str">
-        <f>_xlfn.CONCAT(B44," (",C44," - ",D44,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-STOR (Arquitectura - Mobiliario: almacenamiento (sistema de componentes))</v>
       </c>
       <c r="I44" s="11">
@@ -16549,7 +16591,7 @@
         <v>834</v>
       </c>
       <c r="E45" s="1" t="str">
-        <f>_xlfn.CONCAT(B45," (",C45," - ",D45,")")</f>
+        <f t="shared" si="0"/>
         <v>A-FURN-WKSF (Arquitectura - Mobiliario: superficie de trabajo (sistema de componentes))</v>
       </c>
       <c r="I45" s="11">
@@ -16565,7 +16607,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A46" s="9">
         <v>1</v>
       </c>
@@ -16579,15 +16621,18 @@
         <v>2926</v>
       </c>
       <c r="E46" s="1" t="str">
-        <f>_xlfn.CONCAT(B46," (",C46," - ",D46,")")</f>
+        <f t="shared" si="0"/>
         <v>A-GLAZ (Arquitectura - Acristalamiento (muros transparentes y ventanas))</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>3800</v>
+        <v>3804</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H46" s="11">
+        <v>0.18</v>
+      </c>
       <c r="I46" s="11">
         <v>0</v>
       </c>
@@ -16615,7 +16660,7 @@
         <v>838</v>
       </c>
       <c r="E47" s="1" t="str">
-        <f>_xlfn.CONCAT(B47," (",C47," - ",D47,")")</f>
+        <f t="shared" si="0"/>
         <v>A-GLAZ-FULL (Arquitectura - Acristalamiento: altura completa)</v>
       </c>
       <c r="I47" s="11">
@@ -16645,7 +16690,7 @@
         <v>841</v>
       </c>
       <c r="E48" s="1" t="str">
-        <f>_xlfn.CONCAT(B48," (",C48," - ",D48,")")</f>
+        <f t="shared" si="0"/>
         <v>A-GLAZ-PRHT (Arquitectura - Acristalamiento: altura parcial)</v>
       </c>
       <c r="I48" s="11">
@@ -16675,7 +16720,7 @@
         <v>844</v>
       </c>
       <c r="E49" s="1" t="str">
-        <f>_xlfn.CONCAT(B49," (",C49," - ",D49,")")</f>
+        <f t="shared" si="0"/>
         <v>A-GLAZ-SILL (Arquitectura - Acristalamiento: alféizares de ventanas)</v>
       </c>
       <c r="I49" s="11">
@@ -16705,7 +16750,7 @@
         <v>402</v>
       </c>
       <c r="E50" s="1" t="str">
-        <f>_xlfn.CONCAT(B50," (",C50," - ",D50,")")</f>
+        <f t="shared" si="0"/>
         <v>A-HVAC (Arquitectura - Sistemas de climatización (HVAC))</v>
       </c>
       <c r="I50" s="11">
@@ -16735,7 +16780,7 @@
         <v>848</v>
       </c>
       <c r="E51" s="1" t="str">
-        <f>_xlfn.CONCAT(B51," (",C51," - ",D51,")")</f>
+        <f t="shared" si="0"/>
         <v>A-HVAC-RDFF (Arquitectura - Sistemas de climatización (HVAC): difusores de aire de retorno)</v>
       </c>
       <c r="I51" s="11">
@@ -16765,7 +16810,7 @@
         <v>851</v>
       </c>
       <c r="E52" s="1" t="str">
-        <f>_xlfn.CONCAT(B52," (",C52," - ",D52,")")</f>
+        <f t="shared" si="0"/>
         <v>A-HVAC-SDFF (Arquitectura - Sistemas de climatización (HVAC): difusores de suministro)</v>
       </c>
       <c r="I52" s="11">
@@ -16795,7 +16840,7 @@
         <v>447</v>
       </c>
       <c r="E53" s="1" t="str">
-        <f>_xlfn.CONCAT(B53," (",C53," - ",D53,")")</f>
+        <f t="shared" si="0"/>
         <v>A-LITE (Arquitectura - Iluminación)</v>
       </c>
       <c r="I53" s="11">
@@ -16811,7 +16856,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A54" s="9">
         <v>1</v>
       </c>
@@ -16825,15 +16870,18 @@
         <v>2911</v>
       </c>
       <c r="E54" s="1" t="str">
-        <f>_xlfn.CONCAT(B54," (",C54," - ",D54,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF (Arquitectura - Tejado)</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>3800</v>
+      <c r="F54" s="11">
+        <v>226</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H54" s="11">
+        <v>0.53</v>
+      </c>
       <c r="I54" s="11">
         <v>0</v>
       </c>
@@ -16861,7 +16909,7 @@
         <v>2912</v>
       </c>
       <c r="E55" s="1" t="str">
-        <f>_xlfn.CONCAT(B55," (",C55," - ",D55,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF-HRAL (Arquitectura - Tejado: pasamanos/barandillas)</v>
       </c>
       <c r="I55" s="11">
@@ -16891,7 +16939,7 @@
         <v>2913</v>
       </c>
       <c r="E56" s="1" t="str">
-        <f>_xlfn.CONCAT(B56," (",C56," - ",D56,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF-LEVL (Arquitectura - Tejado: cambios de nivel)</v>
       </c>
       <c r="I56" s="11">
@@ -16921,7 +16969,7 @@
         <v>2914</v>
       </c>
       <c r="E57" s="1" t="str">
-        <f>_xlfn.CONCAT(B57," (",C57," - ",D57,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF-OTLN (Arquitectura - Tejado: contorno)</v>
       </c>
       <c r="I57" s="11">
@@ -16951,7 +16999,7 @@
         <v>2915</v>
       </c>
       <c r="E58" s="1" t="str">
-        <f>_xlfn.CONCAT(B58," (",C58," - ",D58,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF-RISR (Arquitectura - Tejado: contrahuellas)</v>
       </c>
       <c r="I58" s="11">
@@ -16981,7 +17029,7 @@
         <v>2916</v>
       </c>
       <c r="E59" s="1" t="str">
-        <f>_xlfn.CONCAT(B59," (",C59," - ",D59,")")</f>
+        <f t="shared" si="0"/>
         <v>A-ROOF-STRS (Arquitectura - Tejado: peldaños de escalera)</v>
       </c>
       <c r="I59" s="11">
@@ -16997,7 +17045,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A60" s="9">
         <v>1</v>
       </c>
@@ -17011,7 +17059,7 @@
         <v>865</v>
       </c>
       <c r="E60" s="1" t="str">
-        <f>_xlfn.CONCAT(B60," (",C60," - ",D60,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL (Arquitectura - Paredes)</v>
       </c>
       <c r="F60" s="11" t="s">
@@ -17020,6 +17068,9 @@
       <c r="G60" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H60" s="11">
+        <v>0.6</v>
+      </c>
       <c r="I60" s="11">
         <v>0</v>
       </c>
@@ -17047,7 +17098,7 @@
         <v>868</v>
       </c>
       <c r="E61" s="1" t="str">
-        <f>_xlfn.CONCAT(B61," (",C61," - ",D61,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-CAVI (Arquitectura - Paredes: cámara de aire)</v>
       </c>
       <c r="I61" s="11">
@@ -17077,7 +17128,7 @@
         <v>871</v>
       </c>
       <c r="E62" s="1" t="str">
-        <f>_xlfn.CONCAT(B62," (",C62," - ",D62,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-CNTR (Arquitectura - Paredes: centro)</v>
       </c>
       <c r="I62" s="11">
@@ -17107,7 +17158,7 @@
         <v>874</v>
       </c>
       <c r="E63" s="1" t="str">
-        <f>_xlfn.CONCAT(B63," (",C63," - ",D63,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-CURT (Arquitectura - Paredes: cortina)</v>
       </c>
       <c r="I63" s="11">
@@ -17137,7 +17188,7 @@
         <v>877</v>
       </c>
       <c r="E64" s="1" t="str">
-        <f>_xlfn.CONCAT(B64," (",C64," - ",D64,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-FIRE (Arquitectura - Paredes: protección contra incendios)</v>
       </c>
       <c r="I64" s="11">
@@ -17167,7 +17218,7 @@
         <v>880</v>
       </c>
       <c r="E65" s="1" t="str">
-        <f>_xlfn.CONCAT(B65," (",C65," - ",D65,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-FULL (Arquitectura - Paredes: Altura completa)</v>
       </c>
       <c r="I65" s="11">
@@ -17197,7 +17248,7 @@
         <v>883</v>
       </c>
       <c r="E66" s="1" t="str">
-        <f>_xlfn.CONCAT(B66," (",C66," - ",D66,")")</f>
+        <f t="shared" si="0"/>
         <v>A-WALL-FULL-EXTR (Arquitectura - Paredes: altura completa: exterior)</v>
       </c>
       <c r="I66" s="11">
@@ -17227,7 +17278,7 @@
         <v>886</v>
       </c>
       <c r="E67" s="1" t="str">
-        <f>_xlfn.CONCAT(B67," (",C67," - ",D67,")")</f>
+        <f t="shared" ref="E67:E130" si="1">_xlfn.CONCAT(B67," (",C67," - ",D67,")")</f>
         <v>A-WALL-FULL-INTR (Arquitectura - Paredes: altura completa: interior)</v>
       </c>
       <c r="I67" s="11">
@@ -17257,7 +17308,7 @@
         <v>889</v>
       </c>
       <c r="E68" s="1" t="str">
-        <f>_xlfn.CONCAT(B68," (",C68," - ",D68,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-HEAD (Arquitectura - Paredes: dintel de puertas y ventanas)</v>
       </c>
       <c r="I68" s="11">
@@ -17287,7 +17338,7 @@
         <v>892</v>
       </c>
       <c r="E69" s="1" t="str">
-        <f>_xlfn.CONCAT(B69," (",C69," - ",D69,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-JAMB (Arquitectura - Paredes: jambas de puertas y ventanas)</v>
       </c>
       <c r="I69" s="11">
@@ -17317,7 +17368,7 @@
         <v>895</v>
       </c>
       <c r="E70" s="1" t="str">
-        <f>_xlfn.CONCAT(B70," (",C70," - ",D70,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-MESH (Arquitectura - Paredes: malla o alambre)</v>
       </c>
       <c r="I70" s="11">
@@ -17347,7 +17398,7 @@
         <v>898</v>
       </c>
       <c r="E71" s="1" t="str">
-        <f>_xlfn.CONCAT(B71," (",C71," - ",D71,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-MOVE (Arquitectura - Paredes: móviles)</v>
       </c>
       <c r="I71" s="11">
@@ -17377,7 +17428,7 @@
         <v>901</v>
       </c>
       <c r="E72" s="1" t="str">
-        <f>_xlfn.CONCAT(B72," (",C72," - ",D72,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-PATT (Arquitectura - Paredes: textura y patrones de tramado)</v>
       </c>
       <c r="I72" s="11">
@@ -17407,7 +17458,7 @@
         <v>904</v>
       </c>
       <c r="E73" s="1" t="str">
-        <f>_xlfn.CONCAT(B73," (",C73," - ",D73,")")</f>
+        <f t="shared" si="1"/>
         <v>A-WALL-PRHT (Arquitectura - Paredes: altura parcial)</v>
       </c>
       <c r="I73" s="11">
@@ -17437,7 +17488,7 @@
         <v>147</v>
       </c>
       <c r="E74" s="1" t="str">
-        <f>_xlfn.CONCAT(B74," (",C74," - ",D74,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD (Civil - Aeródromos)</v>
       </c>
       <c r="I74" s="11">
@@ -17467,7 +17518,7 @@
         <v>908</v>
       </c>
       <c r="E75" s="1" t="str">
-        <f>_xlfn.CONCAT(B75," (",C75," - ",D75,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-ASPH (Civil - Aeródromos: asfalto)</v>
       </c>
       <c r="I75" s="11">
@@ -17497,7 +17548,7 @@
         <v>911</v>
       </c>
       <c r="E76" s="1" t="str">
-        <f>_xlfn.CONCAT(B76," (",C76," - ",D76,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-CNTR (Civil - Aeródromos: centro)</v>
       </c>
       <c r="I76" s="11">
@@ -17527,7 +17578,7 @@
         <v>914</v>
       </c>
       <c r="E77" s="1" t="str">
-        <f>_xlfn.CONCAT(B77," (",C77," - ",D77,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-CONC (Civil - Aeródromos: hormigón)</v>
       </c>
       <c r="I77" s="11">
@@ -17557,7 +17608,7 @@
         <v>917</v>
       </c>
       <c r="E78" s="1" t="str">
-        <f>_xlfn.CONCAT(B78," (",C78," - ",D78,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-FLNE (Civil - Aeródromos: carril cortafuegos)</v>
       </c>
       <c r="I78" s="11">
@@ -17587,7 +17638,7 @@
         <v>920</v>
       </c>
       <c r="E79" s="1" t="str">
-        <f>_xlfn.CONCAT(B79," (",C79," - ",D79,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-FLNE-MRKG (Civil - Aeródromos: carril cortafuegos: marcas en el pavimento)</v>
       </c>
       <c r="I79" s="11">
@@ -17617,7 +17668,7 @@
         <v>923</v>
       </c>
       <c r="E80" s="1" t="str">
-        <f>_xlfn.CONCAT(B80," (",C80," - ",D80,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-FLNE-SIGN (Civil - Aeródromos: carril cortafuegos: señalización)</v>
       </c>
       <c r="I80" s="11">
@@ -17647,7 +17698,7 @@
         <v>926</v>
       </c>
       <c r="E81" s="1" t="str">
-        <f>_xlfn.CONCAT(B81," (",C81," - ",D81,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-GRVL (Civil - Aeródromos: grava)</v>
       </c>
       <c r="I81" s="11">
@@ -17677,7 +17728,7 @@
         <v>929</v>
       </c>
       <c r="E82" s="1" t="str">
-        <f>_xlfn.CONCAT(B82," (",C82," - ",D82,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-MRKG (Civil - Aeródromos: marcas en el pavimento)</v>
       </c>
       <c r="I82" s="11">
@@ -17707,7 +17758,7 @@
         <v>932</v>
       </c>
       <c r="E83" s="1" t="str">
-        <f>_xlfn.CONCAT(B83," (",C83," - ",D83,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-SIGN (Civil - Aeródromos: señalización)</v>
       </c>
       <c r="I83" s="11">
@@ -17737,7 +17788,7 @@
         <v>935</v>
       </c>
       <c r="E84" s="1" t="str">
-        <f>_xlfn.CONCAT(B84," (",C84," - ",D84,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-STAN (Civil - Aeródromos: estacionamiento)</v>
       </c>
       <c r="I84" s="11">
@@ -17767,7 +17818,7 @@
         <v>938</v>
       </c>
       <c r="E85" s="1" t="str">
-        <f>_xlfn.CONCAT(B85," (",C85," - ",D85,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-WHIT (Civil - Aeródromos: pintura blanca)</v>
       </c>
       <c r="I85" s="11">
@@ -17797,7 +17848,7 @@
         <v>941</v>
       </c>
       <c r="E86" s="1" t="str">
-        <f>_xlfn.CONCAT(B86," (",C86," - ",D86,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-WHIT-TICK (Civil - Aeródromos: pintura blanca: marcas de verificación)</v>
       </c>
       <c r="I86" s="11">
@@ -17827,7 +17878,7 @@
         <v>944</v>
       </c>
       <c r="E87" s="1" t="str">
-        <f>_xlfn.CONCAT(B87," (",C87," - ",D87,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-YELO (Civil - Aeródromos: pintura amarilla)</v>
       </c>
       <c r="I87" s="11">
@@ -17857,7 +17908,7 @@
         <v>947</v>
       </c>
       <c r="E88" s="1" t="str">
-        <f>_xlfn.CONCAT(B88," (",C88," - ",D88,")")</f>
+        <f t="shared" si="1"/>
         <v>C-AFLD-YELO-TICK (Civil - Aeródromos: pintura amarilla: marcas de verificación)</v>
       </c>
       <c r="I88" s="11">
@@ -17887,14 +17938,8 @@
         <v>949</v>
       </c>
       <c r="E89" s="1" t="str">
-        <f>_xlfn.CONCAT(B89," (",C89," - ",D89,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLDG (Civil - Edificios y estructuras principales)</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I89" s="11">
         <v>0</v>
@@ -17923,7 +17968,7 @@
         <v>952</v>
       </c>
       <c r="E90" s="1" t="str">
-        <f>_xlfn.CONCAT(B90," (",C90," - ",D90,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLDG-DECK (Civil - Edificios y estructuras principales: cubierta (adosada, sin techo))</v>
       </c>
       <c r="I90" s="11">
@@ -17953,7 +17998,7 @@
         <v>955</v>
       </c>
       <c r="E91" s="1" t="str">
-        <f>_xlfn.CONCAT(B91," (",C91," - ",D91,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLDG-OTLN (Civil - Edificios y estructuras principales: contorno)</v>
       </c>
       <c r="I91" s="11">
@@ -17983,7 +18028,7 @@
         <v>958</v>
       </c>
       <c r="E92" s="1" t="str">
-        <f>_xlfn.CONCAT(B92," (",C92," - ",D92,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLDG-OVHD (Civil - Edificios y estructuras principales: cubierta)</v>
       </c>
       <c r="I92" s="11">
@@ -18013,7 +18058,7 @@
         <v>961</v>
       </c>
       <c r="E93" s="1" t="str">
-        <f>_xlfn.CONCAT(B93," (",C93," - ",D93,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLDG-PRCH (Civil - Edificios y estructuras principales: pórtico (adosado, techo))</v>
       </c>
       <c r="I93" s="11">
@@ -18043,7 +18088,7 @@
         <v>183</v>
       </c>
       <c r="E94" s="1" t="str">
-        <f>_xlfn.CONCAT(B94," (",C94," - ",D94,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLIN (Civil - Línea base)</v>
       </c>
       <c r="I94" s="11">
@@ -18073,7 +18118,7 @@
         <v>965</v>
       </c>
       <c r="E95" s="1" t="str">
-        <f>_xlfn.CONCAT(B95," (",C95," - ",D95,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BLIN-STAN (Civil - Línea base: estacionamiento)</v>
       </c>
       <c r="I95" s="11">
@@ -18103,7 +18148,7 @@
         <v>189</v>
       </c>
       <c r="E96" s="1" t="str">
-        <f>_xlfn.CONCAT(B96," (",C96," - ",D96,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BORE (Civil - Perforaciones)</v>
       </c>
       <c r="I96" s="11">
@@ -18133,7 +18178,7 @@
         <v>195</v>
       </c>
       <c r="E97" s="1" t="str">
-        <f>_xlfn.CONCAT(B97," (",C97," - ",D97,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG (Civil - Puente)</v>
       </c>
       <c r="I97" s="11">
@@ -18163,7 +18208,7 @@
         <v>970</v>
       </c>
       <c r="E98" s="1" t="str">
-        <f>_xlfn.CONCAT(B98," (",C98," - ",D98,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-CNTJ (Civil - Puente: junta de construcción)</v>
       </c>
       <c r="I98" s="11">
@@ -18193,7 +18238,7 @@
         <v>973</v>
       </c>
       <c r="E99" s="1" t="str">
-        <f>_xlfn.CONCAT(B99," (",C99," - ",D99,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-CNTR (Civil - Puente: centro)</v>
       </c>
       <c r="I99" s="11">
@@ -18223,7 +18268,7 @@
         <v>976</v>
       </c>
       <c r="E100" s="1" t="str">
-        <f>_xlfn.CONCAT(B100," (",C100," - ",D100,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-DECK (Civil - Puente: cubierta)</v>
       </c>
       <c r="I100" s="11">
@@ -18253,7 +18298,7 @@
         <v>979</v>
       </c>
       <c r="E101" s="1" t="str">
-        <f>_xlfn.CONCAT(B101," (",C101," - ",D101,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-EXPJ (Civil - Puente: junta de dilatación)</v>
       </c>
       <c r="I101" s="11">
@@ -18283,7 +18328,7 @@
         <v>982</v>
       </c>
       <c r="E102" s="1" t="str">
-        <f>_xlfn.CONCAT(B102," (",C102," - ",D102,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-FALT (Civil - Puente: línea de falla/rotura)</v>
       </c>
       <c r="I102" s="11">
@@ -18313,7 +18358,7 @@
         <v>985</v>
       </c>
       <c r="E103" s="1" t="str">
-        <f>_xlfn.CONCAT(B103," (",C103," - ",D103,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-HIDD (Civil - Puente: objetos o líneas ocultos Vista)</v>
       </c>
       <c r="I103" s="11">
@@ -18343,7 +18388,7 @@
         <v>988</v>
       </c>
       <c r="E104" s="1" t="str">
-        <f>_xlfn.CONCAT(B104," (",C104," - ",D104,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-OBJT (Civil - Puente: objetos)</v>
       </c>
       <c r="I104" s="11">
@@ -18373,7 +18418,7 @@
         <v>991</v>
       </c>
       <c r="E105" s="1" t="str">
-        <f>_xlfn.CONCAT(B105," (",C105," - ",D105,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-OBJT-PRIM (Civil - Puente: objetos: principal)</v>
       </c>
       <c r="I105" s="11">
@@ -18403,7 +18448,7 @@
         <v>994</v>
       </c>
       <c r="E106" s="1" t="str">
-        <f>_xlfn.CONCAT(B106," (",C106," - ",D106,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-OBJT-SECD (Civil - Puente: objetos: secundario)</v>
       </c>
       <c r="I106" s="11">
@@ -18433,7 +18478,7 @@
         <v>997</v>
       </c>
       <c r="E107" s="1" t="str">
-        <f>_xlfn.CONCAT(B107," (",C107," - ",D107,")")</f>
+        <f t="shared" si="1"/>
         <v>C-BRDG-RBAR (Civil - Puente: barra de refuerzo)</v>
       </c>
       <c r="I107" s="11">
@@ -18463,7 +18508,7 @@
         <v>216</v>
       </c>
       <c r="E108" s="1" t="str">
-        <f>_xlfn.CONCAT(B108," (",C108," - ",D108,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CATV (Civil - Sistema de televisión por cable)</v>
       </c>
       <c r="I108" s="11">
@@ -18493,7 +18538,7 @@
         <v>1001</v>
       </c>
       <c r="E109" s="1" t="str">
-        <f>_xlfn.CONCAT(B109," (",C109," - ",D109,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CATV-OVHD (Civil - Sistema de televisión por cable: aéreo)</v>
       </c>
       <c r="I109" s="11">
@@ -18523,7 +18568,7 @@
         <v>1004</v>
       </c>
       <c r="E110" s="1" t="str">
-        <f>_xlfn.CONCAT(B110," (",C110," - ",D110,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CATV-POLE (Civil - Sistema de televisión por cable: poste)</v>
       </c>
       <c r="I110" s="11">
@@ -18553,7 +18598,7 @@
         <v>1007</v>
       </c>
       <c r="E111" s="1" t="str">
-        <f>_xlfn.CONCAT(B111," (",C111," - ",D111,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CATV-UGND (Civil - Sistema de televisión por cable: subterráneo)</v>
       </c>
       <c r="I111" s="11">
@@ -18583,7 +18628,7 @@
         <v>222</v>
       </c>
       <c r="E112" s="1" t="str">
-        <f>_xlfn.CONCAT(B112," (",C112," - ",D112,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CEME (Civil - Cementerio)</v>
       </c>
       <c r="I112" s="11">
@@ -18613,7 +18658,7 @@
         <v>225</v>
       </c>
       <c r="E113" s="1" t="str">
-        <f>_xlfn.CONCAT(B113," (",C113," - ",D113,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN (Civil - Canales navegables)</v>
       </c>
       <c r="I113" s="11">
@@ -18643,7 +18688,7 @@
         <v>1012</v>
       </c>
       <c r="E114" s="1" t="str">
-        <f>_xlfn.CONCAT(B114," (",C114," - ",D114,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN-BWTR (Civil - Canales navegables: rompeolas)</v>
       </c>
       <c r="I114" s="11">
@@ -18673,7 +18718,7 @@
         <v>1015</v>
       </c>
       <c r="E115" s="1" t="str">
-        <f>_xlfn.CONCAT(B115," (",C115," - ",D115,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN-CNTR (Civil - Canales navegables: centro)</v>
       </c>
       <c r="I115" s="11">
@@ -18703,7 +18748,7 @@
         <v>1018</v>
       </c>
       <c r="E116" s="1" t="str">
-        <f>_xlfn.CONCAT(B116," (",C116," - ",D116,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN-DACL (Civil - Canales navegables: límites de canales no autorizados, fondeaderos, etc.)</v>
       </c>
       <c r="I116" s="11">
@@ -18733,7 +18778,7 @@
         <v>1021</v>
       </c>
       <c r="E117" s="1" t="str">
-        <f>_xlfn.CONCAT(B117," (",C117," - ",D117,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN-DOCK (Civil - Canales navegables: cubiertas, muelles, flotadores, embarcaderos)</v>
       </c>
       <c r="I117" s="11">
@@ -18763,7 +18808,7 @@
         <v>1024</v>
       </c>
       <c r="E118" s="1" t="str">
-        <f>_xlfn.CONCAT(B118," (",C118," - ",D118,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CHAN-NAID (Civil - Canales navegables: ayudas a la navegación)</v>
       </c>
       <c r="I118" s="11">
@@ -18793,7 +18838,7 @@
         <v>258</v>
       </c>
       <c r="E119" s="1" t="str">
-        <f>_xlfn.CONCAT(B119," (",C119," - ",D119,")")</f>
+        <f t="shared" si="1"/>
         <v>C-COMM (Civil - Comunicaciones)</v>
       </c>
       <c r="I119" s="11">
@@ -18823,7 +18868,7 @@
         <v>1028</v>
       </c>
       <c r="E120" s="1" t="str">
-        <f>_xlfn.CONCAT(B120," (",C120," - ",D120,")")</f>
+        <f t="shared" si="1"/>
         <v>C-COMM-OVHD (Civil - Comunicaciones: aéreas)</v>
       </c>
       <c r="I120" s="11">
@@ -18853,7 +18898,7 @@
         <v>1031</v>
       </c>
       <c r="E121" s="1" t="str">
-        <f>_xlfn.CONCAT(B121," (",C121," - ",D121,")")</f>
+        <f t="shared" si="1"/>
         <v>C-COMM-POLE (Civil - Comunicaciones: poste)</v>
       </c>
       <c r="I121" s="11">
@@ -18883,7 +18928,7 @@
         <v>1034</v>
       </c>
       <c r="E122" s="1" t="str">
-        <f>_xlfn.CONCAT(B122," (",C122," - ",D122,")")</f>
+        <f t="shared" si="1"/>
         <v>C- COMM-UGND (Civil - Comunicaciones: subterráneas)</v>
       </c>
       <c r="I122" s="11">
@@ -18913,14 +18958,8 @@
         <v>273</v>
       </c>
       <c r="E123" s="1" t="str">
-        <f>_xlfn.CONCAT(B123," (",C123," - ",D123,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL (Civil - Puntos de control)</v>
-      </c>
-      <c r="F123" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I123" s="11">
         <v>0</v>
@@ -18949,7 +18988,7 @@
         <v>1038</v>
       </c>
       <c r="E124" s="1" t="str">
-        <f>_xlfn.CONCAT(B124," (",C124," - ",D124,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTR L-BMRK (Civil - Puntos de control: puntos de referencia)</v>
       </c>
       <c r="I124" s="11">
@@ -18979,7 +19018,7 @@
         <v>1041</v>
       </c>
       <c r="E125" s="1" t="str">
-        <f>_xlfn.CONCAT(B125," (",C125," - ",D125,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-FLYS (Civil - Puntos de control: estación de vuelo)</v>
       </c>
       <c r="I125" s="11">
@@ -19009,7 +19048,7 @@
         <v>1044</v>
       </c>
       <c r="E126" s="1" t="str">
-        <f>_xlfn.CONCAT(B126," (",C126," - ",D126,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-GRID (Civil - Puntos de control: cuadrícula)</v>
       </c>
       <c r="I126" s="11">
@@ -19039,7 +19078,7 @@
         <v>1047</v>
       </c>
       <c r="E127" s="1" t="str">
-        <f>_xlfn.CONCAT(B127," (",C127," - ",D127,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-HORZ (Civil - Puntos de control: horizontal)</v>
       </c>
       <c r="I127" s="11">
@@ -19069,7 +19108,7 @@
         <v>1050</v>
       </c>
       <c r="E128" s="1" t="str">
-        <f>_xlfn.CONCAT(B128," (",C128," - ",D128,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-HVPT (Civil - Puntos de control: horizontal/vertical)</v>
       </c>
       <c r="I128" s="11">
@@ -19099,7 +19138,7 @@
         <v>1053</v>
       </c>
       <c r="E129" s="1" t="str">
-        <f>_xlfn.CONCAT(B129," (",C129," - ",D129,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-PNPT (Civil - Puntos de control: puntos de panel)</v>
       </c>
       <c r="I129" s="11">
@@ -19129,7 +19168,7 @@
         <v>1056</v>
       </c>
       <c r="E130" s="1" t="str">
-        <f>_xlfn.CONCAT(B130," (",C130," - ",D130,")")</f>
+        <f t="shared" si="1"/>
         <v>C-CTRL-TRAV (Civil - Puntos de control: transversal)</v>
       </c>
       <c r="I130" s="11">
@@ -19159,7 +19198,7 @@
         <v>1059</v>
       </c>
       <c r="E131" s="1" t="str">
-        <f>_xlfn.CONCAT(B131," (",C131," - ",D131,")")</f>
+        <f t="shared" ref="E131:E194" si="2">_xlfn.CONCAT(B131," (",C131," - ",D131,")")</f>
         <v>C-CTRL-VERT (Civil - Puntos de control: vertical)</v>
       </c>
       <c r="I131" s="11">
@@ -19189,7 +19228,7 @@
         <v>288</v>
       </c>
       <c r="E132" s="1" t="str">
-        <f>_xlfn.CONCAT(B132," (",C132," - ",D132,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DFLD (Civil - Campos de drenaje)</v>
       </c>
       <c r="I132" s="11">
@@ -19219,7 +19258,7 @@
         <v>1063</v>
       </c>
       <c r="E133" s="1" t="str">
-        <f>_xlfn.CONCAT(B133," (",C133," - ",D133,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DFLD-OTLN (Civil - Campos de drenaje: contorno)</v>
       </c>
       <c r="I133" s="11">
@@ -19249,7 +19288,7 @@
         <v>1066</v>
       </c>
       <c r="E134" s="1" t="str">
-        <f>_xlfn.CONCAT(B134," (",C134," - ",D134,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DFLD-PROF (Civil - Campos de drenaje: perfil)</v>
       </c>
       <c r="I134" s="11">
@@ -19265,7 +19304,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A135" s="9">
         <v>1</v>
       </c>
@@ -19279,15 +19318,18 @@
         <v>1068</v>
       </c>
       <c r="E135" s="1" t="str">
-        <f>_xlfn.CONCAT(B135," (",C135," - ",D135,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV (Civil - Accesos vehiculares)</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>3800</v>
+        <v>3802</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H135" s="11">
+        <v>0.4</v>
+      </c>
       <c r="I135" s="11">
         <v>0</v>
       </c>
@@ -19315,7 +19357,7 @@
         <v>1071</v>
       </c>
       <c r="E136" s="1" t="str">
-        <f>_xlfn.CONCAT(B136," (",C136," - ",D136,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-ASPH (Civil - Accesos vehiculares: asfalto)</v>
       </c>
       <c r="I136" s="11">
@@ -19345,7 +19387,7 @@
         <v>1074</v>
       </c>
       <c r="E137" s="1" t="str">
-        <f>_xlfn.CONCAT(B137," (",C137," - ",D137,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-CNTR (Civil - Accesos vehiculares: centro)</v>
       </c>
       <c r="I137" s="11">
@@ -19375,7 +19417,7 @@
         <v>1077</v>
       </c>
       <c r="E138" s="1" t="str">
-        <f>_xlfn.CONCAT(B138," (",C138," - ",D138,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-CONC (Civil - Accesos vehiculares: hormigón)</v>
       </c>
       <c r="I138" s="11">
@@ -19405,7 +19447,7 @@
         <v>1080</v>
       </c>
       <c r="E139" s="1" t="str">
-        <f>_xlfn.CONCAT(B139," (",C139," - ",D139,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-CURB (Civil - Accesos vehiculares: Bordillo)</v>
       </c>
       <c r="I139" s="11">
@@ -19435,7 +19477,7 @@
         <v>1083</v>
       </c>
       <c r="E140" s="1" t="str">
-        <f>_xlfn.CONCAT(B140," (",C140," - ",D140,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-CURB-BACK (Civil - Entradas: Bordillo: Parte trasera)</v>
       </c>
       <c r="I140" s="11">
@@ -19465,7 +19507,7 @@
         <v>1086</v>
       </c>
       <c r="E141" s="1" t="str">
-        <f>_xlfn.CONCAT(B141," (",C141," - ",D141,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-CURB-FACE (Civil - Entradas: Bordillo: Cara)</v>
       </c>
       <c r="I141" s="11">
@@ -19495,7 +19537,7 @@
         <v>1089</v>
       </c>
       <c r="E142" s="1" t="str">
-        <f>_xlfn.CONCAT(B142," (",C142," - ",D142,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-FLNE (Civil - Entradas: Carril contra incendios)</v>
       </c>
       <c r="I142" s="11">
@@ -19525,7 +19567,7 @@
         <v>1092</v>
       </c>
       <c r="E143" s="1" t="str">
-        <f>_xlfn.CONCAT(B143," (",C143," - ",D143,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-FLNE-MRKG (Civil - Entradas: Carril contra incendios: Marcas en el pavimento)</v>
       </c>
       <c r="I143" s="11">
@@ -19555,7 +19597,7 @@
         <v>1095</v>
       </c>
       <c r="E144" s="1" t="str">
-        <f>_xlfn.CONCAT(B144," (",C144," - ",D144,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-FLNE-SIGN (Civil - Entradas: Carril contra incendios: Señalización)</v>
       </c>
       <c r="I144" s="11">
@@ -19585,7 +19627,7 @@
         <v>1098</v>
       </c>
       <c r="E145" s="1" t="str">
-        <f>_xlfn.CONCAT(B145," (",C145," - ",D145,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-GRVL (Civil - Entradas: Grava)</v>
       </c>
       <c r="I145" s="11">
@@ -19615,7 +19657,7 @@
         <v>1101</v>
       </c>
       <c r="E146" s="1" t="str">
-        <f>_xlfn.CONCAT(B146," (",C146," - ",D146,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-MRKG (Civil - Entradas: Marcas en el pavimento)</v>
       </c>
       <c r="I146" s="11">
@@ -19645,7 +19687,7 @@
         <v>1104</v>
       </c>
       <c r="E147" s="1" t="str">
-        <f>_xlfn.CONCAT(B147," (",C147," - ",D147,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-SIGN (Civil - Entradas: Señalización)</v>
       </c>
       <c r="I147" s="11">
@@ -19675,7 +19717,7 @@
         <v>1107</v>
       </c>
       <c r="E148" s="1" t="str">
-        <f>_xlfn.CONCAT(B148," (",C148," - ",D148,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRI V-UPVD (Civil - Entradas: Superficie sin pavimentar)</v>
       </c>
       <c r="I148" s="11">
@@ -19705,7 +19747,7 @@
         <v>1110</v>
       </c>
       <c r="E149" s="1" t="str">
-        <f>_xlfn.CONCAT(B149," (",C149," - ",D149,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-WHIT (Civil - Entradas: Pintura blanca)</v>
       </c>
       <c r="I149" s="11">
@@ -19735,7 +19777,7 @@
         <v>1113</v>
       </c>
       <c r="E150" s="1" t="str">
-        <f>_xlfn.CONCAT(B150," (",C150," - ",D150,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-WHIT-TICK (Civil - Entradas: Pintura blanca: Marcas de verificación)</v>
       </c>
       <c r="I150" s="11">
@@ -19765,7 +19807,7 @@
         <v>1116</v>
       </c>
       <c r="E151" s="1" t="str">
-        <f>_xlfn.CONCAT(B151," (",C151," - ",D151,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-YELO (Civil - Entradas: Pintura amarilla)</v>
       </c>
       <c r="I151" s="11">
@@ -19795,7 +19837,7 @@
         <v>1119</v>
       </c>
       <c r="E152" s="1" t="str">
-        <f>_xlfn.CONCAT(B152," (",C152," - ",D152,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DRIV-YELO-TICK (Civil - Entradas: Pintura amarilla: Marcas de verificación)</v>
       </c>
       <c r="I152" s="11">
@@ -19825,7 +19867,7 @@
         <v>1121</v>
       </c>
       <c r="E153" s="1" t="str">
-        <f>_xlfn.CONCAT(B153," (",C153," - ",D153,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DTCH (Civil - Cuencas o zanjas)</v>
       </c>
       <c r="I153" s="11">
@@ -19855,7 +19897,7 @@
         <v>1124</v>
       </c>
       <c r="E154" s="1" t="str">
-        <f>_xlfn.CONCAT(B154," (",C154," - ",D154,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DTCH-BOTM (Civil - Cuencas o zanjas: Parte inferior)</v>
       </c>
       <c r="I154" s="11">
@@ -19885,7 +19927,7 @@
         <v>1127</v>
       </c>
       <c r="E155" s="1" t="str">
-        <f>_xlfn.CONCAT(B155," (",C155," - ",D155,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DTCH-CNTR (Civil - Cuencas o zanjas: Centro)</v>
       </c>
       <c r="I155" s="11">
@@ -19915,7 +19957,7 @@
         <v>1130</v>
       </c>
       <c r="E156" s="1" t="str">
-        <f>_xlfn.CONCAT(B156," (",C156," - ",D156,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DTCH-EWAT (Civil - Cuencas o zanjas: Borde del agua)</v>
       </c>
       <c r="I156" s="11">
@@ -19945,7 +19987,7 @@
         <v>1133</v>
       </c>
       <c r="E157" s="1" t="str">
-        <f>_xlfn.CONCAT(B157," (",C157," - ",D157,")")</f>
+        <f t="shared" si="2"/>
         <v>C-DTCH-TOP~ (Civil - Cuencas o zanjas: Parte superior)</v>
       </c>
       <c r="I157" s="11">
@@ -19975,7 +20017,7 @@
         <v>335</v>
       </c>
       <c r="E158" s="1" t="str">
-        <f>_xlfn.CONCAT(B158," (",C158," - ",D158,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS (Civil - Control de erosión y sedimentos)</v>
       </c>
       <c r="I158" s="11">
@@ -20005,7 +20047,7 @@
         <v>1137</v>
       </c>
       <c r="E159" s="1" t="str">
-        <f>_xlfn.CONCAT(B159," (",C159," - ",D159,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-CIPR (Civil - Control de erosión y sedimentos: Protección de la entrada de la alcantarilla)</v>
       </c>
       <c r="I159" s="11">
@@ -20035,7 +20077,7 @@
         <v>1140</v>
       </c>
       <c r="E160" s="1" t="str">
-        <f>_xlfn.CONCAT(B160," (",C160," - ",D160,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-CNTE (Civil - Control de erosión y sedimentos: Entrada de la construcción)</v>
       </c>
       <c r="I160" s="11">
@@ -20065,7 +20107,7 @@
         <v>1143</v>
       </c>
       <c r="E161" s="1" t="str">
-        <f>_xlfn.CONCAT(B161," (",C161," - ",D161,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-DDIV (Civil - Control de erosión y sedimentos: Divisorias de drenaje)</v>
       </c>
       <c r="I161" s="11">
@@ -20095,7 +20137,7 @@
         <v>1146</v>
       </c>
       <c r="E162" s="1" t="str">
-        <f>_xlfn.CONCAT(B162," (",C162," - ",D162,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-DVDK (Civil - Control de erosión y sedimentos: Dique de derivación)</v>
       </c>
       <c r="I162" s="11">
@@ -20125,7 +20167,7 @@
         <v>1149</v>
       </c>
       <c r="E163" s="1" t="str">
-        <f>_xlfn.CONCAT(B163," (",C163," - ",D163,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-INPR (Civil - Control de erosión y sedimentos: Protección de la entrada)</v>
       </c>
       <c r="I163" s="11">
@@ -20155,7 +20197,7 @@
         <v>1152</v>
       </c>
       <c r="E164" s="1" t="str">
-        <f>_xlfn.CONCAT(B164," (",C164," - ",D164,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-SILT (Civil - Control de erosión y sedimentos: Barrera de sedimentos)</v>
       </c>
       <c r="I164" s="11">
@@ -20185,7 +20227,7 @@
         <v>1155</v>
       </c>
       <c r="E165" s="1" t="str">
-        <f>_xlfn.CONCAT(B165," (",C165," - ",D165,")")</f>
+        <f t="shared" si="2"/>
         <v>C-EROS-SSLT (Civil - Control de erosión y sedimentos: Superlimo Cerca)</v>
       </c>
       <c r="I165" s="11">
@@ -20215,14 +20257,8 @@
         <v>338</v>
       </c>
       <c r="E166" s="1" t="str">
-        <f>_xlfn.CONCAT(B166," (",C166," - ",D166,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT (Civil - Servidumbres)</v>
-      </c>
-      <c r="F166" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G166" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I166" s="11">
         <v>0</v>
@@ -20251,7 +20287,7 @@
         <v>1159</v>
       </c>
       <c r="E167" s="1" t="str">
-        <f>_xlfn.CONCAT(B167," (",C167," - ",D167,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-ACCS (Civil - Servidumbres: acceso (solo para peatones; acceso privado))</v>
       </c>
       <c r="I167" s="11">
@@ -20281,7 +20317,7 @@
         <v>1162</v>
       </c>
       <c r="E168" s="1" t="str">
-        <f>_xlfn.CONCAT(B168," (",C168," - ",D168,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-CATV (Civil - Servidumbres: servicios públicos - sistema de televisión por cable)</v>
       </c>
       <c r="I168" s="11">
@@ -20311,7 +20347,7 @@
         <v>1165</v>
       </c>
       <c r="E169" s="1" t="str">
-        <f>_xlfn.CONCAT(B169," (",C169," - ",D169,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-CONS (Civil - Servidumbres: conservación)</v>
       </c>
       <c r="I169" s="11">
@@ -20341,7 +20377,7 @@
         <v>1168</v>
       </c>
       <c r="E170" s="1" t="str">
-        <f>_xlfn.CONCAT(B170," (",C170," - ",D170,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-CSTG (Civil - Servidumbres: construcción/nivelación)</v>
       </c>
       <c r="I170" s="11">
@@ -20371,7 +20407,7 @@
         <v>1171</v>
       </c>
       <c r="E171" s="1" t="str">
-        <f>_xlfn.CONCAT(B171," (",C171," - ",D171,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-ELEC (Civil - Servidumbres: electricidad)</v>
       </c>
       <c r="I171" s="11">
@@ -20401,7 +20437,7 @@
         <v>1174</v>
       </c>
       <c r="E172" s="1" t="str">
-        <f>_xlfn.CONCAT(B172," (",C172," - ",D172,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-FDPL (Civil - Servidumbres: llanura aluvial)</v>
       </c>
       <c r="I172" s="11">
@@ -20431,7 +20467,7 @@
         <v>1177</v>
       </c>
       <c r="E173" s="1" t="str">
-        <f>_xlfn.CONCAT(B173," (",C173," - ",D173,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-INEG (Civil - Servidumbres: entrada/salida (vehículos; acceso privado))</v>
       </c>
       <c r="I173" s="11">
@@ -20461,7 +20497,7 @@
         <v>1180</v>
       </c>
       <c r="E174" s="1" t="str">
-        <f>_xlfn.CONCAT(B174," (",C174," - ",D174,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-LSCP (Civil - Servidumbres: paisajismo)</v>
       </c>
       <c r="I174" s="11">
@@ -20491,7 +20527,7 @@
         <v>1183</v>
       </c>
       <c r="E175" s="1" t="str">
-        <f>_xlfn.CONCAT(B175," (",C175," - ",D175,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-NGAS (Civil - Servidumbres: línea de gas natural)</v>
       </c>
       <c r="I175" s="11">
@@ -20521,7 +20557,7 @@
         <v>1186</v>
       </c>
       <c r="E176" s="1" t="str">
-        <f>_xlfn.CONCAT(B176," (",C176," - ",D176,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-PHON (Civil - Servidumbres: línea telefónica)</v>
       </c>
       <c r="I176" s="11">
@@ -20551,7 +20587,7 @@
         <v>1189</v>
       </c>
       <c r="E177" s="1" t="str">
-        <f>_xlfn.CONCAT(B177," (",C177," - ",D177,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-ROAD (Civil - Servidumbres: carretera)</v>
       </c>
       <c r="I177" s="11">
@@ -20581,7 +20617,7 @@
         <v>1192</v>
       </c>
       <c r="E178" s="1" t="str">
-        <f>_xlfn.CONCAT(B178," (",C178," - ",D178,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-ROAD-PERM (Civil - Servidumbres: carretera: permanente)</v>
       </c>
       <c r="I178" s="11">
@@ -20611,7 +20647,7 @@
         <v>1195</v>
       </c>
       <c r="E179" s="1" t="str">
-        <f>_xlfn.CONCAT(B179," (",C179," - ",D179,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-ROAD-TEMP (Civil - Servidumbres: carretera: temporal)</v>
       </c>
       <c r="I179" s="11">
@@ -20641,7 +20677,7 @@
         <v>1198</v>
       </c>
       <c r="E180" s="1" t="str">
-        <f>_xlfn.CONCAT(B180," (",C180," - ",D180,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-RWAY (Civil - Servidumbres: derecho de paso (acceso público))</v>
       </c>
       <c r="I180" s="11">
@@ -20671,7 +20707,7 @@
         <v>1201</v>
       </c>
       <c r="E181" s="1" t="str">
-        <f>_xlfn.CONCAT(B181," (",C181," - ",D181,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-SGHT (Civil - Servidumbres: distancia de visibilidad)</v>
       </c>
       <c r="I181" s="11">
@@ -20701,7 +20737,7 @@
         <v>1204</v>
       </c>
       <c r="E182" s="1" t="str">
-        <f>_xlfn.CONCAT(B182," (",C182," - ",D182,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-SSWR (Civil - Servidumbres: alcantarillado sanitario)</v>
       </c>
       <c r="I182" s="11">
@@ -20731,7 +20767,7 @@
         <v>1207</v>
       </c>
       <c r="E183" s="1" t="str">
-        <f>_xlfn.CONCAT(B183," (",C183," - ",D183,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-STRM (Civil - Servidumbres: alcantarillado pluvial)</v>
       </c>
       <c r="I183" s="11">
@@ -20761,7 +20797,7 @@
         <v>1210</v>
       </c>
       <c r="E184" s="1" t="str">
-        <f>_xlfn.CONCAT(B184," (",C184," - ",D184,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-SWMT (Civil - Servidumbres: gestión de aguas pluviales)</v>
       </c>
       <c r="I184" s="11">
@@ -20791,7 +20827,7 @@
         <v>1213</v>
       </c>
       <c r="E185" s="1" t="str">
-        <f>_xlfn.CONCAT(B185," (",C185," - ",D185,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-TRAL (Civil - Servidumbres: sendero o camino (acceso público))</v>
       </c>
       <c r="I185" s="11">
@@ -20821,7 +20857,7 @@
         <v>1216</v>
       </c>
       <c r="E186" s="1" t="str">
-        <f>_xlfn.CONCAT(B186," (",C186," - ",D186,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-UTIL (Civil - Servidumbres: líneas de servicios públicos)</v>
       </c>
       <c r="I186" s="11">
@@ -20851,7 +20887,7 @@
         <v>1219</v>
       </c>
       <c r="E187" s="1" t="str">
-        <f>_xlfn.CONCAT(B187," (",C187," - ",D187,")")</f>
+        <f t="shared" si="2"/>
         <v>C-ESMT-WATR (Civil - Servidumbres: suministro de agua)</v>
       </c>
       <c r="I187" s="11">
@@ -20881,14 +20917,8 @@
         <v>347</v>
       </c>
       <c r="E188" s="1" t="str">
-        <f>_xlfn.CONCAT(B188," (",C188," - ",D188,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FENC (Civil - Cercas)</v>
-      </c>
-      <c r="F188" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G188" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I188" s="11">
         <v>0</v>
@@ -20917,7 +20947,7 @@
         <v>1223</v>
       </c>
       <c r="E189" s="1" t="str">
-        <f>_xlfn.CONCAT(B189," (",C189," - ",D189,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FENC-GRAL (Civil - Cercas: barandilla)</v>
       </c>
       <c r="I189" s="11">
@@ -20947,7 +20977,7 @@
         <v>1226</v>
       </c>
       <c r="E190" s="1" t="str">
-        <f>_xlfn.CONCAT(B190," (",C190," - ",D190,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FENC-POST (Civil - Cercas: postes)</v>
       </c>
       <c r="I190" s="11">
@@ -20977,7 +21007,7 @@
         <v>1229</v>
       </c>
       <c r="E191" s="1" t="str">
-        <f>_xlfn.CONCAT(B191," (",C191," - ",D191,")")</f>
+        <f t="shared" si="2"/>
         <v>C -FENC-STEL (Civil - Cercas: acero (alambre de púas y/o malla metálica))</v>
       </c>
       <c r="I191" s="11">
@@ -21007,7 +21037,7 @@
         <v>1232</v>
       </c>
       <c r="E192" s="1" t="str">
-        <f>_xlfn.CONCAT(B192," (",C192," - ",D192,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FENC-WOOD (Civil - Cercas: madera)</v>
       </c>
       <c r="I192" s="11">
@@ -21037,14 +21067,8 @@
         <v>16</v>
       </c>
       <c r="E193" s="1" t="str">
-        <f>_xlfn.CONCAT(B193," (",C193," - ",D193,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FIRE (Civil - Protección contra incendios)</v>
-      </c>
-      <c r="F193" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G193" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I193" s="11">
         <v>0</v>
@@ -21073,7 +21097,7 @@
         <v>1236</v>
       </c>
       <c r="E194" s="1" t="str">
-        <f>_xlfn.CONCAT(B194," (",C194," - ",D194,")")</f>
+        <f t="shared" si="2"/>
         <v>C-FIRE-HYDT (Civil - Protección contra incendios: Hidrantes y conexiones)</v>
       </c>
       <c r="I194" s="11">
@@ -21103,7 +21127,7 @@
         <v>1239</v>
       </c>
       <c r="E195" s="1" t="str">
-        <f>_xlfn.CONCAT(B195," (",C195," - ",D195,")")</f>
+        <f t="shared" ref="E195:E258" si="3">_xlfn.CONCAT(B195," (",C195," - ",D195,")")</f>
         <v>C-FIRE-PIPE (Civil - Protección contra incendios: tuberías)</v>
       </c>
       <c r="I195" s="11">
@@ -21133,7 +21157,7 @@
         <v>1242</v>
       </c>
       <c r="E196" s="1" t="str">
-        <f>_xlfn.CONCAT(B196," (",C196," - ",D196,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FIRE-UGND (Civil - Protección contra incendios: subterránea)</v>
       </c>
       <c r="I196" s="11">
@@ -21163,7 +21187,7 @@
         <v>1244</v>
       </c>
       <c r="E197" s="1" t="str">
-        <f>_xlfn.CONCAT(B197," (",C197," - ",D197,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FLHA (Civil - Zona de riesgo de inundación)</v>
       </c>
       <c r="I197" s="11">
@@ -21193,7 +21217,7 @@
         <v>1247</v>
       </c>
       <c r="E198" s="1" t="str">
-        <f>_xlfn.CONCAT(B198," (",C198," - ",D198,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FLHA-025Y (Civil - Zona de riesgo de inundación: 25 años)</v>
       </c>
       <c r="I198" s="11">
@@ -21223,7 +21247,7 @@
         <v>1250</v>
       </c>
       <c r="E199" s="1" t="str">
-        <f>_xlfn.CONCAT(B199," (",C199," - ",D199,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FLHA-050Y (Civil - Zona de riesgo de inundación: 50 años)</v>
       </c>
       <c r="I199" s="11">
@@ -21253,7 +21277,7 @@
         <v>1253</v>
       </c>
       <c r="E200" s="1" t="str">
-        <f>_xlfn.CONCAT(B200," (",C200," - ",D200,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FLHA-100Y (Civil - Zona de riesgo de inundación: 100 años)</v>
       </c>
       <c r="I200" s="11">
@@ -21283,7 +21307,7 @@
         <v>1256</v>
       </c>
       <c r="E201" s="1" t="str">
-        <f>_xlfn.CONCAT(B201," (",C201," - ",D201,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FLHA-200Y (Civil - Zona de riesgo de inundación: 200 años)</v>
       </c>
       <c r="I201" s="11">
@@ -21313,7 +21337,7 @@
         <v>370</v>
       </c>
       <c r="E202" s="1" t="str">
-        <f>_xlfn.CONCAT(B202," (",C202," - ",D202,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL (Civil - Sistemas de combustible)</v>
       </c>
       <c r="I202" s="11">
@@ -21343,7 +21367,7 @@
         <v>1260</v>
       </c>
       <c r="E203" s="1" t="str">
-        <f>_xlfn.CONCAT(B203," (",C203," - ",D203,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-EQPM (Civil - Sistemas de combustible: equipos (bombas, motores))</v>
       </c>
       <c r="I203" s="11">
@@ -21373,7 +21397,7 @@
         <v>1263</v>
       </c>
       <c r="E204" s="1" t="str">
-        <f>_xlfn.CONCAT(B204," (",C204," - ",D204,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-INST (Civil - Sistemas de combustible: instrumentación (medidores, válvulas, etc.))</v>
       </c>
       <c r="I204" s="11">
@@ -21403,7 +21427,7 @@
         <v>1266</v>
       </c>
       <c r="E205" s="1" t="str">
-        <f>_xlfn.CONCAT(B205," (",C205," - ",D205,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-MHOL (Civil - Sistemas de combustible: pozo de registro)</v>
       </c>
       <c r="I205" s="11">
@@ -21433,7 +21457,7 @@
         <v>1269</v>
       </c>
       <c r="E206" s="1" t="str">
-        <f>_xlfn.CONCAT(B206," (",C206," - ",D206,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-PIPE (Civil - Sistemas de combustible: tuberías)</v>
       </c>
       <c r="I206" s="11">
@@ -21463,7 +21487,7 @@
         <v>1272</v>
       </c>
       <c r="E207" s="1" t="str">
-        <f>_xlfn.CONCAT(B207," (",C207," - ",D207,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-TANK (Civil - Sistemas de combustible: tanques de almacenamiento)</v>
       </c>
       <c r="I207" s="11">
@@ -21493,7 +21517,7 @@
         <v>1275</v>
       </c>
       <c r="E208" s="1" t="str">
-        <f>_xlfn.CONCAT(B208," (",C208," - ",D208,")")</f>
+        <f t="shared" si="3"/>
         <v>C-FUEL-UGND (Civil - Sistemas de combustible: subterráneos)</v>
       </c>
       <c r="I208" s="11">
@@ -21523,7 +21547,7 @@
         <v>408</v>
       </c>
       <c r="E209" s="1" t="str">
-        <f>_xlfn.CONCAT(B209," (",C209," - ",D209,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR (Civil - Estructura hidráulica)</v>
       </c>
       <c r="I209" s="11">
@@ -21553,7 +21577,7 @@
         <v>1279</v>
       </c>
       <c r="E210" s="1" t="str">
-        <f>_xlfn.CONCAT(B210," (",C210," - ",D210,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-BAFL (Civil - Estructura hidráulica: bloque deflector y plataforma antisalpicaduras)</v>
       </c>
       <c r="I210" s="11">
@@ -21583,7 +21607,7 @@
         <v>1282</v>
       </c>
       <c r="E211" s="1" t="str">
-        <f>_xlfn.CONCAT(B211," (",C211," - ",D211,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-BASN (Civil - Estructura hidráulica: estanques de amortiguación y sedimentación)</v>
       </c>
       <c r="I211" s="11">
@@ -21613,7 +21637,7 @@
         <v>1285</v>
       </c>
       <c r="E212" s="1" t="str">
-        <f>_xlfn.CONCAT(B212," (",C212," - ",D212,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-CNDT (Civil - Estructura hidráulica: conductos de derivación/bypass/alcantarillas)</v>
       </c>
       <c r="I212" s="11">
@@ -21643,7 +21667,7 @@
         <v>1288</v>
       </c>
       <c r="E213" s="1" t="str">
-        <f>_xlfn.CONCAT(B213," (",C213," - ",D213,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-COFF (Civil - Estructura hidráulica: ataguía)</v>
       </c>
       <c r="I213" s="11">
@@ -21673,7 +21697,7 @@
         <v>1291</v>
       </c>
       <c r="E214" s="1" t="str">
-        <f>_xlfn.CONCAT(B214," (",C214," - ",D214,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-DAM~ (Civil - Estructura hidráulica: presa)</v>
       </c>
       <c r="I214" s="11">
@@ -21703,7 +21727,7 @@
         <v>1294</v>
       </c>
       <c r="E215" s="1" t="str">
-        <f>_xlfn.CONCAT(B215," (",C215," - ",D215,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-FISH (Civil - Estructura hidráulica: escala/pasaje para peces)</v>
       </c>
       <c r="I215" s="11">
@@ -21733,7 +21757,7 @@
         <v>1297</v>
       </c>
       <c r="E216" s="1" t="str">
-        <f>_xlfn.CONCAT(B216," (",C216," - ",D216,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-FLUM (Civil - Estructura hidráulica: canal)</v>
       </c>
       <c r="I216" s="11">
@@ -21763,7 +21787,7 @@
         <v>1715</v>
       </c>
       <c r="E217" s="1" t="str">
-        <f>_xlfn.CONCAT(B217," (",C217," - ",D217,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-INTK (Civil - Hidráulica Estructura: toma)</v>
       </c>
       <c r="I217" s="11">
@@ -21793,7 +21817,7 @@
         <v>1716</v>
       </c>
       <c r="E218" s="1" t="str">
-        <f>_xlfn.CONCAT(B218," (",C218," - ",D218,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-NOVR (Civil - Estructura hidráulica: estructura antidesbordamiento)</v>
       </c>
       <c r="I218" s="11">
@@ -21823,7 +21847,7 @@
         <v>1717</v>
       </c>
       <c r="E219" s="1" t="str">
-        <f>_xlfn.CONCAT(B219," (",C219," - ",D219,")")</f>
+        <f t="shared" si="3"/>
         <v>C-HYDR-PENS (Civil - Estructura hidráulica: tubería forzada)</v>
       </c>
       <c r="I219" s="11">
@@ -21853,7 +21877,7 @@
         <v>453</v>
       </c>
       <c r="E220" s="1" t="str">
-        <f>_xlfn.CONCAT(B220," (",C220," - ",D220,")")</f>
+        <f t="shared" si="3"/>
         <v>C-LOCN (Civil - Límites de construcción)</v>
       </c>
       <c r="I220" s="11">
@@ -21883,14 +21907,8 @@
         <v>482</v>
       </c>
       <c r="E221" s="1" t="str">
-        <f>_xlfn.CONCAT(B221," (",C221," - ",D221,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS (Civil - Sistemas de gas natural)</v>
-      </c>
-      <c r="F221" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G221" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I221" s="11">
         <v>0</v>
@@ -21919,7 +21937,7 @@
         <v>1308</v>
       </c>
       <c r="E222" s="1" t="str">
-        <f>_xlfn.CONCAT(B222," (",C222," - ",D222,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-EQPM (Civil - Sistemas de gas natural: Equipos (bombas, motores))</v>
       </c>
       <c r="I222" s="11">
@@ -21949,7 +21967,7 @@
         <v>1311</v>
       </c>
       <c r="E223" s="1" t="str">
-        <f>_xlfn.CONCAT(B223," (",C223," - ",D223,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-INST (Civil - Sistemas de gas natural: Instrumentación (medidores, válvulas, etc.))</v>
       </c>
       <c r="I223" s="11">
@@ -21979,7 +21997,7 @@
         <v>1314</v>
       </c>
       <c r="E224" s="1" t="str">
-        <f>_xlfn.CONCAT(B224," (",C224," - ",D224,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-MHOL (Civil - Sistemas de gas natural: Pozo de registro)</v>
       </c>
       <c r="I224" s="11">
@@ -22009,7 +22027,7 @@
         <v>1317</v>
       </c>
       <c r="E225" s="1" t="str">
-        <f>_xlfn.CONCAT(B225," (",C225," - ",D225,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-PIPE (Civil - Sistemas de gas natural: Tuberías)</v>
       </c>
       <c r="I225" s="11">
@@ -22039,7 +22057,7 @@
         <v>1320</v>
       </c>
       <c r="E226" s="1" t="str">
-        <f>_xlfn.CONCAT(B226," (",C226," - ",D226,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-TANK (Civil - Sistemas de gas natural: Tanques de almacenamiento)</v>
       </c>
       <c r="I226" s="11">
@@ -22069,7 +22087,7 @@
         <v>1323</v>
       </c>
       <c r="E227" s="1" t="str">
-        <f>_xlfn.CONCAT(B227," (",C227," - ",D227,")")</f>
+        <f t="shared" si="3"/>
         <v>C-NGAS-UGND (Civil - Sistemas de gas natural: Subterráneos)</v>
       </c>
       <c r="I227" s="11">
@@ -22099,7 +22117,7 @@
         <v>1325</v>
       </c>
       <c r="E228" s="1" t="str">
-        <f>_xlfn.CONCAT(B228," (",C228," - ",D228,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PERC (Civil - Pruebas de percolación)</v>
       </c>
       <c r="I228" s="11">
@@ -22129,7 +22147,7 @@
         <v>1328</v>
       </c>
       <c r="E229" s="1" t="str">
-        <f>_xlfn.CONCAT(B229," (",C229," - ",D229,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PERC-HOLE (Civil - Pruebas de percolación: Pozos)</v>
       </c>
       <c r="I229" s="11">
@@ -22159,7 +22177,7 @@
         <v>524</v>
       </c>
       <c r="E230" s="1" t="str">
-        <f>_xlfn.CONCAT(B230," (",C230," - ",D230,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POND (Civil - Estanques)</v>
       </c>
       <c r="I230" s="11">
@@ -22189,7 +22207,7 @@
         <v>1332</v>
       </c>
       <c r="E231" s="1" t="str">
-        <f>_xlfn.CONCAT(B231," (",C231," - ",D231,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POND-EDGE (Civil - Estanques: borde)</v>
       </c>
       <c r="I231" s="11">
@@ -22219,7 +22237,7 @@
         <v>1335</v>
       </c>
       <c r="E232" s="1" t="str">
-        <f>_xlfn.CONCAT(B232," (",C232," - ",D232,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POND-SWAY (Civil - Estanques: aliviadero)</v>
       </c>
       <c r="I232" s="11">
@@ -22249,7 +22267,7 @@
         <v>1338</v>
       </c>
       <c r="E233" s="1" t="str">
-        <f>_xlfn.CONCAT(B233," (",C233," - ",D233,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POND-TOPB (Civil - Estanques: parte superior de la ribera)</v>
       </c>
       <c r="I233" s="11">
@@ -22265,7 +22283,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A234" s="9">
         <v>1</v>
       </c>
@@ -22279,7 +22297,7 @@
         <v>527</v>
       </c>
       <c r="E234" s="1" t="str">
-        <f>_xlfn.CONCAT(B234," (",C234," - ",D234,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR (Civil - Energía)</v>
       </c>
       <c r="F234" s="11" t="s">
@@ -22318,7 +22336,7 @@
         <v>1342</v>
       </c>
       <c r="E235" s="1" t="str">
-        <f>_xlfn.CONCAT(B235," (",C235," - ",D235,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-FENC (Civil - Energía: cercas)</v>
       </c>
       <c r="I235" s="11">
@@ -22348,7 +22366,7 @@
         <v>1345</v>
       </c>
       <c r="E236" s="1" t="str">
-        <f>_xlfn.CONCAT(B236," (",C236," - ",D236,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-INST (Civil - Energía: instrumentación (medidores, transformadores))</v>
       </c>
       <c r="I236" s="11">
@@ -22378,7 +22396,7 @@
         <v>1348</v>
       </c>
       <c r="E237" s="1" t="str">
-        <f>_xlfn.CONCAT(B237," (",C237," - ",D237,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-MHOL (Civil - Energía: pozo de registro)</v>
       </c>
       <c r="I237" s="11">
@@ -22408,7 +22426,7 @@
         <v>1351</v>
       </c>
       <c r="E238" s="1" t="str">
-        <f>_xlfn.CONCAT(B238," (",C238," - ",D238,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-OVHD (Civil - Energía: aérea)</v>
       </c>
       <c r="I238" s="11">
@@ -22438,7 +22456,7 @@
         <v>1354</v>
       </c>
       <c r="E239" s="1" t="str">
-        <f>_xlfn.CONCAT(B239," (",C239," - ",D239,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-POLE (Civil - Energía: poste)</v>
       </c>
       <c r="I239" s="11">
@@ -22468,7 +22486,7 @@
         <v>1357</v>
       </c>
       <c r="E240" s="1" t="str">
-        <f>_xlfn.CONCAT(B240," (",C240," - ",D240,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-STRC (Civil - Energía: estructuras)</v>
       </c>
       <c r="I240" s="11">
@@ -22498,7 +22516,7 @@
         <v>1360</v>
       </c>
       <c r="E241" s="1" t="str">
-        <f>_xlfn.CONCAT(B241," (",C241," - ",D241,")")</f>
+        <f t="shared" si="3"/>
         <v>C-POWR-UGND (Civil - Energía: subterránea)</v>
       </c>
       <c r="I241" s="11">
@@ -22528,7 +22546,7 @@
         <v>530</v>
       </c>
       <c r="E242" s="1" t="str">
-        <f>_xlfn.CONCAT(B242," (",C242," - ",D242,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG (Civil - Estacionamientos)</v>
       </c>
       <c r="I242" s="11">
@@ -22558,7 +22576,7 @@
         <v>1364</v>
       </c>
       <c r="E243" s="1" t="str">
-        <f>_xlfn.CONCAT(B243," (",C243," - ",D243,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-ASPH (Civil - Estacionamientos: asfalto)</v>
       </c>
       <c r="I243" s="11">
@@ -22588,7 +22606,7 @@
         <v>1367</v>
       </c>
       <c r="E244" s="1" t="str">
-        <f>_xlfn.CONCAT(B244," (",C244," - ",D244,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-CARS (Civil - Estacionamientos: automóviles y otros vehículos)</v>
       </c>
       <c r="I244" s="11">
@@ -22618,7 +22636,7 @@
         <v>1370</v>
       </c>
       <c r="E245" s="1" t="str">
-        <f>_xlfn.CONCAT(B245," (",C245," - ",D245,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-CONC (Civil - Estacionamientos: concreto)</v>
       </c>
       <c r="I245" s="11">
@@ -22648,7 +22666,7 @@
         <v>1373</v>
       </c>
       <c r="E246" s="1" t="str">
-        <f>_xlfn.CONCAT(B246," (",C246," - ",D246,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-CURB (Civil - Estacionamientos: bordillo)</v>
       </c>
       <c r="I246" s="11">
@@ -22678,7 +22696,7 @@
         <v>1376</v>
       </c>
       <c r="E247" s="1" t="str">
-        <f>_xlfn.CONCAT(B247," (",C247," - ",D247,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-CURB-BACK (Civil - Estacionamientos: bordillo: trasero)</v>
       </c>
       <c r="I247" s="11">
@@ -22708,7 +22726,7 @@
         <v>1379</v>
       </c>
       <c r="E248" s="1" t="str">
-        <f>_xlfn.CONCAT(B248," (",C248," - ",D248,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-CURB-FACE (Civil - Estacionamientos: bordillo: frente)</v>
       </c>
       <c r="I248" s="11">
@@ -22738,7 +22756,7 @@
         <v>1382</v>
       </c>
       <c r="E249" s="1" t="str">
-        <f>_xlfn.CONCAT(B249," (",C249," - ",D249,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-DRAN (Civil - Estacionamientos: indicaciones de pendiente de drenaje)</v>
       </c>
       <c r="I249" s="11">
@@ -22768,7 +22786,7 @@
         <v>1385</v>
       </c>
       <c r="E250" s="1" t="str">
-        <f>_xlfn.CONCAT(B250," (",C250," - ",D250,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-FIXT (Civil - Estacionamientos: accesorios (frenos de rueda, parquímetros, etc.))</v>
       </c>
       <c r="I250" s="11">
@@ -22798,7 +22816,7 @@
         <v>1388</v>
       </c>
       <c r="E251" s="1" t="str">
-        <f>_xlfn.CONCAT(B251," (",C251," - ",D251,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-FLNE (Civil - Estacionamientos: carril de incendios)</v>
       </c>
       <c r="I251" s="11">
@@ -22828,7 +22846,7 @@
         <v>1391</v>
       </c>
       <c r="E252" s="1" t="str">
-        <f>_xlfn.CONCAT(B252," (",C252," - ",D252,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-FLNE-MRKG (Civil - Estacionamientos: carril de incendios: marcas en el pavimento)</v>
       </c>
       <c r="I252" s="11">
@@ -22858,7 +22876,7 @@
         <v>1394</v>
       </c>
       <c r="E253" s="1" t="str">
-        <f>_xlfn.CONCAT(B253," (",C253," - ",D253,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-FLNE-SIGN (Civil - Estacionamientos: carril de incendios: señalización)</v>
       </c>
       <c r="I253" s="11">
@@ -22888,7 +22906,7 @@
         <v>1397</v>
       </c>
       <c r="E254" s="1" t="str">
-        <f>_xlfn.CONCAT(B254," (",C254," - ",D254,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-GRVL (Civil - Estacionamientos: grava)</v>
       </c>
       <c r="I254" s="11">
@@ -22918,7 +22936,7 @@
         <v>1400</v>
       </c>
       <c r="E255" s="1" t="str">
-        <f>_xlfn.CONCAT(B255," (",C255," - ",D255,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-MRKG (Civil - Estacionamientos: marcas en el pavimento)</v>
       </c>
       <c r="I255" s="11">
@@ -22948,7 +22966,7 @@
         <v>1403</v>
       </c>
       <c r="E256" s="1" t="str">
-        <f>_xlfn.CONCAT(B256," (",C256," - ",D256,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-SIGN (Civil - Estacionamientos: señalización)</v>
       </c>
       <c r="I256" s="11">
@@ -22978,7 +22996,7 @@
         <v>1406</v>
       </c>
       <c r="E257" s="1" t="str">
-        <f>_xlfn.CONCAT(B257," (",C257," - ",D257,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-STRP (Civil - Estacionamientos: líneas de señalización)</v>
       </c>
       <c r="I257" s="11">
@@ -23008,7 +23026,7 @@
         <v>1409</v>
       </c>
       <c r="E258" s="1" t="str">
-        <f>_xlfn.CONCAT(B258," (",C258," - ",D258,")")</f>
+        <f t="shared" si="3"/>
         <v>C-PRKG-UPVD (Civil - Estacionamientos: superficie sin pavimentar)</v>
       </c>
       <c r="I258" s="11">
@@ -23038,7 +23056,7 @@
         <v>1412</v>
       </c>
       <c r="E259" s="1" t="str">
-        <f>_xlfn.CONCAT(B259," (",C259," - ",D259,")")</f>
+        <f t="shared" ref="E259:E322" si="4">_xlfn.CONCAT(B259," (",C259," - ",D259,")")</f>
         <v>C-PRKG-WHIT (Civil - Estacionamientos: pintura blanca)</v>
       </c>
       <c r="I259" s="11">
@@ -23068,7 +23086,7 @@
         <v>1415</v>
       </c>
       <c r="E260" s="1" t="str">
-        <f>_xlfn.CONCAT(B260," (",C260," - ",D260,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PRKG-WHIT-TICK (Civil - Estacionamientos: pintura blanca: marcas de verificación)</v>
       </c>
       <c r="I260" s="11">
@@ -23098,7 +23116,7 @@
         <v>1418</v>
       </c>
       <c r="E261" s="1" t="str">
-        <f>_xlfn.CONCAT(B261," (",C261," - ",D261,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PRKG-YELO (Civil - Estacionamientos: pintura amarilla)</v>
       </c>
       <c r="I261" s="11">
@@ -23128,7 +23146,7 @@
         <v>1421</v>
       </c>
       <c r="E262" s="1" t="str">
-        <f>_xlfn.CONCAT(B262," (",C262," - ",D262,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PRKG-YELO-TICK (Civil - Estacionamientos Lotes: pintura amarilla: marcas de verificación)</v>
       </c>
       <c r="I262" s="11">
@@ -23144,7 +23162,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A263" s="9">
         <v>1</v>
       </c>
@@ -23158,15 +23176,18 @@
         <v>539</v>
       </c>
       <c r="E263" s="1" t="str">
-        <f>_xlfn.CONCAT(B263," (",C263," - ",D263,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PROP (Civil - Propiedad)</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>3800</v>
+        <v>3806</v>
       </c>
       <c r="G263" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H263" s="11">
+        <v>0.25</v>
+      </c>
       <c r="I263" s="11">
         <v>0</v>
       </c>
@@ -23194,7 +23215,7 @@
         <v>1425</v>
       </c>
       <c r="E264" s="1" t="str">
-        <f>_xlfn.CONCAT(B264," (",C264," - ",D264,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PROP-LINE (Civil - Propiedad: líneas)</v>
       </c>
       <c r="I264" s="11">
@@ -23224,7 +23245,7 @@
         <v>1428</v>
       </c>
       <c r="E265" s="1" t="str">
-        <f>_xlfn.CONCAT(B265," (",C265," - ",D265,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PROP-SBCK (Civil - Propiedad: líneas de retranqueo)</v>
       </c>
       <c r="I265" s="11">
@@ -23254,7 +23275,7 @@
         <v>551</v>
       </c>
       <c r="E266" s="1" t="str">
-        <f>_xlfn.CONCAT(B266," (",C266," - ",D266,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PVMT (Civil - Pavimento)</v>
       </c>
       <c r="I266" s="11">
@@ -23284,7 +23305,7 @@
         <v>1432</v>
       </c>
       <c r="E267" s="1" t="str">
-        <f>_xlfn.CONCAT(B267," (",C267," - ",D267,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PVMT-ASPH (Civil - Pavimento: asfalto)</v>
       </c>
       <c r="I267" s="11">
@@ -23314,7 +23335,7 @@
         <v>1435</v>
       </c>
       <c r="E268" s="1" t="str">
-        <f>_xlfn.CONCAT(B268," (",C268," - ",D268,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PVMT-CONC (Civil - Pavimento: concreto)</v>
       </c>
       <c r="I268" s="11">
@@ -23344,7 +23365,7 @@
         <v>1438</v>
       </c>
       <c r="E269" s="1" t="str">
-        <f>_xlfn.CONCAT(B269," (",C269," - ",D269,")")</f>
+        <f t="shared" si="4"/>
         <v>C-PVMT-GRVL (Civil - Pavimento: grava)</v>
       </c>
       <c r="I269" s="11">
@@ -23374,7 +23395,7 @@
         <v>554</v>
       </c>
       <c r="E270" s="1" t="str">
-        <f>_xlfn.CONCAT(B270," (",C270," - ",D270,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RAIL (Civil - Ferrocarril)</v>
       </c>
       <c r="I270" s="11">
@@ -23404,7 +23425,7 @@
         <v>1442</v>
       </c>
       <c r="E271" s="1" t="str">
-        <f>_xlfn.CONCAT(B271," (",C271," - ",D271,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RAIL-CNTR (Civil - Ferrocarril: centro)</v>
       </c>
       <c r="I271" s="11">
@@ -23434,7 +23455,7 @@
         <v>1445</v>
       </c>
       <c r="E272" s="1" t="str">
-        <f>_xlfn.CONCAT(B272," (",C272," - ",D272,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RAIL-EQPM (Civil - Ferrocarril: equipo (barreras, señales, etc.))</v>
       </c>
       <c r="I272" s="11">
@@ -23464,7 +23485,7 @@
         <v>1448</v>
       </c>
       <c r="E273" s="1" t="str">
-        <f>_xlfn.CONCAT(B273," (",C273," - ",D273,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RAIL-TRAK (Civil - Ferrocarril: vía)</v>
       </c>
       <c r="I273" s="11">
@@ -23494,14 +23515,8 @@
         <v>569</v>
       </c>
       <c r="E274" s="1" t="str">
-        <f>_xlfn.CONCAT(B274," (",C274," - ",D274,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RIVR (Civil - Río)</v>
-      </c>
-      <c r="F274" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G274" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I274" s="11">
         <v>0</v>
@@ -23530,7 +23545,7 @@
         <v>1452</v>
       </c>
       <c r="E275" s="1" t="str">
-        <f>_xlfn.CONCAT(B275," (",C275," - ",D275,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RIVR-BOTM (Civil - Río: fondo)</v>
       </c>
       <c r="I275" s="11">
@@ -23560,7 +23575,7 @@
         <v>1455</v>
       </c>
       <c r="E276" s="1" t="str">
-        <f>_xlfn.CONCAT(B276," (",C276," - ",D276,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RIVR-CNTR (Civil - Río: centro)</v>
       </c>
       <c r="I276" s="11">
@@ -23590,7 +23605,7 @@
         <v>1458</v>
       </c>
       <c r="E277" s="1" t="str">
-        <f>_xlfn.CONCAT(B277," (",C277," - ",D277,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RIVR-EDGE (Civil - Río: orilla)</v>
       </c>
       <c r="I277" s="11">
@@ -23620,7 +23635,7 @@
         <v>1461</v>
       </c>
       <c r="E278" s="1" t="str">
-        <f>_xlfn.CONCAT(B278," (",C278," - ",D278,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RIVR-TOPB (Civil - Río: parte superior de la orilla)</v>
       </c>
       <c r="I278" s="11">
@@ -23636,7 +23651,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A279" s="9">
         <v>1</v>
       </c>
@@ -23650,15 +23665,18 @@
         <v>572</v>
       </c>
       <c r="E279" s="1" t="str">
-        <f>_xlfn.CONCAT(B279," (",C279," - ",D279,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD (Civil - Carreteras)</v>
       </c>
-      <c r="F279" s="11" t="s">
-        <v>3800</v>
+      <c r="F279" s="11">
+        <v>57</v>
       </c>
       <c r="G279" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H279" s="11">
+        <v>0.4</v>
+      </c>
       <c r="I279" s="11">
         <v>0</v>
       </c>
@@ -23686,7 +23704,7 @@
         <v>1465</v>
       </c>
       <c r="E280" s="1" t="str">
-        <f>_xlfn.CONCAT(B280," (",C280," - ",D280,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-ASPH (Civil - Carreteras: asfalto)</v>
       </c>
       <c r="I280" s="11">
@@ -23716,7 +23734,7 @@
         <v>1468</v>
       </c>
       <c r="E281" s="1" t="str">
-        <f>_xlfn.CONCAT(B281," (",C281," - ",D281,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-CNTR (Civil - Carreteras: centro)</v>
       </c>
       <c r="I281" s="11">
@@ -23746,7 +23764,7 @@
         <v>1471</v>
       </c>
       <c r="E282" s="1" t="str">
-        <f>_xlfn.CONCAT(B282," (",C282," - ",D282,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-CONC (Civil - Carreteras: concreto)</v>
       </c>
       <c r="I282" s="11">
@@ -23776,7 +23794,7 @@
         <v>1474</v>
       </c>
       <c r="E283" s="1" t="str">
-        <f>_xlfn.CONCAT(B283," (",C283," - ",D283,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-CURB (Civil - Carreteras: bordillo)</v>
       </c>
       <c r="I283" s="11">
@@ -23806,7 +23824,7 @@
         <v>1477</v>
       </c>
       <c r="E284" s="1" t="str">
-        <f>_xlfn.CONCAT(B284," (",C284," - ",D284,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-CURB-BACK (Civil - Carreteras: bordillo: parte trasera)</v>
       </c>
       <c r="I284" s="11">
@@ -23836,7 +23854,7 @@
         <v>1480</v>
       </c>
       <c r="E285" s="1" t="str">
-        <f>_xlfn.CONCAT(B285," (",C285," - ",D285,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-CURB-FACE (Civil - Carreteras: bordillo: frente)</v>
       </c>
       <c r="I285" s="11">
@@ -23866,7 +23884,7 @@
         <v>1483</v>
       </c>
       <c r="E286" s="1" t="str">
-        <f>_xlfn.CONCAT(B286," (",C286," - ",D286,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-FLNE (Civil - Carreteras: carril de incendios)</v>
       </c>
       <c r="I286" s="11">
@@ -23896,7 +23914,7 @@
         <v>1486</v>
       </c>
       <c r="E287" s="1" t="str">
-        <f>_xlfn.CONCAT(B287," (",C287," - ",D287,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-FLNE-MRKG (Civil - Carreteras: carril de incendios: marcas en el pavimento)</v>
       </c>
       <c r="I287" s="11">
@@ -23926,7 +23944,7 @@
         <v>1489</v>
       </c>
       <c r="E288" s="1" t="str">
-        <f>_xlfn.CONCAT(B288," (",C288," - ",D288,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-FLNE-SIGN (Civil - Carreteras: carril de incendios: señalización)</v>
       </c>
       <c r="I288" s="11">
@@ -23956,7 +23974,7 @@
         <v>1492</v>
       </c>
       <c r="E289" s="1" t="str">
-        <f>_xlfn.CONCAT(B289," (",C289," - ",D289,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-GRVL (Civil - Carreteras: grava)</v>
       </c>
       <c r="I289" s="11">
@@ -23986,7 +24004,7 @@
         <v>1495</v>
       </c>
       <c r="E290" s="1" t="str">
-        <f>_xlfn.CONCAT(B290," (",C290," - ",D290,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-MRKG (Civil - Carreteras: marcas en el pavimento)</v>
       </c>
       <c r="I290" s="11">
@@ -24016,7 +24034,7 @@
         <v>1498</v>
       </c>
       <c r="E291" s="1" t="str">
-        <f>_xlfn.CONCAT(B291," (",C291," - ",D291,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-PROF (Civil - Carreteras: perfil)</v>
       </c>
       <c r="I291" s="11">
@@ -24046,7 +24064,7 @@
         <v>1501</v>
       </c>
       <c r="E292" s="1" t="str">
-        <f>_xlfn.CONCAT(B292," (",C292," - ",D292,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-SIGN (Civil - Carreteras: señalización)</v>
       </c>
       <c r="I292" s="11">
@@ -24076,7 +24094,7 @@
         <v>1504</v>
       </c>
       <c r="E293" s="1" t="str">
-        <f>_xlfn.CONCAT(B293," (",C293," - ",D293,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-STAN (Civil - Carreteras: estacionamiento)</v>
       </c>
       <c r="I293" s="11">
@@ -24106,7 +24124,7 @@
         <v>1507</v>
       </c>
       <c r="E294" s="1" t="str">
-        <f>_xlfn.CONCAT(B294," (",C294," - ",D294,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-UPVD (Civil - Carreteras: superficie sin pavimentar)</v>
       </c>
       <c r="I294" s="11">
@@ -24136,7 +24154,7 @@
         <v>1510</v>
       </c>
       <c r="E295" s="1" t="str">
-        <f>_xlfn.CONCAT(B295," (",C295," - ",D295,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-WHIT (Civil - Carreteras: pintura blanca)</v>
       </c>
       <c r="I295" s="11">
@@ -24166,7 +24184,7 @@
         <v>1513</v>
       </c>
       <c r="E296" s="1" t="str">
-        <f>_xlfn.CONCAT(B296," (",C296," - ",D296,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-WHIT-TICK (Civil - Carreteras: pintura blanca Marcas de verificación)</v>
       </c>
       <c r="I296" s="11">
@@ -24196,7 +24214,7 @@
         <v>1516</v>
       </c>
       <c r="E297" s="1" t="str">
-        <f>_xlfn.CONCAT(B297," (",C297," - ",D297,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-YELO (Civil - Carreteras: pintura amarilla)</v>
       </c>
       <c r="I297" s="11">
@@ -24226,7 +24244,7 @@
         <v>1519</v>
       </c>
       <c r="E298" s="1" t="str">
-        <f>_xlfn.CONCAT(B298," (",C298," - ",D298,")")</f>
+        <f t="shared" si="4"/>
         <v>C-ROAD-YELO-TICK (Civil - Carreteras: pintura amarilla: marcas de verificación)</v>
       </c>
       <c r="I298" s="11">
@@ -24256,7 +24274,7 @@
         <v>577</v>
       </c>
       <c r="E299" s="1" t="str">
-        <f>_xlfn.CONCAT(B299," (",C299," - ",D299,")")</f>
+        <f t="shared" si="4"/>
         <v>C-RRAP (Civil - Escalones)</v>
       </c>
       <c r="I299" s="11">
@@ -24286,7 +24304,7 @@
         <v>592</v>
       </c>
       <c r="E300" s="1" t="str">
-        <f>_xlfn.CONCAT(B300," (",C300," - ",D300,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SGHT (Civil - Distancia visual)</v>
       </c>
       <c r="I300" s="11">
@@ -24316,7 +24334,7 @@
         <v>1524</v>
       </c>
       <c r="E301" s="1" t="str">
-        <f>_xlfn.CONCAT(B301," (",C301," - ",D301,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SGHT-PROF (Civil - Distancia visual: perfil)</v>
       </c>
       <c r="I301" s="11">
@@ -24346,14 +24364,8 @@
         <v>610</v>
       </c>
       <c r="E302" s="1" t="str">
-        <f>_xlfn.CONCAT(B302," (",C302," - ",D302,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SOIL (Civil - Suelos)</v>
-      </c>
-      <c r="F302" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G302" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I302" s="11">
         <v>0</v>
@@ -24368,7 +24380,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A303" s="9">
         <v>1</v>
       </c>
@@ -24382,15 +24394,18 @@
         <v>625</v>
       </c>
       <c r="E303" s="1" t="str">
-        <f>_xlfn.CONCAT(B303," (",C303," - ",D303,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR (Civil - Alcantarillado sanitario)</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>3800</v>
+        <v>3805</v>
       </c>
       <c r="G303" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H303" s="11">
+        <v>0.3</v>
+      </c>
       <c r="I303" s="11">
         <v>0</v>
       </c>
@@ -24418,7 +24433,7 @@
         <v>1529</v>
       </c>
       <c r="E304" s="1" t="str">
-        <f>_xlfn.CONCAT(B304," (",C304," - ",D304,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-DIAG (Civil - Alcantarillado sanitario: diagramas)</v>
       </c>
       <c r="I304" s="11">
@@ -24448,7 +24463,7 @@
         <v>1532</v>
       </c>
       <c r="E305" s="1" t="str">
-        <f>_xlfn.CONCAT(B305," (",C305," - ",D305,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-FORC (Civil - Alcantarillado sanitario: tubería de impulsión)</v>
       </c>
       <c r="I305" s="11">
@@ -24478,7 +24493,7 @@
         <v>1535</v>
       </c>
       <c r="E306" s="1" t="str">
-        <f>_xlfn.CONCAT(B306," (",C306," - ",D306,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-LATL (Civil - Alcantarillado sanitario: línea lateral)</v>
       </c>
       <c r="I306" s="11">
@@ -24508,7 +24523,7 @@
         <v>1538</v>
       </c>
       <c r="E307" s="1" t="str">
-        <f>_xlfn.CONCAT(B307," (",C307," - ",D307,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-MHOL (Civil - Alcantarillado sanitario: pozo de registro)</v>
       </c>
       <c r="I307" s="11">
@@ -24538,7 +24553,7 @@
         <v>1541</v>
       </c>
       <c r="E308" s="1" t="str">
-        <f>_xlfn.CONCAT(B308," (",C308," - ",D308,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-PIPE (Civil - Alcantarillado sanitario: tuberías)</v>
       </c>
       <c r="I308" s="11">
@@ -24568,7 +24583,7 @@
         <v>1544</v>
       </c>
       <c r="E309" s="1" t="str">
-        <f>_xlfn.CONCAT(B309," (",C309," - ",D309,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-PIPE-RCON (Civil - Alcantarillado sanitario: tuberías: hormigón armado)</v>
       </c>
       <c r="I309" s="11">
@@ -24598,7 +24613,7 @@
         <v>1547</v>
       </c>
       <c r="E310" s="1" t="str">
-        <f>_xlfn.CONCAT(B310," (",C310," - ",D310,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-PIPE-STEL (Civil - Alcantarillado sanitario: tuberías: acero)</v>
       </c>
       <c r="I310" s="11">
@@ -24628,7 +24643,7 @@
         <v>1550</v>
       </c>
       <c r="E311" s="1" t="str">
-        <f>_xlfn.CONCAT(B311," (",C311," - ",D311,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-PROF (Civil - Alcantarillado sanitario: perfil)</v>
       </c>
       <c r="I311" s="11">
@@ -24658,7 +24673,7 @@
         <v>1553</v>
       </c>
       <c r="E312" s="1" t="str">
-        <f>_xlfn.CONCAT(B312," (",C312," - ",D312,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-STAN (Civil - Alcantarillado sanitario: estacionamiento)</v>
       </c>
       <c r="I312" s="11">
@@ -24688,7 +24703,7 @@
         <v>1556</v>
       </c>
       <c r="E313" s="1" t="str">
-        <f>_xlfn.CONCAT(B313," (",C313," - ",D313,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-STRC (Civil - Alcantarillado sanitario: estructuras)</v>
       </c>
       <c r="I313" s="11">
@@ -24718,7 +24733,7 @@
         <v>1559</v>
       </c>
       <c r="E314" s="1" t="str">
-        <f>_xlfn.CONCAT(B314," (",C314," - ",D314,")")</f>
+        <f t="shared" si="4"/>
         <v>C-SSWR-UGND (Civil - Alcantarillado sanitario: subterráneo)</v>
       </c>
       <c r="I314" s="11">
@@ -24748,7 +24763,7 @@
         <v>628</v>
       </c>
       <c r="E315" s="1" t="str">
-        <f>_xlfn.CONCAT(B315," (",C315," - ",D315,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM (Civil - Sistema de vapor)</v>
       </c>
       <c r="I315" s="11">
@@ -24778,7 +24793,7 @@
         <v>1563</v>
       </c>
       <c r="E316" s="1" t="str">
-        <f>_xlfn.CONCAT(B316," (",C316," - ",D316,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM-INST (Civil - Sistema de vapor: instrumentación (medidores, válvulas, etc.))</v>
       </c>
       <c r="I316" s="11">
@@ -24808,7 +24823,7 @@
         <v>1566</v>
       </c>
       <c r="E317" s="1" t="str">
-        <f>_xlfn.CONCAT(B317," (",C317," - ",D317,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM-MHOL (Civil - Sistema de vapor: pozo de registro)</v>
       </c>
       <c r="I317" s="11">
@@ -24838,7 +24853,7 @@
         <v>1569</v>
       </c>
       <c r="E318" s="1" t="str">
-        <f>_xlfn.CONCAT(B318," (",C318," - ",D318,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM-PIPE (Civil - Sistema de vapor: tuberías)</v>
       </c>
       <c r="I318" s="11">
@@ -24868,7 +24883,7 @@
         <v>1572</v>
       </c>
       <c r="E319" s="1" t="str">
-        <f>_xlfn.CONCAT(B319," (",C319," - ",D319,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM-STRC (Civil - Sistema de vapor: estructuras)</v>
       </c>
       <c r="I319" s="11">
@@ -24898,7 +24913,7 @@
         <v>1575</v>
       </c>
       <c r="E320" s="1" t="str">
-        <f>_xlfn.CONCAT(B320," (",C320," - ",D320,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STEM-UGND (Civil - Sistema de vapor: subterráneo)</v>
       </c>
       <c r="I320" s="11">
@@ -24914,7 +24929,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A321" s="9">
         <v>1</v>
       </c>
@@ -24928,15 +24943,18 @@
         <v>634</v>
       </c>
       <c r="E321" s="1" t="str">
-        <f>_xlfn.CONCAT(B321," (",C321," - ",D321,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STRM (Civil - Alcantarillado pluvial)</v>
       </c>
-      <c r="F321" s="11" t="s">
-        <v>3800</v>
+      <c r="F321" s="11">
+        <v>151</v>
       </c>
       <c r="G321" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H321" s="11">
+        <v>0.3</v>
+      </c>
       <c r="I321" s="11">
         <v>0</v>
       </c>
@@ -24964,7 +24982,7 @@
         <v>1579</v>
       </c>
       <c r="E322" s="1" t="str">
-        <f>_xlfn.CONCAT(B322," (",C322," - ",D322,")")</f>
+        <f t="shared" si="4"/>
         <v>C-STRM-CNTR (Civil - Alcantarillado pluvial: centro)</v>
       </c>
       <c r="I322" s="11">
@@ -24994,7 +25012,7 @@
         <v>1582</v>
       </c>
       <c r="E323" s="1" t="str">
-        <f>_xlfn.CONCAT(B323," (",C323," - ",D323,")")</f>
+        <f t="shared" ref="E323:E386" si="5">_xlfn.CONCAT(B323," (",C323," - ",D323,")")</f>
         <v>C-STRM-DIAG (Civil - Alcantarillado pluvial: diagramas)</v>
       </c>
       <c r="I323" s="11">
@@ -25024,7 +25042,7 @@
         <v>1585</v>
       </c>
       <c r="E324" s="1" t="str">
-        <f>_xlfn.CONCAT(B324," (",C324," - ",D324,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-HWAL (Civil - Alcantarillado pluvial: muro de cabecera)</v>
       </c>
       <c r="I324" s="11">
@@ -25054,7 +25072,7 @@
         <v>1588</v>
       </c>
       <c r="E325" s="1" t="str">
-        <f>_xlfn.CONCAT(B325," (",C325," - ",D325,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-MHOL (Civil - Alcantarillado pluvial: pozo de registro)</v>
       </c>
       <c r="I325" s="11">
@@ -25084,7 +25102,7 @@
         <v>1591</v>
       </c>
       <c r="E326" s="1" t="str">
-        <f>_xlfn.CONCAT(B326," (",C326," - ",D326,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-PIPE (Civil - Alcantarillado pluvial: tuberías)</v>
       </c>
       <c r="I326" s="11">
@@ -25114,7 +25132,7 @@
         <v>1594</v>
       </c>
       <c r="E327" s="1" t="str">
-        <f>_xlfn.CONCAT(B327," (",C327," - ",D327,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-PIPE-CMTL (Civil - Alcantarillado pluvial: tuberías: metal corrugado)</v>
       </c>
       <c r="I327" s="11">
@@ -25144,7 +25162,7 @@
         <v>1597</v>
       </c>
       <c r="E328" s="1" t="str">
-        <f>_xlfn.CONCAT(B328," (",C328," - ",D328,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-PIPE-RCON (Civil - Alcantarillado pluvial: tuberías: hormigón armado)</v>
       </c>
       <c r="I328" s="11">
@@ -25174,7 +25192,7 @@
         <v>1600</v>
       </c>
       <c r="E329" s="1" t="str">
-        <f>_xlfn.CONCAT(B329," (",C329," - ",D329,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-PROF (Civil - Alcantarillado pluvial: perfil)</v>
       </c>
       <c r="I329" s="11">
@@ -25204,7 +25222,7 @@
         <v>1603</v>
       </c>
       <c r="E330" s="1" t="str">
-        <f>_xlfn.CONCAT(B330," (",C330," - ",D330,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-STAN (Civil - Alcantarillado pluvial: estacionamiento)</v>
       </c>
       <c r="I330" s="11">
@@ -25234,7 +25252,7 @@
         <v>1606</v>
       </c>
       <c r="E331" s="1" t="str">
-        <f>_xlfn.CONCAT(B331," (",C331," - ",D331,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-STRC (Civil - Alcantarillado pluvial: estructuras)</v>
       </c>
       <c r="I331" s="11">
@@ -25264,7 +25282,7 @@
         <v>1609</v>
       </c>
       <c r="E332" s="1" t="str">
-        <f>_xlfn.CONCAT(B332," (",C332," - ",D332,")")</f>
+        <f t="shared" si="5"/>
         <v>C-STRM-UGND (Civil - Alcantarillado pluvial: subterráneo)</v>
       </c>
       <c r="I332" s="11">
@@ -25294,14 +25312,8 @@
         <v>643</v>
       </c>
       <c r="E333" s="1" t="str">
-        <f>_xlfn.CONCAT(B333," (",C333," - ",D333,")")</f>
+        <f t="shared" si="5"/>
         <v>C-SWLK (Civil - Aceras)</v>
-      </c>
-      <c r="F333" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G333" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I333" s="11">
         <v>0</v>
@@ -25330,7 +25342,7 @@
         <v>1613</v>
       </c>
       <c r="E334" s="1" t="str">
-        <f>_xlfn.CONCAT(B334," (",C334," - ",D334,")")</f>
+        <f t="shared" si="5"/>
         <v>C-SWLK-ASPH (Civil - Aceras: asfalto)</v>
       </c>
       <c r="I334" s="11">
@@ -25360,7 +25372,7 @@
         <v>1616</v>
       </c>
       <c r="E335" s="1" t="str">
-        <f>_xlfn.CONCAT(B335," (",C335," - ",D335,")")</f>
+        <f t="shared" si="5"/>
         <v>C-SWLK-CONC (Civil - Aceras: hormigón)</v>
       </c>
       <c r="I335" s="11">
@@ -25390,14 +25402,8 @@
         <v>1618</v>
       </c>
       <c r="E336" s="1" t="str">
-        <f>_xlfn.CONCAT(B336," (",C336," - ",D336,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TINN (Civil - Red irregular triangulada)</v>
-      </c>
-      <c r="F336" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G336" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I336" s="11">
         <v>0</v>
@@ -25426,7 +25432,7 @@
         <v>1621</v>
       </c>
       <c r="E337" s="1" t="str">
-        <f>_xlfn.CONCAT(B337," (",C337," - ",D337,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TINN-BNDY (Civil - Red irregular triangulada: límite)</v>
       </c>
       <c r="I337" s="11">
@@ -25456,7 +25462,7 @@
         <v>1624</v>
       </c>
       <c r="E338" s="1" t="str">
-        <f>_xlfn.CONCAT(B338," (",C338," - ",D338,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TINN-FALT (Civil - Red irregular triangulada: líneas de falla/ruptura)</v>
       </c>
       <c r="I338" s="11">
@@ -25486,7 +25492,7 @@
         <v>1627</v>
       </c>
       <c r="E339" s="1" t="str">
-        <f>_xlfn.CONCAT(B339," (",C339," - ",D339,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TINN-VIEW (Civil - Red irregular triangulada: vista de triangulación)</v>
       </c>
       <c r="I339" s="11">
@@ -25516,7 +25522,7 @@
         <v>1630</v>
       </c>
       <c r="E340" s="1" t="str">
-        <f>_xlfn.CONCAT(B340," (",C340," - ",D340,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TINN-VOID (Civil - Red irregular triangulada: regiones vacías)</v>
       </c>
       <c r="I340" s="11">
@@ -25546,14 +25552,8 @@
         <v>655</v>
       </c>
       <c r="E341" s="1" t="str">
-        <f>_xlfn.CONCAT(B341," (",C341," - ",D341,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO (Civil - Característica topográfica)</v>
-      </c>
-      <c r="F341" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G341" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I341" s="11">
         <v>0</v>
@@ -25582,7 +25582,7 @@
         <v>1634</v>
       </c>
       <c r="E342" s="1" t="str">
-        <f>_xlfn.CONCAT(B342," (",C342," - ",D342,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO-DEPR (Civil - Característica topográfica: depresión)</v>
       </c>
       <c r="I342" s="11">
@@ -25612,7 +25612,7 @@
         <v>1637</v>
       </c>
       <c r="E343" s="1" t="str">
-        <f>_xlfn.CONCAT(B343," (",C343," - ",D343,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO-MAJR (Civil - Característica topográfica: principal (curvas de nivel))</v>
       </c>
       <c r="I343" s="11">
@@ -25642,7 +25642,7 @@
         <v>1640</v>
       </c>
       <c r="E344" s="1" t="str">
-        <f>_xlfn.CONCAT(B344," (",C344," - ",D344,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO-MINR (Civil - Característica topográfica: menor (curvas de nivel))</v>
       </c>
       <c r="I344" s="11">
@@ -25672,7 +25672,7 @@
         <v>1643</v>
       </c>
       <c r="E345" s="1" t="str">
-        <f>_xlfn.CONCAT(B345," (",C345," - ",D345,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO-SPOT (Civil - Característica topográfica: elevaciones puntuales)</v>
       </c>
       <c r="I345" s="11">
@@ -25702,7 +25702,7 @@
         <v>1646</v>
       </c>
       <c r="E346" s="1" t="str">
-        <f>_xlfn.CONCAT(B346," (",C346," - ",D346,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TOPO-TPIT (Civil - Característica topográfica: pozos de sondeo)</v>
       </c>
       <c r="I346" s="11">
@@ -25732,14 +25732,8 @@
         <v>658</v>
       </c>
       <c r="E347" s="1" t="str">
-        <f>_xlfn.CONCAT(B347," (",C347," - ",D347,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL (Civil - Senderos o caminos)</v>
-      </c>
-      <c r="F347" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G347" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I347" s="11">
         <v>0</v>
@@ -25768,7 +25762,7 @@
         <v>1650</v>
       </c>
       <c r="E348" s="1" t="str">
-        <f>_xlfn.CONCAT(B348," (",C348," - ",D348,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-ASPH (Civil - Senderos o caminos: asfalto)</v>
       </c>
       <c r="I348" s="11">
@@ -25798,7 +25792,7 @@
         <v>1653</v>
       </c>
       <c r="E349" s="1" t="str">
-        <f>_xlfn.CONCAT(B349," (",C349," - ",D349,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-CONC (Civil - Senderos o caminos: hormigón)</v>
       </c>
       <c r="I349" s="11">
@@ -25828,7 +25822,7 @@
         <v>1656</v>
       </c>
       <c r="E350" s="1" t="str">
-        <f>_xlfn.CONCAT(B350," (",C350," - ",D350,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-GRVL (Civil - Senderos o Caminos: grava)</v>
       </c>
       <c r="I350" s="11">
@@ -25858,7 +25852,7 @@
         <v>1659</v>
       </c>
       <c r="E351" s="1" t="str">
-        <f>_xlfn.CONCAT(B351," (",C351," - ",D351,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-MRKG (Civil - Senderos o senderos: marcas en el pavimento)</v>
       </c>
       <c r="I351" s="11">
@@ -25888,7 +25882,7 @@
         <v>1662</v>
       </c>
       <c r="E352" s="1" t="str">
-        <f>_xlfn.CONCAT(B352," (",C352," - ",D352,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-SIGN (Civil - Senderos o senderos: señalización)</v>
       </c>
       <c r="I352" s="11">
@@ -25918,7 +25912,7 @@
         <v>1665</v>
       </c>
       <c r="E353" s="1" t="str">
-        <f>_xlfn.CONCAT(B353," (",C353," - ",D353,")")</f>
+        <f t="shared" si="5"/>
         <v>C-TRAL-UPVD (Civil - Senderos o senderos: superficie sin pavimentar)</v>
       </c>
       <c r="I353" s="11">
@@ -25934,7 +25928,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A354" s="9">
         <v>1</v>
       </c>
@@ -25948,7 +25942,7 @@
         <v>685</v>
       </c>
       <c r="E354" s="1" t="str">
-        <f>_xlfn.CONCAT(B354," (",C354," - ",D354,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WALL (Civil - Muros)</v>
       </c>
       <c r="F354" s="11" t="s">
@@ -25957,6 +25951,9 @@
       <c r="G354" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H354" s="11">
+        <v>0.6</v>
+      </c>
       <c r="I354" s="11">
         <v>0</v>
       </c>
@@ -25984,7 +25981,7 @@
         <v>1669</v>
       </c>
       <c r="E355" s="1" t="str">
-        <f>_xlfn.CONCAT(B355," (",C355," - ",D355,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WALL-CTLJ (Civil - Muros: junta de control)</v>
       </c>
       <c r="I355" s="11">
@@ -26014,7 +26011,7 @@
         <v>1672</v>
       </c>
       <c r="E356" s="1" t="str">
-        <f>_xlfn.CONCAT(B356," (",C356," - ",D356,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WALL-NSBR (Civil - Muros: barrera acústica)</v>
       </c>
       <c r="I356" s="11">
@@ -26044,7 +26041,7 @@
         <v>1675</v>
       </c>
       <c r="E357" s="1" t="str">
-        <f>_xlfn.CONCAT(B357," (",C357," - ",D357,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WALL-RTWL (Civil - Muros: muro de contención)</v>
       </c>
       <c r="I357" s="11">
@@ -26074,7 +26071,7 @@
         <v>1678</v>
       </c>
       <c r="E358" s="1" t="str">
-        <f>_xlfn.CONCAT(B358," (",C358," - ",D358,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WALL-SHEA (Civil - Muros: muros de carga o de corte)</v>
       </c>
       <c r="I358" s="11">
@@ -26104,14 +26101,8 @@
         <v>688</v>
       </c>
       <c r="E359" s="1" t="str">
-        <f>_xlfn.CONCAT(B359," (",C359," - ",D359,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR (Civil - Suministro de agua)</v>
-      </c>
-      <c r="F359" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G359" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I359" s="11">
         <v>0</v>
@@ -26140,7 +26131,7 @@
         <v>1682</v>
       </c>
       <c r="E360" s="1" t="str">
-        <f>_xlfn.CONCAT(B360," (",C360," - ",D360,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-DIAG (Civil - Suministro de agua: diagramas)</v>
       </c>
       <c r="I360" s="11">
@@ -26170,7 +26161,7 @@
         <v>1685</v>
       </c>
       <c r="E361" s="1" t="str">
-        <f>_xlfn.CONCAT(B361," (",C361," - ",D361,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-INST (Civil - Suministro de agua: instrumentación (medidores, válvulas, etc.))</v>
       </c>
       <c r="I361" s="11">
@@ -26200,7 +26191,7 @@
         <v>1688</v>
       </c>
       <c r="E362" s="1" t="str">
-        <f>_xlfn.CONCAT(B362," (",C362," - ",D362,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-PIPE (Civil - Suministro de agua: tuberías)</v>
       </c>
       <c r="I362" s="11">
@@ -26230,7 +26221,7 @@
         <v>1691</v>
       </c>
       <c r="E363" s="1" t="str">
-        <f>_xlfn.CONCAT(B363," (",C363," - ",D363,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-PROF (Civil - Suministro de agua: perfil)</v>
       </c>
       <c r="I363" s="11">
@@ -26260,7 +26251,7 @@
         <v>1694</v>
       </c>
       <c r="E364" s="1" t="str">
-        <f>_xlfn.CONCAT(B364," (",C364," - ",D364,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-STAN (Civil - Suministro de agua: estacionamiento)</v>
       </c>
       <c r="I364" s="11">
@@ -26290,7 +26281,7 @@
         <v>1697</v>
       </c>
       <c r="E365" s="1" t="str">
-        <f>_xlfn.CONCAT(B365," (",C365," - ",D365,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-STRC (Civil - Suministro de agua: estructuras)</v>
       </c>
       <c r="I365" s="11">
@@ -26320,7 +26311,7 @@
         <v>1700</v>
       </c>
       <c r="E366" s="1" t="str">
-        <f>_xlfn.CONCAT(B366," (",C366," - ",D366,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-UGND (Civil - Suministro de agua: subterráneo)</v>
       </c>
       <c r="I366" s="11">
@@ -26350,7 +26341,7 @@
         <v>1703</v>
       </c>
       <c r="E367" s="1" t="str">
-        <f>_xlfn.CONCAT(B367," (",C367," - ",D367,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WATR-WELL (Civil - Suministro de agua: pozo)</v>
       </c>
       <c r="I367" s="11">
@@ -26380,7 +26371,7 @@
         <v>691</v>
       </c>
       <c r="E368" s="1" t="str">
-        <f>_xlfn.CONCAT(B368," (",C368," - ",D368,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WETL (Civil - Humedales)</v>
       </c>
       <c r="I368" s="11">
@@ -26410,7 +26401,7 @@
         <v>697</v>
       </c>
       <c r="E369" s="1" t="str">
-        <f>_xlfn.CONCAT(B369," (",C369," - ",D369,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WWAY (Civil - Vía fluvial)</v>
       </c>
       <c r="I369" s="11">
@@ -26440,7 +26431,7 @@
         <v>1708</v>
       </c>
       <c r="E370" s="1" t="str">
-        <f>_xlfn.CONCAT(B370," (",C370," - ",D370,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WWAY-DLPH (Civil - Vía fluvial: delfín)</v>
       </c>
       <c r="I370" s="11">
@@ -26470,7 +26461,7 @@
         <v>1711</v>
       </c>
       <c r="E371" s="1" t="str">
-        <f>_xlfn.CONCAT(B371," (",C371," - ",D371,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WWAY-FEND (Civil - Vía fluvial: defensa)</v>
       </c>
       <c r="I371" s="11">
@@ -26500,7 +26491,7 @@
         <v>1714</v>
       </c>
       <c r="E372" s="1" t="str">
-        <f>_xlfn.CONCAT(B372," (",C372," - ",D372,")")</f>
+        <f t="shared" si="5"/>
         <v>C-WWAY-MOOR (Civil - Vía fluvial: amarre)</v>
       </c>
       <c r="I372" s="11">
@@ -26530,7 +26521,7 @@
         <v>156</v>
       </c>
       <c r="E373" s="1" t="str">
-        <f>_xlfn.CONCAT(B373," (",C373," - ",D373,")")</f>
+        <f t="shared" si="5"/>
         <v>E-ALRM (Electricidad - Sistema de alarma)</v>
       </c>
       <c r="I373" s="11">
@@ -26560,14 +26551,8 @@
         <v>162</v>
       </c>
       <c r="E374" s="1" t="str">
-        <f>_xlfn.CONCAT(B374," (",C374," - ",D374,")")</f>
+        <f t="shared" si="5"/>
         <v>E-AREA (Electricidad - Área)</v>
-      </c>
-      <c r="F374" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G374" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I374" s="11">
         <v>0</v>
@@ -26596,7 +26581,7 @@
         <v>2019</v>
       </c>
       <c r="E375" s="1" t="str">
-        <f>_xlfn.CONCAT(B375," (",C375," - ",D375,")")</f>
+        <f t="shared" si="5"/>
         <v>E-AREA-OFST (Electricidad - Área: zonas descentradas)</v>
       </c>
       <c r="I375" s="11">
@@ -26626,7 +26611,7 @@
         <v>2020</v>
       </c>
       <c r="E376" s="1" t="str">
-        <f>_xlfn.CONCAT(B376," (",C376," - ",D376,")")</f>
+        <f t="shared" si="5"/>
         <v>E-AREA-SHAD (Electricidad - Área: zonas de sombra)</v>
       </c>
       <c r="I376" s="11">
@@ -26656,14 +26641,8 @@
         <v>165</v>
       </c>
       <c r="E377" s="1" t="str">
-        <f>_xlfn.CONCAT(B377," (",C377," - ",D377,")")</f>
+        <f t="shared" si="5"/>
         <v>E-AUXL (Electricidad - Sistemas auxiliares)</v>
-      </c>
-      <c r="F377" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G377" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I377" s="11">
         <v>0</v>
@@ -26692,7 +26671,7 @@
         <v>2021</v>
       </c>
       <c r="E378" s="1" t="str">
-        <f>_xlfn.CONCAT(B378," (",C378," - ",D378,")")</f>
+        <f t="shared" si="5"/>
         <v>E-BELL (Electricidad - Sistema de timbre)</v>
       </c>
       <c r="I378" s="11">
@@ -26708,7 +26687,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A379" s="9">
         <v>1</v>
       </c>
@@ -26722,14 +26701,17 @@
         <v>210</v>
       </c>
       <c r="E379" s="1" t="str">
-        <f>_xlfn.CONCAT(B379," (",C379," - ",D379,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CABL (Electricidad - Sistemas de cable)</v>
       </c>
-      <c r="F379" s="11" t="s">
-        <v>3800</v>
+      <c r="F379" s="11">
+        <v>201</v>
       </c>
       <c r="G379" s="11" t="s">
-        <v>3799</v>
+        <v>3807</v>
+      </c>
+      <c r="H379" s="11">
+        <v>201</v>
       </c>
       <c r="I379" s="11">
         <v>0</v>
@@ -26758,7 +26740,7 @@
         <v>2022</v>
       </c>
       <c r="E380" s="1" t="str">
-        <f>_xlfn.CONCAT(B380," (",C380," - ",D380,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CABL-COAX (Electricidad - Sistemas de cable: cable coaxial)</v>
       </c>
       <c r="I380" s="11">
@@ -26788,7 +26770,7 @@
         <v>2023</v>
       </c>
       <c r="E381" s="1" t="str">
-        <f>_xlfn.CONCAT(B381," (",C381," - ",D381,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CABL-FIBR (Electricidad - Sistemas de cable: cable de fibra óptica)</v>
       </c>
       <c r="I381" s="11">
@@ -26818,7 +26800,7 @@
         <v>2024</v>
       </c>
       <c r="E382" s="1" t="str">
-        <f>_xlfn.CONCAT(B382," (",C382," - ",D382,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CABL-MULT (Electricidad - Sistemas de cable: cable multiconductor)</v>
       </c>
       <c r="I382" s="11">
@@ -26848,7 +26830,7 @@
         <v>2025</v>
       </c>
       <c r="E383" s="1" t="str">
-        <f>_xlfn.CONCAT(B383," (",C383," - ",D383,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CABL-TRAY (Electricidad - Sistemas de cable: bandejas y canaletas)</v>
       </c>
       <c r="I383" s="11">
@@ -26878,7 +26860,7 @@
         <v>213</v>
       </c>
       <c r="E384" s="1" t="str">
-        <f>_xlfn.CONCAT(B384," (",C384," - ",D384,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CATH (Electricidad - Sistema de protección catódica)</v>
       </c>
       <c r="I384" s="11">
@@ -26908,7 +26890,7 @@
         <v>2026</v>
       </c>
       <c r="E385" s="1" t="str">
-        <f>_xlfn.CONCAT(B385," (",C385," - ",D385,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CATH-ANOD (Electricidad - Sistema de protección catódica: ánodo de sacrificio)</v>
       </c>
       <c r="I385" s="11">
@@ -26938,7 +26920,7 @@
         <v>2027</v>
       </c>
       <c r="E386" s="1" t="str">
-        <f>_xlfn.CONCAT(B386," (",C386," - ",D386,")")</f>
+        <f t="shared" si="5"/>
         <v>E-CATH-CURR (Electricidad - Sistema de protección catódica: corriente de impresión)</v>
       </c>
       <c r="I386" s="11">
@@ -26968,7 +26950,7 @@
         <v>2028</v>
       </c>
       <c r="E387" s="1" t="str">
-        <f>_xlfn.CONCAT(B387," (",C387," - ",D387,")")</f>
+        <f t="shared" ref="E387:E450" si="6">_xlfn.CONCAT(B387," (",C387," - ",D387,")")</f>
         <v>E-CATH-TEST (Electricidad - Sistema de protección catódica: estaciones de prueba)</v>
       </c>
       <c r="I387" s="11">
@@ -26998,7 +26980,7 @@
         <v>219</v>
       </c>
       <c r="E388" s="1" t="str">
-        <f>_xlfn.CONCAT(B388," (",C388," - ",D388,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CCTV (Electricidad - Sistema de circuito cerrado de televisión)</v>
       </c>
       <c r="I388" s="11">
@@ -27028,7 +27010,7 @@
         <v>2029</v>
       </c>
       <c r="E389" s="1" t="str">
-        <f>_xlfn.CONCAT(B389," (",C389," - ",D389,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK (Electricidad - Sistema de reloj)</v>
       </c>
       <c r="I389" s="11">
@@ -27058,7 +27040,7 @@
         <v>2030</v>
       </c>
       <c r="E390" s="1" t="str">
-        <f>_xlfn.CONCAT(B390," (",C390," - ",D390,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-CIRC (Electricidad - Sistema de reloj: circuitos)</v>
       </c>
       <c r="I390" s="11">
@@ -27088,7 +27070,7 @@
         <v>2031</v>
       </c>
       <c r="E391" s="1" t="str">
-        <f>_xlfn.CONCAT(B391," (",C391," - ",D391,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-CLNG (Electricidad - Sistema de reloj: techo)</v>
       </c>
       <c r="I391" s="11">
@@ -27118,7 +27100,7 @@
         <v>2032</v>
       </c>
       <c r="E392" s="1" t="str">
-        <f>_xlfn.CONCAT(B392," (",C392," - ",D392,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-CNMB (Electricidad - Sistema de reloj: número de circuito)</v>
       </c>
       <c r="I392" s="11">
@@ -27148,7 +27130,7 @@
         <v>2033</v>
       </c>
       <c r="E393" s="1" t="str">
-        <f>_xlfn.CONCAT(B393," (",C393," - ",D393,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-EQPM (Electricidad - Sistema de reloj: equipo)</v>
       </c>
       <c r="I393" s="11">
@@ -27178,7 +27160,7 @@
         <v>2034</v>
       </c>
       <c r="E394" s="1" t="str">
-        <f>_xlfn.CONCAT(B394," (",C394," - ",D394,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-FLOR (Electricidad - Sistema de reloj: suelo)</v>
       </c>
       <c r="I394" s="11">
@@ -27208,7 +27190,7 @@
         <v>2035</v>
       </c>
       <c r="E395" s="1" t="str">
-        <f>_xlfn.CONCAT(B395," (",C395," - ",D395,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CLOK-WALL (Electricidad - Sistema de reloj: pared)</v>
       </c>
       <c r="I395" s="11">
@@ -27238,7 +27220,7 @@
         <v>258</v>
       </c>
       <c r="E396" s="1" t="str">
-        <f>_xlfn.CONCAT(B396," (",C396," - ",D396,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM (Electricidad - Comunicaciones)</v>
       </c>
       <c r="I396" s="11">
@@ -27268,7 +27250,7 @@
         <v>2036</v>
       </c>
       <c r="E397" s="1" t="str">
-        <f>_xlfn.CONCAT(B397," (",C397," - ",D397,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM-CIRC (Electricidad - Comunicaciones: circuitos)</v>
       </c>
       <c r="I397" s="11">
@@ -27298,7 +27280,7 @@
         <v>2037</v>
       </c>
       <c r="E398" s="1" t="str">
-        <f>_xlfn.CONCAT(B398," (",C398," - ",D398,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM-CLNG (Electricidad - Comunicaciones: techo)</v>
       </c>
       <c r="I398" s="11">
@@ -27328,7 +27310,7 @@
         <v>2038</v>
       </c>
       <c r="E399" s="1" t="str">
-        <f>_xlfn.CONCAT(B399," (",C399," - ",D399,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM-CNMB (Electricidad - Comunicaciones: número de circuito)</v>
       </c>
       <c r="I399" s="11">
@@ -27358,7 +27340,7 @@
         <v>2039</v>
       </c>
       <c r="E400" s="1" t="str">
-        <f>_xlfn.CONCAT(B400," (",C400," - ",D400,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM-EQPM (Electricidad - Comunicaciones: equipo)</v>
       </c>
       <c r="I400" s="11">
@@ -27388,7 +27370,7 @@
         <v>2040</v>
       </c>
       <c r="E401" s="1" t="str">
-        <f>_xlfn.CONCAT(B401," (",C401," - ",D401,")")</f>
+        <f t="shared" si="6"/>
         <v>E-COMM-WALL (Electricidad - Comunicaciones: pared)</v>
       </c>
       <c r="I401" s="11">
@@ -27418,14 +27400,8 @@
         <v>261</v>
       </c>
       <c r="E402" s="1" t="str">
-        <f>_xlfn.CONCAT(B402," (",C402," - ",D402,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CONT (Electricidad - Controles e instrumentación)</v>
-      </c>
-      <c r="F402" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G402" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I402" s="11">
         <v>0</v>
@@ -27454,7 +27430,7 @@
         <v>2041</v>
       </c>
       <c r="E403" s="1" t="str">
-        <f>_xlfn.CONCAT(B403," (",C403," - ",D403,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CONT DEVC (Electricidad - Controles e instrumentación: dispositivos)</v>
       </c>
       <c r="I403" s="11">
@@ -27484,7 +27460,7 @@
         <v>2042</v>
       </c>
       <c r="E404" s="1" t="str">
-        <f>_xlfn.CONCAT(B404," (",C404," - ",D404,")")</f>
+        <f t="shared" si="6"/>
         <v>E-CONT-WIRE (Electricidad - Controles e instrumentación: cableado)</v>
       </c>
       <c r="I404" s="11">
@@ -27514,7 +27490,7 @@
         <v>2043</v>
       </c>
       <c r="E405" s="1" t="str">
-        <f>_xlfn.CONCAT(B405," (",C405," - ",D405,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA (Electricidad - Sistema de datos/LAN)</v>
       </c>
       <c r="I405" s="11">
@@ -27544,7 +27520,7 @@
         <v>2044</v>
       </c>
       <c r="E406" s="1" t="str">
-        <f>_xlfn.CONCAT(B406," (",C406," - ",D406,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-CIRC (Electricidad - Sistema de datos/LAN: circuitos)</v>
       </c>
       <c r="I406" s="11">
@@ -27574,7 +27550,7 @@
         <v>2045</v>
       </c>
       <c r="E407" s="1" t="str">
-        <f>_xlfn.CONCAT(B407," (",C407," - ",D407,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-CLNG (Electricidad - Sistema de datos/LAN: Techo)</v>
       </c>
       <c r="I407" s="11">
@@ -27604,7 +27580,7 @@
         <v>2046</v>
       </c>
       <c r="E408" s="1" t="str">
-        <f>_xlfn.CONCAT(B408," (",C408," - ",D408,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-CNMB (Electricidad - Sistema de datos/LAN: número de circuito)</v>
       </c>
       <c r="I408" s="11">
@@ -27634,7 +27610,7 @@
         <v>2047</v>
       </c>
       <c r="E409" s="1" t="str">
-        <f>_xlfn.CONCAT(B409," (",C409," - ",D409,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-EQPM (Electricidad - Sistema de datos/LAN: equipo)</v>
       </c>
       <c r="I409" s="11">
@@ -27664,7 +27640,7 @@
         <v>2048</v>
       </c>
       <c r="E410" s="1" t="str">
-        <f>_xlfn.CONCAT(B410," (",C410," - ",D410,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-FLOR (Electricidad - Sistema de datos/LAN: suelo)</v>
       </c>
       <c r="I410" s="11">
@@ -27694,7 +27670,7 @@
         <v>2049</v>
       </c>
       <c r="E411" s="1" t="str">
-        <f>_xlfn.CONCAT(B411," (",C411," - ",D411,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DATA-WALL (Electricidad - Sistema de datos/LAN: pared)</v>
       </c>
       <c r="I411" s="11">
@@ -27724,14 +27700,8 @@
         <v>291</v>
       </c>
       <c r="E412" s="1" t="str">
-        <f>_xlfn.CONCAT(B412," (",C412," - ",D412,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG (Electricidad - Diagramas)</v>
-      </c>
-      <c r="F412" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G412" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I412" s="11">
         <v>0</v>
@@ -27760,7 +27730,7 @@
         <v>2050</v>
       </c>
       <c r="E413" s="1" t="str">
-        <f>_xlfn.CONCAT(B413," (",C413," - ",D413,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-BKRS (Electricidad - Diagramas: interruptores)</v>
       </c>
       <c r="I413" s="11">
@@ -27790,7 +27760,7 @@
         <v>2051</v>
       </c>
       <c r="E414" s="1" t="str">
-        <f>_xlfn.CONCAT(B414," (",C414," - ",D414,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-BUSS (Electricidad - Diagramas: conducto de barras)</v>
       </c>
       <c r="I414" s="11">
@@ -27820,7 +27790,7 @@
         <v>2052</v>
       </c>
       <c r="E415" s="1" t="str">
-        <f>_xlfn.CONCAT(B415," (",C415," - ",D415,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-ENCL (Electricidad - Diagramas: envolventes de equipos)</v>
       </c>
       <c r="I415" s="11">
@@ -27850,7 +27820,7 @@
         <v>2053</v>
       </c>
       <c r="E416" s="1" t="str">
-        <f>_xlfn.CONCAT(B416," (",C416," - ",D416,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-EQPM (Electricidad - Diagramas: equipos)</v>
       </c>
       <c r="I416" s="11">
@@ -27880,7 +27850,7 @@
         <v>2054</v>
       </c>
       <c r="E417" s="1" t="str">
-        <f>_xlfn.CONCAT(B417," (",C417," - ",D417,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-FEED (Electricidad - Diagramas: alimentadores)</v>
       </c>
       <c r="I417" s="11">
@@ -27910,7 +27880,7 @@
         <v>2055</v>
       </c>
       <c r="E418" s="1" t="str">
-        <f>_xlfn.CONCAT(B418," (",C418," - ",D418,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-FLOR (Electricidad - Diagramas: suelo)</v>
       </c>
       <c r="I418" s="11">
@@ -27940,7 +27910,7 @@
         <v>2056</v>
       </c>
       <c r="E419" s="1" t="str">
-        <f>_xlfn.CONCAT(B419," (",C419," - ",D419,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-GRND (Electricidad - Diagramas: tierra)</v>
       </c>
       <c r="I419" s="11">
@@ -27970,7 +27940,7 @@
         <v>2050</v>
       </c>
       <c r="E420" s="1" t="str">
-        <f>_xlfn.CONCAT(B420," (",C420," - ",D420,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-SWCH (Electricidad - Diagramas: interruptores)</v>
       </c>
       <c r="I420" s="11">
@@ -28000,7 +27970,7 @@
         <v>2057</v>
       </c>
       <c r="E421" s="1" t="str">
-        <f>_xlfn.CONCAT(B421," (",C421," - ",D421,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DIAG-XFMR (Electricidad - Diagramas: transformadores)</v>
       </c>
       <c r="I421" s="11">
@@ -28030,7 +28000,7 @@
         <v>294</v>
       </c>
       <c r="E422" s="1" t="str">
-        <f>_xlfn.CONCAT(B422," (",C422," - ",D422,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT (Electricidad - Sistema de dictado)</v>
       </c>
       <c r="I422" s="11">
@@ -28060,7 +28030,7 @@
         <v>2058</v>
       </c>
       <c r="E423" s="1" t="str">
-        <f>_xlfn.CONCAT(B423," (",C423," - ",D423,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT-CIRC (Electricidad - Sistema de dictado: circuitos)</v>
       </c>
       <c r="I423" s="11">
@@ -28090,7 +28060,7 @@
         <v>2059</v>
       </c>
       <c r="E424" s="1" t="str">
-        <f>_xlfn.CONCAT(B424," (",C424," - ",D424,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT-CLNG (Electricidad - Sistema de dictado: techo)</v>
       </c>
       <c r="I424" s="11">
@@ -28120,7 +28090,7 @@
         <v>2060</v>
       </c>
       <c r="E425" s="1" t="str">
-        <f>_xlfn.CONCAT(B425," (",C425," - ",D425,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT-CNMB (Electricidad - Sistema de dictado: número de circuito)</v>
       </c>
       <c r="I425" s="11">
@@ -28150,7 +28120,7 @@
         <v>2061</v>
       </c>
       <c r="E426" s="1" t="str">
-        <f>_xlfn.CONCAT(B426," (",C426," - ",D426,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT-EQPM (Electricidad - Sistema de dictado: equipo)</v>
       </c>
       <c r="I426" s="11">
@@ -28180,7 +28150,7 @@
         <v>2062</v>
       </c>
       <c r="E427" s="1" t="str">
-        <f>_xlfn.CONCAT(B427," (",C427," - ",D427,")")</f>
+        <f t="shared" si="6"/>
         <v>E-DICT-WALL (Electricidad - Sistema de dictado: pared)</v>
       </c>
       <c r="I427" s="11">
@@ -28210,14 +28180,8 @@
         <v>16</v>
       </c>
       <c r="E428" s="1" t="str">
-        <f>_xlfn.CONCAT(B428," (",C428," - ",D428,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE (Electricidad - Protección contra incendios)</v>
-      </c>
-      <c r="F428" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G428" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I428" s="11">
         <v>0</v>
@@ -28246,7 +28210,7 @@
         <v>2063</v>
       </c>
       <c r="E429" s="1" t="str">
-        <f>_xlfn.CONCAT(B429," (",C429," - ",D429,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-BARR (Electricidad - Protección contra incendios: barrera)</v>
       </c>
       <c r="I429" s="11">
@@ -28276,7 +28240,7 @@
         <v>2064</v>
       </c>
       <c r="E430" s="1" t="str">
-        <f>_xlfn.CONCAT(B430," (",C430," - ",D430,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-CIRC (Electricidad - Protección contra incendios: circuitos)</v>
       </c>
       <c r="I430" s="11">
@@ -28306,7 +28270,7 @@
         <v>2065</v>
       </c>
       <c r="E431" s="1" t="str">
-        <f>_xlfn.CONCAT(B431," (",C431," - ",D431,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-CLNG (Electricidad - Protección contra incendios: techo)</v>
       </c>
       <c r="I431" s="11">
@@ -28336,7 +28300,7 @@
         <v>2066</v>
       </c>
       <c r="E432" s="1" t="str">
-        <f>_xlfn.CONCAT(B432," (",C432," - ",D432,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-CNMB (Electricidad - Protección contra incendios: número de circuito)</v>
       </c>
       <c r="I432" s="11">
@@ -28366,7 +28330,7 @@
         <v>2067</v>
       </c>
       <c r="E433" s="1" t="str">
-        <f>_xlfn.CONCAT(B433," (",C433," - ",D433,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-EQPM (Electricidad - Protección contra incendios: equipo)</v>
       </c>
       <c r="I433" s="11">
@@ -28396,7 +28360,7 @@
         <v>2068</v>
       </c>
       <c r="E434" s="1" t="str">
-        <f>_xlfn.CONCAT(B434," (",C434," - ",D434,")")</f>
+        <f t="shared" si="6"/>
         <v>E-FIRE-WALL (Electricidad - Protección contra incendios: pared)</v>
       </c>
       <c r="I434" s="11">
@@ -28426,14 +28390,8 @@
         <v>2069</v>
       </c>
       <c r="E435" s="1" t="str">
-        <f>_xlfn.CONCAT(B435," (",C435," - ",D435,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND (Electricidad - Sistema de tierra)</v>
-      </c>
-      <c r="F435" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G435" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I435" s="11">
         <v>0</v>
@@ -28462,7 +28420,7 @@
         <v>2070</v>
       </c>
       <c r="E436" s="1" t="str">
-        <f>_xlfn.CONCAT(B436," (",C436," - ",D436,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-CIRC (Electricidad - Sistema de tierra: circuitos)</v>
       </c>
       <c r="I436" s="11">
@@ -28492,7 +28450,7 @@
         <v>2071</v>
       </c>
       <c r="E437" s="1" t="str">
-        <f>_xlfn.CONCAT(B437," (",C437," - ",D437,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-CLNG (Electricidad - Sistema de tierra: techo)</v>
       </c>
       <c r="I437" s="11">
@@ -28522,7 +28480,7 @@
         <v>2072</v>
       </c>
       <c r="E438" s="1" t="str">
-        <f>_xlfn.CONCAT(B438," (",C438," - ",D438,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-CNMB (Electricidad - Sistema de tierra: número de circuito)</v>
       </c>
       <c r="I438" s="11">
@@ -28552,7 +28510,7 @@
         <v>2073</v>
       </c>
       <c r="E439" s="1" t="str">
-        <f>_xlfn.CONCAT(B439," (",C439," - ",D439,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-DIAG (Electricidad - Sistema de tierra: diagramas)</v>
       </c>
       <c r="I439" s="11">
@@ -28582,7 +28540,7 @@
         <v>2074</v>
       </c>
       <c r="E440" s="1" t="str">
-        <f>_xlfn.CONCAT(B440," (",C440," - ",D440,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-EQPM (Electricidad - Sistema de tierra: equipo)</v>
       </c>
       <c r="I440" s="11">
@@ -28612,7 +28570,7 @@
         <v>2075</v>
       </c>
       <c r="E441" s="1" t="str">
-        <f>_xlfn.CONCAT(B441," (",C441," - ",D441,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-EQUI (Electricidad - Sistema de tierra: equipotencial)</v>
       </c>
       <c r="I441" s="11">
@@ -28642,7 +28600,7 @@
         <v>2076</v>
       </c>
       <c r="E442" s="1" t="str">
-        <f>_xlfn.CONCAT(B442," (",C442," - ",D442,")")</f>
+        <f t="shared" si="6"/>
         <v>E-GRND-WALL (Electricidad - Sistema de tierra: pared)</v>
       </c>
       <c r="I442" s="11">
@@ -28672,14 +28630,8 @@
         <v>2077</v>
       </c>
       <c r="E443" s="1" t="str">
-        <f>_xlfn.CONCAT(B443," (",C443," - ",D443,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST (Electricidad - Instrumentación Sistema)</v>
-      </c>
-      <c r="F443" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G443" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I443" s="11">
         <v>0</v>
@@ -28708,7 +28660,7 @@
         <v>2078</v>
       </c>
       <c r="E444" s="1" t="str">
-        <f>_xlfn.CONCAT(B444," (",C444," - ",D444,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST-CIRC (Electricidad - Sistema de instrumentación: circuitos)</v>
       </c>
       <c r="I444" s="11">
@@ -28738,7 +28690,7 @@
         <v>2079</v>
       </c>
       <c r="E445" s="1" t="str">
-        <f>_xlfn.CONCAT(B445," (",C445," - ",D445,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST-CLNG (Electricidad - Sistema de instrumentación: techo)</v>
       </c>
       <c r="I445" s="11">
@@ -28768,7 +28720,7 @@
         <v>2080</v>
       </c>
       <c r="E446" s="1" t="str">
-        <f>_xlfn.CONCAT(B446," (",C446," - ",D446,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST-CNMB (Electricidad - Sistema de instrumentación: número de circuito)</v>
       </c>
       <c r="I446" s="11">
@@ -28798,7 +28750,7 @@
         <v>2081</v>
       </c>
       <c r="E447" s="1" t="str">
-        <f>_xlfn.CONCAT(B447," (",C447," - ",D447,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST-EQPM (Electricidad - Sistema de instrumentación: equipo)</v>
       </c>
       <c r="I447" s="11">
@@ -28828,7 +28780,7 @@
         <v>2082</v>
       </c>
       <c r="E448" s="1" t="str">
-        <f>_xlfn.CONCAT(B448," (",C448," - ",D448,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INST-WALL (Electricidad - Sistema de instrumentación: pared)</v>
       </c>
       <c r="I448" s="11">
@@ -28858,7 +28810,7 @@
         <v>2083</v>
       </c>
       <c r="E449" s="1" t="str">
-        <f>_xlfn.CONCAT(B449," (",C449," - ",D449,")")</f>
+        <f t="shared" si="6"/>
         <v>E-INTC (Electricidad - Sistemas de intercomunicación/megafonía)</v>
       </c>
       <c r="I449" s="11">
@@ -28888,14 +28840,8 @@
         <v>447</v>
       </c>
       <c r="E450" s="1" t="str">
-        <f>_xlfn.CONCAT(B450," (",C450," - ",D450,")")</f>
+        <f t="shared" si="6"/>
         <v>E-LITE (Electricidad - Iluminación)</v>
-      </c>
-      <c r="F450" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G450" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I450" s="11">
         <v>0</v>
@@ -28924,7 +28870,7 @@
         <v>2084</v>
       </c>
       <c r="E451" s="1" t="str">
-        <f>_xlfn.CONCAT(B451," (",C451," - ",D451,")")</f>
+        <f t="shared" ref="E451:E514" si="7">_xlfn.CONCAT(B451," (",C451," - ",D451,")")</f>
         <v>E-LITE-CIRC (Electricidad - Iluminación: circuitos)</v>
       </c>
       <c r="I451" s="11">
@@ -28954,7 +28900,7 @@
         <v>2085</v>
       </c>
       <c r="E452" s="1" t="str">
-        <f>_xlfn.CONCAT(B452," (",C452," - ",D452,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CIRC-CRIT (Electricidad - Iluminación: circuitos: críticos)</v>
       </c>
       <c r="I452" s="11">
@@ -28984,7 +28930,7 @@
         <v>2086</v>
       </c>
       <c r="E453" s="1" t="str">
-        <f>_xlfn.CONCAT(B453," (",C453," - ",D453,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CIRC-EMER (Electricidad - Iluminación: circuitos: emergencia)</v>
       </c>
       <c r="I453" s="11">
@@ -29014,7 +28960,7 @@
         <v>2087</v>
       </c>
       <c r="E454" s="1" t="str">
-        <f>_xlfn.CONCAT(B454," (",C454," - ",D454,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CLNG (Electricidad - Iluminación: techo)</v>
       </c>
       <c r="I454" s="11">
@@ -29044,7 +28990,7 @@
         <v>2088</v>
       </c>
       <c r="E455" s="1" t="str">
-        <f>_xlfn.CONCAT(B455," (",C455," - ",D455,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CLNG-CRIT (Electricidad - Iluminación: techo: crítico)</v>
       </c>
       <c r="I455" s="11">
@@ -29074,7 +29020,7 @@
         <v>2089</v>
       </c>
       <c r="E456" s="1" t="str">
-        <f>_xlfn.CONCAT(B456," (",C456," - ",D456,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CLNG-EMER (Electricidad - Iluminación: techo: emergencia)</v>
       </c>
       <c r="I456" s="11">
@@ -29104,7 +29050,7 @@
         <v>2090</v>
       </c>
       <c r="E457" s="1" t="str">
-        <f>_xlfn.CONCAT(B457," (",C457," - ",D457,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CLNG-EXIT (Electricidad - Iluminación: techo: salida)</v>
       </c>
       <c r="I457" s="11">
@@ -29134,7 +29080,7 @@
         <v>2091</v>
       </c>
       <c r="E458" s="1" t="str">
-        <f>_xlfn.CONCAT(B458," (",C458," - ",D458,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CNMB (Electricidad - Iluminación: número de circuito)</v>
       </c>
       <c r="I458" s="11">
@@ -29164,7 +29110,7 @@
         <v>2092</v>
       </c>
       <c r="E459" s="1" t="str">
-        <f>_xlfn.CONCAT(B459," (",C459," - ",D459,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CNMB-CRIT (Electricidad - Iluminación: número de circuito: crítico)</v>
       </c>
       <c r="I459" s="11">
@@ -29194,7 +29140,7 @@
         <v>2093</v>
       </c>
       <c r="E460" s="1" t="str">
-        <f>_xlfn.CONCAT(B460," (",C460," - ",D460,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-CNMB-EMER (Electricidad - Iluminación: número de circuito: emergencia)</v>
       </c>
       <c r="I460" s="11">
@@ -29224,7 +29170,7 @@
         <v>2094</v>
       </c>
       <c r="E461" s="1" t="str">
-        <f>_xlfn.CONCAT(B461," (",C461," - ",D461,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EMER (Electricidad - Iluminación: emergencia)</v>
       </c>
       <c r="I461" s="11">
@@ -29254,7 +29200,7 @@
         <v>2095</v>
       </c>
       <c r="E462" s="1" t="str">
-        <f>_xlfn.CONCAT(B462," (",C462," - ",D462,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EQPM (Electricidad - Iluminación: equipo)</v>
       </c>
       <c r="I462" s="11">
@@ -29284,7 +29230,7 @@
         <v>2096</v>
       </c>
       <c r="E463" s="1" t="str">
-        <f>_xlfn.CONCAT(B463," (",C463," - ",D463,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EQPM-CRIT (Electricidad - Iluminación: equipo: crítico)</v>
       </c>
       <c r="I463" s="11">
@@ -29314,7 +29260,7 @@
         <v>2097</v>
       </c>
       <c r="E464" s="1" t="str">
-        <f>_xlfn.CONCAT(B464," (",C464," - ",D464,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EQPM-EMER (Electricidad - Iluminación: equipo: emergencia)</v>
       </c>
       <c r="I464" s="11">
@@ -29344,7 +29290,7 @@
         <v>2098</v>
       </c>
       <c r="E465" s="1" t="str">
-        <f>_xlfn.CONCAT(B465," (",C465," - ",D465,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EXIT (Electricidad - Iluminación: salida)</v>
       </c>
       <c r="I465" s="11">
@@ -29374,7 +29320,7 @@
         <v>2099</v>
       </c>
       <c r="E466" s="1" t="str">
-        <f>_xlfn.CONCAT(B466," (",C466," - ",D466,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-EXTR (Electricidad - Iluminación: exterior)</v>
       </c>
       <c r="I466" s="11">
@@ -29404,7 +29350,7 @@
         <v>2100</v>
       </c>
       <c r="E467" s="1" t="str">
-        <f>_xlfn.CONCAT(B467," (",C467," - ",D467,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-FLOR (Electricidad - Iluminación: suelo)</v>
       </c>
       <c r="I467" s="11">
@@ -29434,7 +29380,7 @@
         <v>2101</v>
       </c>
       <c r="E468" s="1" t="str">
-        <f>_xlfn.CONCAT(B468," (",C468," - ",D468,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-JBOX (Electricidad - Iluminación: caja de conexiones)</v>
       </c>
       <c r="I468" s="11">
@@ -29464,7 +29410,7 @@
         <v>2102</v>
       </c>
       <c r="E469" s="1" t="str">
-        <f>_xlfn.CONCAT(B469," (",C469," - ",D469,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-OTLN (Electricidad - Iluminación: contorno)</v>
       </c>
       <c r="I469" s="11">
@@ -29494,7 +29440,7 @@
         <v>2087</v>
       </c>
       <c r="E470" s="1" t="str">
-        <f>_xlfn.CONCAT(B470," (",C470," - ",D470,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-ROOF (Electricidad - Iluminación: techo)</v>
       </c>
       <c r="I470" s="11">
@@ -29524,7 +29470,7 @@
         <v>2103</v>
       </c>
       <c r="E471" s="1" t="str">
-        <f>_xlfn.CONCAT(B471," (",C471," - ",D471,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-SPCL (Electricidad - Iluminación: especial)</v>
       </c>
       <c r="I471" s="11">
@@ -29554,7 +29500,7 @@
         <v>2104</v>
       </c>
       <c r="E472" s="1" t="str">
-        <f>_xlfn.CONCAT(B472," (",C472," - ",D472,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-SWCH (Electricidad - Iluminación: interruptores)</v>
       </c>
       <c r="I472" s="11">
@@ -29584,7 +29530,7 @@
         <v>2105</v>
       </c>
       <c r="E473" s="1" t="str">
-        <f>_xlfn.CONCAT(B473," (",C473," - ",D473,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-SWCH-CRIT (Electricidad - Iluminación: interruptores: críticos)</v>
       </c>
       <c r="I473" s="11">
@@ -29614,7 +29560,7 @@
         <v>2106</v>
       </c>
       <c r="E474" s="1" t="str">
-        <f>_xlfn.CONCAT(B474," (",C474," - ",D474,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-SWCH-EMER (Electricidad - Iluminación: interruptores: emergencia)</v>
       </c>
       <c r="I474" s="11">
@@ -29644,7 +29590,7 @@
         <v>2107</v>
       </c>
       <c r="E475" s="1" t="str">
-        <f>_xlfn.CONCAT(B475," (",C475," - ",D475,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-WALL (Electricidad - Iluminación: pared)</v>
       </c>
       <c r="I475" s="11">
@@ -29674,7 +29620,7 @@
         <v>2108</v>
       </c>
       <c r="E476" s="1" t="str">
-        <f>_xlfn.CONCAT(B476," (",C476," - ",D476,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-WALL-CRIT (Electricidad - Iluminación: pared: crítico)</v>
       </c>
       <c r="I476" s="11">
@@ -29704,7 +29650,7 @@
         <v>2109</v>
       </c>
       <c r="E477" s="1" t="str">
-        <f>_xlfn.CONCAT(B477," (",C477," - ",D477,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-WALL-EMER (Electricidad - Iluminación: pared: emergencia)</v>
       </c>
       <c r="I477" s="11">
@@ -29734,7 +29680,7 @@
         <v>2110</v>
       </c>
       <c r="E478" s="1" t="str">
-        <f>_xlfn.CONCAT(B478," (",C478," - ",D478,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LITE-WALL-EXIT (Electricidad - Iluminación: pared: salida)</v>
       </c>
       <c r="I478" s="11">
@@ -29764,14 +29710,8 @@
         <v>456</v>
       </c>
       <c r="E479" s="1" t="str">
-        <f>_xlfn.CONCAT(B479," (",C479," - ",D479,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG (Electricidad - Sistema de protección contra rayos)</v>
-      </c>
-      <c r="F479" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G479" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I479" s="11">
         <v>0</v>
@@ -29800,7 +29740,7 @@
         <v>2111</v>
       </c>
       <c r="E480" s="1" t="str">
-        <f>_xlfn.CONCAT(B480," (",C480," - ",D480,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG-CIRC (Electricidad - Sistema de protección contra rayos: Circuitos)</v>
       </c>
       <c r="I480" s="11">
@@ -29830,7 +29770,7 @@
         <v>2112</v>
       </c>
       <c r="E481" s="1" t="str">
-        <f>_xlfn.CONCAT(B481," (",C481," - ",D481,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG-CLNG (Electricidad - Sistema de protección contra rayos: techo)</v>
       </c>
       <c r="I481" s="11">
@@ -29860,7 +29800,7 @@
         <v>2113</v>
       </c>
       <c r="E482" s="1" t="str">
-        <f>_xlfn.CONCAT(B482," (",C482," - ",D482,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG-CNMB (Electricidad - Sistema de protección contra rayos: número de circuito)</v>
       </c>
       <c r="I482" s="11">
@@ -29890,7 +29830,7 @@
         <v>2114</v>
       </c>
       <c r="E483" s="1" t="str">
-        <f>_xlfn.CONCAT(B483," (",C483," - ",D483,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG-EQPM (Electricidad - Sistema de protección contra rayos: equipo)</v>
       </c>
       <c r="I483" s="11">
@@ -29920,7 +29860,7 @@
         <v>2115</v>
       </c>
       <c r="E484" s="1" t="str">
-        <f>_xlfn.CONCAT(B484," (",C484," - ",D484,")")</f>
+        <f t="shared" si="7"/>
         <v>E-LTNG-WALL (Electricidad - Sistema de protección contra rayos: pared)</v>
       </c>
       <c r="I484" s="11">
@@ -29950,7 +29890,7 @@
         <v>476</v>
       </c>
       <c r="E485" s="1" t="str">
-        <f>_xlfn.CONCAT(B485," (",C485," - ",D485,")")</f>
+        <f t="shared" si="7"/>
         <v>E-MNTG (Electricidad - Sistema de montaje)</v>
       </c>
       <c r="I485" s="11">
@@ -29980,7 +29920,7 @@
         <v>488</v>
       </c>
       <c r="E486" s="1" t="str">
-        <f>_xlfn.CONCAT(B486," (",C486," - ",D486,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS (Electricidad - Sistema de llamada a enfermeras)</v>
       </c>
       <c r="I486" s="11">
@@ -30010,7 +29950,7 @@
         <v>2116</v>
       </c>
       <c r="E487" s="1" t="str">
-        <f>_xlfn.CONCAT(B487," (",C487," - ",D487,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-CIRC (Electricidad - Sistema de llamada a enfermeras: circuitos)</v>
       </c>
       <c r="I487" s="11">
@@ -30040,7 +29980,7 @@
         <v>2117</v>
       </c>
       <c r="E488" s="1" t="str">
-        <f>_xlfn.CONCAT(B488," (",C488," - ",D488,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-CLNG (Electricidad - Sistema de llamada a enfermeras: techo)</v>
       </c>
       <c r="I488" s="11">
@@ -30070,7 +30010,7 @@
         <v>2118</v>
       </c>
       <c r="E489" s="1" t="str">
-        <f>_xlfn.CONCAT(B489," (",C489," - ",D489,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-CNMB (Electricidad - Sistema de llamada a enfermeras: número de circuito)</v>
       </c>
       <c r="I489" s="11">
@@ -30100,7 +30040,7 @@
         <v>2119</v>
       </c>
       <c r="E490" s="1" t="str">
-        <f>_xlfn.CONCAT(B490," (",C490," - ",D490,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-EQPM (Electricidad - Sistema de llamada a enfermeras: equipo)</v>
       </c>
       <c r="I490" s="11">
@@ -30130,7 +30070,7 @@
         <v>2120</v>
       </c>
       <c r="E491" s="1" t="str">
-        <f>_xlfn.CONCAT(B491," (",C491," - ",D491,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-FLOR (Electricidad - Sistema de llamada a enfermeras: planta)</v>
       </c>
       <c r="I491" s="11">
@@ -30160,7 +30100,7 @@
         <v>2121</v>
       </c>
       <c r="E492" s="1" t="str">
-        <f>_xlfn.CONCAT(B492," (",C492," - ",D492,")")</f>
+        <f t="shared" si="7"/>
         <v>E-NURS-WALL (Electricidad - Sistema de llamada a enfermeras: pared)</v>
       </c>
       <c r="I492" s="11">
@@ -30190,7 +30130,7 @@
         <v>491</v>
       </c>
       <c r="E493" s="1" t="str">
-        <f>_xlfn.CONCAT(B493," (",C493," - ",D493,")")</f>
+        <f t="shared" si="7"/>
         <v>E-OBST (Electricidad - Obstrucciones)</v>
       </c>
       <c r="I493" s="11">
@@ -30220,7 +30160,7 @@
         <v>506</v>
       </c>
       <c r="E494" s="1" t="str">
-        <f>_xlfn.CONCAT(B494," (",C494," - ",D494,")")</f>
+        <f t="shared" si="7"/>
         <v>E-PGNG (Electricidad - Sistema de buscapersonas)</v>
       </c>
       <c r="I494" s="11">
@@ -30236,7 +30176,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="495" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A495" s="9">
         <v>1</v>
       </c>
@@ -30250,7 +30190,7 @@
         <v>2122</v>
       </c>
       <c r="E495" s="1" t="str">
-        <f>_xlfn.CONCAT(B495," (",C495," - ",D495,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR (Electricidad - Alimentación)</v>
       </c>
       <c r="F495" s="11" t="s">
@@ -30289,7 +30229,7 @@
         <v>2123</v>
       </c>
       <c r="E496" s="1" t="str">
-        <f>_xlfn.CONCAT(B496," (",C496," - ",D496,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-BUSW (Electricidad - Alimentación: conductos de barras)</v>
       </c>
       <c r="I496" s="11">
@@ -30319,7 +30259,7 @@
         <v>2124</v>
       </c>
       <c r="E497" s="1" t="str">
-        <f>_xlfn.CONCAT(B497," (",C497," - ",D497,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CABL (Electricidad - Alimentación: sistemas de cableado)</v>
       </c>
       <c r="I497" s="11">
@@ -30349,7 +30289,7 @@
         <v>2125</v>
       </c>
       <c r="E498" s="1" t="str">
-        <f>_xlfn.CONCAT(B498," (",C498," - ",D498,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CBOX (Electricidad - Alimentación: caja de conexiones)</v>
       </c>
       <c r="I498" s="11">
@@ -30379,7 +30319,7 @@
         <v>2126</v>
       </c>
       <c r="E499" s="1" t="str">
-        <f>_xlfn.CONCAT(B499," (",C499," - ",D499,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CBOX-FTPT (Electricidad - Alimentación: caja de conexiones: áreas)</v>
       </c>
       <c r="I499" s="11">
@@ -30409,7 +30349,7 @@
         <v>2127</v>
       </c>
       <c r="E500" s="1" t="str">
-        <f>_xlfn.CONCAT(B500," (",C500," - ",D500,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CIRC (Electricidad - Alimentación: circuitos)</v>
       </c>
       <c r="I500" s="11">
@@ -30439,7 +30379,7 @@
         <v>2128</v>
       </c>
       <c r="E501" s="1" t="str">
-        <f>_xlfn.CONCAT(B501," (",C501," - ",D501,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CIRC-CRIT (Electricidad - Alimentación: circuitos: crítico)</v>
       </c>
       <c r="I501" s="11">
@@ -30469,7 +30409,7 @@
         <v>2129</v>
       </c>
       <c r="E502" s="1" t="str">
-        <f>_xlfn.CONCAT(B502," (",C502," - ",D502,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CLNG (Electricidad - Alimentación: techo)</v>
       </c>
       <c r="I502" s="11">
@@ -30499,7 +30439,7 @@
         <v>2130</v>
       </c>
       <c r="E503" s="1" t="str">
-        <f>_xlfn.CONCAT(B503," (",C503," - ",D503,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CLNG-CRIT (Electricidad - Alimentación: techo: crítico)</v>
       </c>
       <c r="I503" s="11">
@@ -30529,7 +30469,7 @@
         <v>2131</v>
       </c>
       <c r="E504" s="1" t="str">
-        <f>_xlfn.CONCAT(B504," (",C504," - ",D504,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CNDT (Electricidad - Alimentación: conducto)</v>
       </c>
       <c r="I504" s="11">
@@ -30559,7 +30499,7 @@
         <v>2132</v>
       </c>
       <c r="E505" s="1" t="str">
-        <f>_xlfn.CONCAT(B505," (",C505," - ",D505,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CNMB (Electricidad - Alimentación: número de circuito)</v>
       </c>
       <c r="I505" s="11">
@@ -30589,7 +30529,7 @@
         <v>2133</v>
       </c>
       <c r="E506" s="1" t="str">
-        <f>_xlfn.CONCAT(B506," (",C506," - ",D506,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-CNMB-CRIT (Electricidad - Alimentación: número de circuito: crítico)</v>
       </c>
       <c r="I506" s="11">
@@ -30619,7 +30559,7 @@
         <v>2134</v>
       </c>
       <c r="E507" s="1" t="str">
-        <f>_xlfn.CONCAT(B507," (",C507," - ",D507,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DEVC (Electricidad - Alimentación: dispositivos)</v>
       </c>
       <c r="I507" s="11">
@@ -30649,7 +30589,7 @@
         <v>2135</v>
       </c>
       <c r="E508" s="1" t="str">
-        <f>_xlfn.CONCAT(B508," (",C508," - ",D508,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DSCO (Electricidad - Alimentación: interruptores de desconexión)</v>
       </c>
       <c r="I508" s="11">
@@ -30679,7 +30619,7 @@
         <v>2136</v>
       </c>
       <c r="E509" s="1" t="str">
-        <f>_xlfn.CONCAT(B509," (",C509," - ",D509,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DSCO-ACFU (Electricidad - Alimentación: interruptores de desconexión: CA con fusible)</v>
       </c>
       <c r="I509" s="11">
@@ -30709,7 +30649,7 @@
         <v>2137</v>
       </c>
       <c r="E510" s="1" t="str">
-        <f>_xlfn.CONCAT(B510," (",C510," - ",D510,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DSCO-ACNF (Electricidad - Alimentación: interruptores de desconexión: CA sin fusible)</v>
       </c>
       <c r="I510" s="11">
@@ -30739,7 +30679,7 @@
         <v>2138</v>
       </c>
       <c r="E511" s="1" t="str">
-        <f>_xlfn.CONCAT(B511," (",C511," - ",D511,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DSCO-DCFU (Electricidad - Alimentación: interruptores de desconexión: CC con fusible)</v>
       </c>
       <c r="I511" s="11">
@@ -30769,7 +30709,7 @@
         <v>2139</v>
       </c>
       <c r="E512" s="1" t="str">
-        <f>_xlfn.CONCAT(B512," (",C512," - ",D512,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-DSCO-DCNF (Electricidad - Alimentación: interruptores de desconexión: CC sin fusible)</v>
       </c>
       <c r="I512" s="11">
@@ -30799,7 +30739,7 @@
         <v>2140</v>
       </c>
       <c r="E513" s="1" t="str">
-        <f>_xlfn.CONCAT(B513," (",C513," - ",D513,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-EQPM (Electricidad - Alimentación: equipo)</v>
       </c>
       <c r="I513" s="11">
@@ -30829,7 +30769,7 @@
         <v>2141</v>
       </c>
       <c r="E514" s="1" t="str">
-        <f>_xlfn.CONCAT(B514," (",C514," - ",D514,")")</f>
+        <f t="shared" si="7"/>
         <v>E-POWR-EQPM-CRIT (Electricidad - Alimentación: equipo: crítico)</v>
       </c>
       <c r="I514" s="11">
@@ -30859,7 +30799,7 @@
         <v>2142</v>
       </c>
       <c r="E515" s="1" t="str">
-        <f>_xlfn.CONCAT(B515," (",C515," - ",D515,")")</f>
+        <f t="shared" ref="E515:E578" si="8">_xlfn.CONCAT(B515," (",C515," - ",D515,")")</f>
         <v>E-POWR-EXTR (Electricidad - Alimentación: exterior)</v>
       </c>
       <c r="I515" s="11">
@@ -30889,7 +30829,7 @@
         <v>2143</v>
       </c>
       <c r="E516" s="1" t="str">
-        <f>_xlfn.CONCAT(B516," (",C516," - ",D516,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-FEED (Electricidad - Alimentación: alimentadores)</v>
       </c>
       <c r="I516" s="11">
@@ -30919,7 +30859,7 @@
         <v>2144</v>
       </c>
       <c r="E517" s="1" t="str">
-        <f>_xlfn.CONCAT(B517," (",C517," - ",D517,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-FLOR (Electricidad - Alimentación: planta)</v>
       </c>
       <c r="I517" s="11">
@@ -30949,7 +30889,7 @@
         <v>2145</v>
       </c>
       <c r="E518" s="1" t="str">
-        <f>_xlfn.CONCAT(B518," (",C518," - ",D518,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-FLOR-CRIT (Electricidad - Alimentación: planta: crítico)</v>
       </c>
       <c r="I518" s="11">
@@ -30979,7 +30919,7 @@
         <v>2146</v>
       </c>
       <c r="E519" s="1" t="str">
-        <f>_xlfn.CONCAT(B519," (",C519," - ",D519,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-JBOX (Electricidad - Energía: caja de conexiones)</v>
       </c>
       <c r="I519" s="11">
@@ -31009,7 +30949,7 @@
         <v>2147</v>
       </c>
       <c r="E520" s="1" t="str">
-        <f>_xlfn.CONCAT(B520," (",C520," - ",D520,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-PANL (Electricidad - Energía: paneles)</v>
       </c>
       <c r="I520" s="11">
@@ -31039,7 +30979,7 @@
         <v>2148</v>
       </c>
       <c r="E521" s="1" t="str">
-        <f>_xlfn.CONCAT(B521," (",C521," - ",D521,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-POCC (Electricidad - Energía: punto de acoplamiento común)</v>
       </c>
       <c r="I521" s="11">
@@ -31069,7 +31009,7 @@
         <v>2149</v>
       </c>
       <c r="E522" s="1" t="str">
-        <f>_xlfn.CONCAT(B522," (",C522," - ",D522,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-POI~ (Electricidad - Energía: punto de interconexión)</v>
       </c>
       <c r="I522" s="11">
@@ -31099,7 +31039,7 @@
         <v>2150</v>
       </c>
       <c r="E523" s="1" t="str">
-        <f>_xlfn.CONCAT(B523," (",C523," - ",D523,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-ROOF (Electricidad - Energía: tejado)</v>
       </c>
       <c r="I523" s="11">
@@ -31129,7 +31069,7 @@
         <v>2151</v>
       </c>
       <c r="E524" s="1" t="str">
-        <f>_xlfn.CONCAT(B524," (",C524," - ",D524,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-SWBD (Electricidad - Energía: cuadros eléctricos)</v>
       </c>
       <c r="I524" s="11">
@@ -31159,7 +31099,7 @@
         <v>2152</v>
       </c>
       <c r="E525" s="1" t="str">
-        <f>_xlfn.CONCAT(B525," (",C525," - ",D525,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-UCPT (Electricidad - Energía: cableado bajo moqueta)</v>
       </c>
       <c r="I525" s="11">
@@ -31189,7 +31129,7 @@
         <v>2153</v>
       </c>
       <c r="E526" s="1" t="str">
-        <f>_xlfn.CONCAT(B526," (",C526," - ",D526,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-URAC (Electricidad - Energía: canalizaciones bajo suelo)</v>
       </c>
       <c r="I526" s="11">
@@ -31219,7 +31159,7 @@
         <v>2154</v>
       </c>
       <c r="E527" s="1" t="str">
-        <f>_xlfn.CONCAT(B527," (",C527," - ",D527,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-WALL (Electricidad - Energía: pared)</v>
       </c>
       <c r="I527" s="11">
@@ -31249,7 +31189,7 @@
         <v>2155</v>
       </c>
       <c r="E528" s="1" t="str">
-        <f>_xlfn.CONCAT(B528," (",C528," - ",D528,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-WALL-CRIT (Electricidad - Energía: pared: crítico)</v>
       </c>
       <c r="I528" s="11">
@@ -31279,7 +31219,7 @@
         <v>2156</v>
       </c>
       <c r="E529" s="1" t="str">
-        <f>_xlfn.CONCAT(B529," (",C529," - ",D529,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-XFMR-PADM (Electricidad - Energía: transformadores montados en pedestal)</v>
       </c>
       <c r="I529" s="11">
@@ -31309,7 +31249,7 @@
         <v>2157</v>
       </c>
       <c r="E530" s="1" t="str">
-        <f>_xlfn.CONCAT(B530," (",C530," - ",D530,")")</f>
+        <f t="shared" si="8"/>
         <v>E-POWR-XFMR-POLM (Electricidad - Energía: transformadores montados en postes)</v>
       </c>
       <c r="I530" s="11">
@@ -31339,7 +31279,7 @@
         <v>548</v>
       </c>
       <c r="E531" s="1" t="str">
-        <f>_xlfn.CONCAT(B531," (",C531," - ",D531,")")</f>
+        <f t="shared" si="8"/>
         <v>E-PVMD (Electricidad - Módulos fotovoltaicos)</v>
       </c>
       <c r="I531" s="11">
@@ -31369,7 +31309,7 @@
         <v>2158</v>
       </c>
       <c r="E532" s="1" t="str">
-        <f>_xlfn.CONCAT(B532," (",C532," - ",D532,")")</f>
+        <f t="shared" si="8"/>
         <v>E-SITE (Electricidad - Características del emplazamiento)</v>
       </c>
       <c r="I532" s="11">
@@ -31399,7 +31339,7 @@
         <v>2159</v>
       </c>
       <c r="E533" s="1" t="str">
-        <f>_xlfn.CONCAT(B533," (",C533," - ",D533,")")</f>
+        <f t="shared" si="8"/>
         <v>E-SITE-OVHD (Electricidad - Características del emplazamiento: aéreo)</v>
       </c>
       <c r="I533" s="11">
@@ -31429,7 +31369,7 @@
         <v>2160</v>
       </c>
       <c r="E534" s="1" t="str">
-        <f>_xlfn.CONCAT(B534," (",C534," - ",D534,")")</f>
+        <f t="shared" si="8"/>
         <v>E-SITE-POLE (Electricidad - Características del emplazamiento: poste)</v>
       </c>
       <c r="I534" s="11">
@@ -31459,7 +31399,7 @@
         <v>2161</v>
       </c>
       <c r="E535" s="1" t="str">
-        <f>_xlfn.CONCAT(B535," (",C535," - ",D535,")")</f>
+        <f t="shared" si="8"/>
         <v>E-SITE-UGND (Electricidad - Características del emplazamiento: subterráneo)</v>
       </c>
       <c r="I535" s="11">
@@ -31489,7 +31429,7 @@
         <v>613</v>
       </c>
       <c r="E536" s="1" t="str">
-        <f>_xlfn.CONCAT(B536," (",C536," - ",D536,")")</f>
+        <f t="shared" si="8"/>
         <v>E-SOUN (Electricidad - Sistema de sonido)</v>
       </c>
       <c r="I536" s="11">
@@ -31519,7 +31459,7 @@
         <v>153</v>
       </c>
       <c r="E537" s="1" t="str">
-        <f>_xlfn.CONCAT(B537," (",C537," - ",D537,")")</f>
+        <f t="shared" si="8"/>
         <v>S-ALGN (Estructura - Alineación)</v>
       </c>
       <c r="I537" s="11">
@@ -31535,7 +31475,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="538" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A538" s="9">
         <v>1</v>
       </c>
@@ -31549,15 +31489,18 @@
         <v>174</v>
       </c>
       <c r="E538" s="1" t="str">
-        <f>_xlfn.CONCAT(B538," (",C538," - ",D538,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BEAM (Estructura - Vigas)</v>
       </c>
       <c r="F538" s="11" t="s">
-        <v>3800</v>
+        <v>3803</v>
       </c>
       <c r="G538" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H538" s="11">
+        <v>0.5</v>
+      </c>
       <c r="I538" s="11">
         <v>0</v>
       </c>
@@ -31585,7 +31528,7 @@
         <v>2388</v>
       </c>
       <c r="E539" s="1" t="str">
-        <f>_xlfn.CONCAT(B539," (",C539," - ",D539,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BEAM-ALUM (Estructura - Vigas: aluminio)</v>
       </c>
       <c r="I539" s="11">
@@ -31615,7 +31558,7 @@
         <v>2389</v>
       </c>
       <c r="E540" s="1" t="str">
-        <f>_xlfn.CONCAT(B540," (",C540," - ",D540,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BEAM-CONC (Estructura - Vigas: hormigón)</v>
       </c>
       <c r="I540" s="11">
@@ -31645,7 +31588,7 @@
         <v>2390</v>
       </c>
       <c r="E541" s="1" t="str">
-        <f>_xlfn.CONCAT(B541," (",C541," - ",D541,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BEAM-STEL (Estructura - Vigas: acero)</v>
       </c>
       <c r="I541" s="11">
@@ -31675,7 +31618,7 @@
         <v>2391</v>
       </c>
       <c r="E542" s="1" t="str">
-        <f>_xlfn.CONCAT(B542," (",C542," - ",D542,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BEAM-WOOD (Estructura - Vigas: madera)</v>
       </c>
       <c r="I542" s="11">
@@ -31705,14 +31648,8 @@
         <v>192</v>
       </c>
       <c r="E543" s="1" t="str">
-        <f>_xlfn.CONCAT(B543," (",C543," - ",D543,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG (Estructura - Arriostramiento)</v>
-      </c>
-      <c r="F543" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G543" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I543" s="11">
         <v>0</v>
@@ -31741,7 +31678,7 @@
         <v>2392</v>
       </c>
       <c r="E544" s="1" t="str">
-        <f>_xlfn.CONCAT(B544," (",C544," - ",D544,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-ALUM (Estructura - Arriostramiento: aluminio)</v>
       </c>
       <c r="I544" s="11">
@@ -31771,7 +31708,7 @@
         <v>2393</v>
       </c>
       <c r="E545" s="1" t="str">
-        <f>_xlfn.CONCAT(B545," (",C545," - ",D545,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-ALUM-HORZ (Estructura - Arriostramiento: aluminio: horizontal)</v>
       </c>
       <c r="I545" s="11">
@@ -31801,7 +31738,7 @@
         <v>2394</v>
       </c>
       <c r="E546" s="1" t="str">
-        <f>_xlfn.CONCAT(B546," (",C546," - ",D546,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-ALUM-VERT (Estructura - Arriostramiento: aluminio: vertical)</v>
       </c>
       <c r="I546" s="11">
@@ -31831,7 +31768,7 @@
         <v>2395</v>
       </c>
       <c r="E547" s="1" t="str">
-        <f>_xlfn.CONCAT(B547," (",C547," - ",D547,")")</f>
+        <f t="shared" si="8"/>
         <v xml:space="preserve"> S-BRCG-METL (Estructura - Arriostramiento: metal)</v>
       </c>
       <c r="I547" s="11">
@@ -31861,7 +31798,7 @@
         <v>2396</v>
       </c>
       <c r="E548" s="1" t="str">
-        <f>_xlfn.CONCAT(B548," (",C548," - ",D548,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-STEL (Estructura - Arriostramiento: acero)</v>
       </c>
       <c r="I548" s="11">
@@ -31891,7 +31828,7 @@
         <v>2397</v>
       </c>
       <c r="E549" s="1" t="str">
-        <f>_xlfn.CONCAT(B549," (",C549," - ",D549,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-STEL-HORZ (Estructura - Arriostramiento: acero: horizontal)</v>
       </c>
       <c r="I549" s="11">
@@ -31921,7 +31858,7 @@
         <v>2398</v>
       </c>
       <c r="E550" s="1" t="str">
-        <f>_xlfn.CONCAT(B550," (",C550," - ",D550,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-STEL-VERT (Estructura - Arriostramiento: acero: vertical)</v>
       </c>
       <c r="I550" s="11">
@@ -31951,7 +31888,7 @@
         <v>2399</v>
       </c>
       <c r="E551" s="1" t="str">
-        <f>_xlfn.CONCAT(B551," (",C551," - ",D551,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-WOOD (Estructura - Arriostramiento: madera)</v>
       </c>
       <c r="I551" s="11">
@@ -31981,7 +31918,7 @@
         <v>2400</v>
       </c>
       <c r="E552" s="1" t="str">
-        <f>_xlfn.CONCAT(B552," (",C552," - ",D552,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-WOOD-HORZ (Estructura - Arriostramiento: madera: horizontal)</v>
       </c>
       <c r="I552" s="11">
@@ -32011,7 +31948,7 @@
         <v>2401</v>
       </c>
       <c r="E553" s="1" t="str">
-        <f>_xlfn.CONCAT(B553," (",C553," - ",D553,")")</f>
+        <f t="shared" si="8"/>
         <v>S-BRCG-WOOD-VERT (Estructura - Arriostramiento: madera: vertical)</v>
       </c>
       <c r="I553" s="11">
@@ -32027,7 +31964,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="554" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A554" s="9">
         <v>1</v>
       </c>
@@ -32041,15 +31978,18 @@
         <v>255</v>
       </c>
       <c r="E554" s="1" t="str">
-        <f>_xlfn.CONCAT(B554," (",C554," - ",D554,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS (Estructura - Columnas)</v>
       </c>
       <c r="F554" s="11" t="s">
-        <v>3800</v>
+        <v>3803</v>
       </c>
       <c r="G554" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H554" s="11">
+        <v>0.5</v>
+      </c>
       <c r="I554" s="11">
         <v>0</v>
       </c>
@@ -32077,7 +32017,7 @@
         <v>2402</v>
       </c>
       <c r="E555" s="1" t="str">
-        <f>_xlfn.CONCAT(B555," (",C555," - ",D555,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS-ABLT (Estructura - Columnas: pernos de anclaje)</v>
       </c>
       <c r="I555" s="11">
@@ -32107,7 +32047,7 @@
         <v>2403</v>
       </c>
       <c r="E556" s="1" t="str">
-        <f>_xlfn.CONCAT(B556," (",C556," - ",D556,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS-ALUM (Estructura - Columnas: aluminio)</v>
       </c>
       <c r="I556" s="11">
@@ -32137,7 +32077,7 @@
         <v>2404</v>
       </c>
       <c r="E557" s="1" t="str">
-        <f>_xlfn.CONCAT(B557," (",C557," - ",D557,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS-CONC (Estructura - Columnas: hormigón)</v>
       </c>
       <c r="I557" s="11">
@@ -32167,7 +32107,7 @@
         <v>2405</v>
       </c>
       <c r="E558" s="1" t="str">
-        <f>_xlfn.CONCAT(B558," (",C558," - ",D558,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS-STEL (Estructura - Columnas: acero)</v>
       </c>
       <c r="I558" s="11">
@@ -32197,7 +32137,7 @@
         <v>2406</v>
       </c>
       <c r="E559" s="1" t="str">
-        <f>_xlfn.CONCAT(B559," (",C559," - ",D559,")")</f>
+        <f t="shared" si="8"/>
         <v>S-COLS-WOOD (Estructura - Columnas: madera)</v>
       </c>
       <c r="I559" s="11">
@@ -32227,14 +32167,8 @@
         <v>282</v>
       </c>
       <c r="E560" s="1" t="str">
-        <f>_xlfn.CONCAT(B560," (",C560," - ",D560,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DECK (Estructura - Cubierta)</v>
-      </c>
-      <c r="F560" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G560" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I560" s="11">
         <v>0</v>
@@ -32263,7 +32197,7 @@
         <v>2407</v>
       </c>
       <c r="E561" s="1" t="str">
-        <f>_xlfn.CONCAT(B561," (",C561," - ",D561,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DECK-FLOR (Estructura - Cubierta: suelo)</v>
       </c>
       <c r="I561" s="11">
@@ -32293,7 +32227,7 @@
         <v>2408</v>
       </c>
       <c r="E562" s="1" t="str">
-        <f>_xlfn.CONCAT(B562," (",C562," - ",D562,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DECK-FLOR-OPNG (Estructura - Cubierta: suelo: aberturas)</v>
       </c>
       <c r="I562" s="11">
@@ -32323,7 +32257,7 @@
         <v>2409</v>
       </c>
       <c r="E563" s="1" t="str">
-        <f>_xlfn.CONCAT(B563," (",C563," - ",D563,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DECK-ROOF (Estructura - Cubierta: techo)</v>
       </c>
       <c r="I563" s="11">
@@ -32353,7 +32287,7 @@
         <v>2410</v>
       </c>
       <c r="E564" s="1" t="str">
-        <f>_xlfn.CONCAT(B564," (",C564," - ",D564,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DECK-ROOF-OPNG (Estructura - Cubierta: techo: aberturas)</v>
       </c>
       <c r="I564" s="11">
@@ -32383,14 +32317,8 @@
         <v>285</v>
       </c>
       <c r="E565" s="1" t="str">
-        <f>_xlfn.CONCAT(B565," (",C565," - ",D565,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DETL (Estructura - Detalle)</v>
-      </c>
-      <c r="F565" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G565" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I565" s="11">
         <v>0</v>
@@ -32419,7 +32347,7 @@
         <v>2411</v>
       </c>
       <c r="E566" s="1" t="str">
-        <f>_xlfn.CONCAT(B566," (",C566," - ",D566,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DETL-HSSS (Estructura - Detalle: acero estructural hueco)</v>
       </c>
       <c r="I566" s="11">
@@ -32449,7 +32377,7 @@
         <v>2412</v>
       </c>
       <c r="E567" s="1" t="str">
-        <f>_xlfn.CONCAT(B567," (",C567," - ",D567,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DETL-PLYW (Estructura - Detalle: madera contrachapada)</v>
       </c>
       <c r="I567" s="11">
@@ -32479,7 +32407,7 @@
         <v>2413</v>
       </c>
       <c r="E568" s="1" t="str">
-        <f>_xlfn.CONCAT(B568," (",C568," - ",D568,")")</f>
+        <f t="shared" si="8"/>
         <v>S-DETL-W2XS (Estructura - Detalle: madera dimensional)</v>
       </c>
       <c r="I568" s="11">
@@ -32509,14 +32437,8 @@
         <v>358</v>
       </c>
       <c r="E569" s="1" t="str">
-        <f>_xlfn.CONCAT(B569," (",C569," - ",D569,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN (Estructura - Cimentación)</v>
-      </c>
-      <c r="F569" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G569" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I569" s="11">
         <v>0</v>
@@ -32545,7 +32467,7 @@
         <v>2414</v>
       </c>
       <c r="E570" s="1" t="str">
-        <f>_xlfn.CONCAT(B570," (",C570," - ",D570,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-FTNG (Estructura - Cimentación: zapatas)</v>
       </c>
       <c r="I570" s="11">
@@ -32575,7 +32497,7 @@
         <v>2415</v>
       </c>
       <c r="E571" s="1" t="str">
-        <f>_xlfn.CONCAT(B571," (",C571," - ",D571,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-GRBM (Estructura - Cimentación: vigas de cimentación)</v>
       </c>
       <c r="I571" s="11">
@@ -32605,7 +32527,7 @@
         <v>2416</v>
       </c>
       <c r="E572" s="1" t="str">
-        <f>_xlfn.CONCAT(B572," (",C572," - ",D572,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-PCAP (Estructura - Cimentación: encepados)</v>
       </c>
       <c r="I572" s="11">
@@ -32635,7 +32557,7 @@
         <v>2417</v>
       </c>
       <c r="E573" s="1" t="str">
-        <f>_xlfn.CONCAT(B573," (",C573," - ",D573,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-PIER (Estructura - Cimentación: pilotes perforados)</v>
       </c>
       <c r="I573" s="11">
@@ -32665,7 +32587,7 @@
         <v>2418</v>
       </c>
       <c r="E574" s="1" t="str">
-        <f>_xlfn.CONCAT(B574," (",C574," - ",D574,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-PILE (Estructura - Cimentación: Pilotes)</v>
       </c>
       <c r="I574" s="11">
@@ -32695,7 +32617,7 @@
         <v>2419</v>
       </c>
       <c r="E575" s="1" t="str">
-        <f>_xlfn.CONCAT(B575," (",C575," - ",D575,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-RBAR (Estructura - Cimentación: barra de refuerzo)</v>
       </c>
       <c r="I575" s="11">
@@ -32725,7 +32647,7 @@
         <v>2420</v>
       </c>
       <c r="E576" s="1" t="str">
-        <f>_xlfn.CONCAT(B576," (",C576," - ",D576,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-RBAR-BOT1 (Estructura - Cimentación: barra de refuerzo: grupo inferior 1)</v>
       </c>
       <c r="I576" s="11">
@@ -32755,7 +32677,7 @@
         <v>2421</v>
       </c>
       <c r="E577" s="1" t="str">
-        <f>_xlfn.CONCAT(B577," (",C577," - ",D577,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-RBAR-BOT2 (Estructura - Cimentación: barra de refuerzo: grupo inferior 2)</v>
       </c>
       <c r="I577" s="11">
@@ -32785,7 +32707,7 @@
         <v>2422</v>
       </c>
       <c r="E578" s="1" t="str">
-        <f>_xlfn.CONCAT(B578," (",C578," - ",D578,")")</f>
+        <f t="shared" si="8"/>
         <v>S-FNDN-RBAR-TOP1 (Estructura - Cimentación: barra de refuerzo: grupo superior 1)</v>
       </c>
       <c r="I578" s="11">
@@ -32815,7 +32737,7 @@
         <v>2423</v>
       </c>
       <c r="E579" s="1" t="str">
-        <f>_xlfn.CONCAT(B579," (",C579," - ",D579,")")</f>
+        <f t="shared" ref="E579:E642" si="9">_xlfn.CONCAT(B579," (",C579," - ",D579,")")</f>
         <v>S-FNDN-RBAR-TOP2 (Estructura - Cimentación: barra de refuerzo: grupo superior 2)</v>
       </c>
       <c r="I579" s="11">
@@ -32845,7 +32767,7 @@
         <v>364</v>
       </c>
       <c r="E580" s="1" t="str">
-        <f>_xlfn.CONCAT(B580," (",C580," - ",D580,")")</f>
+        <f t="shared" si="9"/>
         <v>S-FRAM (Estructura - Marco arriostrado o marco de momento)</v>
       </c>
       <c r="I580" s="11">
@@ -32875,7 +32797,7 @@
         <v>2424</v>
       </c>
       <c r="E581" s="1" t="str">
-        <f>_xlfn.CONCAT(B581," (",C581," - ",D581,")")</f>
+        <f t="shared" si="9"/>
         <v>S-FSTN (Estructura - Fijaciones y conexiones)</v>
       </c>
       <c r="I581" s="11">
@@ -32891,7 +32813,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="582" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A582" s="9">
         <v>1</v>
       </c>
@@ -32905,14 +32827,17 @@
         <v>2425</v>
       </c>
       <c r="E582" s="1" t="str">
-        <f>_xlfn.CONCAT(B582," (",C582," - ",D582,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GATE (Estructura - Puerta)</v>
       </c>
-      <c r="F582" s="11" t="s">
-        <v>3800</v>
+      <c r="F582" s="11">
+        <v>251</v>
       </c>
       <c r="G582" s="11" t="s">
         <v>3799</v>
+      </c>
+      <c r="H582" s="11">
+        <v>0.18</v>
       </c>
       <c r="I582" s="11">
         <v>0</v>
@@ -32941,14 +32866,8 @@
         <v>390</v>
       </c>
       <c r="E583" s="1" t="str">
-        <f>_xlfn.CONCAT(B583," (",C583," - ",D583,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRID (Estructura - Rejillas)</v>
-      </c>
-      <c r="F583" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G583" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I583" s="11">
         <v>0</v>
@@ -32977,7 +32896,7 @@
         <v>2426</v>
       </c>
       <c r="E584" s="1" t="str">
-        <f>_xlfn.CONCAT(B584," (",C584," - ",D584,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRID-EXTR (Estructura - Rejillas: exterior)</v>
       </c>
       <c r="I584" s="11">
@@ -33007,7 +32926,7 @@
         <v>2427</v>
       </c>
       <c r="E585" s="1" t="str">
-        <f>_xlfn.CONCAT(B585," (",C585," - ",D585,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRID-INTR (Estructura - Rejillas: interior)</v>
       </c>
       <c r="I585" s="11">
@@ -33037,7 +32956,7 @@
         <v>393</v>
       </c>
       <c r="E586" s="1" t="str">
-        <f>_xlfn.CONCAT(B586," (",C586," - ",D586,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRLN (Estructura - Línea de rasante)</v>
       </c>
       <c r="I586" s="11">
@@ -33067,7 +32986,7 @@
         <v>2428</v>
       </c>
       <c r="E587" s="1" t="str">
-        <f>_xlfn.CONCAT(B587," (",C587," - ",D587,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRLN-SURF (Estructura - Línea de rasante: superficies)</v>
       </c>
       <c r="I587" s="11">
@@ -33097,7 +33016,7 @@
         <v>2429</v>
       </c>
       <c r="E588" s="1" t="str">
-        <f>_xlfn.CONCAT(B588," (",C588," - ",D588,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRTG (Estructura - Rejilla)</v>
       </c>
       <c r="I588" s="11">
@@ -33127,7 +33046,7 @@
         <v>2430</v>
       </c>
       <c r="E589" s="1" t="str">
-        <f>_xlfn.CONCAT(B589," (",C589," - ",D589,")")</f>
+        <f t="shared" si="9"/>
         <v>S-GRTG-OVHD (Estructura - Rejilla: superior)</v>
       </c>
       <c r="I589" s="11">
@@ -33157,7 +33076,7 @@
         <v>408</v>
       </c>
       <c r="E590" s="1" t="str">
-        <f>_xlfn.CONCAT(B590," (",C590," - ",D590,")")</f>
+        <f t="shared" si="9"/>
         <v>S-HYDR (Estructura - Estructura hidráulica)</v>
       </c>
       <c r="I590" s="11">
@@ -33187,7 +33106,7 @@
         <v>426</v>
       </c>
       <c r="E591" s="1" t="str">
-        <f>_xlfn.CONCAT(B591," (",C591," - ",D591,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JNTS (Estructura - Juntas)</v>
       </c>
       <c r="I591" s="11">
@@ -33217,7 +33136,7 @@
         <v>2431</v>
       </c>
       <c r="E592" s="1" t="str">
-        <f>_xlfn.CONCAT(B592," (",C592," - ",D592,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JNTS-CNTJ (Estructura - Juntas: junta de construcción)</v>
       </c>
       <c r="I592" s="11">
@@ -33247,7 +33166,7 @@
         <v>2432</v>
       </c>
       <c r="E593" s="1" t="str">
-        <f>_xlfn.CONCAT(B593," (",C593," - ",D593,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JNTS-CTLJ (Estructura - Juntas: junta de control)</v>
       </c>
       <c r="I593" s="11">
@@ -33277,7 +33196,7 @@
         <v>2433</v>
       </c>
       <c r="E594" s="1" t="str">
-        <f>_xlfn.CONCAT(B594," (",C594," - ",D594,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JNTS-EXPJ (Estructura - Juntas: junta de dilatación)</v>
       </c>
       <c r="I594" s="11">
@@ -33293,7 +33212,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="595" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A595" s="9">
         <v>1</v>
       </c>
@@ -33307,15 +33226,18 @@
         <v>429</v>
       </c>
       <c r="E595" s="1" t="str">
-        <f>_xlfn.CONCAT(B595," (",C595," - ",D595,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JOIS (Estructura - Viguetas)</v>
       </c>
-      <c r="F595" s="11" t="s">
-        <v>3800</v>
+      <c r="F595" s="11">
+        <v>38</v>
       </c>
       <c r="G595" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H595" s="11">
+        <v>0.09</v>
+      </c>
       <c r="I595" s="11">
         <v>0</v>
       </c>
@@ -33343,7 +33265,7 @@
         <v>2434</v>
       </c>
       <c r="E596" s="1" t="str">
-        <f>_xlfn.CONCAT(B596," (",C596," - ",D596,")")</f>
+        <f t="shared" si="9"/>
         <v>S-JOIS-BRGX (Estructura - Viguetas: puentes)</v>
       </c>
       <c r="I596" s="11">
@@ -33373,14 +33295,8 @@
         <v>450</v>
       </c>
       <c r="E597" s="1" t="str">
-        <f>_xlfn.CONCAT(B597," (",C597," - ",D597,")")</f>
+        <f t="shared" si="9"/>
         <v>S-LNTL (Estructura - Dinteles)</v>
-      </c>
-      <c r="F597" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G597" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I597" s="11">
         <v>0</v>
@@ -33409,7 +33325,7 @@
         <v>2435</v>
       </c>
       <c r="E598" s="1" t="str">
-        <f>_xlfn.CONCAT(B598," (",C598," - ",D598,")")</f>
+        <f t="shared" si="9"/>
         <v>S-PADS (Estructura - Plataformas)</v>
       </c>
       <c r="I598" s="11">
@@ -33439,7 +33355,7 @@
         <v>2436</v>
       </c>
       <c r="E599" s="1" t="str">
-        <f>_xlfn.CONCAT(B599," (",C599," - ",D599,")")</f>
+        <f t="shared" si="9"/>
         <v>S-PADS-EQPM (Estructura - Plataforma: equipo)</v>
       </c>
       <c r="I599" s="11">
@@ -33469,14 +33385,8 @@
         <v>2437</v>
       </c>
       <c r="E600" s="1" t="str">
-        <f>_xlfn.CONCAT(B600," (",C600," - ",D600,")")</f>
+        <f t="shared" si="9"/>
         <v>S-PLAT (Estructura - Plataforma)</v>
-      </c>
-      <c r="F600" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G600" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I600" s="11">
         <v>0</v>
@@ -33505,7 +33415,7 @@
         <v>2438</v>
       </c>
       <c r="E601" s="1" t="str">
-        <f>_xlfn.CONCAT(B601," (",C601," - ",D601,")")</f>
+        <f t="shared" si="9"/>
         <v>S-PLAT-FRMG (Estructura - Plataforma: estructura)</v>
       </c>
       <c r="I601" s="11">
@@ -33535,7 +33445,7 @@
         <v>2439</v>
       </c>
       <c r="E602" s="1" t="str">
-        <f>_xlfn.CONCAT(B602," (",C602," - ",D602,")")</f>
+        <f t="shared" si="9"/>
         <v>S-PLAT-GRTG (Estructura - Plataforma: rejilla)</v>
       </c>
       <c r="I602" s="11">
@@ -33565,7 +33475,7 @@
         <v>595</v>
       </c>
       <c r="E603" s="1" t="str">
-        <f>_xlfn.CONCAT(B603," (",C603," - ",D603,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN (Estructura - Señal)</v>
       </c>
       <c r="I603" s="11">
@@ -33595,7 +33505,7 @@
         <v>2440</v>
       </c>
       <c r="E604" s="1" t="str">
-        <f>_xlfn.CONCAT(B604," (",C604," - ",D604,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN-BOUY (Estructura - Señal: boya)</v>
       </c>
       <c r="I604" s="11">
@@ -33625,7 +33535,7 @@
         <v>2441</v>
       </c>
       <c r="E605" s="1" t="str">
-        <f>_xlfn.CONCAT(B605," (",C605," - ",D605,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN-FRMG (Estructura - Señal: estructura)</v>
       </c>
       <c r="I605" s="11">
@@ -33655,7 +33565,7 @@
         <v>2442</v>
       </c>
       <c r="E606" s="1" t="str">
-        <f>_xlfn.CONCAT(B606," (",C606," - ",D606,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN-GAGE (Estructura - Señal: calibrador (mira))</v>
       </c>
       <c r="I606" s="11">
@@ -33685,7 +33595,7 @@
         <v>2443</v>
       </c>
       <c r="E607" s="1" t="str">
-        <f>_xlfn.CONCAT(B607," (",C607," - ",D607,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN-TEXT (Estructura - Señal: texto de señalización)</v>
       </c>
       <c r="I607" s="11">
@@ -33715,7 +33625,7 @@
         <v>2444</v>
       </c>
       <c r="E608" s="1" t="str">
-        <f>_xlfn.CONCAT(B608," (",C608," - ",D608,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SIGN-XTRU (Estructura - Señal: extrusión)</v>
       </c>
       <c r="I608" s="11">
@@ -33745,14 +33655,8 @@
         <v>601</v>
       </c>
       <c r="E609" s="1" t="str">
-        <f>_xlfn.CONCAT(B609," (",C609," - ",D609,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB (Estructura - Losa)</v>
-      </c>
-      <c r="F609" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G609" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I609" s="11">
         <v>0</v>
@@ -33781,7 +33685,7 @@
         <v>2445</v>
       </c>
       <c r="E610" s="1" t="str">
-        <f>_xlfn.CONCAT(B610," (",C610," - ",D610,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-CONC (Estructura - Losa: hormigón)</v>
       </c>
       <c r="I610" s="11">
@@ -33811,7 +33715,7 @@
         <v>2446</v>
       </c>
       <c r="E611" s="1" t="str">
-        <f>_xlfn.CONCAT(B611," (",C611," - ",D611,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-EDGE (Estructura - Losa: Borde)</v>
       </c>
       <c r="I611" s="11">
@@ -33841,7 +33745,7 @@
         <v>2447</v>
       </c>
       <c r="E612" s="1" t="str">
-        <f>_xlfn.CONCAT(B612," (",C612," - ",D612,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-OPNG (Estructura - Losa: Aberturas (y depresiones))</v>
       </c>
       <c r="I612" s="11">
@@ -33871,7 +33775,7 @@
         <v>2448</v>
       </c>
       <c r="E613" s="1" t="str">
-        <f>_xlfn.CONCAT(B613," (",C613," - ",D613,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-OPNX (Estructura - Losa: Indicación de abertura ("x"))</v>
       </c>
       <c r="I613" s="11">
@@ -33901,7 +33805,7 @@
         <v>2449</v>
       </c>
       <c r="E614" s="1" t="str">
-        <f>_xlfn.CONCAT(B614," (",C614," - ",D614,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-STEL (Estructura - Losa: Acero)</v>
       </c>
       <c r="I614" s="11">
@@ -33931,7 +33835,7 @@
         <v>2450</v>
       </c>
       <c r="E615" s="1" t="str">
-        <f>_xlfn.CONCAT(B615," (",C615," - ",D615,")")</f>
+        <f t="shared" si="9"/>
         <v>S-SLAB-WOOD (Estructura - Losa: Madera)</v>
       </c>
       <c r="I615" s="11">
@@ -33961,14 +33865,8 @@
         <v>631</v>
       </c>
       <c r="E616" s="1" t="str">
-        <f>_xlfn.CONCAT(B616," (",C616," - ",D616,")")</f>
+        <f t="shared" si="9"/>
         <v>S-STIF (Estructura - Refuerzo)</v>
-      </c>
-      <c r="F616" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G616" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I616" s="11">
         <v>0</v>
@@ -33997,7 +33895,7 @@
         <v>2451</v>
       </c>
       <c r="E617" s="1" t="str">
-        <f>_xlfn.CONCAT(B617," (",C617," - ",D617,")")</f>
+        <f t="shared" si="9"/>
         <v>S-STIF-LONG (Estructura - Refuerzo: Longitudinal)</v>
       </c>
       <c r="I617" s="11">
@@ -34027,7 +33925,7 @@
         <v>2452</v>
       </c>
       <c r="E618" s="1" t="str">
-        <f>_xlfn.CONCAT(B618," (",C618," - ",D618,")")</f>
+        <f t="shared" si="9"/>
         <v>S-STIF-TRAV (Estructura - Refuerzo: Transversal)</v>
       </c>
       <c r="I618" s="11">
@@ -34043,7 +33941,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="619" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A619" s="9">
         <v>1</v>
       </c>
@@ -34057,15 +33955,18 @@
         <v>637</v>
       </c>
       <c r="E619" s="1" t="str">
-        <f>_xlfn.CONCAT(B619," (",C619," - ",D619,")")</f>
+        <f t="shared" si="9"/>
         <v>S-STRS (Estructura - Escaleras)</v>
       </c>
       <c r="F619" s="11" t="s">
-        <v>3800</v>
+        <v>3802</v>
       </c>
       <c r="G619" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H619" s="11">
+        <v>0.4</v>
+      </c>
       <c r="I619" s="11">
         <v>0</v>
       </c>
@@ -34093,7 +33994,7 @@
         <v>2453</v>
       </c>
       <c r="E620" s="1" t="str">
-        <f>_xlfn.CONCAT(B620," (",C620," - ",D620,")")</f>
+        <f t="shared" si="9"/>
         <v>S-STRS-LADD (Estructura - Escaleras: Escaleras y conjuntos de escaleras)</v>
       </c>
       <c r="I620" s="11">
@@ -34123,14 +34024,8 @@
         <v>664</v>
       </c>
       <c r="E621" s="1" t="str">
-        <f>_xlfn.CONCAT(B621," (",C621," - ",D621,")")</f>
+        <f t="shared" si="9"/>
         <v>S-TRUS (Estructura - Cerchas)</v>
-      </c>
-      <c r="F621" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G621" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I621" s="11">
         <v>0</v>
@@ -34145,7 +34040,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="622" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A622" s="9">
         <v>1</v>
       </c>
@@ -34159,7 +34054,7 @@
         <v>685</v>
       </c>
       <c r="E622" s="1" t="str">
-        <f>_xlfn.CONCAT(B622," (",C622," - ",D622,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL (Estructura - Muros)</v>
       </c>
       <c r="F622" s="11" t="s">
@@ -34168,6 +34063,9 @@
       <c r="G622" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H622" s="11">
+        <v>0.6</v>
+      </c>
       <c r="I622" s="11">
         <v>0</v>
       </c>
@@ -34195,7 +34093,7 @@
         <v>2454</v>
       </c>
       <c r="E623" s="1" t="str">
-        <f>_xlfn.CONCAT(B623," (",C623," - ",D623,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-ABOV (Estructura - Muros: Superior)</v>
       </c>
       <c r="I623" s="11">
@@ -34225,7 +34123,7 @@
         <v>2455</v>
       </c>
       <c r="E624" s="1" t="str">
-        <f>_xlfn.CONCAT(B624," (",C624," - ",D624,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-CMUW (Estructura - Muros: Unidad de mampostería de hormigón)</v>
       </c>
       <c r="I624" s="11">
@@ -34255,7 +34153,7 @@
         <v>2456</v>
       </c>
       <c r="E625" s="1" t="str">
-        <f>_xlfn.CONCAT(B625," (",C625," - ",D625,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-CONC (Estructura - Muros: Hormigón)</v>
       </c>
       <c r="I625" s="11">
@@ -34285,7 +34183,7 @@
         <v>2457</v>
       </c>
       <c r="E626" s="1" t="str">
-        <f>_xlfn.CONCAT(B626," (",C626," - ",D626,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-MSNW (Estructura - Muros: Mampostería)</v>
       </c>
       <c r="I626" s="11">
@@ -34315,7 +34213,7 @@
         <v>2458</v>
       </c>
       <c r="E627" s="1" t="str">
-        <f>_xlfn.CONCAT(B627," (",C627," - ",D627,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-PCST (Estructura - Muros: Hormigón prefabricado)</v>
       </c>
       <c r="I627" s="11">
@@ -34345,7 +34243,7 @@
         <v>2459</v>
       </c>
       <c r="E628" s="1" t="str">
-        <f>_xlfn.CONCAT(B628," (",C628," - ",D628,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-SHEA (Estructura - Muros: Muros de carga o de corte)</v>
       </c>
       <c r="I628" s="11">
@@ -34375,7 +34273,7 @@
         <v>2460</v>
       </c>
       <c r="E629" s="1" t="str">
-        <f>_xlfn.CONCAT(B629," (",C629," - ",D629,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-STEL (Estructura - Muros: Montante de acero)</v>
       </c>
       <c r="I629" s="11">
@@ -34405,7 +34303,7 @@
         <v>2461</v>
       </c>
       <c r="E630" s="1" t="str">
-        <f>_xlfn.CONCAT(B630," (",C630," - ",D630,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-VENR (Estructura - Muros: Enchapado)</v>
       </c>
       <c r="I630" s="11">
@@ -34435,7 +34333,7 @@
         <v>2462</v>
       </c>
       <c r="E631" s="1" t="str">
-        <f>_xlfn.CONCAT(B631," (",C631," - ",D631,")")</f>
+        <f t="shared" si="9"/>
         <v>S-WALL-WOOD (Estructura - Muros: Madera)</v>
       </c>
       <c r="I631" s="11">
@@ -34465,14 +34363,8 @@
         <v>180</v>
       </c>
       <c r="E632" s="1" t="str">
-        <f>_xlfn.CONCAT(B632," (",C632," - ",D632,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BLDG (Topografía / Cartografía - Edificios y estructuras primarias)</v>
-      </c>
-      <c r="F632" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G632" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I632" s="11">
         <v>0</v>
@@ -34501,7 +34393,7 @@
         <v>2785</v>
       </c>
       <c r="E633" s="1" t="str">
-        <f>_xlfn.CONCAT(B633," (",C633," - ",D633,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BLDG-DECK (Topografía / Cartografía - Edificios y estructuras primarias: cubierta (adosada, sin techo))</v>
       </c>
       <c r="I633" s="11">
@@ -34531,7 +34423,7 @@
         <v>2786</v>
       </c>
       <c r="E634" s="1" t="str">
-        <f>_xlfn.CONCAT(B634," (",C634," - ",D634,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BLDG-OTLN (Topografía / Cartografía - Edificios y estructuras primarias: contorno)</v>
       </c>
       <c r="I634" s="11">
@@ -34561,7 +34453,7 @@
         <v>2787</v>
       </c>
       <c r="E635" s="1" t="str">
-        <f>_xlfn.CONCAT(B635," (",C635," - ",D635,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BLDG-OVHD (Topografía / Cartografía - Edificios y estructuras primarias: techo)</v>
       </c>
       <c r="I635" s="11">
@@ -34591,7 +34483,7 @@
         <v>2788</v>
       </c>
       <c r="E636" s="1" t="str">
-        <f>_xlfn.CONCAT(B636," (",C636," - ",D636,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BLDG-PRCH (Topografía / Cartografía - Edificios y estructuras primarias: pórtico (adosado, techo))</v>
       </c>
       <c r="I636" s="11">
@@ -34621,14 +34513,8 @@
         <v>186</v>
       </c>
       <c r="E637" s="1" t="str">
-        <f>_xlfn.CONCAT(B637," (",C637," - ",D637,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY (Topografía / Cartografía - Límites políticos)</v>
-      </c>
-      <c r="F637" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G637" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I637" s="11">
         <v>0</v>
@@ -34657,7 +34543,7 @@
         <v>2789</v>
       </c>
       <c r="E638" s="1" t="str">
-        <f>_xlfn.CONCAT(B638," (",C638," - ",D638,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY-BORO (Topografía / Cartografía - Límites políticos: municipio)</v>
       </c>
       <c r="I638" s="11">
@@ -34687,7 +34573,7 @@
         <v>2790</v>
       </c>
       <c r="E639" s="1" t="str">
-        <f>_xlfn.CONCAT(B639," (",C639," - ",D639,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY-CITY (Topografía / Cartografía - Límites políticos: ciudad)</v>
       </c>
       <c r="I639" s="11">
@@ -34717,7 +34603,7 @@
         <v>2791</v>
       </c>
       <c r="E640" s="1" t="str">
-        <f>_xlfn.CONCAT(B640," (",C640," - ",D640,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY-CNTY (Topografía / Cartografía - Límites políticos: condado)</v>
       </c>
       <c r="I640" s="11">
@@ -34747,7 +34633,7 @@
         <v>2792</v>
       </c>
       <c r="E641" s="1" t="str">
-        <f>_xlfn.CONCAT(B641," (",C641," - ",D641,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY-CORP (Topografía / Cartografía - Límites políticos: corporación)</v>
       </c>
       <c r="I641" s="11">
@@ -34777,7 +34663,7 @@
         <v>2793</v>
       </c>
       <c r="E642" s="1" t="str">
-        <f>_xlfn.CONCAT(B642," (",C642," - ",D642,")")</f>
+        <f t="shared" si="9"/>
         <v>V-BNDY-NATL (Topografía / Cartografía - Límites políticos: nacional)</v>
       </c>
       <c r="I642" s="11">
@@ -34807,7 +34693,7 @@
         <v>2794</v>
       </c>
       <c r="E643" s="1" t="str">
-        <f>_xlfn.CONCAT(B643," (",C643," - ",D643,")")</f>
+        <f t="shared" ref="E643:E706" si="10">_xlfn.CONCAT(B643," (",C643," - ",D643,")")</f>
         <v>V-BNDY-PROV (Topografía / Cartografía - Límites políticos: provincia)</v>
       </c>
       <c r="I643" s="11">
@@ -34837,7 +34723,7 @@
         <v>2795</v>
       </c>
       <c r="E644" s="1" t="str">
-        <f>_xlfn.CONCAT(B644," (",C644," - ",D644,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BNDY-STAT (Topografía / Cartografía - Límites políticos: estado)</v>
       </c>
       <c r="I644" s="11">
@@ -34867,7 +34753,7 @@
         <v>2796</v>
       </c>
       <c r="E645" s="1" t="str">
-        <f>_xlfn.CONCAT(B645," (",C645," - ",D645,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BNDY-TSHP (Topografía / Cartografía - Límites políticos: pueblo o municipio)</v>
       </c>
       <c r="I645" s="11">
@@ -34897,7 +34783,7 @@
         <v>2797</v>
       </c>
       <c r="E646" s="1" t="str">
-        <f>_xlfn.CONCAT(B646," (",C646," - ",D646,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BNDY-ZONE (Topografía / Cartografía - Límites políticos: zonificación)</v>
       </c>
       <c r="I646" s="11">
@@ -34927,14 +34813,8 @@
         <v>189</v>
       </c>
       <c r="E647" s="1" t="str">
-        <f>_xlfn.CONCAT(B647," (",C647," - ",D647,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BORE (Topografía / Cartografía - Perforaciones)</v>
-      </c>
-      <c r="F647" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G647" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I647" s="11">
         <v>0</v>
@@ -34963,7 +34843,7 @@
         <v>195</v>
       </c>
       <c r="E648" s="1" t="str">
-        <f>_xlfn.CONCAT(B648," (",C648," - ",D648,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG (Topografía / Cartografía - Puente)</v>
       </c>
       <c r="I648" s="11">
@@ -34993,7 +34873,7 @@
         <v>2798</v>
       </c>
       <c r="E649" s="1" t="str">
-        <f>_xlfn.CONCAT(B649," (",C649," - ",D649,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG-BENT (Topografía / Cartografía - Puente: parte superior del recodo)</v>
       </c>
       <c r="I649" s="11">
@@ -35023,7 +34903,7 @@
         <v>973</v>
       </c>
       <c r="E650" s="1" t="str">
-        <f>_xlfn.CONCAT(B650," (",C650," - ",D650,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG-CNTR (Topografía / Cartografía - Puente: centro)</v>
       </c>
       <c r="I650" s="11">
@@ -35053,7 +34933,7 @@
         <v>2799</v>
       </c>
       <c r="E651" s="1" t="str">
-        <f>_xlfn.CONCAT(B651," (",C651," - ",D651,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG-CTLJ (Topografía / Cartografía - Puente: junta de control)</v>
       </c>
       <c r="I651" s="11">
@@ -35083,7 +34963,7 @@
         <v>976</v>
       </c>
       <c r="E652" s="1" t="str">
-        <f>_xlfn.CONCAT(B652," (",C652," - ",D652,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG-DECK (Topografía / Cartografía - Puente: cubierta)</v>
       </c>
       <c r="I652" s="11">
@@ -35113,7 +34993,7 @@
         <v>2800</v>
       </c>
       <c r="E653" s="1" t="str">
-        <f>_xlfn.CONCAT(B653," (",C653," - ",D653,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRDG-GRAL (Topografía / Cartografía - Puente: barandilla)</v>
       </c>
       <c r="I653" s="11">
@@ -35143,7 +35023,7 @@
         <v>201</v>
       </c>
       <c r="E654" s="1" t="str">
-        <f>_xlfn.CONCAT(B654," (",C654," - ",D654,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRKL (Topografía / Cartografía - Líneas de rotura/falla)</v>
       </c>
       <c r="I654" s="11">
@@ -35173,7 +35053,7 @@
         <v>2801</v>
       </c>
       <c r="E655" s="1" t="str">
-        <f>_xlfn.CONCAT(B655," (",C655," - ",D655,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRKL-BOTB (Topografía / Cartografía - Líneas de rotura/falla: parte inferior del terraplén)</v>
       </c>
       <c r="I655" s="11">
@@ -35203,7 +35083,7 @@
         <v>2802</v>
       </c>
       <c r="E656" s="1" t="str">
-        <f>_xlfn.CONCAT(B656," (",C656," - ",D656,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRKL-FLOW (Topografía / Cartografía - Líneas de rotura/falla: línea de flujo (punto más bajo de la zanja))</v>
       </c>
       <c r="I656" s="11">
@@ -35233,7 +35113,7 @@
         <v>2803</v>
       </c>
       <c r="E657" s="1" t="str">
-        <f>_xlfn.CONCAT(B657," (",C657," - ",D657,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRKL-TOPB (Topografía / Cartografía - Línea de rotura/falla: parte superior del terraplén)</v>
       </c>
       <c r="I657" s="11">
@@ -35263,7 +35143,7 @@
         <v>2804</v>
       </c>
       <c r="E658" s="1" t="str">
-        <f>_xlfn.CONCAT(B658," (",C658," - ",D658,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BRLN (Topografía / Cartografía - Línea de restricción de edificación)</v>
       </c>
       <c r="I658" s="11">
@@ -35293,7 +35173,7 @@
         <v>207</v>
       </c>
       <c r="E659" s="1" t="str">
-        <f>_xlfn.CONCAT(B659," (",C659," - ",D659,")")</f>
+        <f t="shared" si="10"/>
         <v>V-BZNA (Topografía / Cartografía - Zona de amortiguamiento)</v>
       </c>
       <c r="I659" s="11">
@@ -35323,7 +35203,7 @@
         <v>225</v>
       </c>
       <c r="E660" s="1" t="str">
-        <f>_xlfn.CONCAT(B660," (",C660," - ",D660,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN (Topografía / Cartografía - Canales navegables)</v>
       </c>
       <c r="I660" s="11">
@@ -35353,7 +35233,7 @@
         <v>2805</v>
       </c>
       <c r="E661" s="1" t="str">
-        <f>_xlfn.CONCAT(B661," (",C661," - ",D661,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN-BWTR (Topografía / Cartografía - Navegable Canales: rompeolas)</v>
       </c>
       <c r="I661" s="11">
@@ -35383,7 +35263,7 @@
         <v>1015</v>
       </c>
       <c r="E662" s="1" t="str">
-        <f>_xlfn.CONCAT(B662," (",C662," - ",D662,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN-CNTR (Topografía / Cartografía - Canales navegables: centro)</v>
       </c>
       <c r="I662" s="11">
@@ -35413,7 +35293,7 @@
         <v>1018</v>
       </c>
       <c r="E663" s="1" t="str">
-        <f>_xlfn.CONCAT(B663," (",C663," - ",D663,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN-DACL (Topografía / Cartografía - Canales navegables: límites de canales no autorizados, fondeaderos, etc.)</v>
       </c>
       <c r="I663" s="11">
@@ -35443,7 +35323,7 @@
         <v>1021</v>
       </c>
       <c r="E664" s="1" t="str">
-        <f>_xlfn.CONCAT(B664," (",C664," - ",D664,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN-DOCK (Topografía / Cartografía - Canales navegables: cubiertas, muelles, flotadores, embarcaderos)</v>
       </c>
       <c r="I664" s="11">
@@ -35473,7 +35353,7 @@
         <v>1024</v>
       </c>
       <c r="E665" s="1" t="str">
-        <f>_xlfn.CONCAT(B665," (",C665," - ",D665,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CHAN-NAID (Topografía / Cartografía - Canales navegables: ayudas a la navegación)</v>
       </c>
       <c r="I665" s="11">
@@ -35503,7 +35383,7 @@
         <v>258</v>
       </c>
       <c r="E666" s="1" t="str">
-        <f>_xlfn.CONCAT(B666," (",C666," - ",D666,")")</f>
+        <f t="shared" si="10"/>
         <v>V-COMM (Topografía / Cartografía - Comunicaciones)</v>
       </c>
       <c r="I666" s="11">
@@ -35533,7 +35413,7 @@
         <v>2806</v>
       </c>
       <c r="E667" s="1" t="str">
-        <f>_xlfn.CONCAT(B667," (",C667," - ",D667,")")</f>
+        <f t="shared" si="10"/>
         <v>V-COMM-MHOL (Topografía / Cartografía - Comunicaciones: pozo de registro)</v>
       </c>
       <c r="I667" s="11">
@@ -35563,7 +35443,7 @@
         <v>1028</v>
       </c>
       <c r="E668" s="1" t="str">
-        <f>_xlfn.CONCAT(B668," (",C668," - ",D668,")")</f>
+        <f t="shared" si="10"/>
         <v>V-COMM-OVHD (Topografía / Cartografía - Comunicaciones: aéreas)</v>
       </c>
       <c r="I668" s="11">
@@ -35593,7 +35473,7 @@
         <v>1031</v>
       </c>
       <c r="E669" s="1" t="str">
-        <f>_xlfn.CONCAT(B669," (",C669," - ",D669,")")</f>
+        <f t="shared" si="10"/>
         <v>V-COMM-POLE (Topografía / Cartografía - Comunicaciones: poste)</v>
       </c>
       <c r="I669" s="11">
@@ -35623,7 +35503,7 @@
         <v>1034</v>
       </c>
       <c r="E670" s="1" t="str">
-        <f>_xlfn.CONCAT(B670," (",C670," - ",D670,")")</f>
+        <f t="shared" si="10"/>
         <v>V-COMM-UGND (Topografía / Cartografía - Comunicaciones: subterráneas)</v>
       </c>
       <c r="I670" s="11">
@@ -35653,14 +35533,8 @@
         <v>273</v>
       </c>
       <c r="E671" s="1" t="str">
-        <f>_xlfn.CONCAT(B671," (",C671," - ",D671,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL (Topografía / Cartografía - Puntos de control)</v>
-      </c>
-      <c r="F671" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G671" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I671" s="11">
         <v>0</v>
@@ -35689,7 +35563,7 @@
         <v>1038</v>
       </c>
       <c r="E672" s="1" t="str">
-        <f>_xlfn.CONCAT(B672," (",C672," - ",D672,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-BMRK (Topografía / Cartografía - Puntos de control: puntos de referencia)</v>
       </c>
       <c r="I672" s="11">
@@ -35719,7 +35593,7 @@
         <v>1041</v>
       </c>
       <c r="E673" s="1" t="str">
-        <f>_xlfn.CONCAT(B673," (",C673," - ",D673,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-FLYS (Topografía / Cartografía - Puntos de control: estación de vuelo)</v>
       </c>
       <c r="I673" s="11">
@@ -35749,7 +35623,7 @@
         <v>1044</v>
       </c>
       <c r="E674" s="1" t="str">
-        <f>_xlfn.CONCAT(B674," (",C674," - ",D674,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-GRID (Topografía / Cartografía - Puntos de control: cuadrícula)</v>
       </c>
       <c r="I674" s="11">
@@ -35779,7 +35653,7 @@
         <v>2807</v>
       </c>
       <c r="E675" s="1" t="str">
-        <f>_xlfn.CONCAT(B675," (",C675," - ",D675,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-HORZ (Topografía / Cartografía - Puntos de control: horizontales)</v>
       </c>
       <c r="I675" s="11">
@@ -35809,7 +35683,7 @@
         <v>2808</v>
       </c>
       <c r="E676" s="1" t="str">
-        <f>_xlfn.CONCAT(B676," (",C676," - ",D676,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-HVPT (Topografía / Cartografía - Puntos de control: horizontales/verticales)</v>
       </c>
       <c r="I676" s="11">
@@ -35839,7 +35713,7 @@
         <v>1053</v>
       </c>
       <c r="E677" s="1" t="str">
-        <f>_xlfn.CONCAT(B677," (",C677," - ",D677,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-PNPT (Topografía / Cartografía - Puntos de control: puntos de panel)</v>
       </c>
       <c r="I677" s="11">
@@ -35869,7 +35743,7 @@
         <v>2809</v>
       </c>
       <c r="E678" s="1" t="str">
-        <f>_xlfn.CONCAT(B678," (",C678," - ",D678,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-TRAV (Topografía / Cartografía - Puntos de control: transversales)</v>
       </c>
       <c r="I678" s="11">
@@ -35899,7 +35773,7 @@
         <v>2810</v>
       </c>
       <c r="E679" s="1" t="str">
-        <f>_xlfn.CONCAT(B679," (",C679," - ",D679,")")</f>
+        <f t="shared" si="10"/>
         <v>V-CTRL-VERT (Topografía / Cartografía - Puntos de control: verticales)</v>
       </c>
       <c r="I679" s="11">
@@ -35915,7 +35789,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="680" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A680" s="9">
         <v>1</v>
       </c>
@@ -35929,15 +35803,18 @@
         <v>1068</v>
       </c>
       <c r="E680" s="1" t="str">
-        <f>_xlfn.CONCAT(B680," (",C680," - ",D680,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV (Topografía / Cartografía - Accesos vehiculares)</v>
       </c>
       <c r="F680" s="11" t="s">
-        <v>3800</v>
+        <v>3802</v>
       </c>
       <c r="G680" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H680" s="11">
+        <v>0.4</v>
+      </c>
       <c r="I680" s="11">
         <v>0</v>
       </c>
@@ -35965,7 +35842,7 @@
         <v>1071</v>
       </c>
       <c r="E681" s="1" t="str">
-        <f>_xlfn.CONCAT(B681," (",C681," - ",D681,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-ASPH (Topografía / Cartografía - Accesos vehiculares: asfalto)</v>
       </c>
       <c r="I681" s="11">
@@ -35995,7 +35872,7 @@
         <v>1074</v>
       </c>
       <c r="E682" s="1" t="str">
-        <f>_xlfn.CONCAT(B682," (",C682," - ",D682,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-CNTR (Topografía / Cartografía - Accesos vehiculares: centro)</v>
       </c>
       <c r="I682" s="11">
@@ -36025,7 +35902,7 @@
         <v>1077</v>
       </c>
       <c r="E683" s="1" t="str">
-        <f>_xlfn.CONCAT(B683," (",C683," - ",D683,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-CONC (Topografía / Cartografía - Accesos vehiculares: hormigón)</v>
       </c>
       <c r="I683" s="11">
@@ -36055,7 +35932,7 @@
         <v>2811</v>
       </c>
       <c r="E684" s="1" t="str">
-        <f>_xlfn.CONCAT(B684," (",C684," - ",D684,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-CURB (Topografía / Cartografía - Accesos vehiculares: bordillo)</v>
       </c>
       <c r="I684" s="11">
@@ -36085,7 +35962,7 @@
         <v>2812</v>
       </c>
       <c r="E685" s="1" t="str">
-        <f>_xlfn.CONCAT(B685," (",C685," - ",D685,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-FLNE (Topografía / Cartografía - Accesos vehiculares: carril de incendios)</v>
       </c>
       <c r="I685" s="11">
@@ -36115,7 +35992,7 @@
         <v>2813</v>
       </c>
       <c r="E686" s="1" t="str">
-        <f>_xlfn.CONCAT(B686," (",C686," - ",D686,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-GRVL (Topografía / Cartografía - Accesos vehiculares: grava)</v>
       </c>
       <c r="I686" s="11">
@@ -36145,7 +36022,7 @@
         <v>2814</v>
       </c>
       <c r="E687" s="1" t="str">
-        <f>_xlfn.CONCAT(B687," (",C687," - ",D687,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-MRKG (Topografía / Cartografía - Accesos vehiculares: marcas en el pavimento)</v>
       </c>
       <c r="I687" s="11">
@@ -36175,7 +36052,7 @@
         <v>2815</v>
       </c>
       <c r="E688" s="1" t="str">
-        <f>_xlfn.CONCAT(B688," (",C688," - ",D688,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DRIV-UPVD (Topografía / Cartografía - Accesos vehiculares: superficie sin pavimentar)</v>
       </c>
       <c r="I688" s="11">
@@ -36205,14 +36082,8 @@
         <v>2921</v>
       </c>
       <c r="E689" s="1" t="str">
-        <f>_xlfn.CONCAT(B689," (",C689," - ",D689,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DTCH (Topografía / Cartografía - Cunetas o arroyos)</v>
-      </c>
-      <c r="F689" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G689" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I689" s="11">
         <v>0</v>
@@ -36241,7 +36112,7 @@
         <v>2922</v>
       </c>
       <c r="E690" s="1" t="str">
-        <f>_xlfn.CONCAT(B690," (",C690," - ",D690,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DTCH-BOTM (Topografía / Cartografía - Cunetas o arroyos: fondo)</v>
       </c>
       <c r="I690" s="11">
@@ -36271,7 +36142,7 @@
         <v>2923</v>
       </c>
       <c r="E691" s="1" t="str">
-        <f>_xlfn.CONCAT(B691," (",C691," - ",D691,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DTCH-CNTR (Topografía / Cartografía - Cunetas o arroyos: centro)</v>
       </c>
       <c r="I691" s="11">
@@ -36301,7 +36172,7 @@
         <v>2924</v>
       </c>
       <c r="E692" s="1" t="str">
-        <f>_xlfn.CONCAT(B692," (",C692," - ",D692,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DTCH-EWAT (Topografía / Cartografía - Cunetas o arroyos: borde del agua)</v>
       </c>
       <c r="I692" s="11">
@@ -36331,7 +36202,7 @@
         <v>2925</v>
       </c>
       <c r="E693" s="1" t="str">
-        <f>_xlfn.CONCAT(B693," (",C693," - ",D693,")")</f>
+        <f t="shared" si="10"/>
         <v>V-DTCH-TOP~ (Topografía / Cartografía - Cunetas o arroyos: Arriba)</v>
       </c>
       <c r="I693" s="11">
@@ -36361,14 +36232,8 @@
         <v>338</v>
       </c>
       <c r="E694" s="1" t="str">
-        <f>_xlfn.CONCAT(B694," (",C694," - ",D694,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT (Topografía / Cartografía - Servidumbres)</v>
-      </c>
-      <c r="F694" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G694" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I694" s="11">
         <v>0</v>
@@ -36397,7 +36262,7 @@
         <v>1159</v>
       </c>
       <c r="E695" s="1" t="str">
-        <f>_xlfn.CONCAT(B695," (",C695," - ",D695,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-ACCS (Topografía / Cartografía - Servidumbres: acceso (solo para peatones; acceso privado))</v>
       </c>
       <c r="I695" s="11">
@@ -36427,7 +36292,7 @@
         <v>2816</v>
       </c>
       <c r="E696" s="1" t="str">
-        <f>_xlfn.CONCAT(B696," (",C696," - ",D696,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-CATV (Topografía / Cartografía - Servidumbres: sistema de televisión por cable)</v>
       </c>
       <c r="I696" s="11">
@@ -36457,7 +36322,7 @@
         <v>1165</v>
       </c>
       <c r="E697" s="1" t="str">
-        <f>_xlfn.CONCAT(B697," (",C697," - ",D697,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-CONS (Topografía / Cartografía - Servidumbres: conservación)</v>
       </c>
       <c r="I697" s="11">
@@ -36487,7 +36352,7 @@
         <v>1168</v>
       </c>
       <c r="E698" s="1" t="str">
-        <f>_xlfn.CONCAT(B698," (",C698," - ",D698,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-CSTG (Topografía / Cartografía - Servidumbres: construcción/nivelación)</v>
       </c>
       <c r="I698" s="11">
@@ -36517,7 +36382,7 @@
         <v>1171</v>
       </c>
       <c r="E699" s="1" t="str">
-        <f>_xlfn.CONCAT(B699," (",C699," - ",D699,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-ELEC (Topografía / Cartografía - Servidumbres: electricidad)</v>
       </c>
       <c r="I699" s="11">
@@ -36547,7 +36412,7 @@
         <v>1174</v>
       </c>
       <c r="E700" s="1" t="str">
-        <f>_xlfn.CONCAT(B700," (",C700," - ",D700,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-FDPL (Topografía / Cartografía - Servidumbres: llanura aluvial)</v>
       </c>
       <c r="I700" s="11">
@@ -36577,7 +36442,7 @@
         <v>1177</v>
       </c>
       <c r="E701" s="1" t="str">
-        <f>_xlfn.CONCAT(B701," (",C701," - ",D701,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-INEG (Topografía / Cartografía - Servidumbres: entrada/salida (vehículos; acceso privado))</v>
       </c>
       <c r="I701" s="11">
@@ -36607,7 +36472,7 @@
         <v>1180</v>
       </c>
       <c r="E702" s="1" t="str">
-        <f>_xlfn.CONCAT(B702," (",C702," - ",D702,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-LSCP (Topografía / Cartografía - Servidumbres: paisajismo)</v>
       </c>
       <c r="I702" s="11">
@@ -36637,7 +36502,7 @@
         <v>1183</v>
       </c>
       <c r="E703" s="1" t="str">
-        <f>_xlfn.CONCAT(B703," (",C703," - ",D703,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-NGAS (Topografía / Cartografía - Servidumbres: línea de gas natural)</v>
       </c>
       <c r="I703" s="11">
@@ -36667,7 +36532,7 @@
         <v>1186</v>
       </c>
       <c r="E704" s="1" t="str">
-        <f>_xlfn.CONCAT(B704," (",C704," - ",D704,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-PHON (Topografía / Cartografía - Servidumbres: línea telefónica)</v>
       </c>
       <c r="I704" s="11">
@@ -36697,7 +36562,7 @@
         <v>2817</v>
       </c>
       <c r="E705" s="1" t="str">
-        <f>_xlfn.CONCAT(B705," (",C705," - ",D705,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-ROAD (Topografía / Cartografía - Servidumbres: calzada)</v>
       </c>
       <c r="I705" s="11">
@@ -36727,7 +36592,7 @@
         <v>2818</v>
       </c>
       <c r="E706" s="1" t="str">
-        <f>_xlfn.CONCAT(B706," (",C706," - ",D706,")")</f>
+        <f t="shared" si="10"/>
         <v>V-ESMT-ROAD-PERM (Topografía / Cartografía - Servidumbres: calzada: permanente)</v>
       </c>
       <c r="I706" s="11">
@@ -36757,7 +36622,7 @@
         <v>2819</v>
       </c>
       <c r="E707" s="1" t="str">
-        <f>_xlfn.CONCAT(B707," (",C707," - ",D707,")")</f>
+        <f t="shared" ref="E707:E770" si="11">_xlfn.CONCAT(B707," (",C707," - ",D707,")")</f>
         <v>V-ESMT-ROAD-TEMP (Topografía / Cartografía - Servidumbres: calzada: temporal)</v>
       </c>
       <c r="I707" s="11">
@@ -36787,7 +36652,7 @@
         <v>1198</v>
       </c>
       <c r="E708" s="1" t="str">
-        <f>_xlfn.CONCAT(B708," (",C708," - ",D708,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-RWAY (Topografía / Cartografía - Servidumbres: derecho de paso (acceso público))</v>
       </c>
       <c r="I708" s="11">
@@ -36817,7 +36682,7 @@
         <v>1201</v>
       </c>
       <c r="E709" s="1" t="str">
-        <f>_xlfn.CONCAT(B709," (",C709," - ",D709,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-SGHT (Topografía / Cartografía - Servidumbres: distancia de visibilidad)</v>
       </c>
       <c r="I709" s="11">
@@ -36847,7 +36712,7 @@
         <v>1204</v>
       </c>
       <c r="E710" s="1" t="str">
-        <f>_xlfn.CONCAT(B710," (",C710," - ",D710,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-SSWR (Topografía / Cartografía - Servidumbres: alcantarillado sanitario)</v>
       </c>
       <c r="I710" s="11">
@@ -36877,7 +36742,7 @@
         <v>1207</v>
       </c>
       <c r="E711" s="1" t="str">
-        <f>_xlfn.CONCAT(B711," (",C711," - ",D711,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-STRM (Topografía / Cartografía - Servidumbres: alcantarillado pluvial)</v>
       </c>
       <c r="I711" s="11">
@@ -36907,7 +36772,7 @@
         <v>1210</v>
       </c>
       <c r="E712" s="1" t="str">
-        <f>_xlfn.CONCAT(B712," (",C712," - ",D712,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-SWMT (Topografía / Cartografía - Servidumbres: gestión de aguas pluviales)</v>
       </c>
       <c r="I712" s="11">
@@ -36937,7 +36802,7 @@
         <v>1213</v>
       </c>
       <c r="E713" s="1" t="str">
-        <f>_xlfn.CONCAT(B713," (",C713," - ",D713,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-TRAL (Topografía / Cartografía - Servidumbres: sendero o camino (acceso público))</v>
       </c>
       <c r="I713" s="11">
@@ -36967,7 +36832,7 @@
         <v>1216</v>
       </c>
       <c r="E714" s="1" t="str">
-        <f>_xlfn.CONCAT(B714," (",C714," - ",D714,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-UTIL (Topografía / Cartografía - Servidumbres: líneas de servicios públicos)</v>
       </c>
       <c r="I714" s="11">
@@ -36997,7 +36862,7 @@
         <v>1219</v>
       </c>
       <c r="E715" s="1" t="str">
-        <f>_xlfn.CONCAT(B715," (",C715," - ",D715,")")</f>
+        <f t="shared" si="11"/>
         <v>V-ESMT-WATR (Topografía / Cartografía - Servidumbres: suministro de agua)</v>
       </c>
       <c r="I715" s="11">
@@ -37027,7 +36892,7 @@
         <v>352</v>
       </c>
       <c r="E716" s="1" t="str">
-        <f>_xlfn.CONCAT(B716," (",C716," - ",D716,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FLHA (Topografía / Cartografía - Zona con riesgo de inundación)</v>
       </c>
       <c r="I716" s="11">
@@ -37057,7 +36922,7 @@
         <v>370</v>
       </c>
       <c r="E717" s="1" t="str">
-        <f>_xlfn.CONCAT(B717," (",C717," - ",D717,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FUEL (Topografía / Cartografía - Sistemas de combustible)</v>
       </c>
       <c r="I717" s="11">
@@ -37087,7 +36952,7 @@
         <v>1266</v>
       </c>
       <c r="E718" s="1" t="str">
-        <f>_xlfn.CONCAT(B718," (",C718," - ",D718,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FUEL-MHOL (Topografía / Cartografía - Sistemas de combustible: pozo de registro)</v>
       </c>
       <c r="I718" s="11">
@@ -37117,7 +36982,7 @@
         <v>1269</v>
       </c>
       <c r="E719" s="1" t="str">
-        <f>_xlfn.CONCAT(B719," (",C719," - ",D719,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FUEL-PIPE (Topografía / Cartografía - Sistemas de combustible: tuberías)</v>
       </c>
       <c r="I719" s="11">
@@ -37147,7 +37012,7 @@
         <v>1272</v>
       </c>
       <c r="E720" s="1" t="str">
-        <f>_xlfn.CONCAT(B720," (",C720," - ",D720,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FUEL-TANK (Topografía / Cartografía - Sistemas de combustible: tanques de almacenamiento)</v>
       </c>
       <c r="I720" s="11">
@@ -37177,7 +37042,7 @@
         <v>1275</v>
       </c>
       <c r="E721" s="1" t="str">
-        <f>_xlfn.CONCAT(B721," (",C721," - ",D721,")")</f>
+        <f t="shared" si="11"/>
         <v>V-FUEL-UGND (Topografía / Cartografía - Sistemas de combustible: subterráneos)</v>
       </c>
       <c r="I721" s="11">
@@ -37207,7 +37072,7 @@
         <v>482</v>
       </c>
       <c r="E722" s="1" t="str">
-        <f>_xlfn.CONCAT(B722," (",C722," - ",D722,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NGAS (Topografía / Cartografía - Sistemas de gas natural)</v>
       </c>
       <c r="I722" s="11">
@@ -37237,7 +37102,7 @@
         <v>2885</v>
       </c>
       <c r="E723" s="1" t="str">
-        <f>_xlfn.CONCAT(B723," (",C723," - ",D723,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NGAS-MHOL (Topografía / Cartografía - Sistemas de gas natural: pozo de registro)</v>
       </c>
       <c r="I723" s="11">
@@ -37267,7 +37132,7 @@
         <v>2820</v>
       </c>
       <c r="E724" s="1" t="str">
-        <f>_xlfn.CONCAT(B724," (",C724," - ",D724,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NGAS-PIPE (Topografía / Cartografía - Sistemas de gas natural: tuberías)</v>
       </c>
       <c r="I724" s="11">
@@ -37297,7 +37162,7 @@
         <v>2821</v>
       </c>
       <c r="E725" s="1" t="str">
-        <f>_xlfn.CONCAT(B725," (",C725," - ",D725,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NGAS-TANK (Topografía / Cartografía - Sistemas de gas natural: tanques de almacenamiento)</v>
       </c>
       <c r="I725" s="11">
@@ -37327,7 +37192,7 @@
         <v>2822</v>
       </c>
       <c r="E726" s="1" t="str">
-        <f>_xlfn.CONCAT(B726," (",C726," - ",D726,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NGAS-UGND (Topografía / Cartografía - Sistemas de gas natural: subterráneos)</v>
       </c>
       <c r="I726" s="11">
@@ -37357,14 +37222,8 @@
         <v>485</v>
       </c>
       <c r="E727" s="1" t="str">
-        <f>_xlfn.CONCAT(B727," (",C727," - ",D727,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE (Topografía / Cartografía - Nodo)</v>
-      </c>
-      <c r="F727" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G727" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I727" s="11">
         <v>0</v>
@@ -37393,7 +37252,7 @@
         <v>2823</v>
       </c>
       <c r="E728" s="1" t="str">
-        <f>_xlfn.CONCAT(B728," (",C728," - ",D728,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-ABUT (Topografía / Cartografía - Nodo: estribo)</v>
       </c>
       <c r="I728" s="11">
@@ -37423,7 +37282,7 @@
         <v>2824</v>
       </c>
       <c r="E729" s="1" t="str">
-        <f>_xlfn.CONCAT(B729," (",C729," - ",D729,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-ACTL (Topografía / Cartografía - Nodo: puntos de control aéreos horizontales y verticales)</v>
       </c>
       <c r="I729" s="11">
@@ -37453,7 +37312,7 @@
         <v>2825</v>
       </c>
       <c r="E730" s="1" t="str">
-        <f>_xlfn.CONCAT(B730," (",C730," - ",D730,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BLDG (Topografía / Cartografía - Nodo: puntos de construcción)</v>
       </c>
       <c r="I730" s="11">
@@ -37483,7 +37342,7 @@
         <v>2826</v>
       </c>
       <c r="E731" s="1" t="str">
-        <f>_xlfn.CONCAT(B731," (",C731," - ",D731,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BLIN (Topografía / Cartografía - Nodo: línea base)</v>
       </c>
       <c r="I731" s="11">
@@ -37513,7 +37372,7 @@
         <v>2886</v>
       </c>
       <c r="E732" s="1" t="str">
-        <f>_xlfn.CONCAT(B732," (",C732," - ",D732,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BRDG (Topografía / Cartografía - Nodo: puntos de medición de puentes)</v>
       </c>
       <c r="I732" s="11">
@@ -37543,7 +37402,7 @@
         <v>2827</v>
       </c>
       <c r="E733" s="1" t="str">
-        <f>_xlfn.CONCAT(B733," (",C733," - ",D733,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BRKL (Topografía / Cartografía - Nodo: líneas de corte, elevación puntual Puntos y líneas para la creación de líneas de quiebre como parte superior del terraplén)</v>
       </c>
       <c r="I733" s="11">
@@ -37573,7 +37432,7 @@
         <v>2828</v>
       </c>
       <c r="E734" s="1" t="str">
-        <f>_xlfn.CONCAT(B734," (",C734," - ",D734,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BROW (Topografía / Cartografía - Nodo: Puntos de hilera de maleza)</v>
       </c>
       <c r="I734" s="11">
@@ -37603,7 +37462,7 @@
         <v>2829</v>
       </c>
       <c r="E735" s="1" t="str">
-        <f>_xlfn.CONCAT(B735," (",C735," - ",D735,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-BRSH (Topografía / Cartografía - Nodo: Puntos de maleza)</v>
       </c>
       <c r="I735" s="11">
@@ -37633,7 +37492,7 @@
         <v>2830</v>
       </c>
       <c r="E736" s="1" t="str">
-        <f>_xlfn.CONCAT(B736," (",C736," - ",D736,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-CABL (Topografía / Cartografía - Nodo: Sistemas de cableado subterráneo)</v>
       </c>
       <c r="I736" s="11">
@@ -37663,7 +37522,7 @@
         <v>2831</v>
       </c>
       <c r="E737" s="1" t="str">
-        <f>_xlfn.CONCAT(B737," (",C737," - ",D737,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-CURB (Topografía / Cartografía - Nodo: Bordillo)</v>
       </c>
       <c r="I737" s="11">
@@ -37693,7 +37552,7 @@
         <v>2832</v>
       </c>
       <c r="E738" s="1" t="str">
-        <f>_xlfn.CONCAT(B738," (",C738," - ",D738,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-DASP (Topografía / Cartografía - Nodo: Atributos de descripción para puntos topográficos)</v>
       </c>
       <c r="I738" s="11">
@@ -37723,7 +37582,7 @@
         <v>2833</v>
       </c>
       <c r="E739" s="1" t="str">
-        <f>_xlfn.CONCAT(B739," (",C739," - ",D739,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-DECK (Topografía / Cartografía - Nodo: Plataforma)</v>
       </c>
       <c r="I739" s="11">
@@ -37753,7 +37612,7 @@
         <v>2834</v>
       </c>
       <c r="E740" s="1" t="str">
-        <f>_xlfn.CONCAT(B740," (",C740," - ",D740,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-DRIV (Topografía / Cartografía - Nodo: Acceso vehicular)</v>
       </c>
       <c r="I740" s="11">
@@ -37783,7 +37642,7 @@
         <v>2835</v>
       </c>
       <c r="E741" s="1" t="str">
-        <f>_xlfn.CONCAT(B741," (",C741," - ",D741,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-EASP (Topografía / Cartografía - Nodo: Atributos de elevación para puntos topográficos)</v>
       </c>
       <c r="I741" s="11">
@@ -37813,7 +37672,7 @@
         <v>2836</v>
       </c>
       <c r="E742" s="1" t="str">
-        <f>_xlfn.CONCAT(B742," (",C742," - ",D742,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-EXPJ (Topografía / Cartografía - Nodo: Junta de dilatación)</v>
       </c>
       <c r="I742" s="11">
@@ -37843,7 +37702,7 @@
         <v>2837</v>
       </c>
       <c r="E743" s="1" t="str">
-        <f>_xlfn.CONCAT(B743," (",C743," - ",D743,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-GRND (Topografía / Cartografía - Nodo: Suelo)</v>
       </c>
       <c r="I743" s="11">
@@ -37873,7 +37732,7 @@
         <v>2838</v>
       </c>
       <c r="E744" s="1" t="str">
-        <f>_xlfn.CONCAT(B744," (",C744," - ",D744,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-MHOL (Topografía / Cartografía - Nodo: Pozo de registro)</v>
       </c>
       <c r="I744" s="11">
@@ -37903,7 +37762,7 @@
         <v>2839</v>
       </c>
       <c r="E745" s="1" t="str">
-        <f>_xlfn.CONCAT(B745," (",C745," - ",D745,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-MRKG (Topografía / Cartografía - Nodo: Marcas en el pavimento (franjas amarillas/blancas))</v>
       </c>
       <c r="I745" s="11">
@@ -37933,7 +37792,7 @@
         <v>2840</v>
       </c>
       <c r="E746" s="1" t="str">
-        <f>_xlfn.CONCAT(B746," (",C746," - ",D746,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-NGAS (Topografía / Cartografía - Nodo: Línea de gas natural)</v>
       </c>
       <c r="I746" s="11">
@@ -37963,7 +37822,7 @@
         <v>2841</v>
       </c>
       <c r="E747" s="1" t="str">
-        <f>_xlfn.CONCAT(B747," (",C747," - ",D747,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-PASP (Topografía / Cartografía - Nodo: Atributos de número de punto para puntos topográficos)</v>
       </c>
       <c r="I747" s="11">
@@ -37993,7 +37852,7 @@
         <v>2842</v>
       </c>
       <c r="E748" s="1" t="str">
-        <f>_xlfn.CONCAT(B748," (",C748," - ",D748,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-PIPE (Topografía / Cartografía - Nodo: Tuberías (alcantarillas de acceso vehicular/carretera))</v>
       </c>
       <c r="I748" s="11">
@@ -38023,7 +37882,7 @@
         <v>2843</v>
       </c>
       <c r="E749" s="1" t="str">
-        <f>_xlfn.CONCAT(B749," (",C749," - ",D749,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-POLE (Topografía / Cartografía - Nodo: Poste (eléctrico, telefónico, etc.))</v>
       </c>
       <c r="I749" s="11">
@@ -38053,7 +37912,7 @@
         <v>2844</v>
       </c>
       <c r="E750" s="1" t="str">
-        <f>_xlfn.CONCAT(B750," (",C750," - ",D750,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-PVMT (Topografía / Cartografía - Nodo: Pavimento)</v>
       </c>
       <c r="I750" s="11">
@@ -38083,7 +37942,7 @@
         <v>2845</v>
       </c>
       <c r="E751" s="1" t="str">
-        <f>_xlfn.CONCAT(B751," (",C751," - ",D751,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-SIGN (Topografía / Cartografía - Nodo: Señalización)</v>
       </c>
       <c r="I751" s="11">
@@ -38113,7 +37972,7 @@
         <v>2846</v>
       </c>
       <c r="E752" s="1" t="str">
-        <f>_xlfn.CONCAT(B752," (",C752," - ",D752,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-SSWR (Topografía / Cartografía - Nodo: Alcantarillado sanitario)</v>
       </c>
       <c r="I752" s="11">
@@ -38143,7 +38002,7 @@
         <v>2847</v>
       </c>
       <c r="E753" s="1" t="str">
-        <f>_xlfn.CONCAT(B753," (",C753," - ",D753,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-STRM (Topografía / Cartografía - Nodo: Alcantarillado pluvial)</v>
       </c>
       <c r="I753" s="11">
@@ -38173,7 +38032,7 @@
         <v>2848</v>
       </c>
       <c r="E754" s="1" t="str">
-        <f>_xlfn.CONCAT(B754," (",C754," - ",D754,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-SWLK (Topografía / Cartografía - Nodo: Aceras)</v>
       </c>
       <c r="I754" s="11">
@@ -38203,7 +38062,7 @@
         <v>2849</v>
       </c>
       <c r="E755" s="1" t="str">
-        <f>_xlfn.CONCAT(B755," (",C755," - ",D755,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-TREE (Topografía / Cartografía - Nodo: Árbol)</v>
       </c>
       <c r="I755" s="11">
@@ -38233,7 +38092,7 @@
         <v>2850</v>
       </c>
       <c r="E756" s="1" t="str">
-        <f>_xlfn.CONCAT(B756," (",C756," - ",D756,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-TROW (Topografía / Cartografía - Nodo: Hilera de árboles)</v>
       </c>
       <c r="I756" s="11">
@@ -38263,7 +38122,7 @@
         <v>2851</v>
       </c>
       <c r="E757" s="1" t="str">
-        <f>_xlfn.CONCAT(B757," (",C757," - ",D757,")")</f>
+        <f t="shared" si="11"/>
         <v>V-NODE-WATR (Topografía / Cartografía - Nodo: Suministro de agua)</v>
       </c>
       <c r="I757" s="11">
@@ -38279,7 +38138,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="758" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A758" s="9">
         <v>1</v>
       </c>
@@ -38293,7 +38152,7 @@
         <v>527</v>
       </c>
       <c r="E758" s="1" t="str">
-        <f>_xlfn.CONCAT(B758," (",C758," - ",D758,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR (Topografía / Cartografía - Energía)</v>
       </c>
       <c r="F758" s="11" t="s">
@@ -38332,7 +38191,7 @@
         <v>2852</v>
       </c>
       <c r="E759" s="1" t="str">
-        <f>_xlfn.CONCAT(B759," (",C759," - ",D759,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-FENC (Topografía / Cartografía - Energía: Cercas)</v>
       </c>
       <c r="I759" s="11">
@@ -38362,7 +38221,7 @@
         <v>2853</v>
       </c>
       <c r="E760" s="1" t="str">
-        <f>_xlfn.CONCAT(B760," (",C760," - ",D760,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-INST (Topografía / Cartografía - Energía: Instrumentación (medidores, transformadores))</v>
       </c>
       <c r="I760" s="11">
@@ -38392,7 +38251,7 @@
         <v>2854</v>
       </c>
       <c r="E761" s="1" t="str">
-        <f>_xlfn.CONCAT(B761," (",C761," - ",D761,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-MHOL (Topografía / Cartografía - Energía: Pozo de registro)</v>
       </c>
       <c r="I761" s="11">
@@ -38422,7 +38281,7 @@
         <v>2855</v>
       </c>
       <c r="E762" s="1" t="str">
-        <f>_xlfn.CONCAT(B762," (",C762," - ",D762,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-OVHD (Topografía / Cartografía - Energía: Aérea)</v>
       </c>
       <c r="I762" s="11">
@@ -38452,7 +38311,7 @@
         <v>2856</v>
       </c>
       <c r="E763" s="1" t="str">
-        <f>_xlfn.CONCAT(B763," (",C763," - ",D763,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-POLE (Topografía / Cartografía - Energía: Poste)</v>
       </c>
       <c r="I763" s="11">
@@ -38482,7 +38341,7 @@
         <v>2857</v>
       </c>
       <c r="E764" s="1" t="str">
-        <f>_xlfn.CONCAT(B764," (",C764," - ",D764,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-STRC (Topografía / Cartografía - Energía: Estructuras)</v>
       </c>
       <c r="I764" s="11">
@@ -38512,7 +38371,7 @@
         <v>2858</v>
       </c>
       <c r="E765" s="1" t="str">
-        <f>_xlfn.CONCAT(B765," (",C765," - ",D765,")")</f>
+        <f t="shared" si="11"/>
         <v>V-POWR-UGND (Topografía / Cartografía - Energía: Subterráneo)</v>
       </c>
       <c r="I765" s="11">
@@ -38542,14 +38401,8 @@
         <v>530</v>
       </c>
       <c r="E766" s="1" t="str">
-        <f>_xlfn.CONCAT(B766," (",C766," - ",D766,")")</f>
+        <f t="shared" si="11"/>
         <v>V-PRKG (Topografía / Cartografía - Estacionamientos)</v>
-      </c>
-      <c r="F766" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G766" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I766" s="11">
         <v>0</v>
@@ -38578,7 +38431,7 @@
         <v>1364</v>
       </c>
       <c r="E767" s="1" t="str">
-        <f>_xlfn.CONCAT(B767," (",C767," - ",D767,")")</f>
+        <f t="shared" si="11"/>
         <v>V-PRKG-ASPH (Topografía / Cartografía - Estacionamientos: asfalto)</v>
       </c>
       <c r="I767" s="11">
@@ -38608,7 +38461,7 @@
         <v>2859</v>
       </c>
       <c r="E768" s="1" t="str">
-        <f>_xlfn.CONCAT(B768," (",C768," - ",D768,")")</f>
+        <f t="shared" si="11"/>
         <v>V-PRKG-CNTR (Topografía / Cartografía - Estacionamientos: centro)</v>
       </c>
       <c r="I768" s="11">
@@ -38638,7 +38491,7 @@
         <v>1370</v>
       </c>
       <c r="E769" s="1" t="str">
-        <f>_xlfn.CONCAT(B769," (",C769," - ",D769,")")</f>
+        <f t="shared" si="11"/>
         <v>V-PRKG-CONC (Topografía / Cartografía - Estacionamientos: concreto)</v>
       </c>
       <c r="I769" s="11">
@@ -38668,7 +38521,7 @@
         <v>1373</v>
       </c>
       <c r="E770" s="1" t="str">
-        <f>_xlfn.CONCAT(B770," (",C770," - ",D770,")")</f>
+        <f t="shared" si="11"/>
         <v>V-PRKG-CURB (Topografía / Cartografía - Estacionamientos: bordillo)</v>
       </c>
       <c r="I770" s="11">
@@ -38698,7 +38551,7 @@
         <v>1382</v>
       </c>
       <c r="E771" s="1" t="str">
-        <f>_xlfn.CONCAT(B771," (",C771," - ",D771,")")</f>
+        <f t="shared" ref="E771:E834" si="12">_xlfn.CONCAT(B771," (",C771," - ",D771,")")</f>
         <v>V-PRKG-DRAN (Topografía / Cartografía - Estacionamientos: indicaciones de pendiente de drenaje)</v>
       </c>
       <c r="I771" s="11">
@@ -38728,7 +38581,7 @@
         <v>1388</v>
       </c>
       <c r="E772" s="1" t="str">
-        <f>_xlfn.CONCAT(B772," (",C772," - ",D772,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PRKG-FLNE (Topografía / Cartografía - Estacionamientos: carril de incendios)</v>
       </c>
       <c r="I772" s="11">
@@ -38758,7 +38611,7 @@
         <v>1397</v>
       </c>
       <c r="E773" s="1" t="str">
-        <f>_xlfn.CONCAT(B773," (",C773," - ",D773,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PRKG-GRVL (Topografía / Cartografía - Estacionamientos: grava)</v>
       </c>
       <c r="I773" s="11">
@@ -38788,7 +38641,7 @@
         <v>1400</v>
       </c>
       <c r="E774" s="1" t="str">
-        <f>_xlfn.CONCAT(B774," (",C774," - ",D774,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PRKG-MRKG (Topografía / Cartografía - Estacionamientos: marcas en el pavimento)</v>
       </c>
       <c r="I774" s="11">
@@ -38818,7 +38671,7 @@
         <v>2860</v>
       </c>
       <c r="E775" s="1" t="str">
-        <f>_xlfn.CONCAT(B775," (",C775," - ",D775,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PRKG-STRP (Topografía / Cartografía - Estacionamientos: líneas)</v>
       </c>
       <c r="I775" s="11">
@@ -38848,7 +38701,7 @@
         <v>1409</v>
       </c>
       <c r="E776" s="1" t="str">
-        <f>_xlfn.CONCAT(B776," (",C776," - ",D776,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PRKG-UPVD (Topografía / Cartografía - Estacionamientos: superficie sin pavimentar)</v>
       </c>
       <c r="I776" s="11">
@@ -38878,14 +38731,8 @@
         <v>539</v>
       </c>
       <c r="E777" s="1" t="str">
-        <f>_xlfn.CONCAT(B777," (",C777," - ",D777,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP (Topografía / Cartografía - Propiedad)</v>
-      </c>
-      <c r="F777" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G777" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I777" s="11">
         <v>0</v>
@@ -38914,7 +38761,7 @@
         <v>1425</v>
       </c>
       <c r="E778" s="1" t="str">
-        <f>_xlfn.CONCAT(B778," (",C778," - ",D778,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-LINE (Topografía / Cartografía - Propiedad: líneas)</v>
       </c>
       <c r="I778" s="11">
@@ -38944,7 +38791,7 @@
         <v>2861</v>
       </c>
       <c r="E779" s="1" t="str">
-        <f>_xlfn.CONCAT(B779," (",C779," - ",D779,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-QTRS (Topografía / Cartografía - Propiedad: cuarto de sección)</v>
       </c>
       <c r="I779" s="11">
@@ -38974,7 +38821,7 @@
         <v>2862</v>
       </c>
       <c r="E780" s="1" t="str">
-        <f>_xlfn.CONCAT(B780," (",C780," - ",D780,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-RSRV (Topografía / Cartografía - Propiedad: reserva)</v>
       </c>
       <c r="I780" s="11">
@@ -39004,7 +38851,7 @@
         <v>1428</v>
       </c>
       <c r="E781" s="1" t="str">
-        <f>_xlfn.CONCAT(B781," (",C781," - ",D781,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-SBCK (Topografía / Cartografía - Propiedad: líneas de retranqueo)</v>
       </c>
       <c r="I781" s="11">
@@ -39034,7 +38881,7 @@
         <v>2863</v>
       </c>
       <c r="E782" s="1" t="str">
-        <f>_xlfn.CONCAT(B782," (",C782," - ",D782,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-SECT (Topografía / Cartografía - Propiedad: sección)</v>
       </c>
       <c r="I782" s="11">
@@ -39064,7 +38911,7 @@
         <v>2864</v>
       </c>
       <c r="E783" s="1" t="str">
-        <f>_xlfn.CONCAT(B783," (",C783," - ",D783,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-SUBD (Topografía / Cartografía - Propiedad: líneas de subdivisión (interiores))</v>
       </c>
       <c r="I783" s="11">
@@ -39094,7 +38941,7 @@
         <v>2865</v>
       </c>
       <c r="E784" s="1" t="str">
-        <f>_xlfn.CONCAT(B784," (",C784," - ",D784,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PROP-SXTS (Topografía / Cartografía - Propiedad: decimosexta sección)</v>
       </c>
       <c r="I784" s="11">
@@ -39124,7 +38971,7 @@
         <v>551</v>
       </c>
       <c r="E785" s="1" t="str">
-        <f>_xlfn.CONCAT(B785," (",C785," - ",D785,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PVMT (Topografía / Cartografía - Pavimento)</v>
       </c>
       <c r="I785" s="11">
@@ -39154,7 +39001,7 @@
         <v>1432</v>
       </c>
       <c r="E786" s="1" t="str">
-        <f>_xlfn.CONCAT(B786," (",C786," - ",D786,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PVMT-ASPH (Topografía / Cartografía - Pavimento: asfalto)</v>
       </c>
       <c r="I786" s="11">
@@ -39184,7 +39031,7 @@
         <v>1435</v>
       </c>
       <c r="E787" s="1" t="str">
-        <f>_xlfn.CONCAT(B787," (",C787," - ",D787,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PVMT-CONC (Topografía / Cartografía - Pavimento: concreto)</v>
       </c>
       <c r="I787" s="11">
@@ -39214,7 +39061,7 @@
         <v>1438</v>
       </c>
       <c r="E788" s="1" t="str">
-        <f>_xlfn.CONCAT(B788," (",C788," - ",D788,")")</f>
+        <f t="shared" si="12"/>
         <v>V-PVMT-GRVL (Topografía / Cartografía - Pavimento: grava)</v>
       </c>
       <c r="I788" s="11">
@@ -39244,7 +39091,7 @@
         <v>554</v>
       </c>
       <c r="E789" s="1" t="str">
-        <f>_xlfn.CONCAT(B789," (",C789," - ",D789,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RAIL (Topografía / Cartografía - Ferrocarril)</v>
       </c>
       <c r="I789" s="11">
@@ -39274,7 +39121,7 @@
         <v>1442</v>
       </c>
       <c r="E790" s="1" t="str">
-        <f>_xlfn.CONCAT(B790," (",C790," - ",D790,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RAIL-CNTR (Topografía / Cartografía - Ferrocarril: centro)</v>
       </c>
       <c r="I790" s="11">
@@ -39304,7 +39151,7 @@
         <v>1445</v>
       </c>
       <c r="E791" s="1" t="str">
-        <f>_xlfn.CONCAT(B791," (",C791," - ",D791,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RAIL-EQPM (Topografía / Cartografía - Ferrocarril: equipo (barreras, señales, etc.))</v>
       </c>
       <c r="I791" s="11">
@@ -39334,7 +39181,7 @@
         <v>1448</v>
       </c>
       <c r="E792" s="1" t="str">
-        <f>_xlfn.CONCAT(B792," (",C792," - ",D792,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RAIL-TRAK (Topografía / Cartografía - Ferrocarril: vía)</v>
       </c>
       <c r="I792" s="11">
@@ -39364,14 +39211,8 @@
         <v>569</v>
       </c>
       <c r="E793" s="1" t="str">
-        <f>_xlfn.CONCAT(B793," (",C793," - ",D793,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RIVR (Topografía / Cartografía - Río)</v>
-      </c>
-      <c r="F793" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G793" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I793" s="11">
         <v>0</v>
@@ -39400,7 +39241,7 @@
         <v>1452</v>
       </c>
       <c r="E794" s="1" t="str">
-        <f>_xlfn.CONCAT(B794," (",C794," - ",D794,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RIVR-BOTM (Topografía / Cartografía - Río: fondo)</v>
       </c>
       <c r="I794" s="11">
@@ -39430,7 +39271,7 @@
         <v>1455</v>
       </c>
       <c r="E795" s="1" t="str">
-        <f>_xlfn.CONCAT(B795," (",C795," - ",D795,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RIVR-CNTR (Topografía / Cartografía - Río: centro)</v>
       </c>
       <c r="I795" s="11">
@@ -39460,7 +39301,7 @@
         <v>1458</v>
       </c>
       <c r="E796" s="1" t="str">
-        <f>_xlfn.CONCAT(B796," (",C796," - ",D796,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RIVR-EDGE (Topografía / Cartografía - Río: orilla)</v>
       </c>
       <c r="I796" s="11">
@@ -39490,7 +39331,7 @@
         <v>2866</v>
       </c>
       <c r="E797" s="1" t="str">
-        <f>_xlfn.CONCAT(B797," (",C797," - ",D797,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RIVR-TOPB (Topografía / Cartografía - Río: parte superior de la ribera)</v>
       </c>
       <c r="I797" s="11">
@@ -39520,14 +39361,8 @@
         <v>572</v>
       </c>
       <c r="E798" s="1" t="str">
-        <f>_xlfn.CONCAT(B798," (",C798," - ",D798,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD (Topografía / Cartografía - Carreteras)</v>
-      </c>
-      <c r="F798" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G798" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I798" s="11">
         <v>0</v>
@@ -39556,7 +39391,7 @@
         <v>1465</v>
       </c>
       <c r="E799" s="1" t="str">
-        <f>_xlfn.CONCAT(B799," (",C799," - ",D799,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-ASPH (Topografía / Cartografía - Carreteras: asfalto)</v>
       </c>
       <c r="I799" s="11">
@@ -39586,7 +39421,7 @@
         <v>1468</v>
       </c>
       <c r="E800" s="1" t="str">
-        <f>_xlfn.CONCAT(B800," (",C800," - ",D800,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-CNTR (Topografía / Cartografía - Carreteras: centro)</v>
       </c>
       <c r="I800" s="11">
@@ -39616,7 +39451,7 @@
         <v>1471</v>
       </c>
       <c r="E801" s="1" t="str">
-        <f>_xlfn.CONCAT(B801," (",C801," - ",D801,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-CONC (Topografía / Cartografía - Carreteras: concreto)</v>
       </c>
       <c r="I801" s="11">
@@ -39646,7 +39481,7 @@
         <v>2867</v>
       </c>
       <c r="E802" s="1" t="str">
-        <f>_xlfn.CONCAT(B802," (",C802," - ",D802,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-CURB (Topografía / Cartografía - Carreteras: Bordillo)</v>
       </c>
       <c r="I802" s="11">
@@ -39676,7 +39511,7 @@
         <v>2868</v>
       </c>
       <c r="E803" s="1" t="str">
-        <f>_xlfn.CONCAT(B803," (",C803," - ",D803,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-FLNE (Topografía / Cartografía - Vías: carril de incendios)</v>
       </c>
       <c r="I803" s="11">
@@ -39706,7 +39541,7 @@
         <v>2869</v>
       </c>
       <c r="E804" s="1" t="str">
-        <f>_xlfn.CONCAT(B804," (",C804," - ",D804,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-GRVL (Topografía / Cartografía - Vías: grava)</v>
       </c>
       <c r="I804" s="11">
@@ -39736,7 +39571,7 @@
         <v>2870</v>
       </c>
       <c r="E805" s="1" t="str">
-        <f>_xlfn.CONCAT(B805," (",C805," - ",D805,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-MRKG (Topografía / Cartografía - Vías: marcas viales)</v>
       </c>
       <c r="I805" s="11">
@@ -39766,7 +39601,7 @@
         <v>2871</v>
       </c>
       <c r="E806" s="1" t="str">
-        <f>_xlfn.CONCAT(B806," (",C806," - ",D806,")")</f>
+        <f t="shared" si="12"/>
         <v>V-ROAD-UPVD (Topografía / Cartografía - Vías: superficie sin pavimentar)</v>
       </c>
       <c r="I806" s="11">
@@ -39796,14 +39631,8 @@
         <v>577</v>
       </c>
       <c r="E807" s="1" t="str">
-        <f>_xlfn.CONCAT(B807," (",C807," - ",D807,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RRAP (Topografía / Cartografía - Escalones)</v>
-      </c>
-      <c r="F807" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G807" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I807" s="11">
         <v>0</v>
@@ -39832,7 +39661,7 @@
         <v>583</v>
       </c>
       <c r="E808" s="1" t="str">
-        <f>_xlfn.CONCAT(B808," (",C808," - ",D808,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY (Topografía / Cartografía - Derecho de paso)</v>
       </c>
       <c r="I808" s="11">
@@ -39862,7 +39691,7 @@
         <v>2872</v>
       </c>
       <c r="E809" s="1" t="str">
-        <f>_xlfn.CONCAT(B809," (",C809," - ",D809,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-CNTR (Topografía / Cartografía - Derecho de paso: centro)</v>
       </c>
       <c r="I809" s="11">
@@ -39892,7 +39721,7 @@
         <v>2873</v>
       </c>
       <c r="E810" s="1" t="str">
-        <f>_xlfn.CONCAT(B810," (",C810," - ",D810,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-CTLA (Topografía / Cartografía - Derecho de paso: acceso controlado)</v>
       </c>
       <c r="I810" s="11">
@@ -39922,7 +39751,7 @@
         <v>2874</v>
       </c>
       <c r="E811" s="1" t="str">
-        <f>_xlfn.CONCAT(B811," (",C811," - ",D811,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-LINE (Topografía / Cartografía - Derecho de paso: líneas)</v>
       </c>
       <c r="I811" s="11">
@@ -39952,7 +39781,7 @@
         <v>2875</v>
       </c>
       <c r="E812" s="1" t="str">
-        <f>_xlfn.CONCAT(B812," (",C812," - ",D812,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-LMTA (Topografía / Cartografía - Derecho de paso: acceso limitado)</v>
       </c>
       <c r="I812" s="11">
@@ -39982,7 +39811,7 @@
         <v>2876</v>
       </c>
       <c r="E813" s="1" t="str">
-        <f>_xlfn.CONCAT(B813," (",C813," - ",D813,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-MRKR (Topografía / Cartografía - Derecho de paso: marcador)</v>
       </c>
       <c r="I813" s="11">
@@ -40012,7 +39841,7 @@
         <v>2877</v>
       </c>
       <c r="E814" s="1" t="str">
-        <f>_xlfn.CONCAT(B814," (",C814," - ",D814,")")</f>
+        <f t="shared" si="12"/>
         <v>V-RWAY-STAN (Topografía / Cartografía - Derecho de paso: estacionamiento)</v>
       </c>
       <c r="I814" s="11">
@@ -40042,14 +39871,8 @@
         <v>598</v>
       </c>
       <c r="E815" s="1" t="str">
-        <f>_xlfn.CONCAT(B815," (",C815," - ",D815,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE (Topografía / Cartografía - Características del sitio)</v>
-      </c>
-      <c r="F815" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G815" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I815" s="11">
         <v>0</v>
@@ -40078,7 +39901,7 @@
         <v>2878</v>
       </c>
       <c r="E816" s="1" t="str">
-        <f>_xlfn.CONCAT(B816," (",C816," - ",D816,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-EWAT (Topografía / Cartografía - Características del sitio: borde del agua)</v>
       </c>
       <c r="I816" s="11">
@@ -40108,7 +39931,7 @@
         <v>2879</v>
       </c>
       <c r="E817" s="1" t="str">
-        <f>_xlfn.CONCAT(B817," (",C817," - ",D817,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-FENC (Topografía / Cartografía - Características del sitio: cercas)</v>
       </c>
       <c r="I817" s="11">
@@ -40138,7 +39961,7 @@
         <v>2880</v>
       </c>
       <c r="E818" s="1" t="str">
-        <f>_xlfn.CONCAT(B818," (",C818," - ",D818,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-ROCK (Topografía / Cartografía - Características del sitio: rocas grandes y afloramientos rocosos)</v>
       </c>
       <c r="I818" s="11">
@@ -40168,7 +39991,7 @@
         <v>2881</v>
       </c>
       <c r="E819" s="1" t="str">
-        <f>_xlfn.CONCAT(B819," (",C819," - ",D819,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-RTWL (Topografía / Cartografía - Características del sitio: muro de contención)</v>
       </c>
       <c r="I819" s="11">
@@ -40198,7 +40021,7 @@
         <v>2882</v>
       </c>
       <c r="E820" s="1" t="str">
-        <f>_xlfn.CONCAT(B820," (",C820," - ",D820,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-SIGN (Topografía / Cartografía - Características del sitio: señalización)</v>
       </c>
       <c r="I820" s="11">
@@ -40228,7 +40051,7 @@
         <v>2883</v>
       </c>
       <c r="E821" s="1" t="str">
-        <f>_xlfn.CONCAT(B821," (",C821," - ",D821,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SITE-VEGE (Topografía / Cartografía - Características del sitio: árboles, arbustos y otra vegetación)</v>
       </c>
       <c r="I821" s="11">
@@ -40244,7 +40067,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="822" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A822" s="9">
         <v>1</v>
       </c>
@@ -40258,15 +40081,18 @@
         <v>625</v>
       </c>
       <c r="E822" s="1" t="str">
-        <f>_xlfn.CONCAT(B822," (",C822," - ",D822,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SSWR (Topografía / Cartografía - Alcantarillado sanitario)</v>
       </c>
       <c r="F822" s="11" t="s">
-        <v>3800</v>
+        <v>3805</v>
       </c>
       <c r="G822" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H822" s="11">
+        <v>0.3</v>
+      </c>
       <c r="I822" s="11">
         <v>0</v>
       </c>
@@ -40294,7 +40120,7 @@
         <v>1538</v>
       </c>
       <c r="E823" s="1" t="str">
-        <f>_xlfn.CONCAT(B823," (",C823," - ",D823,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SSWR-MHOL (Topografía / Cartografía - Alcantarillado sanitario: pozo de registro)</v>
       </c>
       <c r="I823" s="11">
@@ -40324,7 +40150,7 @@
         <v>1541</v>
       </c>
       <c r="E824" s="1" t="str">
-        <f>_xlfn.CONCAT(B824," (",C824," - ",D824,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SSWR-PIPE (Topografía / Cartografía - Alcantarillado sanitario: tuberías)</v>
       </c>
       <c r="I824" s="11">
@@ -40354,7 +40180,7 @@
         <v>1556</v>
       </c>
       <c r="E825" s="1" t="str">
-        <f>_xlfn.CONCAT(B825," (",C825," - ",D825,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SSWR-STRC (Topografía / Cartografía - Alcantarillado sanitario: estructuras)</v>
       </c>
       <c r="I825" s="11">
@@ -40384,7 +40210,7 @@
         <v>1559</v>
       </c>
       <c r="E826" s="1" t="str">
-        <f>_xlfn.CONCAT(B826," (",C826," - ",D826,")")</f>
+        <f t="shared" si="12"/>
         <v>V-SSWR-UGND (Topografía / Cartografía - Alcantarillado sanitario: subterráneo)</v>
       </c>
       <c r="I826" s="11">
@@ -40414,7 +40240,7 @@
         <v>628</v>
       </c>
       <c r="E827" s="1" t="str">
-        <f>_xlfn.CONCAT(B827," (",C827," - ",D827,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM (Topografía / Cartografía - Sistema de vapor)</v>
       </c>
       <c r="I827" s="11">
@@ -40444,7 +40270,7 @@
         <v>2884</v>
       </c>
       <c r="E828" s="1" t="str">
-        <f>_xlfn.CONCAT(B828," (",C828," - ",D828,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM-INST (Topografía / Cartografía - Sistema de vapor: instrumentación (medidores, válvulas, bombas))</v>
       </c>
       <c r="I828" s="11">
@@ -40474,7 +40300,7 @@
         <v>1566</v>
       </c>
       <c r="E829" s="1" t="str">
-        <f>_xlfn.CONCAT(B829," (",C829," - ",D829,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM-MHOL (Topografía / Cartografía - Sistema de vapor: pozo de registro)</v>
       </c>
       <c r="I829" s="11">
@@ -40504,7 +40330,7 @@
         <v>1569</v>
       </c>
       <c r="E830" s="1" t="str">
-        <f>_xlfn.CONCAT(B830," (",C830," - ",D830,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM-PIPE (Topografía / Cartografía - Sistema de vapor: tuberías)</v>
       </c>
       <c r="I830" s="11">
@@ -40534,7 +40360,7 @@
         <v>1572</v>
       </c>
       <c r="E831" s="1" t="str">
-        <f>_xlfn.CONCAT(B831," (",C831," - ",D831,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM-STRC (Topografía / Cartografía - Sistema de vapor: estructuras)</v>
       </c>
       <c r="I831" s="11">
@@ -40564,7 +40390,7 @@
         <v>2887</v>
       </c>
       <c r="E832" s="1" t="str">
-        <f>_xlfn.CONCAT(B832," (",C832," - ",D832,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STEM-UGND (Topografía / Cartografía - Sistema de vapor: Subterráneo)</v>
       </c>
       <c r="I832" s="11">
@@ -40580,7 +40406,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="833" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
       <c r="A833" s="9">
         <v>1</v>
       </c>
@@ -40594,15 +40420,18 @@
         <v>634</v>
       </c>
       <c r="E833" s="1" t="str">
-        <f>_xlfn.CONCAT(B833," (",C833," - ",D833,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STRM (Topografía / Cartografía - Alcantarillado pluvial)</v>
       </c>
-      <c r="F833" s="11" t="s">
-        <v>3800</v>
+      <c r="F833" s="11">
+        <v>151</v>
       </c>
       <c r="G833" s="11" t="s">
         <v>3799</v>
       </c>
+      <c r="H833" s="11">
+        <v>0.3</v>
+      </c>
       <c r="I833" s="11">
         <v>0</v>
       </c>
@@ -40630,7 +40459,7 @@
         <v>2888</v>
       </c>
       <c r="E834" s="1" t="str">
-        <f>_xlfn.CONCAT(B834," (",C834," - ",D834,")")</f>
+        <f t="shared" si="12"/>
         <v>V-STRM-DTCH (Topografía / Cartografía - Alcantarillado pluvial: zanjas o lavaderos)</v>
       </c>
       <c r="I834" s="11">
@@ -40660,7 +40489,7 @@
         <v>1588</v>
       </c>
       <c r="E835" s="1" t="str">
-        <f>_xlfn.CONCAT(B835," (",C835," - ",D835,")")</f>
+        <f t="shared" ref="E835:E898" si="13">_xlfn.CONCAT(B835," (",C835," - ",D835,")")</f>
         <v>V-STRM-MHOL (Topografía / Cartografía - Alcantarillado pluvial: pozo de registro)</v>
       </c>
       <c r="I835" s="11">
@@ -40690,7 +40519,7 @@
         <v>1591</v>
       </c>
       <c r="E836" s="1" t="str">
-        <f>_xlfn.CONCAT(B836," (",C836," - ",D836,")")</f>
+        <f t="shared" si="13"/>
         <v>V-STRM-PIPE (Topografía / Cartografía - Alcantarillado pluvial: tuberías)</v>
       </c>
       <c r="I836" s="11">
@@ -40720,7 +40549,7 @@
         <v>2889</v>
       </c>
       <c r="E837" s="1" t="str">
-        <f>_xlfn.CONCAT(B837," (",C837," - ",D837,")")</f>
+        <f t="shared" si="13"/>
         <v>V-STRM-POND (Topografía / Cartografía - Alcantarillado pluvial: estanque de retención)</v>
       </c>
       <c r="I837" s="11">
@@ -40750,7 +40579,7 @@
         <v>1606</v>
       </c>
       <c r="E838" s="1" t="str">
-        <f>_xlfn.CONCAT(B838," (",C838," - ",D838,")")</f>
+        <f t="shared" si="13"/>
         <v>V-STRM-STRC (Topografía / Cartografía - Alcantarillado pluvial: estructuras)</v>
       </c>
       <c r="I838" s="11">
@@ -40780,7 +40609,7 @@
         <v>1609</v>
       </c>
       <c r="E839" s="1" t="str">
-        <f>_xlfn.CONCAT(B839," (",C839," - ",D839,")")</f>
+        <f t="shared" si="13"/>
         <v>V-STRM-UGND (Topografía / Cartografía - Alcantarillado pluvial: subterráneo)</v>
       </c>
       <c r="I839" s="11">
@@ -40810,14 +40639,8 @@
         <v>2890</v>
       </c>
       <c r="E840" s="1" t="str">
-        <f>_xlfn.CONCAT(B840," (",C840," - ",D840,")")</f>
+        <f t="shared" si="13"/>
         <v>V-SURV (Topografía / Cartografía - Levantamiento)</v>
-      </c>
-      <c r="F840" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G840" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I840" s="11">
         <v>0</v>
@@ -40846,7 +40669,7 @@
         <v>2891</v>
       </c>
       <c r="E841" s="1" t="str">
-        <f>_xlfn.CONCAT(B841," (",C841," - ",D841,")")</f>
+        <f t="shared" si="13"/>
         <v>V-SURV-DATA (Topografía / Cartografía - Levantamiento: datos)</v>
       </c>
       <c r="I841" s="11">
@@ -40876,14 +40699,8 @@
         <v>643</v>
       </c>
       <c r="E842" s="1" t="str">
-        <f>_xlfn.CONCAT(B842," (",C842," - ",D842,")")</f>
+        <f t="shared" si="13"/>
         <v>V-SWLK (Topografía / Cartografía - Aceras)</v>
-      </c>
-      <c r="F842" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G842" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I842" s="11">
         <v>0</v>
@@ -40912,7 +40729,7 @@
         <v>1613</v>
       </c>
       <c r="E843" s="1" t="str">
-        <f>_xlfn.CONCAT(B843," (",C843," - ",D843,")")</f>
+        <f t="shared" si="13"/>
         <v>V-SWLK-ASPH (Topografía / Cartografía - Aceras: asfalto)</v>
       </c>
       <c r="I843" s="11">
@@ -40942,7 +40759,7 @@
         <v>1616</v>
       </c>
       <c r="E844" s="1" t="str">
-        <f>_xlfn.CONCAT(B844," (",C844," - ",D844,")")</f>
+        <f t="shared" si="13"/>
         <v>V-SWLK-CONC (Topografía / Cartografía - Aceras: hormigón)</v>
       </c>
       <c r="I844" s="11">
@@ -40972,14 +40789,8 @@
         <v>655</v>
       </c>
       <c r="E845" s="1" t="str">
-        <f>_xlfn.CONCAT(B845," (",C845," - ",D845,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO (Topografía / Cartografía - Característica topográfica)</v>
-      </c>
-      <c r="F845" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G845" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I845" s="11">
         <v>0</v>
@@ -41008,7 +40819,7 @@
         <v>2892</v>
       </c>
       <c r="E846" s="1" t="str">
-        <f>_xlfn.CONCAT(B846," (",C846," - ",D846,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-EWAT (Topografía / Cartografía - Característica topográfica: borde del agua)</v>
       </c>
       <c r="I846" s="11">
@@ -41038,7 +40849,7 @@
         <v>2893</v>
       </c>
       <c r="E847" s="1" t="str">
-        <f>_xlfn.CONCAT(B847," (",C847," - ",D847,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-GRID (Topografía / Cartografía - Característica topográfica: cuadrícula)</v>
       </c>
       <c r="I847" s="11">
@@ -41068,7 +40879,7 @@
         <v>1637</v>
       </c>
       <c r="E848" s="1" t="str">
-        <f>_xlfn.CONCAT(B848," (",C848," - ",D848,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-MAJR (Topografía / Cartografía - Característica topográfica: principal (curvas de nivel))</v>
       </c>
       <c r="I848" s="11">
@@ -41098,7 +40909,7 @@
         <v>1640</v>
       </c>
       <c r="E849" s="1" t="str">
-        <f>_xlfn.CONCAT(B849," (",C849," - ",D849,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-MINR (Topografía / Cartografía - Característica topográfica: menor (curvas de nivel))</v>
       </c>
       <c r="I849" s="11">
@@ -41128,7 +40939,7 @@
         <v>2894</v>
       </c>
       <c r="E850" s="1" t="str">
-        <f>_xlfn.CONCAT(B850," (",C850," - ",D850,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-SOUN (Topografía / Cartografía - Característica topográfica: sondeos)</v>
       </c>
       <c r="I850" s="11">
@@ -41158,7 +40969,7 @@
         <v>1643</v>
       </c>
       <c r="E851" s="1" t="str">
-        <f>_xlfn.CONCAT(B851," (",C851," - ",D851,")")</f>
+        <f t="shared" si="13"/>
         <v>V-TOPO-SPOT (Topografía / Cartografía - Característica topográfica: elevaciones puntuales)</v>
       </c>
       <c r="I851" s="11">
@@ -41188,14 +40999,8 @@
         <v>673</v>
       </c>
       <c r="E852" s="1" t="str">
-        <f>_xlfn.CONCAT(B852," (",C852," - ",D852,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID (Topografía / Cartografía - Objetos no identificados del sitio)</v>
-      </c>
-      <c r="F852" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G852" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I852" s="11">
         <v>0</v>
@@ -41224,7 +41029,7 @@
         <v>2895</v>
       </c>
       <c r="E853" s="1" t="str">
-        <f>_xlfn.CONCAT(B853," (",C853," - ",D853,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-CABL (Topografía / Cartografía - Objetos no identificados del sitio: sistemas de cableado)</v>
       </c>
       <c r="I853" s="11">
@@ -41254,7 +41059,7 @@
         <v>2896</v>
       </c>
       <c r="E854" s="1" t="str">
-        <f>_xlfn.CONCAT(B854," (",C854," - ",D854,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-PIPE (Topografía / Cartografía - Objetos no identificados del sitio: tuberías)</v>
       </c>
       <c r="I854" s="11">
@@ -41284,7 +41089,7 @@
         <v>2897</v>
       </c>
       <c r="E855" s="1" t="str">
-        <f>_xlfn.CONCAT(B855," (",C855," - ",D855,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-TANK (Topografía / Cartografía - Objetos no identificados del sitio: tanques de almacenamiento)</v>
       </c>
       <c r="I855" s="11">
@@ -41314,7 +41119,7 @@
         <v>2898</v>
       </c>
       <c r="E856" s="1" t="str">
-        <f>_xlfn.CONCAT(B856," (",C856," - ",D856,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-UTIL (Topografía / Cartografía - Objetos no identificados del sitio: líneas de servicios públicos)</v>
       </c>
       <c r="I856" s="11">
@@ -41344,7 +41149,7 @@
         <v>2899</v>
       </c>
       <c r="E857" s="1" t="str">
-        <f>_xlfn.CONCAT(B857," (",C857," - ",D857,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-UTIL-OVHD (Topografía / Cartografía - Objetos no identificados del sitio: líneas de servicios públicos aéreas)</v>
       </c>
       <c r="I857" s="11">
@@ -41374,7 +41179,7 @@
         <v>2900</v>
       </c>
       <c r="E858" s="1" t="str">
-        <f>_xlfn.CONCAT(B858," (",C858," - ",D858,")")</f>
+        <f t="shared" si="13"/>
         <v>V-UNID-UTIL-UGND (Topografía / Cartografía - Objetos no identificados del sitio: líneas de servicios públicos subterráneas)</v>
       </c>
       <c r="I858" s="11">
@@ -41404,14 +41209,8 @@
         <v>688</v>
       </c>
       <c r="E859" s="1" t="str">
-        <f>_xlfn.CONCAT(B859," (",C859," - ",D859,")")</f>
+        <f t="shared" si="13"/>
         <v xml:space="preserve"> V-WATR (Topografía / Cartografía - Suministro de agua)</v>
-      </c>
-      <c r="F859" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="G859" s="11" t="s">
-        <v>3799</v>
       </c>
       <c r="I859" s="11">
         <v>0</v>
@@ -41440,7 +41239,7 @@
         <v>2901</v>
       </c>
       <c r="E860" s="1" t="str">
-        <f>_xlfn.CONCAT(B860," (",C860," - ",D860,")")</f>
+        <f t="shared" si="13"/>
         <v>V-WATR-INST (Topografía / Cartografía - Suministro de agua: instrumentación (medidores, válvulas, bombas))</v>
       </c>
       <c r="I860" s="11">
@@ -41470,7 +41269,7 @@
         <v>2902</v>
       </c>
       <c r="E861" s="1" t="str">
-        <f>_xlfn.CONCAT(B861," (",C861," - ",D861,")")</f>
+        <f t="shared" si="13"/>
         <v>V-WATR-MHOL (Topografía / Cartografía - Suministro de agua: pozo de registro)</v>
       </c>
       <c r="I861" s="11">
@@ -41500,7 +41299,7 @@
         <v>2903</v>
       </c>
       <c r="E862" s="1" t="str">
-        <f>_xlfn.CONCAT(B862," (",C862," - ",D862,")")</f>
+        <f t="shared" si="13"/>
         <v>V-WATR-PIPE (Topografía / Cartografía - Suministro de agua: Tuberías)</v>
       </c>
       <c r="I862" s="11">
@@ -41530,7 +41329,7 @@
         <v>2904</v>
       </c>
       <c r="E863" s="1" t="str">
-        <f>_xlfn.CONCAT(B863," (",C863," - ",D863,")")</f>
+        <f t="shared" si="13"/>
         <v>V-WATR-STRC (Topografía / Cartografía - Abastecimiento de agua: estructuras)</v>
       </c>
       <c r="I863" s="11">
@@ -41560,7 +41359,7 @@
         <v>2905</v>
       </c>
       <c r="E864" s="1" t="str">
-        <f>_xlfn.CONCAT(B864," (",C864," - ",D864,")")</f>
+        <f t="shared" si="13"/>
         <v>V-WATR-UGND (Topografía / Cartografía - Abastecimiento de agua: subterráneo)</v>
       </c>
       <c r="I864" s="11">
@@ -41582,6 +41381,9 @@
       <filters>
         <filter val="1"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41654,20 +41456,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="85273d68-90a1-4455-8abc-8dc013f26eed" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="85273d68-90a1-4455-8abc-8dc013f26eed" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41924,6 +41726,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1556B-F96F-4768-A5C1-84E54B001EF8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E66BA-068D-48E6-8C46-D96E2B6CA4E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -41936,14 +41746,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1556B-F96F-4768-A5C1-84E54B001EF8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/file/table/DAPC_AIALayerName.xlsx
+++ b/file/table/DAPC_AIALayerName.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B201D16-2648-4405-877B-7945B2388F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3456712C-B81E-4C33-8A2D-A0D5AAD77963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5100" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="4" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
   </bookViews>
@@ -11468,9 +11468,6 @@
     <t>V-UNID-UTIL-UGND</t>
   </si>
   <si>
-    <t xml:space="preserve"> V-WATR</t>
-  </si>
-  <si>
     <t>V-WATR-INST</t>
   </si>
   <si>
@@ -11532,6 +11529,9 @@
   </si>
   <si>
     <t>HIDDEN2</t>
+  </si>
+  <si>
+    <t>V-WATR</t>
   </si>
 </sst>
 </file>
@@ -15204,7 +15204,7 @@
         <v>2781</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.6">
@@ -15212,7 +15212,7 @@
         <v>2910</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>2783</v>
@@ -15224,19 +15224,19 @@
         <v>2930</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>3792</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>3793</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>3794</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>3795</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>3796</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>2784</v>
@@ -15245,7 +15245,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -15263,10 +15263,10 @@
         <v>A-AREA (Arquitectura - Área)</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H3" s="11">
         <v>0.05</v>
@@ -15374,7 +15374,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A7" s="9">
         <v>1</v>
       </c>
@@ -15395,7 +15395,7 @@
         <v>226</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H7" s="11">
         <v>0.25</v>
@@ -15563,7 +15563,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A13" s="9">
         <v>1</v>
       </c>
@@ -15581,10 +15581,10 @@
         <v>A-COLS (Arquitectura - Columnas)</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H13" s="11">
         <v>0.5</v>
@@ -15632,7 +15632,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A15" s="9">
         <v>1</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>251</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H15" s="11">
         <v>0.18</v>
@@ -15731,7 +15731,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A18" s="9">
         <v>1</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H18" s="11">
         <v>0.18</v>
@@ -15860,7 +15860,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A22" s="9">
         <v>1</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>252</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H22" s="11">
         <v>0.35</v>
@@ -16019,7 +16019,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A27" s="9">
         <v>1</v>
       </c>
@@ -16040,7 +16040,7 @@
         <v>145</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H27" s="11">
         <v>0.18</v>
@@ -16328,7 +16328,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A37" s="9">
         <v>1</v>
       </c>
@@ -16349,7 +16349,7 @@
         <v>46</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H37" s="11">
         <v>0.18</v>
@@ -16607,7 +16607,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A46" s="9">
         <v>1</v>
       </c>
@@ -16625,10 +16625,10 @@
         <v>A-GLAZ (Arquitectura - Acristalamiento (muros transparentes y ventanas))</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H46" s="11">
         <v>0.18</v>
@@ -16856,7 +16856,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A54" s="9">
         <v>1</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>226</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H54" s="11">
         <v>0.53</v>
@@ -17045,7 +17045,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A60" s="9">
         <v>1</v>
       </c>
@@ -17063,10 +17063,10 @@
         <v>A-WALL (Arquitectura - Paredes)</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H60" s="11">
         <v>0.6</v>
@@ -19304,7 +19304,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A135" s="9">
         <v>1</v>
       </c>
@@ -19322,10 +19322,10 @@
         <v>C-DRIV (Civil - Accesos vehiculares)</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H135" s="11">
         <v>0.4</v>
@@ -22283,7 +22283,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A234" s="9">
         <v>1</v>
       </c>
@@ -22301,10 +22301,10 @@
         <v>C-POWR (Civil - Energía)</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="H234" s="11">
         <v>0.15</v>
@@ -23162,7 +23162,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A263" s="9">
         <v>1</v>
       </c>
@@ -23180,10 +23180,10 @@
         <v>C-PROP (Civil - Propiedad)</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H263" s="11">
         <v>0.25</v>
@@ -23651,7 +23651,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A279" s="9">
         <v>1</v>
       </c>
@@ -23672,7 +23672,7 @@
         <v>57</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H279" s="11">
         <v>0.4</v>
@@ -24380,7 +24380,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A303" s="9">
         <v>1</v>
       </c>
@@ -24398,10 +24398,10 @@
         <v>C-SSWR (Civil - Alcantarillado sanitario)</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H303" s="11">
         <v>0.3</v>
@@ -24929,7 +24929,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A321" s="9">
         <v>1</v>
       </c>
@@ -24950,7 +24950,7 @@
         <v>151</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H321" s="11">
         <v>0.3</v>
@@ -25928,7 +25928,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A354" s="9">
         <v>1</v>
       </c>
@@ -25946,10 +25946,10 @@
         <v>C-WALL (Civil - Muros)</v>
       </c>
       <c r="F354" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G354" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H354" s="11">
         <v>0.6</v>
@@ -26687,7 +26687,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A379" s="9">
         <v>1</v>
       </c>
@@ -26708,7 +26708,7 @@
         <v>201</v>
       </c>
       <c r="G379" s="11" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="H379" s="11">
         <v>201</v>
@@ -30176,7 +30176,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="495" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A495" s="9">
         <v>1</v>
       </c>
@@ -30194,10 +30194,10 @@
         <v>E-POWR (Electricidad - Alimentación)</v>
       </c>
       <c r="F495" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G495" s="11" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="H495" s="11">
         <v>0.15</v>
@@ -31475,7 +31475,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="538" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A538" s="9">
         <v>1</v>
       </c>
@@ -31493,10 +31493,10 @@
         <v>S-BEAM (Estructura - Vigas)</v>
       </c>
       <c r="F538" s="11" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="G538" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H538" s="11">
         <v>0.5</v>
@@ -31964,7 +31964,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="554" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A554" s="9">
         <v>1</v>
       </c>
@@ -31982,10 +31982,10 @@
         <v>S-COLS (Estructura - Columnas)</v>
       </c>
       <c r="F554" s="11" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="G554" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H554" s="11">
         <v>0.5</v>
@@ -32813,7 +32813,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="582" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A582" s="9">
         <v>1</v>
       </c>
@@ -32834,7 +32834,7 @@
         <v>251</v>
       </c>
       <c r="G582" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H582" s="11">
         <v>0.18</v>
@@ -33212,7 +33212,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="595" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A595" s="9">
         <v>1</v>
       </c>
@@ -33233,7 +33233,7 @@
         <v>38</v>
       </c>
       <c r="G595" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H595" s="11">
         <v>0.09</v>
@@ -33941,7 +33941,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="619" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A619" s="9">
         <v>1</v>
       </c>
@@ -33959,10 +33959,10 @@
         <v>S-STRS (Estructura - Escaleras)</v>
       </c>
       <c r="F619" s="11" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="G619" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H619" s="11">
         <v>0.4</v>
@@ -34040,7 +34040,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="622" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A622" s="9">
         <v>1</v>
       </c>
@@ -34058,10 +34058,10 @@
         <v>S-WALL (Estructura - Muros)</v>
       </c>
       <c r="F622" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G622" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H622" s="11">
         <v>0.6</v>
@@ -35789,7 +35789,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="680" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A680" s="9">
         <v>1</v>
       </c>
@@ -35807,10 +35807,10 @@
         <v>V-DRIV (Topografía / Cartografía - Accesos vehiculares)</v>
       </c>
       <c r="F680" s="11" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="G680" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H680" s="11">
         <v>0.4</v>
@@ -38138,7 +38138,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="758" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A758" s="9">
         <v>1</v>
       </c>
@@ -38156,10 +38156,10 @@
         <v>V-POWR (Topografía / Cartografía - Energía)</v>
       </c>
       <c r="F758" s="11" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G758" s="11" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="H758" s="11">
         <v>0.15</v>
@@ -40067,7 +40067,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="822" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A822" s="9">
         <v>1</v>
       </c>
@@ -40085,10 +40085,10 @@
         <v>V-SSWR (Topografía / Cartografía - Alcantarillado sanitario)</v>
       </c>
       <c r="F822" s="11" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="G822" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H822" s="11">
         <v>0.3</v>
@@ -40406,7 +40406,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="833" spans="1:12" hidden="1" x14ac:dyDescent="0.6">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A833" s="9">
         <v>1</v>
       </c>
@@ -40427,7 +40427,7 @@
         <v>151</v>
       </c>
       <c r="G833" s="11" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="H833" s="11">
         <v>0.3</v>
@@ -41200,7 +41200,7 @@
         <v>1</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>3786</v>
+        <v>3807</v>
       </c>
       <c r="C859" s="1" t="s">
         <v>51</v>
@@ -41210,7 +41210,7 @@
       </c>
       <c r="E859" s="1" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve"> V-WATR (Topografía / Cartografía - Suministro de agua)</v>
+        <v>V-WATR (Topografía / Cartografía - Suministro de agua)</v>
       </c>
       <c r="I859" s="11">
         <v>0</v>
@@ -41230,7 +41230,7 @@
         <v>0</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="C860" s="1" t="s">
         <v>51</v>
@@ -41260,7 +41260,7 @@
         <v>0</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="C861" s="1" t="s">
         <v>51</v>
@@ -41290,7 +41290,7 @@
         <v>0</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="C862" s="1" t="s">
         <v>51</v>
@@ -41320,7 +41320,7 @@
         <v>0</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="C863" s="1" t="s">
         <v>51</v>
@@ -41350,7 +41350,7 @@
         <v>0</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="C864" s="1" t="s">
         <v>51</v>
@@ -41381,9 +41381,6 @@
       <filters>
         <filter val="1"/>
       </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file/table/DAPC_AIALayerName.xlsx
+++ b/file/table/DAPC_AIALayerName.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B016E794-F617-4E9D-A98F-F457F315B8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5488CD01-C53B-4104-9686-D28A12529F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="819" activeTab="4" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
   </bookViews>

--- a/file/table/DAPC_AIALayerName.xlsx
+++ b/file/table/DAPC_AIALayerName.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A0878D-0F3C-4A75-998D-68184B9C175C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC58FC7-30EF-4C7A-AD32-8E4AAA07A1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="819" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="819" activeTab="4" xr2:uid="{42944890-2C1C-4F24-9ED8-2D12D6DBCB66}"/>
   </bookViews>
   <sheets>
     <sheet name="Level1" sheetId="1" r:id="rId1"/>
@@ -11844,6 +11844,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>685067</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>157529</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3586</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>185438</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36142275-554F-41D9-B0FF-DFBDA05367E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3154240" y="157529"/>
+          <a:ext cx="1022029" cy="236727"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12425,8 +12480,10 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="bYHlb7wRsGOmqazHDuPyXJC1OS/zRvPYs2m56OQV8NQ29CU3V47OtZJcbJYNNaf8fKK3RWcHywGAQ84nc6CACg==" saltValue="MMHMZcLjo4daCX5If0VDog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A3:C3" xr:uid="{D8B2CA5A-51EA-479E-80EC-557721136700}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13088,6 +13145,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Qzeuiom1SBwOc22n0a2fANInVcQYQzY4KLmqOFXXMlECOIJ37kOIJUUYCuPPRxcwgJge+5efkvFUq01uwF7DTA==" saltValue="AXpMcdiKXb3enF8X6k9xqw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A3:C3" xr:uid="{D8B2CA5A-51EA-479E-80EC-557721136700}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15213,6 +15271,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="xAg6hnhP6o4pNjdTMeujnW06vgCXD81sQ/LPG9co4Mpc9+0Z2h4TakxYsCy2FtfuJgxLGpq5HcXykhxEmHKVUQ==" saltValue="Du0vhsoC/7kDmNJhm/2o+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A3:C3" xr:uid="{D8B2CA5A-51EA-479E-80EC-557721136700}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15347,6 +15406,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="AYVztuuDoBZBw9PjqmHfaMHumFKedbBhTZOA3DfzPLrv2bQzckruCznmVpIBHkM4xJlEoZXS0gcyVSh4M7OPAA==" saltValue="b84L4FpcQPSiOXoOJLlizg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A3:C12" xr:uid="{9581777B-1AA3-48B5-86FA-B375601B16B9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15354,6 +15414,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA60E93-22D8-4E5B-AC58-CD121D74306E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S865"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15542,7 +15603,7 @@
 A-AREA  </v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>0</v>
       </c>
@@ -15613,7 +15674,7 @@
 A-AREA-OCCP  </v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -15684,7 +15745,7 @@
 A-BARR  </v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>0</v>
       </c>
@@ -15826,7 +15887,7 @@
 A-CLNG  </v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>0</v>
       </c>
@@ -15897,7 +15958,7 @@
 A-CLNG-ACCS  </v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>0</v>
       </c>
@@ -15968,7 +16029,7 @@
 A-CLNG-GRID  </v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>0</v>
       </c>
@@ -16039,7 +16100,7 @@
 A-CLNG-OPNG  </v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>0</v>
       </c>
@@ -16110,7 +16171,7 @@
 A-CLNG-SUSP  </v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7">
         <v>0</v>
       </c>
@@ -16252,7 +16313,7 @@
 A-COLS  </v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7">
         <v>0</v>
       </c>
@@ -16394,7 +16455,7 @@
 A-DOOR  </v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="7">
         <v>0</v>
       </c>
@@ -16465,7 +16526,7 @@
 A-DOOR-FULL  </v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7">
         <v>0</v>
       </c>
@@ -16607,7 +16668,7 @@
 A-EQPM  </v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7">
         <v>0</v>
       </c>
@@ -16678,7 +16739,7 @@
 A-EQPM-ACCS  </v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7">
         <v>0</v>
       </c>
@@ -16749,7 +16810,7 @@
 A-EQPM-FIXD  </v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7">
         <v>0</v>
       </c>
@@ -16891,7 +16952,7 @@
 A-FLOR  </v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7">
         <v>0</v>
       </c>
@@ -16962,7 +17023,7 @@
 A-FLOR-CSWK  </v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7">
         <v>0</v>
       </c>
@@ -17033,7 +17094,7 @@
 A-FLOR-EVTR  </v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7">
         <v>0</v>
       </c>
@@ -17104,7 +17165,7 @@
 A-FLOR-FIXT  </v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7">
         <v>0</v>
       </c>
@@ -17246,7 +17307,7 @@
 A-FLOR-LEVL  </v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7">
         <v>0</v>
       </c>
@@ -17317,7 +17378,7 @@
 A-FLOR-OTLN  </v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="7">
         <v>0</v>
       </c>
@@ -17388,7 +17449,7 @@
 A-FLOR-OVHD  </v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="7">
         <v>0</v>
       </c>
@@ -17459,7 +17520,7 @@
 A-FLOR-RAIS  </v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7">
         <v>0</v>
       </c>
@@ -17530,7 +17591,7 @@
 A-FLOR-RISR  </v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7">
         <v>0</v>
       </c>
@@ -17601,7 +17662,7 @@
 A-FLOR-SIGN  </v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7">
         <v>0</v>
       </c>
@@ -17672,7 +17733,7 @@
 A-FLOR-SPCL  </v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7">
         <v>0</v>
       </c>
@@ -17743,7 +17804,7 @@
 A-FLOR-STRS  </v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="7">
         <v>0</v>
       </c>
@@ -17814,7 +17875,7 @@
 A-FLOR-TPTN  </v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="7">
         <v>0</v>
       </c>
@@ -17956,7 +18017,7 @@
 A-FURN  </v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7">
         <v>0</v>
       </c>
@@ -18027,7 +18088,7 @@
 A-FURN-FILE  </v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7">
         <v>0</v>
       </c>
@@ -18098,7 +18159,7 @@
 A-FURN-FIXD  </v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="7">
         <v>0</v>
       </c>
@@ -18169,7 +18230,7 @@
 A-FURN-FREE  </v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="7">
         <v>0</v>
       </c>
@@ -18240,7 +18301,7 @@
 A-FURN-PLNT  </v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="7">
         <v>0</v>
       </c>
@@ -18311,7 +18372,7 @@
 A-FURN-PNLS  </v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="7">
         <v>0</v>
       </c>
@@ -18382,7 +18443,7 @@
 A-FURN-SEAT  </v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7">
         <v>0</v>
       </c>
@@ -18453,7 +18514,7 @@
 A-FURN-STOR  </v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7">
         <v>0</v>
       </c>
@@ -18595,7 +18656,7 @@
 A-GLAZ  </v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="7">
         <v>0</v>
       </c>
@@ -18666,7 +18727,7 @@
 A-GLAZ-FULL  </v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="7">
         <v>0</v>
       </c>
@@ -18737,7 +18798,7 @@
 A-GLAZ-PRHT  </v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7">
         <v>0</v>
       </c>
@@ -18808,7 +18869,7 @@
 A-GLAZ-SILL  </v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="7">
         <v>0</v>
       </c>
@@ -18879,7 +18940,7 @@
 A-HVAC  </v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="7">
         <v>0</v>
       </c>
@@ -18950,7 +19011,7 @@
 A-HVAC-RDFF  </v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="7">
         <v>0</v>
       </c>
@@ -19021,7 +19082,7 @@
 A-HVAC-SDFF  </v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="7">
         <v>0</v>
       </c>
@@ -19163,7 +19224,7 @@
 A-ROOF  </v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="7">
         <v>0</v>
       </c>
@@ -19234,7 +19295,7 @@
 A-ROOF-HRAL  </v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="7">
         <v>0</v>
       </c>
@@ -19305,7 +19366,7 @@
 A-ROOF-LEVL  </v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="7">
         <v>0</v>
       </c>
@@ -19376,7 +19437,7 @@
 A-ROOF-OTLN  </v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="7">
         <v>0</v>
       </c>
@@ -19447,7 +19508,7 @@
 A-ROOF-RISR  </v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="7">
         <v>0</v>
       </c>
@@ -19589,7 +19650,7 @@
 A-WALL  </v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="7">
         <v>0</v>
       </c>
@@ -19660,7 +19721,7 @@
 A-WALL-CAVI  </v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="7">
         <v>0</v>
       </c>
@@ -19731,7 +19792,7 @@
 A-WALL-CNTR  </v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="7">
         <v>0</v>
       </c>
@@ -19802,7 +19863,7 @@
 A-WALL-CURT  </v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="7">
         <v>0</v>
       </c>
@@ -19873,7 +19934,7 @@
 A-WALL-FIRE  </v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="7">
         <v>0</v>
       </c>
@@ -19944,7 +20005,7 @@
 A-WALL-FULL  </v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="7">
         <v>0</v>
       </c>
@@ -20015,7 +20076,7 @@
 A-WALL-FULL-EXTR  </v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="7">
         <v>0</v>
       </c>
@@ -20086,7 +20147,7 @@
 A-WALL-FULL-INTR  </v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="7">
         <v>0</v>
       </c>
@@ -20157,7 +20218,7 @@
 A-WALL-HEAD  </v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="7">
         <v>0</v>
       </c>
@@ -20228,7 +20289,7 @@
 A-WALL-JAMB  </v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="7">
         <v>0</v>
       </c>
@@ -20299,7 +20360,7 @@
 A-WALL-MESH  </v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="7">
         <v>0</v>
       </c>
@@ -20370,7 +20431,7 @@
 A-WALL-MOVE  </v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="7">
         <v>0</v>
       </c>
@@ -20441,7 +20502,7 @@
 A-WALL-PATT  </v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="7">
         <v>0</v>
       </c>
@@ -20512,7 +20573,7 @@
 A-WALL-PRHT  </v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="7">
         <v>0</v>
       </c>
@@ -20583,7 +20644,7 @@
 C-AFLD  </v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="7">
         <v>0</v>
       </c>
@@ -20654,7 +20715,7 @@
 C-AFLD-ASPH  </v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="7">
         <v>0</v>
       </c>
@@ -20725,7 +20786,7 @@
 C-AFLD-CNTR  </v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="7">
         <v>0</v>
       </c>
@@ -20796,7 +20857,7 @@
 C-AFLD-CONC  </v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="7">
         <v>0</v>
       </c>
@@ -20867,7 +20928,7 @@
 C-AFLD-FLNE  </v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="7">
         <v>0</v>
       </c>
@@ -20938,7 +20999,7 @@
 C-AFLD-FLNE-MRKG  </v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="7">
         <v>0</v>
       </c>
@@ -21009,7 +21070,7 @@
 C-AFLD-FLNE-SIGN  </v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="7">
         <v>0</v>
       </c>
@@ -21080,7 +21141,7 @@
 C-AFLD-GRVL  </v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" s="7">
         <v>0</v>
       </c>
@@ -21151,7 +21212,7 @@
 C-AFLD-MRKG  </v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="7">
         <v>0</v>
       </c>
@@ -21222,7 +21283,7 @@
 C-AFLD-SIGN  </v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="7">
         <v>0</v>
       </c>
@@ -21293,7 +21354,7 @@
 C-AFLD-STAN  </v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="7">
         <v>0</v>
       </c>
@@ -21364,7 +21425,7 @@
 C-AFLD-WHIT  </v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="7">
         <v>0</v>
       </c>
@@ -21435,7 +21496,7 @@
 C-AFLD-WHIT-TICK  </v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="7">
         <v>0</v>
       </c>
@@ -21506,7 +21567,7 @@
 C-AFLD-YELO  </v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="7">
         <v>0</v>
       </c>
@@ -21648,7 +21709,7 @@
 C-BLDG  </v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="7">
         <v>0</v>
       </c>
@@ -21719,7 +21780,7 @@
 C-BLDG-DECK  </v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="7">
         <v>0</v>
       </c>
@@ -21790,7 +21851,7 @@
 C-BLDG-OTLN  </v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="7">
         <v>0</v>
       </c>
@@ -21861,7 +21922,7 @@
 C-BLDG-OVHD  </v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="7">
         <v>0</v>
       </c>
@@ -21932,7 +21993,7 @@
 C-BLDG-PRCH  </v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="7">
         <v>0</v>
       </c>
@@ -22003,7 +22064,7 @@
 C-BLIN  </v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="7">
         <v>0</v>
       </c>
@@ -22074,7 +22135,7 @@
 C-BLIN-STAN  </v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="7">
         <v>0</v>
       </c>
@@ -22145,7 +22206,7 @@
 C-BORE  </v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="7">
         <v>0</v>
       </c>
@@ -22216,7 +22277,7 @@
 C-BRDG  </v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="7">
         <v>0</v>
       </c>
@@ -22287,7 +22348,7 @@
 C-BRDG-CNTJ  </v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="7">
         <v>0</v>
       </c>
@@ -22358,7 +22419,7 @@
 C-BRDG-CNTR  </v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="7">
         <v>0</v>
       </c>
@@ -22429,7 +22490,7 @@
 C-BRDG-DECK  </v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="7">
         <v>0</v>
       </c>
@@ -22500,7 +22561,7 @@
 C-BRDG-EXPJ  </v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="7">
         <v>0</v>
       </c>
@@ -22571,7 +22632,7 @@
 C-BRDG-FALT  </v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="7">
         <v>0</v>
       </c>
@@ -22642,7 +22703,7 @@
 C-BRDG-HIDD  </v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="7">
         <v>0</v>
       </c>
@@ -22713,7 +22774,7 @@
 C-BRDG-OBJT  </v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="7">
         <v>0</v>
       </c>
@@ -22784,7 +22845,7 @@
 C-BRDG-OBJT-PRIM  </v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="7">
         <v>0</v>
       </c>
@@ -22855,7 +22916,7 @@
 C-BRDG-OBJT-SECD  </v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="7">
         <v>0</v>
       </c>
@@ -22926,7 +22987,7 @@
 C-BRDG-RBAR  </v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="7">
         <v>0</v>
       </c>
@@ -22997,7 +23058,7 @@
 C-CATV  </v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="7">
         <v>0</v>
       </c>
@@ -23068,7 +23129,7 @@
 C-CATV-OVHD  </v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="7">
         <v>0</v>
       </c>
@@ -23139,7 +23200,7 @@
 C-CATV-POLE  </v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="7">
         <v>0</v>
       </c>
@@ -23210,7 +23271,7 @@
 C-CATV-UGND  </v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="7">
         <v>0</v>
       </c>
@@ -23281,7 +23342,7 @@
 C-CEME  </v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="7">
         <v>0</v>
       </c>
@@ -23352,7 +23413,7 @@
 C-CHAN  </v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="7">
         <v>0</v>
       </c>
@@ -23423,7 +23484,7 @@
 C-CHAN-BWTR  </v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="7">
         <v>0</v>
       </c>
@@ -23494,7 +23555,7 @@
 C-CHAN-CNTR  </v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" s="7">
         <v>0</v>
       </c>
@@ -23565,7 +23626,7 @@
 C-CHAN-DACL  </v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" s="7">
         <v>0</v>
       </c>
@@ -23636,7 +23697,7 @@
 C-CHAN-DOCK  </v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" s="7">
         <v>0</v>
       </c>
@@ -23707,7 +23768,7 @@
 C-CHAN-NAID  </v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" s="7">
         <v>0</v>
       </c>
@@ -23778,7 +23839,7 @@
 C-COMM  </v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="7">
         <v>0</v>
       </c>
@@ -23849,7 +23910,7 @@
 C-COMM-OVHD  </v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="7">
         <v>0</v>
       </c>
@@ -23920,7 +23981,7 @@
 C-COMM-POLE  </v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="7">
         <v>0</v>
       </c>
@@ -24062,7 +24123,7 @@
 C-CTRL  </v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="7">
         <v>0</v>
       </c>
@@ -24133,7 +24194,7 @@
 C-CTR L-BMRK  </v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="7">
         <v>0</v>
       </c>
@@ -24204,7 +24265,7 @@
 C-CTRL-FLYS  </v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="7">
         <v>0</v>
       </c>
@@ -24275,7 +24336,7 @@
 C-CTRL-GRID  </v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="7">
         <v>0</v>
       </c>
@@ -24346,7 +24407,7 @@
 C-CTRL-HORZ  </v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="7">
         <v>0</v>
       </c>
@@ -24417,7 +24478,7 @@
 C-CTRL-HVPT  </v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="7">
         <v>0</v>
       </c>
@@ -24488,7 +24549,7 @@
 C-CTRL-PNPT  </v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="7">
         <v>0</v>
       </c>
@@ -24559,7 +24620,7 @@
 C-CTRL-TRAV  </v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" s="7">
         <v>0</v>
       </c>
@@ -24630,7 +24691,7 @@
 C-CTRL-VERT  </v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" s="7">
         <v>0</v>
       </c>
@@ -24701,7 +24762,7 @@
 C-DFLD  </v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" s="7">
         <v>0</v>
       </c>
@@ -24772,7 +24833,7 @@
 C-DFLD-OTLN  </v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" s="7">
         <v>0</v>
       </c>
@@ -24914,7 +24975,7 @@
 C-DRIV  </v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" s="7">
         <v>0</v>
       </c>
@@ -24985,7 +25046,7 @@
 C-DRIV-ASPH  </v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" s="7">
         <v>0</v>
       </c>
@@ -25056,7 +25117,7 @@
 C-DRIV-CNTR  </v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" s="7">
         <v>0</v>
       </c>
@@ -25127,7 +25188,7 @@
 C-DRIV-CONC  </v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" s="7">
         <v>0</v>
       </c>
@@ -25198,7 +25259,7 @@
 C-DRIV-CURB  </v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" s="7">
         <v>0</v>
       </c>
@@ -25269,7 +25330,7 @@
 C-DRIV-CURB-BACK  </v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="7">
         <v>0</v>
       </c>
@@ -25340,7 +25401,7 @@
 C-DRIV-CURB-FACE  </v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="7">
         <v>0</v>
       </c>
@@ -25411,7 +25472,7 @@
 C-DRIV-FLNE  </v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" s="7">
         <v>0</v>
       </c>
@@ -25482,7 +25543,7 @@
 C-DRIV-FLNE-MRKG  </v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="7">
         <v>0</v>
       </c>
@@ -25553,7 +25614,7 @@
 C-DRIV-FLNE-SIGN  </v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" s="7">
         <v>0</v>
       </c>
@@ -25624,7 +25685,7 @@
 C-DRIV-GRVL  </v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" s="7">
         <v>0</v>
       </c>
@@ -25695,7 +25756,7 @@
 C-DRIV-MRKG  </v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="7">
         <v>0</v>
       </c>
@@ -25766,7 +25827,7 @@
 C-DRIV-SIGN  </v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="7">
         <v>0</v>
       </c>
@@ -25837,7 +25898,7 @@
 C-DRI V-UPVD  </v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="7">
         <v>0</v>
       </c>
@@ -25908,7 +25969,7 @@
 C-DRIV-WHIT  </v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" s="7">
         <v>0</v>
       </c>
@@ -25979,7 +26040,7 @@
 C-DRIV-WHIT-TICK  </v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="7">
         <v>0</v>
       </c>
@@ -26050,7 +26111,7 @@
 C-DRIV-YELO  </v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="7">
         <v>0</v>
       </c>
@@ -26121,7 +26182,7 @@
 C-DRIV-YELO-TICK  </v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="7">
         <v>0</v>
       </c>
@@ -26192,7 +26253,7 @@
 C-DTCH  </v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="7">
         <v>0</v>
       </c>
@@ -26263,7 +26324,7 @@
 C-DTCH-BOTM  </v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" s="7">
         <v>0</v>
       </c>
@@ -26334,7 +26395,7 @@
 C-DTCH-CNTR  </v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" s="7">
         <v>0</v>
       </c>
@@ -26405,7 +26466,7 @@
 C-DTCH-EWAT  </v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" s="7">
         <v>0</v>
       </c>
@@ -26476,7 +26537,7 @@
 C-DTCH-TOP~  </v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="7">
         <v>0</v>
       </c>
@@ -26547,7 +26608,7 @@
 C-EROS  </v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" s="7">
         <v>0</v>
       </c>
@@ -26618,7 +26679,7 @@
 C-EROS-CIPR  </v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" s="7">
         <v>0</v>
       </c>
@@ -26689,7 +26750,7 @@
 C-EROS-CNTE  </v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" s="7">
         <v>0</v>
       </c>
@@ -26760,7 +26821,7 @@
 C-EROS-DDIV  </v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" s="7">
         <v>0</v>
       </c>
@@ -26831,7 +26892,7 @@
 C-EROS-DVDK  </v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" s="7">
         <v>0</v>
       </c>
@@ -26902,7 +26963,7 @@
 C-EROS-INPR  </v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" s="7">
         <v>0</v>
       </c>
@@ -26973,7 +27034,7 @@
 C-EROS-SILT  </v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" s="7">
         <v>0</v>
       </c>
@@ -27115,7 +27176,7 @@
 C-ESMT  </v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" s="7">
         <v>0</v>
       </c>
@@ -27186,7 +27247,7 @@
 C-ESMT-ACCS  </v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" s="7">
         <v>0</v>
       </c>
@@ -27257,7 +27318,7 @@
 C-ESMT-CATV  </v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" s="7">
         <v>0</v>
       </c>
@@ -27328,7 +27389,7 @@
 C-ESMT-CONS  </v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" s="7">
         <v>0</v>
       </c>
@@ -27399,7 +27460,7 @@
 C-ESMT-CSTG  </v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" s="7">
         <v>0</v>
       </c>
@@ -27470,7 +27531,7 @@
 C-ESMT-ELEC  </v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" s="7">
         <v>0</v>
       </c>
@@ -27541,7 +27602,7 @@
 C-ESMT-FDPL  </v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" s="7">
         <v>0</v>
       </c>
@@ -27612,7 +27673,7 @@
 C-ESMT-INEG  </v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" s="7">
         <v>0</v>
       </c>
@@ -27683,7 +27744,7 @@
 C-ESMT-LSCP  </v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" s="7">
         <v>0</v>
       </c>
@@ -27754,7 +27815,7 @@
 C-ESMT-NGAS  </v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" s="7">
         <v>0</v>
       </c>
@@ -27825,7 +27886,7 @@
 C-ESMT-PHON  </v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" s="7">
         <v>0</v>
       </c>
@@ -27896,7 +27957,7 @@
 C-ESMT-ROAD  </v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" s="7">
         <v>0</v>
       </c>
@@ -27967,7 +28028,7 @@
 C-ESMT-ROAD-PERM  </v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" s="7">
         <v>0</v>
       </c>
@@ -28038,7 +28099,7 @@
 C-ESMT-ROAD-TEMP  </v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" s="7">
         <v>0</v>
       </c>
@@ -28109,7 +28170,7 @@
 C-ESMT-RWAY  </v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" s="7">
         <v>0</v>
       </c>
@@ -28180,7 +28241,7 @@
 C-ESMT-SGHT  </v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" s="7">
         <v>0</v>
       </c>
@@ -28251,7 +28312,7 @@
 C-ESMT-SSWR  </v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" s="7">
         <v>0</v>
       </c>
@@ -28322,7 +28383,7 @@
 C-ESMT-STRM  </v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" s="7">
         <v>0</v>
       </c>
@@ -28393,7 +28454,7 @@
 C-ESMT-SWMT  </v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" s="7">
         <v>0</v>
       </c>
@@ -28464,7 +28525,7 @@
 C-ESMT-TRAL  </v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" s="7">
         <v>0</v>
       </c>
@@ -28535,7 +28596,7 @@
 C-ESMT-UTIL  </v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" s="7">
         <v>0</v>
       </c>
@@ -28677,7 +28738,7 @@
 C-FENC  </v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" s="7">
         <v>0</v>
       </c>
@@ -28748,7 +28809,7 @@
 C-FENC-GRAL  </v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" s="7">
         <v>0</v>
       </c>
@@ -28819,7 +28880,7 @@
 C-FENC-POST  </v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" s="7">
         <v>0</v>
       </c>
@@ -28890,7 +28951,7 @@
 C -FENC-STEL  </v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" s="7">
         <v>0</v>
       </c>
@@ -29032,7 +29093,7 @@
 C-FIRE  </v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" s="7">
         <v>0</v>
       </c>
@@ -29103,7 +29164,7 @@
 C-FIRE-HYDT  </v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" s="7">
         <v>0</v>
       </c>
@@ -29174,7 +29235,7 @@
 C-FIRE-PIPE  </v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="7">
         <v>0</v>
       </c>
@@ -29245,7 +29306,7 @@
 C-FIRE-UGND  </v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" s="7">
         <v>0</v>
       </c>
@@ -29316,7 +29377,7 @@
 C-FLHA  </v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" s="7">
         <v>0</v>
       </c>
@@ -29387,7 +29448,7 @@
 C-FLHA-025Y  </v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" s="7">
         <v>0</v>
       </c>
@@ -29458,7 +29519,7 @@
 C-FLHA-050Y  </v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" s="7">
         <v>0</v>
       </c>
@@ -29529,7 +29590,7 @@
 C-FLHA-100Y  </v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" s="7">
         <v>0</v>
       </c>
@@ -29600,7 +29661,7 @@
 C-FLHA-200Y  </v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" s="7">
         <v>0</v>
       </c>
@@ -29671,7 +29732,7 @@
 C-FUEL  </v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" s="7">
         <v>0</v>
       </c>
@@ -29742,7 +29803,7 @@
 C-FUEL-EQPM  </v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" s="7">
         <v>0</v>
       </c>
@@ -29813,7 +29874,7 @@
 C-FUEL-INST  </v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" s="7">
         <v>0</v>
       </c>
@@ -29884,7 +29945,7 @@
 C-FUEL-MHOL  </v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" s="7">
         <v>0</v>
       </c>
@@ -29955,7 +30016,7 @@
 C-FUEL-PIPE  </v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" s="7">
         <v>0</v>
       </c>
@@ -30026,7 +30087,7 @@
 C-FUEL-TANK  </v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" s="7">
         <v>0</v>
       </c>
@@ -30097,7 +30158,7 @@
 C-FUEL-UGND  </v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" s="7">
         <v>0</v>
       </c>
@@ -30168,7 +30229,7 @@
 C-HYDR  </v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" s="7">
         <v>0</v>
       </c>
@@ -30239,7 +30300,7 @@
 C-HYDR-BAFL  </v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" s="7">
         <v>0</v>
       </c>
@@ -30310,7 +30371,7 @@
 C-HYDR-BASN  </v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" s="7">
         <v>0</v>
       </c>
@@ -30381,7 +30442,7 @@
 C-HYDR-CNDT  </v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" s="7">
         <v>0</v>
       </c>
@@ -30452,7 +30513,7 @@
 C-HYDR-COFF  </v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" s="7">
         <v>0</v>
       </c>
@@ -30523,7 +30584,7 @@
 C-HYDR-DAM~  </v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" s="7">
         <v>0</v>
       </c>
@@ -30594,7 +30655,7 @@
 C-HYDR-FISH  </v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" s="7">
         <v>0</v>
       </c>
@@ -30665,7 +30726,7 @@
 C-HYDR-FLUM  </v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" s="7">
         <v>0</v>
       </c>
@@ -30736,7 +30797,7 @@
 C-HYDR-INTK  </v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" s="7">
         <v>0</v>
       </c>
@@ -30807,7 +30868,7 @@
 C-HYDR-NOVR  </v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" s="7">
         <v>0</v>
       </c>
@@ -30878,7 +30939,7 @@
 C-HYDR-PENS  </v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" s="7">
         <v>0</v>
       </c>
@@ -31020,7 +31081,7 @@
 C-NGAS  </v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" s="7">
         <v>0</v>
       </c>
@@ -31091,7 +31152,7 @@
 C-NGAS-EQPM  </v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" s="7">
         <v>0</v>
       </c>
@@ -31162,7 +31223,7 @@
 C-NGAS-INST  </v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" s="7">
         <v>0</v>
       </c>
@@ -31233,7 +31294,7 @@
 C-NGAS-MHOL  </v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" s="7">
         <v>0</v>
       </c>
@@ -31304,7 +31365,7 @@
 C-NGAS-PIPE  </v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" s="7">
         <v>0</v>
       </c>
@@ -31375,7 +31436,7 @@
 C-NGAS-TANK  </v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" s="7">
         <v>0</v>
       </c>
@@ -31446,7 +31507,7 @@
 C-NGAS-UGND  </v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" s="7">
         <v>0</v>
       </c>
@@ -31517,7 +31578,7 @@
 C-PERC  </v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" s="7">
         <v>0</v>
       </c>
@@ -31588,7 +31649,7 @@
 C-PERC-HOLE  </v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" s="7">
         <v>0</v>
       </c>
@@ -31659,7 +31720,7 @@
 C-POND  </v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" s="7">
         <v>0</v>
       </c>
@@ -31730,7 +31791,7 @@
 C-POND-EDGE  </v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" s="7">
         <v>0</v>
       </c>
@@ -31801,7 +31862,7 @@
 C-POND-SWAY  </v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" s="7">
         <v>0</v>
       </c>
@@ -31943,7 +32004,7 @@
 C-POWR  </v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" s="7">
         <v>0</v>
       </c>
@@ -32014,7 +32075,7 @@
 C-POWR-FENC  </v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" s="7">
         <v>0</v>
       </c>
@@ -32085,7 +32146,7 @@
 C-POWR-INST  </v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" s="7">
         <v>0</v>
       </c>
@@ -32156,7 +32217,7 @@
 C-POWR-MHOL  </v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" s="7">
         <v>0</v>
       </c>
@@ -32227,7 +32288,7 @@
 C-POWR-OVHD  </v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" s="7">
         <v>0</v>
       </c>
@@ -32298,7 +32359,7 @@
 C-POWR-POLE  </v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" s="7">
         <v>0</v>
       </c>
@@ -32369,7 +32430,7 @@
 C-POWR-STRC  </v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" s="7">
         <v>0</v>
       </c>
@@ -32440,7 +32501,7 @@
 C-POWR-UGND  </v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" s="7">
         <v>0</v>
       </c>
@@ -32511,7 +32572,7 @@
 C-PRKG  </v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" s="7">
         <v>0</v>
       </c>
@@ -32582,7 +32643,7 @@
 C-PRKG-ASPH  </v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" s="7">
         <v>0</v>
       </c>
@@ -32653,7 +32714,7 @@
 C-PRKG-CARS  </v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" s="7">
         <v>0</v>
       </c>
@@ -32724,7 +32785,7 @@
 C-PRKG-CONC  </v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" s="7">
         <v>0</v>
       </c>
@@ -32795,7 +32856,7 @@
 C-PRKG-CURB  </v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" s="7">
         <v>0</v>
       </c>
@@ -32866,7 +32927,7 @@
 C-PRKG-CURB-BACK  </v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" s="7">
         <v>0</v>
       </c>
@@ -32937,7 +32998,7 @@
 C-PRKG-CURB-FACE  </v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" s="7">
         <v>0</v>
       </c>
@@ -33008,7 +33069,7 @@
 C-PRKG-DRAN  </v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" s="7">
         <v>0</v>
       </c>
@@ -33079,7 +33140,7 @@
 C-PRKG-FIXT  </v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" s="7">
         <v>0</v>
       </c>
@@ -33150,7 +33211,7 @@
 C-PRKG-FLNE  </v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" s="7">
         <v>0</v>
       </c>
@@ -33221,7 +33282,7 @@
 C-PRKG-FLNE-MRKG  </v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" s="7">
         <v>0</v>
       </c>
@@ -33292,7 +33353,7 @@
 C-PRKG-FLNE-SIGN  </v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" s="7">
         <v>0</v>
       </c>
@@ -33363,7 +33424,7 @@
 C-PRKG-GRVL  </v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" s="7">
         <v>0</v>
       </c>
@@ -33434,7 +33495,7 @@
 C-PRKG-MRKG  </v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" s="7">
         <v>0</v>
       </c>
@@ -33505,7 +33566,7 @@
 C-PRKG-SIGN  </v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" s="7">
         <v>0</v>
       </c>
@@ -33576,7 +33637,7 @@
 C-PRKG-STRP  </v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" s="7">
         <v>0</v>
       </c>
@@ -33647,7 +33708,7 @@
 C-PRKG-UPVD  </v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" s="7">
         <v>0</v>
       </c>
@@ -33718,7 +33779,7 @@
 C-PRKG-WHIT  </v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" s="7">
         <v>0</v>
       </c>
@@ -33789,7 +33850,7 @@
 C-PRKG-WHIT-TICK  </v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" s="7">
         <v>0</v>
       </c>
@@ -33860,7 +33921,7 @@
 C-PRKG-YELO  </v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" s="7">
         <v>0</v>
       </c>
@@ -34002,7 +34063,7 @@
 C-PROP  </v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" s="7">
         <v>0</v>
       </c>
@@ -34073,7 +34134,7 @@
 C-PROP-LINE  </v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" s="7">
         <v>0</v>
       </c>
@@ -34144,7 +34205,7 @@
 C-PROP-SBCK  </v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" s="7">
         <v>0</v>
       </c>
@@ -34215,7 +34276,7 @@
 C-PVMT  </v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" s="7">
         <v>0</v>
       </c>
@@ -34286,7 +34347,7 @@
 C-PVMT-ASPH  </v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" s="7">
         <v>0</v>
       </c>
@@ -34357,7 +34418,7 @@
 C-PVMT-CONC  </v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" s="7">
         <v>0</v>
       </c>
@@ -34428,7 +34489,7 @@
 C-PVMT-GRVL  </v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" s="7">
         <v>0</v>
       </c>
@@ -34499,7 +34560,7 @@
 C-RAIL  </v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" s="7">
         <v>0</v>
       </c>
@@ -34570,7 +34631,7 @@
 C-RAIL-CNTR  </v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" s="7">
         <v>0</v>
       </c>
@@ -34641,7 +34702,7 @@
 C-RAIL-EQPM  </v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" s="7">
         <v>0</v>
       </c>
@@ -34783,7 +34844,7 @@
 C-RIVR  </v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" s="7">
         <v>0</v>
       </c>
@@ -34854,7 +34915,7 @@
 C-RIVR-BOTM  </v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" s="7">
         <v>0</v>
       </c>
@@ -34925,7 +34986,7 @@
 C-RIVR-CNTR  </v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" s="7">
         <v>0</v>
       </c>
@@ -34996,7 +35057,7 @@
 C-RIVR-EDGE  </v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" s="7">
         <v>0</v>
       </c>
@@ -35138,7 +35199,7 @@
 C-ROAD  </v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" s="7">
         <v>0</v>
       </c>
@@ -35209,7 +35270,7 @@
 C-ROAD-ASPH  </v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" s="7">
         <v>0</v>
       </c>
@@ -35280,7 +35341,7 @@
 C-ROAD-CNTR  </v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283" s="7">
         <v>0</v>
       </c>
@@ -35351,7 +35412,7 @@
 C-ROAD-CONC  </v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" s="7">
         <v>0</v>
       </c>
@@ -35422,7 +35483,7 @@
 C-ROAD-CURB  </v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" s="7">
         <v>0</v>
       </c>
@@ -35493,7 +35554,7 @@
 C-ROAD-CURB-BACK  </v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" s="7">
         <v>0</v>
       </c>
@@ -35564,7 +35625,7 @@
 C-ROAD-CURB-FACE  </v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" s="7">
         <v>0</v>
       </c>
@@ -35635,7 +35696,7 @@
 C-ROAD-FLNE  </v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" s="7">
         <v>0</v>
       </c>
@@ -35706,7 +35767,7 @@
 C-ROAD-FLNE-MRKG  </v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289" s="7">
         <v>0</v>
       </c>
@@ -35777,7 +35838,7 @@
 C-ROAD-FLNE-SIGN  </v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" s="7">
         <v>0</v>
       </c>
@@ -35848,7 +35909,7 @@
 C-ROAD-GRVL  </v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" s="7">
         <v>0</v>
       </c>
@@ -35919,7 +35980,7 @@
 C-ROAD-MRKG  </v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" s="7">
         <v>0</v>
       </c>
@@ -35990,7 +36051,7 @@
 C-ROAD-PROF  </v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" s="7">
         <v>0</v>
       </c>
@@ -36061,7 +36122,7 @@
 C-ROAD-SIGN  </v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294" s="7">
         <v>0</v>
       </c>
@@ -36132,7 +36193,7 @@
 C-ROAD-STAN  </v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" s="7">
         <v>0</v>
       </c>
@@ -36203,7 +36264,7 @@
 C-ROAD-UPVD  </v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" s="7">
         <v>0</v>
       </c>
@@ -36274,7 +36335,7 @@
 C-ROAD-WHIT  </v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" s="7">
         <v>0</v>
       </c>
@@ -36345,7 +36406,7 @@
 C-ROAD-WHIT-TICK  </v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" s="7">
         <v>0</v>
       </c>
@@ -36416,7 +36477,7 @@
 C-ROAD-YELO  </v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" s="7">
         <v>0</v>
       </c>
@@ -36487,7 +36548,7 @@
 C-ROAD-YELO-TICK  </v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" s="7">
         <v>0</v>
       </c>
@@ -36558,7 +36619,7 @@
 C-RRAP  </v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" s="7">
         <v>0</v>
       </c>
@@ -36629,7 +36690,7 @@
 C-SGHT  </v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" s="7">
         <v>0</v>
       </c>
@@ -36842,7 +36903,7 @@
 C-SSWR  </v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" s="7">
         <v>0</v>
       </c>
@@ -36913,7 +36974,7 @@
 C-SSWR-DIAG  </v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" s="7">
         <v>0</v>
       </c>
@@ -36984,7 +37045,7 @@
 C-SSWR-FORC  </v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" s="7">
         <v>0</v>
       </c>
@@ -37055,7 +37116,7 @@
 C-SSWR-LATL  </v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" s="7">
         <v>0</v>
       </c>
@@ -37126,7 +37187,7 @@
 C-SSWR-MHOL  </v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" s="7">
         <v>0</v>
       </c>
@@ -37197,7 +37258,7 @@
 C-SSWR-PIPE  </v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" s="7">
         <v>0</v>
       </c>
@@ -37268,7 +37329,7 @@
 C-SSWR-PIPE-RCON  </v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" s="7">
         <v>0</v>
       </c>
@@ -37339,7 +37400,7 @@
 C-SSWR-PIPE-STEL  </v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" s="7">
         <v>0</v>
       </c>
@@ -37410,7 +37471,7 @@
 C-SSWR-PROF  </v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" s="7">
         <v>0</v>
       </c>
@@ -37481,7 +37542,7 @@
 C-SSWR-STAN  </v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" s="7">
         <v>0</v>
       </c>
@@ -37552,7 +37613,7 @@
 C-SSWR-STRC  </v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" s="7">
         <v>0</v>
       </c>
@@ -37623,7 +37684,7 @@
 C-SSWR-UGND  </v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" s="7">
         <v>0</v>
       </c>
@@ -37694,7 +37755,7 @@
 C-STEM  </v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" s="7">
         <v>0</v>
       </c>
@@ -37765,7 +37826,7 @@
 C-STEM-INST  </v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" s="7">
         <v>0</v>
       </c>
@@ -37836,7 +37897,7 @@
 C-STEM-MHOL  </v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" s="7">
         <v>0</v>
       </c>
@@ -37907,7 +37968,7 @@
 C-STEM-PIPE  </v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" s="7">
         <v>0</v>
       </c>
@@ -37978,7 +38039,7 @@
 C-STEM-STRC  </v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" s="7">
         <v>0</v>
       </c>
@@ -38120,7 +38181,7 @@
 C-STRM  </v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" s="7">
         <v>0</v>
       </c>
@@ -38191,7 +38252,7 @@
 C-STRM-CNTR  </v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" s="7">
         <v>0</v>
       </c>
@@ -38262,7 +38323,7 @@
 C-STRM-DIAG  </v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" s="7">
         <v>0</v>
       </c>
@@ -38333,7 +38394,7 @@
 C-STRM-HWAL  </v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" s="7">
         <v>0</v>
       </c>
@@ -38404,7 +38465,7 @@
 C-STRM-MHOL  </v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" s="7">
         <v>0</v>
       </c>
@@ -38475,7 +38536,7 @@
 C-STRM-PIPE  </v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" s="7">
         <v>0</v>
       </c>
@@ -38546,7 +38607,7 @@
 C-STRM-PIPE-CMTL  </v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" s="7">
         <v>0</v>
       </c>
@@ -38617,7 +38678,7 @@
 C-STRM-PIPE-RCON  </v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" s="7">
         <v>0</v>
       </c>
@@ -38688,7 +38749,7 @@
 C-STRM-PROF  </v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" s="7">
         <v>0</v>
       </c>
@@ -38759,7 +38820,7 @@
 C-STRM-STAN  </v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" s="7">
         <v>0</v>
       </c>
@@ -38830,7 +38891,7 @@
 C-STRM-STRC  </v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" s="7">
         <v>0</v>
       </c>
@@ -38972,7 +39033,7 @@
 C-SWLK  </v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" s="7">
         <v>0</v>
       </c>
@@ -39043,7 +39104,7 @@
 C-SWLK-ASPH  </v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" s="7">
         <v>0</v>
       </c>
@@ -39185,7 +39246,7 @@
 C-TINN  </v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" s="7">
         <v>0</v>
       </c>
@@ -39256,7 +39317,7 @@
 C-TINN-BNDY  </v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" s="7">
         <v>0</v>
       </c>
@@ -39327,7 +39388,7 @@
 C-TINN-FALT  </v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340" s="7">
         <v>0</v>
       </c>
@@ -39398,7 +39459,7 @@
 C-TINN-VIEW  </v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" s="7">
         <v>0</v>
       </c>
@@ -39540,7 +39601,7 @@
 C-TOPO  </v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" s="7">
         <v>0</v>
       </c>
@@ -39611,7 +39672,7 @@
 C-TOPO-DEPR  </v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" s="7">
         <v>0</v>
       </c>
@@ -39682,7 +39743,7 @@
 C-TOPO-MAJR  </v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345" s="7">
         <v>0</v>
       </c>
@@ -39753,7 +39814,7 @@
 C-TOPO-MINR  </v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" s="7">
         <v>0</v>
       </c>
@@ -39824,7 +39885,7 @@
 C-TOPO-SPOT  </v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" s="7">
         <v>0</v>
       </c>
@@ -39966,7 +40027,7 @@
 C-TRAL  </v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" s="7">
         <v>0</v>
       </c>
@@ -40037,7 +40098,7 @@
 C-TRAL-ASPH  </v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" s="7">
         <v>0</v>
       </c>
@@ -40108,7 +40169,7 @@
 C-TRAL-CONC  </v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" s="7">
         <v>0</v>
       </c>
@@ -40179,7 +40240,7 @@
 C-TRAL-GRVL  </v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352" s="7">
         <v>0</v>
       </c>
@@ -40250,7 +40311,7 @@
 C-TRAL-MRKG  </v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" s="7">
         <v>0</v>
       </c>
@@ -40321,7 +40382,7 @@
 C-TRAL-SIGN  </v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" s="7">
         <v>0</v>
       </c>
@@ -40463,7 +40524,7 @@
 C-WALL  </v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" s="7">
         <v>0</v>
       </c>
@@ -40534,7 +40595,7 @@
 C-WALL-CTLJ  </v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" s="7">
         <v>0</v>
       </c>
@@ -40605,7 +40666,7 @@
 C-WALL-NSBR  </v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" s="7">
         <v>0</v>
       </c>
@@ -40676,7 +40737,7 @@
 C-WALL-RTWL  </v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" s="7">
         <v>0</v>
       </c>
@@ -40818,7 +40879,7 @@
 C-WATR  </v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" s="7">
         <v>0</v>
       </c>
@@ -40889,7 +40950,7 @@
 C-WATR-DIAG  </v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" s="7">
         <v>0</v>
       </c>
@@ -40960,7 +41021,7 @@
 C-WATR-INST  </v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" s="7">
         <v>0</v>
       </c>
@@ -41031,7 +41092,7 @@
 C-WATR-PIPE  </v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" s="7">
         <v>0</v>
       </c>
@@ -41102,7 +41163,7 @@
 C-WATR-PROF  </v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" s="7">
         <v>0</v>
       </c>
@@ -41173,7 +41234,7 @@
 C-WATR-STAN  </v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" s="7">
         <v>0</v>
       </c>
@@ -41244,7 +41305,7 @@
 C-WATR-STRC  </v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" s="7">
         <v>0</v>
       </c>
@@ -41315,7 +41376,7 @@
 C-WATR-UGND  </v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" s="7">
         <v>0</v>
       </c>
@@ -41386,7 +41447,7 @@
 C-WATR-WELL  </v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" s="7">
         <v>0</v>
       </c>
@@ -41457,7 +41518,7 @@
 C-WETL  </v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" s="7">
         <v>0</v>
       </c>
@@ -41528,7 +41589,7 @@
 C-WWAY  </v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" s="7">
         <v>0</v>
       </c>
@@ -41599,7 +41660,7 @@
 C-WWAY-DLPH  </v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" s="7">
         <v>0</v>
       </c>
@@ -41670,7 +41731,7 @@
 C-WWAY-FEND  </v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" s="7">
         <v>0</v>
       </c>
@@ -41741,7 +41802,7 @@
 C-WWAY-MOOR  </v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" s="7">
         <v>0</v>
       </c>
@@ -41883,7 +41944,7 @@
 E-AREA  </v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" s="7">
         <v>0</v>
       </c>
@@ -41954,7 +42015,7 @@
 E-AREA-OFST  </v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" s="7">
         <v>0</v>
       </c>
@@ -42096,7 +42157,7 @@
 E-AUXL  </v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" s="7">
         <v>0</v>
       </c>
@@ -42238,7 +42299,7 @@
 E-CABL  </v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" s="7">
         <v>0</v>
       </c>
@@ -42309,7 +42370,7 @@
 E-CABL-COAX  </v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382" s="7">
         <v>0</v>
       </c>
@@ -42380,7 +42441,7 @@
 E-CABL-FIBR  </v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" s="7">
         <v>0</v>
       </c>
@@ -42451,7 +42512,7 @@
 E-CABL-MULT  </v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" s="7">
         <v>0</v>
       </c>
@@ -42522,7 +42583,7 @@
 E-CABL-TRAY  </v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385" s="7">
         <v>0</v>
       </c>
@@ -42593,7 +42654,7 @@
 E-CATH  </v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" s="7">
         <v>0</v>
       </c>
@@ -42664,7 +42725,7 @@
 E-CATH-ANOD  </v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" s="7">
         <v>0</v>
       </c>
@@ -42735,7 +42796,7 @@
 E-CATH-CURR  </v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" s="7">
         <v>0</v>
       </c>
@@ -42806,7 +42867,7 @@
 E-CATH-TEST  </v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389" s="7">
         <v>0</v>
       </c>
@@ -42877,7 +42938,7 @@
 E-CCTV  </v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390" s="7">
         <v>0</v>
       </c>
@@ -42948,7 +43009,7 @@
 E-CLOK  </v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" s="7">
         <v>0</v>
       </c>
@@ -43019,7 +43080,7 @@
 E-CLOK-CIRC  </v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" s="7">
         <v>0</v>
       </c>
@@ -43090,7 +43151,7 @@
 E-CLOK-CLNG  </v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" s="7">
         <v>0</v>
       </c>
@@ -43161,7 +43222,7 @@
 E-CLOK-CNMB  </v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" s="7">
         <v>0</v>
       </c>
@@ -43232,7 +43293,7 @@
 E-CLOK-EQPM  </v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" s="7">
         <v>0</v>
       </c>
@@ -43303,7 +43364,7 @@
 E-CLOK-FLOR  </v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" s="7">
         <v>0</v>
       </c>
@@ -43374,7 +43435,7 @@
 E-CLOK-WALL  </v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" s="7">
         <v>0</v>
       </c>
@@ -43445,7 +43506,7 @@
 E-COMM  </v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" s="7">
         <v>0</v>
       </c>
@@ -43516,7 +43577,7 @@
 E-COMM-CIRC  </v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" s="7">
         <v>0</v>
       </c>
@@ -43587,7 +43648,7 @@
 E-COMM-CLNG  </v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" s="7">
         <v>0</v>
       </c>
@@ -43658,7 +43719,7 @@
 E-COMM-CNMB  </v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" s="7">
         <v>0</v>
       </c>
@@ -43729,7 +43790,7 @@
 E-COMM-EQPM  </v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" s="7">
         <v>0</v>
       </c>
@@ -43871,7 +43932,7 @@
 E-CONT  </v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" s="7">
         <v>0</v>
       </c>
@@ -43942,7 +44003,7 @@
 E-CONT DEVC  </v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" s="7">
         <v>0</v>
       </c>
@@ -44013,7 +44074,7 @@
 E-CONT-WIRE  </v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" s="7">
         <v>0</v>
       </c>
@@ -44084,7 +44145,7 @@
 E-DATA  </v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" s="7">
         <v>0</v>
       </c>
@@ -44155,7 +44216,7 @@
 E-DATA-CIRC  </v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" s="7">
         <v>0</v>
       </c>
@@ -44226,7 +44287,7 @@
 E-DATA-CLNG  </v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" s="7">
         <v>0</v>
       </c>
@@ -44297,7 +44358,7 @@
 E-DATA-CNMB  </v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" s="7">
         <v>0</v>
       </c>
@@ -44368,7 +44429,7 @@
 E-DATA-EQPM  </v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" s="7">
         <v>0</v>
       </c>
@@ -44439,7 +44500,7 @@
 E-DATA-FLOR  </v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" s="7">
         <v>0</v>
       </c>
@@ -44581,7 +44642,7 @@
 E-DIAG  </v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" s="7">
         <v>0</v>
       </c>
@@ -44652,7 +44713,7 @@
 E-DIAG-BKRS  </v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" s="7">
         <v>0</v>
       </c>
@@ -44723,7 +44784,7 @@
 E-DIAG-BUSS  </v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" s="7">
         <v>0</v>
       </c>
@@ -44794,7 +44855,7 @@
 E-DIAG-ENCL  </v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" s="7">
         <v>0</v>
       </c>
@@ -44865,7 +44926,7 @@
 E-DIAG-EQPM  </v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" s="7">
         <v>0</v>
       </c>
@@ -44936,7 +44997,7 @@
 E-DIAG-FEED  </v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" s="7">
         <v>0</v>
       </c>
@@ -45007,7 +45068,7 @@
 E-DIAG-FLOR  </v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" s="7">
         <v>0</v>
       </c>
@@ -45078,7 +45139,7 @@
 E-DIAG-GRND  </v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" s="7">
         <v>0</v>
       </c>
@@ -45149,7 +45210,7 @@
 E-DIAG-SWCH  </v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" s="7">
         <v>0</v>
       </c>
@@ -45220,7 +45281,7 @@
 E-DIAG-XFMR  </v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" s="7">
         <v>0</v>
       </c>
@@ -45291,7 +45352,7 @@
 E-DICT  </v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" s="7">
         <v>0</v>
       </c>
@@ -45362,7 +45423,7 @@
 E-DICT-CIRC  </v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" s="7">
         <v>0</v>
       </c>
@@ -45433,7 +45494,7 @@
 E-DICT-CLNG  </v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" s="7">
         <v>0</v>
       </c>
@@ -45504,7 +45565,7 @@
 E-DICT-CNMB  </v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427" s="7">
         <v>0</v>
       </c>
@@ -45575,7 +45636,7 @@
 E-DICT-EQPM  </v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" s="7">
         <v>0</v>
       </c>
@@ -45717,7 +45778,7 @@
 E-FIRE  </v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" s="7">
         <v>0</v>
       </c>
@@ -45788,7 +45849,7 @@
 E-FIRE-BARR  </v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" s="7">
         <v>0</v>
       </c>
@@ -45859,7 +45920,7 @@
 E-FIRE-CIRC  </v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" s="7">
         <v>0</v>
       </c>
@@ -45930,7 +45991,7 @@
 E-FIRE-CLNG  </v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" s="7">
         <v>0</v>
       </c>
@@ -46001,7 +46062,7 @@
 E-FIRE-CNMB  </v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" s="7">
         <v>0</v>
       </c>
@@ -46072,7 +46133,7 @@
 E-FIRE-EQPM  </v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" s="7">
         <v>0</v>
       </c>
@@ -46214,7 +46275,7 @@
 E-GRND  </v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" s="7">
         <v>0</v>
       </c>
@@ -46285,7 +46346,7 @@
 E-GRND-CIRC  </v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" s="7">
         <v>0</v>
       </c>
@@ -46356,7 +46417,7 @@
 E-GRND-CLNG  </v>
       </c>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" s="7">
         <v>0</v>
       </c>
@@ -46427,7 +46488,7 @@
 E-GRND-CNMB  </v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" s="7">
         <v>0</v>
       </c>
@@ -46498,7 +46559,7 @@
 E-GRND-DIAG  </v>
       </c>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" s="7">
         <v>0</v>
       </c>
@@ -46569,7 +46630,7 @@
 E-GRND-EQPM  </v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" s="7">
         <v>0</v>
       </c>
@@ -46640,7 +46701,7 @@
 E-GRND-EQUI  </v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" s="7">
         <v>0</v>
       </c>
@@ -46782,7 +46843,7 @@
 E-INST  </v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" s="7">
         <v>0</v>
       </c>
@@ -46853,7 +46914,7 @@
 E-INST-CIRC  </v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" s="7">
         <v>0</v>
       </c>
@@ -46924,7 +46985,7 @@
 E-INST-CLNG  </v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" s="7">
         <v>0</v>
       </c>
@@ -46995,7 +47056,7 @@
 E-INST-CNMB  </v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" s="7">
         <v>0</v>
       </c>
@@ -47066,7 +47127,7 @@
 E-INST-EQPM  </v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" s="7">
         <v>0</v>
       </c>
@@ -47137,7 +47198,7 @@
 E-INST-WALL  </v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" s="7">
         <v>0</v>
       </c>
@@ -47279,7 +47340,7 @@
 E-LITE  </v>
       </c>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" s="7">
         <v>0</v>
       </c>
@@ -47350,7 +47411,7 @@
 E-LITE-CIRC  </v>
       </c>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" s="7">
         <v>0</v>
       </c>
@@ -47421,7 +47482,7 @@
 E-LITE-CIRC-CRIT  </v>
       </c>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" s="7">
         <v>0</v>
       </c>
@@ -47492,7 +47553,7 @@
 E-LITE-CIRC-EMER  </v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" s="7">
         <v>0</v>
       </c>
@@ -47563,7 +47624,7 @@
 E-LITE-CLNG  </v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" s="7">
         <v>0</v>
       </c>
@@ -47634,7 +47695,7 @@
 E-LITE-CLNG-CRIT  </v>
       </c>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" s="7">
         <v>0</v>
       </c>
@@ -47705,7 +47766,7 @@
 E-LITE-CLNG-EMER  </v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" s="7">
         <v>0</v>
       </c>
@@ -47776,7 +47837,7 @@
 E-LITE-CLNG-EXIT  </v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" s="7">
         <v>0</v>
       </c>
@@ -47847,7 +47908,7 @@
 E-LITE-CNMB  </v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" s="7">
         <v>0</v>
       </c>
@@ -47918,7 +47979,7 @@
 E-LITE-CNMB-CRIT  </v>
       </c>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" s="7">
         <v>0</v>
       </c>
@@ -47989,7 +48050,7 @@
 E-LITE-CNMB-EMER  </v>
       </c>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" s="7">
         <v>0</v>
       </c>
@@ -48060,7 +48121,7 @@
 E-LITE-EMER  </v>
       </c>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" s="7">
         <v>0</v>
       </c>
@@ -48131,7 +48192,7 @@
 E-LITE-EQPM  </v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" s="7">
         <v>0</v>
       </c>
@@ -48202,7 +48263,7 @@
 E-LITE-EQPM-CRIT  </v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465" s="7">
         <v>0</v>
       </c>
@@ -48273,7 +48334,7 @@
 E-LITE-EQPM-EMER  </v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A466" s="7">
         <v>0</v>
       </c>
@@ -48344,7 +48405,7 @@
 E-LITE-EXIT  </v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" s="7">
         <v>0</v>
       </c>
@@ -48415,7 +48476,7 @@
 E-LITE-EXTR  </v>
       </c>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468" s="7">
         <v>0</v>
       </c>
@@ -48486,7 +48547,7 @@
 E-LITE-FLOR  </v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" s="7">
         <v>0</v>
       </c>
@@ -48557,7 +48618,7 @@
 E-LITE-JBOX  </v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" s="7">
         <v>0</v>
       </c>
@@ -48628,7 +48689,7 @@
 E-LITE-OTLN  </v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" s="7">
         <v>0</v>
       </c>
@@ -48699,7 +48760,7 @@
 E-LITE-ROOF  </v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" s="7">
         <v>0</v>
       </c>
@@ -48770,7 +48831,7 @@
 E-LITE-SPCL  </v>
       </c>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" s="7">
         <v>0</v>
       </c>
@@ -48841,7 +48902,7 @@
 E-LITE-SWCH  </v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" s="7">
         <v>0</v>
       </c>
@@ -48912,7 +48973,7 @@
 E-LITE-SWCH-CRIT  </v>
       </c>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475" s="7">
         <v>0</v>
       </c>
@@ -48983,7 +49044,7 @@
 E-LITE-SWCH-EMER  </v>
       </c>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A476" s="7">
         <v>0</v>
       </c>
@@ -49054,7 +49115,7 @@
 E-LITE-WALL  </v>
       </c>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A477" s="7">
         <v>0</v>
       </c>
@@ -49125,7 +49186,7 @@
 E-LITE-WALL-CRIT  </v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A478" s="7">
         <v>0</v>
       </c>
@@ -49196,7 +49257,7 @@
 E-LITE-WALL-EMER  </v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" s="7">
         <v>0</v>
       </c>
@@ -49338,7 +49399,7 @@
 E-LTNG  </v>
       </c>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" s="7">
         <v>0</v>
       </c>
@@ -49409,7 +49470,7 @@
 E-LTNG-CIRC  </v>
       </c>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482" s="7">
         <v>0</v>
       </c>
@@ -49480,7 +49541,7 @@
 E-LTNG-CLNG  </v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" s="7">
         <v>0</v>
       </c>
@@ -49551,7 +49612,7 @@
 E-LTNG-CNMB  </v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" s="7">
         <v>0</v>
       </c>
@@ -49622,7 +49683,7 @@
 E-LTNG-EQPM  </v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485" s="7">
         <v>0</v>
       </c>
@@ -49693,7 +49754,7 @@
 E-LTNG-WALL  </v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486" s="7">
         <v>0</v>
       </c>
@@ -49764,7 +49825,7 @@
 E-MNTG  </v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" s="7">
         <v>0</v>
       </c>
@@ -49835,7 +49896,7 @@
 E-NURS  </v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488" s="7">
         <v>0</v>
       </c>
@@ -49906,7 +49967,7 @@
 E-NURS-CIRC  </v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" s="7">
         <v>0</v>
       </c>
@@ -49977,7 +50038,7 @@
 E-NURS-CLNG  </v>
       </c>
     </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" s="7">
         <v>0</v>
       </c>
@@ -50048,7 +50109,7 @@
 E-NURS-CNMB  </v>
       </c>
     </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491" s="7">
         <v>0</v>
       </c>
@@ -50119,7 +50180,7 @@
 E-NURS-EQPM  </v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492" s="7">
         <v>0</v>
       </c>
@@ -50190,7 +50251,7 @@
 E-NURS-FLOR  </v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493" s="7">
         <v>0</v>
       </c>
@@ -50261,7 +50322,7 @@
 E-NURS-WALL  </v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A494" s="7">
         <v>0</v>
       </c>
@@ -50332,7 +50393,7 @@
 E-OBST  </v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" s="7">
         <v>0</v>
       </c>
@@ -50474,7 +50535,7 @@
 E-POWR  </v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" s="7">
         <v>0</v>
       </c>
@@ -50545,7 +50606,7 @@
 E-POWR-BUSW  </v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" s="7">
         <v>0</v>
       </c>
@@ -50616,7 +50677,7 @@
 E-POWR-CABL  </v>
       </c>
     </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499" s="7">
         <v>0</v>
       </c>
@@ -50687,7 +50748,7 @@
 E-POWR-CBOX  </v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" s="7">
         <v>0</v>
       </c>
@@ -50758,7 +50819,7 @@
 E-POWR-CBOX-FTPT  </v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501" s="7">
         <v>0</v>
       </c>
@@ -50829,7 +50890,7 @@
 E-POWR-CIRC  </v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" s="7">
         <v>0</v>
       </c>
@@ -50900,7 +50961,7 @@
 E-POWR-CIRC-CRIT  </v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" s="7">
         <v>0</v>
       </c>
@@ -50971,7 +51032,7 @@
 E-POWR-CLNG  </v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504" s="7">
         <v>0</v>
       </c>
@@ -51042,7 +51103,7 @@
 E-POWR-CLNG-CRIT  </v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" s="7">
         <v>0</v>
       </c>
@@ -51113,7 +51174,7 @@
 E-POWR-CNDT  </v>
       </c>
     </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506" s="7">
         <v>0</v>
       </c>
@@ -51184,7 +51245,7 @@
 E-POWR-CNMB  </v>
       </c>
     </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507" s="7">
         <v>0</v>
       </c>
@@ -51255,7 +51316,7 @@
 E-POWR-CNMB-CRIT  </v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" s="7">
         <v>0</v>
       </c>
@@ -51326,7 +51387,7 @@
 E-POWR-DEVC  </v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" s="7">
         <v>0</v>
       </c>
@@ -51397,7 +51458,7 @@
 E-POWR-DSCO  </v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510" s="7">
         <v>0</v>
       </c>
@@ -51468,7 +51529,7 @@
 E-POWR-DSCO-ACFU  </v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511" s="7">
         <v>0</v>
       </c>
@@ -51539,7 +51600,7 @@
 E-POWR-DSCO-ACNF  </v>
       </c>
     </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512" s="7">
         <v>0</v>
       </c>
@@ -51610,7 +51671,7 @@
 E-POWR-DSCO-DCFU  </v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513" s="7">
         <v>0</v>
       </c>
@@ -51681,7 +51742,7 @@
 E-POWR-DSCO-DCNF  </v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" s="7">
         <v>0</v>
       </c>
@@ -51752,7 +51813,7 @@
 E-POWR-EQPM  </v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" s="7">
         <v>0</v>
       </c>
@@ -51823,7 +51884,7 @@
 E-POWR-EQPM-CRIT  </v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" s="7">
         <v>0</v>
       </c>
@@ -51894,7 +51955,7 @@
 E-POWR-EXTR  </v>
       </c>
     </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" s="7">
         <v>0</v>
       </c>
@@ -51965,7 +52026,7 @@
 E-POWR-FEED  </v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518" s="7">
         <v>0</v>
       </c>
@@ -52036,7 +52097,7 @@
 E-POWR-FLOR  </v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519" s="7">
         <v>0</v>
       </c>
@@ -52107,7 +52168,7 @@
 E-POWR-FLOR-CRIT  </v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520" s="7">
         <v>0</v>
       </c>
@@ -52178,7 +52239,7 @@
 E-POWR-JBOX  </v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521" s="7">
         <v>0</v>
       </c>
@@ -52249,7 +52310,7 @@
 E-POWR-PANL  </v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" s="7">
         <v>0</v>
       </c>
@@ -52320,7 +52381,7 @@
 E-POWR-POCC  </v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523" s="7">
         <v>0</v>
       </c>
@@ -52391,7 +52452,7 @@
 E-POWR-POI~  </v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524" s="7">
         <v>0</v>
       </c>
@@ -52462,7 +52523,7 @@
 E-POWR-ROOF  </v>
       </c>
     </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A525" s="7">
         <v>0</v>
       </c>
@@ -52533,7 +52594,7 @@
 E-POWR-SWBD  </v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A526" s="7">
         <v>0</v>
       </c>
@@ -52604,7 +52665,7 @@
 E-POWR-UCPT  </v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527" s="7">
         <v>0</v>
       </c>
@@ -52675,7 +52736,7 @@
 E-POWR-URAC  </v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A528" s="7">
         <v>0</v>
       </c>
@@ -52746,7 +52807,7 @@
 E-POWR-WALL  </v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529" s="7">
         <v>0</v>
       </c>
@@ -52817,7 +52878,7 @@
 E-POWR-WALL-CRIT  </v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" s="7">
         <v>0</v>
       </c>
@@ -52888,7 +52949,7 @@
 E-POWR-XFMR-PADM  </v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531" s="7">
         <v>0</v>
       </c>
@@ -52959,7 +53020,7 @@
 E-POWR-XFMR-POLM  </v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532" s="7">
         <v>0</v>
       </c>
@@ -53030,7 +53091,7 @@
 E-PVMD  </v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A533" s="7">
         <v>0</v>
       </c>
@@ -53101,7 +53162,7 @@
 E-SITE  </v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" s="7">
         <v>0</v>
       </c>
@@ -53172,7 +53233,7 @@
 E-SITE-OVHD  </v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A535" s="7">
         <v>0</v>
       </c>
@@ -53243,7 +53304,7 @@
 E-SITE-POLE  </v>
       </c>
     </row>
-    <row r="536" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A536" s="7">
         <v>0</v>
       </c>
@@ -53314,7 +53375,7 @@
 E-SITE-UGND  </v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A537" s="7">
         <v>0</v>
       </c>
@@ -53385,7 +53446,7 @@
 E-SOUN  </v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A538" s="7">
         <v>0</v>
       </c>
@@ -53527,7 +53588,7 @@
 S-BEAM  </v>
       </c>
     </row>
-    <row r="540" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A540" s="7">
         <v>0</v>
       </c>
@@ -53598,7 +53659,7 @@
 S-BEAM-ALUM  </v>
       </c>
     </row>
-    <row r="541" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A541" s="7">
         <v>0</v>
       </c>
@@ -53669,7 +53730,7 @@
 S-BEAM-CONC  </v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A542" s="7">
         <v>0</v>
       </c>
@@ -53740,7 +53801,7 @@
 S-BEAM-STEL  </v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A543" s="7">
         <v>0</v>
       </c>
@@ -53882,7 +53943,7 @@
 S-BRCG  </v>
       </c>
     </row>
-    <row r="545" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A545" s="7">
         <v>0</v>
       </c>
@@ -53953,7 +54014,7 @@
 S-BRCG-ALUM  </v>
       </c>
     </row>
-    <row r="546" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A546" s="7">
         <v>0</v>
       </c>
@@ -54024,7 +54085,7 @@
 S-BRCG-ALUM-HORZ  </v>
       </c>
     </row>
-    <row r="547" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A547" s="7">
         <v>0</v>
       </c>
@@ -54095,7 +54156,7 @@
 S-BRCG-ALUM-VERT  </v>
       </c>
     </row>
-    <row r="548" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A548" s="7">
         <v>0</v>
       </c>
@@ -54166,7 +54227,7 @@
  S-BRCG-METL  </v>
       </c>
     </row>
-    <row r="549" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A549" s="7">
         <v>0</v>
       </c>
@@ -54237,7 +54298,7 @@
 S-BRCG-STEL  </v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A550" s="7">
         <v>0</v>
       </c>
@@ -54308,7 +54369,7 @@
 S-BRCG-STEL-HORZ  </v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551" s="7">
         <v>0</v>
       </c>
@@ -54379,7 +54440,7 @@
 S-BRCG-STEL-VERT  </v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A552" s="7">
         <v>0</v>
       </c>
@@ -54450,7 +54511,7 @@
 S-BRCG-WOOD  </v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553" s="7">
         <v>0</v>
       </c>
@@ -54521,7 +54582,7 @@
 S-BRCG-WOOD-HORZ  </v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554" s="7">
         <v>0</v>
       </c>
@@ -54663,7 +54724,7 @@
 S-COLS  </v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A556" s="7">
         <v>0</v>
       </c>
@@ -54734,7 +54795,7 @@
 S-COLS-ABLT  </v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A557" s="7">
         <v>0</v>
       </c>
@@ -54805,7 +54866,7 @@
 S-COLS-ALUM  </v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A558" s="7">
         <v>0</v>
       </c>
@@ -54876,7 +54937,7 @@
 S-COLS-CONC  </v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559" s="7">
         <v>0</v>
       </c>
@@ -54947,7 +55008,7 @@
 S-COLS-STEL  </v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A560" s="7">
         <v>0</v>
       </c>
@@ -55089,7 +55150,7 @@
 S-DECK  </v>
       </c>
     </row>
-    <row r="562" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A562" s="7">
         <v>0</v>
       </c>
@@ -55160,7 +55221,7 @@
 S-DECK-FLOR  </v>
       </c>
     </row>
-    <row r="563" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A563" s="7">
         <v>0</v>
       </c>
@@ -55231,7 +55292,7 @@
 S-DECK-FLOR-OPNG  </v>
       </c>
     </row>
-    <row r="564" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A564" s="7">
         <v>0</v>
       </c>
@@ -55302,7 +55363,7 @@
 S-DECK-ROOF  </v>
       </c>
     </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565" s="7">
         <v>0</v>
       </c>
@@ -55444,7 +55505,7 @@
 S-DETL  </v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A567" s="7">
         <v>0</v>
       </c>
@@ -55515,7 +55576,7 @@
 S-DETL-HSSS  </v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A568" s="7">
         <v>0</v>
       </c>
@@ -55586,7 +55647,7 @@
 S-DETL-PLYW  </v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569" s="7">
         <v>0</v>
       </c>
@@ -55728,7 +55789,7 @@
 S-FNDN  </v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A571" s="7">
         <v>0</v>
       </c>
@@ -55799,7 +55860,7 @@
 S-FNDN-FTNG  </v>
       </c>
     </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A572" s="7">
         <v>0</v>
       </c>
@@ -55870,7 +55931,7 @@
 S-FNDN-GRBM  </v>
       </c>
     </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A573" s="7">
         <v>0</v>
       </c>
@@ -55941,7 +56002,7 @@
 S-FNDN-PCAP  </v>
       </c>
     </row>
-    <row r="574" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574" s="7">
         <v>0</v>
       </c>
@@ -56012,7 +56073,7 @@
 S-FNDN-PIER  </v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575" s="7">
         <v>0</v>
       </c>
@@ -56083,7 +56144,7 @@
 S-FNDN-PILE  </v>
       </c>
     </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576" s="7">
         <v>0</v>
       </c>
@@ -56154,7 +56215,7 @@
 S-FNDN-RBAR  </v>
       </c>
     </row>
-    <row r="577" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577" s="7">
         <v>0</v>
       </c>
@@ -56225,7 +56286,7 @@
 S-FNDN-RBAR-BOT1  </v>
       </c>
     </row>
-    <row r="578" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A578" s="7">
         <v>0</v>
       </c>
@@ -56296,7 +56357,7 @@
 S-FNDN-RBAR-BOT2  </v>
       </c>
     </row>
-    <row r="579" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579" s="7">
         <v>0</v>
       </c>
@@ -56367,7 +56428,7 @@
 S-FNDN-RBAR-TOP1  </v>
       </c>
     </row>
-    <row r="580" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A580" s="7">
         <v>0</v>
       </c>
@@ -56438,7 +56499,7 @@
 S-FNDN-RBAR-TOP2  </v>
       </c>
     </row>
-    <row r="581" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A581" s="7">
         <v>0</v>
       </c>
@@ -56509,7 +56570,7 @@
 S-FRAM  </v>
       </c>
     </row>
-    <row r="582" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582" s="7">
         <v>0</v>
       </c>
@@ -56722,7 +56783,7 @@
 S-GRID  </v>
       </c>
     </row>
-    <row r="585" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A585" s="7">
         <v>0</v>
       </c>
@@ -56793,7 +56854,7 @@
 S-GRID-EXTR  </v>
       </c>
     </row>
-    <row r="586" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586" s="7">
         <v>0</v>
       </c>
@@ -56864,7 +56925,7 @@
 S-GRID-INTR  </v>
       </c>
     </row>
-    <row r="587" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587" s="7">
         <v>0</v>
       </c>
@@ -56935,7 +56996,7 @@
 S-GRLN  </v>
       </c>
     </row>
-    <row r="588" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588" s="7">
         <v>0</v>
       </c>
@@ -57006,7 +57067,7 @@
 S-GRLN-SURF  </v>
       </c>
     </row>
-    <row r="589" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589" s="7">
         <v>0</v>
       </c>
@@ -57077,7 +57138,7 @@
 S-GRTG  </v>
       </c>
     </row>
-    <row r="590" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590" s="7">
         <v>0</v>
       </c>
@@ -57148,7 +57209,7 @@
 S-GRTG-OVHD  </v>
       </c>
     </row>
-    <row r="591" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A591" s="7">
         <v>0</v>
       </c>
@@ -57219,7 +57280,7 @@
 S-HYDR  </v>
       </c>
     </row>
-    <row r="592" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A592" s="7">
         <v>0</v>
       </c>
@@ -57290,7 +57351,7 @@
 S-JNTS  </v>
       </c>
     </row>
-    <row r="593" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A593" s="7">
         <v>0</v>
       </c>
@@ -57361,7 +57422,7 @@
 S-JNTS-CNTJ  </v>
       </c>
     </row>
-    <row r="594" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A594" s="7">
         <v>0</v>
       </c>
@@ -57432,7 +57493,7 @@
 S-JNTS-CTLJ  </v>
       </c>
     </row>
-    <row r="595" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A595" s="7">
         <v>0</v>
       </c>
@@ -57574,7 +57635,7 @@
 S-JOIS  </v>
       </c>
     </row>
-    <row r="597" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597" s="7">
         <v>0</v>
       </c>
@@ -57716,7 +57777,7 @@
 S-LNTL  </v>
       </c>
     </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599" s="7">
         <v>0</v>
       </c>
@@ -57787,7 +57848,7 @@
 S-PADS  </v>
       </c>
     </row>
-    <row r="600" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600" s="7">
         <v>0</v>
       </c>
@@ -57929,7 +57990,7 @@
 S-PLAT  </v>
       </c>
     </row>
-    <row r="602" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A602" s="7">
         <v>0</v>
       </c>
@@ -58000,7 +58061,7 @@
 S-PLAT-FRMG  </v>
       </c>
     </row>
-    <row r="603" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603" s="7">
         <v>0</v>
       </c>
@@ -58071,7 +58132,7 @@
 S-PLAT-GRTG  </v>
       </c>
     </row>
-    <row r="604" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604" s="7">
         <v>0</v>
       </c>
@@ -58142,7 +58203,7 @@
 S-SIGN  </v>
       </c>
     </row>
-    <row r="605" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A605" s="7">
         <v>0</v>
       </c>
@@ -58213,7 +58274,7 @@
 S-SIGN-BOUY  </v>
       </c>
     </row>
-    <row r="606" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A606" s="7">
         <v>0</v>
       </c>
@@ -58284,7 +58345,7 @@
 S-SIGN-FRMG  </v>
       </c>
     </row>
-    <row r="607" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607" s="7">
         <v>0</v>
       </c>
@@ -58355,7 +58416,7 @@
 S-SIGN-GAGE  </v>
       </c>
     </row>
-    <row r="608" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608" s="7">
         <v>0</v>
       </c>
@@ -58426,7 +58487,7 @@
 S-SIGN-TEXT  </v>
       </c>
     </row>
-    <row r="609" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609" s="7">
         <v>0</v>
       </c>
@@ -58568,7 +58629,7 @@
 S-SLAB  </v>
       </c>
     </row>
-    <row r="611" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611" s="7">
         <v>0</v>
       </c>
@@ -58639,7 +58700,7 @@
 S-SLAB-CONC  </v>
       </c>
     </row>
-    <row r="612" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A612" s="7">
         <v>0</v>
       </c>
@@ -58710,7 +58771,7 @@
 S-SLAB-EDGE  </v>
       </c>
     </row>
-    <row r="613" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A613" s="7">
         <v>0</v>
       </c>
@@ -58781,7 +58842,7 @@
 S-SLAB-OPNG  </v>
       </c>
     </row>
-    <row r="614" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A614" s="7">
         <v>0</v>
       </c>
@@ -58852,7 +58913,7 @@
 S-SLAB-OPNX  </v>
       </c>
     </row>
-    <row r="615" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A615" s="7">
         <v>0</v>
       </c>
@@ -58923,7 +58984,7 @@
 S-SLAB-STEL  </v>
       </c>
     </row>
-    <row r="616" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616" s="7">
         <v>0</v>
       </c>
@@ -59065,7 +59126,7 @@
 S-STIF  </v>
       </c>
     </row>
-    <row r="618" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618" s="7">
         <v>0</v>
       </c>
@@ -59136,7 +59197,7 @@
 S-STIF-LONG  </v>
       </c>
     </row>
-    <row r="619" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A619" s="7">
         <v>0</v>
       </c>
@@ -59278,7 +59339,7 @@
 S-STRS  </v>
       </c>
     </row>
-    <row r="621" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A621" s="7">
         <v>0</v>
       </c>
@@ -59491,7 +59552,7 @@
 S-WALL  </v>
       </c>
     </row>
-    <row r="624" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A624" s="7">
         <v>0</v>
       </c>
@@ -59562,7 +59623,7 @@
 S-WALL-ABOV  </v>
       </c>
     </row>
-    <row r="625" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A625" s="7">
         <v>0</v>
       </c>
@@ -59633,7 +59694,7 @@
 S-WALL-CMUW  </v>
       </c>
     </row>
-    <row r="626" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A626" s="7">
         <v>0</v>
       </c>
@@ -59704,7 +59765,7 @@
 S-WALL-CONC  </v>
       </c>
     </row>
-    <row r="627" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A627" s="7">
         <v>0</v>
       </c>
@@ -59775,7 +59836,7 @@
 S-WALL-MSNW  </v>
       </c>
     </row>
-    <row r="628" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A628" s="7">
         <v>0</v>
       </c>
@@ -59846,7 +59907,7 @@
 S-WALL-PCST  </v>
       </c>
     </row>
-    <row r="629" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A629" s="7">
         <v>0</v>
       </c>
@@ -59917,7 +59978,7 @@
 S-WALL-SHEA  </v>
       </c>
     </row>
-    <row r="630" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A630" s="7">
         <v>0</v>
       </c>
@@ -59988,7 +60049,7 @@
 S-WALL-STEL  </v>
       </c>
     </row>
-    <row r="631" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A631" s="7">
         <v>0</v>
       </c>
@@ -60059,7 +60120,7 @@
 S-WALL-VENR  </v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632" s="7">
         <v>0</v>
       </c>
@@ -60201,7 +60262,7 @@
 V-BLDG  </v>
       </c>
     </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A634" s="7">
         <v>0</v>
       </c>
@@ -60272,7 +60333,7 @@
 V-BLDG-DECK  </v>
       </c>
     </row>
-    <row r="635" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A635" s="7">
         <v>0</v>
       </c>
@@ -60343,7 +60404,7 @@
 V-BLDG-OTLN  </v>
       </c>
     </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A636" s="7">
         <v>0</v>
       </c>
@@ -60414,7 +60475,7 @@
 V-BLDG-OVHD  </v>
       </c>
     </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A637" s="7">
         <v>0</v>
       </c>
@@ -60556,7 +60617,7 @@
 V-BNDY  </v>
       </c>
     </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A639" s="7">
         <v>0</v>
       </c>
@@ -60627,7 +60688,7 @@
 V-BNDY-BORO  </v>
       </c>
     </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640" s="7">
         <v>0</v>
       </c>
@@ -60698,7 +60759,7 @@
 V-BNDY-CITY  </v>
       </c>
     </row>
-    <row r="641" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A641" s="7">
         <v>0</v>
       </c>
@@ -60769,7 +60830,7 @@
 V-BNDY-CNTY  </v>
       </c>
     </row>
-    <row r="642" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642" s="7">
         <v>0</v>
       </c>
@@ -60840,7 +60901,7 @@
 V-BNDY-CORP  </v>
       </c>
     </row>
-    <row r="643" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A643" s="7">
         <v>0</v>
       </c>
@@ -60911,7 +60972,7 @@
 V-BNDY-NATL  </v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A644" s="7">
         <v>0</v>
       </c>
@@ -60982,7 +61043,7 @@
 V-BNDY-PROV  </v>
       </c>
     </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A645" s="7">
         <v>0</v>
       </c>
@@ -61053,7 +61114,7 @@
 V-BNDY-STAT  </v>
       </c>
     </row>
-    <row r="646" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A646" s="7">
         <v>0</v>
       </c>
@@ -61124,7 +61185,7 @@
 V-BNDY-TSHP  </v>
       </c>
     </row>
-    <row r="647" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A647" s="7">
         <v>0</v>
       </c>
@@ -61266,7 +61327,7 @@
 V-BORE  </v>
       </c>
     </row>
-    <row r="649" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649" s="7">
         <v>0</v>
       </c>
@@ -61337,7 +61398,7 @@
 V-BRDG  </v>
       </c>
     </row>
-    <row r="650" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A650" s="7">
         <v>0</v>
       </c>
@@ -61408,7 +61469,7 @@
 V-BRDG-BENT  </v>
       </c>
     </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" s="7">
         <v>0</v>
       </c>
@@ -61479,7 +61540,7 @@
 V-BRDG-CNTR  </v>
       </c>
     </row>
-    <row r="652" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A652" s="7">
         <v>0</v>
       </c>
@@ -61550,7 +61611,7 @@
 V-BRDG-CTLJ  </v>
       </c>
     </row>
-    <row r="653" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A653" s="7">
         <v>0</v>
       </c>
@@ -61621,7 +61682,7 @@
 V-BRDG-DECK  </v>
       </c>
     </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654" s="7">
         <v>0</v>
       </c>
@@ -61692,7 +61753,7 @@
 V-BRDG-GRAL  </v>
       </c>
     </row>
-    <row r="655" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655" s="7">
         <v>0</v>
       </c>
@@ -61763,7 +61824,7 @@
 V-BRKL  </v>
       </c>
     </row>
-    <row r="656" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A656" s="7">
         <v>0</v>
       </c>
@@ -61834,7 +61895,7 @@
 V-BRKL-BOTB  </v>
       </c>
     </row>
-    <row r="657" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A657" s="7">
         <v>0</v>
       </c>
@@ -61905,7 +61966,7 @@
 V-BRKL-FLOW  </v>
       </c>
     </row>
-    <row r="658" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A658" s="7">
         <v>0</v>
       </c>
@@ -61976,7 +62037,7 @@
 V-BRKL-TOPB  </v>
       </c>
     </row>
-    <row r="659" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A659" s="7">
         <v>0</v>
       </c>
@@ -62047,7 +62108,7 @@
 V-BRLN  </v>
       </c>
     </row>
-    <row r="660" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A660" s="7">
         <v>0</v>
       </c>
@@ -62118,7 +62179,7 @@
 V-BZNA  </v>
       </c>
     </row>
-    <row r="661" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A661" s="7">
         <v>0</v>
       </c>
@@ -62189,7 +62250,7 @@
 V-CHAN  </v>
       </c>
     </row>
-    <row r="662" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662" s="7">
         <v>0</v>
       </c>
@@ -62260,7 +62321,7 @@
 V-CHAN-BWTR  </v>
       </c>
     </row>
-    <row r="663" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A663" s="7">
         <v>0</v>
       </c>
@@ -62331,7 +62392,7 @@
 V-CHAN-CNTR  </v>
       </c>
     </row>
-    <row r="664" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664" s="7">
         <v>0</v>
       </c>
@@ -62402,7 +62463,7 @@
 V-CHAN-DACL  </v>
       </c>
     </row>
-    <row r="665" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A665" s="7">
         <v>0</v>
       </c>
@@ -62473,7 +62534,7 @@
 V-CHAN-DOCK  </v>
       </c>
     </row>
-    <row r="666" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A666" s="7">
         <v>0</v>
       </c>
@@ -62544,7 +62605,7 @@
 V-CHAN-NAID  </v>
       </c>
     </row>
-    <row r="667" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A667" s="7">
         <v>0</v>
       </c>
@@ -62615,7 +62676,7 @@
 V-COMM  </v>
       </c>
     </row>
-    <row r="668" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A668" s="7">
         <v>0</v>
       </c>
@@ -62686,7 +62747,7 @@
 V-COMM-MHOL  </v>
       </c>
     </row>
-    <row r="669" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A669" s="7">
         <v>0</v>
       </c>
@@ -62757,7 +62818,7 @@
 V-COMM-OVHD  </v>
       </c>
     </row>
-    <row r="670" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A670" s="7">
         <v>0</v>
       </c>
@@ -62828,7 +62889,7 @@
 V-COMM-POLE  </v>
       </c>
     </row>
-    <row r="671" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A671" s="7">
         <v>0</v>
       </c>
@@ -62970,7 +63031,7 @@
 V-CTRL  </v>
       </c>
     </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A673" s="7">
         <v>0</v>
       </c>
@@ -63041,7 +63102,7 @@
 V-CTRL-BMRK  </v>
       </c>
     </row>
-    <row r="674" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674" s="7">
         <v>0</v>
       </c>
@@ -63112,7 +63173,7 @@
 V-CTRL-FLYS  </v>
       </c>
     </row>
-    <row r="675" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A675" s="7">
         <v>0</v>
       </c>
@@ -63183,7 +63244,7 @@
 V-CTRL-GRID  </v>
       </c>
     </row>
-    <row r="676" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A676" s="7">
         <v>0</v>
       </c>
@@ -63254,7 +63315,7 @@
 V-CTRL-HORZ  </v>
       </c>
     </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A677" s="7">
         <v>0</v>
       </c>
@@ -63325,7 +63386,7 @@
 V-CTRL-HVPT  </v>
       </c>
     </row>
-    <row r="678" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678" s="7">
         <v>0</v>
       </c>
@@ -63396,7 +63457,7 @@
 V-CTRL-PNPT  </v>
       </c>
     </row>
-    <row r="679" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A679" s="7">
         <v>0</v>
       </c>
@@ -63467,7 +63528,7 @@
 V-CTRL-TRAV  </v>
       </c>
     </row>
-    <row r="680" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A680" s="7">
         <v>0</v>
       </c>
@@ -63609,7 +63670,7 @@
 V-DRIV  </v>
       </c>
     </row>
-    <row r="682" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A682" s="7">
         <v>0</v>
       </c>
@@ -63680,7 +63741,7 @@
 V-DRIV-ASPH  </v>
       </c>
     </row>
-    <row r="683" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A683" s="7">
         <v>0</v>
       </c>
@@ -63751,7 +63812,7 @@
 V-DRIV-CNTR  </v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A684" s="7">
         <v>0</v>
       </c>
@@ -63822,7 +63883,7 @@
 V-DRIV-CONC  </v>
       </c>
     </row>
-    <row r="685" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A685" s="7">
         <v>0</v>
       </c>
@@ -63893,7 +63954,7 @@
 V-DRIV-CURB  </v>
       </c>
     </row>
-    <row r="686" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686" s="7">
         <v>0</v>
       </c>
@@ -63964,7 +64025,7 @@
 V-DRIV-FLNE  </v>
       </c>
     </row>
-    <row r="687" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687" s="7">
         <v>0</v>
       </c>
@@ -64035,7 +64096,7 @@
 V-DRIV-GRVL  </v>
       </c>
     </row>
-    <row r="688" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688" s="7">
         <v>0</v>
       </c>
@@ -64106,7 +64167,7 @@
 V-DRIV-MRKG  </v>
       </c>
     </row>
-    <row r="689" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A689" s="7">
         <v>0</v>
       </c>
@@ -64248,7 +64309,7 @@
 V-DTCH  </v>
       </c>
     </row>
-    <row r="691" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691" s="7">
         <v>0</v>
       </c>
@@ -64319,7 +64380,7 @@
 V-DTCH-BOTM  </v>
       </c>
     </row>
-    <row r="692" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A692" s="7">
         <v>0</v>
       </c>
@@ -64390,7 +64451,7 @@
 V-DTCH-CNTR  </v>
       </c>
     </row>
-    <row r="693" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693" s="7">
         <v>0</v>
       </c>
@@ -64461,7 +64522,7 @@
 V-DTCH-EWAT  </v>
       </c>
     </row>
-    <row r="694" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A694" s="7">
         <v>0</v>
       </c>
@@ -64603,7 +64664,7 @@
 V-ESMT  </v>
       </c>
     </row>
-    <row r="696" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A696" s="7">
         <v>0</v>
       </c>
@@ -64674,7 +64735,7 @@
 V-ESMT-ACCS  </v>
       </c>
     </row>
-    <row r="697" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A697" s="7">
         <v>0</v>
       </c>
@@ -64745,7 +64806,7 @@
 V-ESMT-CATV  </v>
       </c>
     </row>
-    <row r="698" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A698" s="7">
         <v>0</v>
       </c>
@@ -64816,7 +64877,7 @@
 V-ESMT-CONS  </v>
       </c>
     </row>
-    <row r="699" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A699" s="7">
         <v>0</v>
       </c>
@@ -64887,7 +64948,7 @@
 V-ESMT-CSTG  </v>
       </c>
     </row>
-    <row r="700" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A700" s="7">
         <v>0</v>
       </c>
@@ -64958,7 +65019,7 @@
 V-ESMT-ELEC  </v>
       </c>
     </row>
-    <row r="701" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A701" s="7">
         <v>0</v>
       </c>
@@ -65029,7 +65090,7 @@
 V-ESMT-FDPL  </v>
       </c>
     </row>
-    <row r="702" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A702" s="7">
         <v>0</v>
       </c>
@@ -65100,7 +65161,7 @@
 V-ESMT-INEG  </v>
       </c>
     </row>
-    <row r="703" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A703" s="7">
         <v>0</v>
       </c>
@@ -65171,7 +65232,7 @@
 V-ESMT-LSCP  </v>
       </c>
     </row>
-    <row r="704" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A704" s="7">
         <v>0</v>
       </c>
@@ -65242,7 +65303,7 @@
 V-ESMT-NGAS  </v>
       </c>
     </row>
-    <row r="705" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A705" s="7">
         <v>0</v>
       </c>
@@ -65313,7 +65374,7 @@
 V-ESMT-PHON  </v>
       </c>
     </row>
-    <row r="706" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A706" s="7">
         <v>0</v>
       </c>
@@ -65384,7 +65445,7 @@
 V-ESMT-ROAD  </v>
       </c>
     </row>
-    <row r="707" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A707" s="7">
         <v>0</v>
       </c>
@@ -65455,7 +65516,7 @@
 V-ESMT-ROAD-PERM  </v>
       </c>
     </row>
-    <row r="708" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A708" s="7">
         <v>0</v>
       </c>
@@ -65526,7 +65587,7 @@
 V-ESMT-ROAD-TEMP  </v>
       </c>
     </row>
-    <row r="709" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A709" s="7">
         <v>0</v>
       </c>
@@ -65597,7 +65658,7 @@
 V-ESMT-RWAY  </v>
       </c>
     </row>
-    <row r="710" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A710" s="7">
         <v>0</v>
       </c>
@@ -65668,7 +65729,7 @@
 V-ESMT-SGHT  </v>
       </c>
     </row>
-    <row r="711" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A711" s="7">
         <v>0</v>
       </c>
@@ -65739,7 +65800,7 @@
 V-ESMT-SSWR  </v>
       </c>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A712" s="7">
         <v>0</v>
       </c>
@@ -65810,7 +65871,7 @@
 V-ESMT-STRM  </v>
       </c>
     </row>
-    <row r="713" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A713" s="7">
         <v>0</v>
       </c>
@@ -65881,7 +65942,7 @@
 V-ESMT-SWMT  </v>
       </c>
     </row>
-    <row r="714" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A714" s="7">
         <v>0</v>
       </c>
@@ -65952,7 +66013,7 @@
 V-ESMT-TRAL  </v>
       </c>
     </row>
-    <row r="715" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A715" s="7">
         <v>0</v>
       </c>
@@ -66023,7 +66084,7 @@
 V-ESMT-UTIL  </v>
       </c>
     </row>
-    <row r="716" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A716" s="7">
         <v>0</v>
       </c>
@@ -66094,7 +66155,7 @@
 V-ESMT-WATR  </v>
       </c>
     </row>
-    <row r="717" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A717" s="7">
         <v>0</v>
       </c>
@@ -66165,7 +66226,7 @@
 V-FLHA  </v>
       </c>
     </row>
-    <row r="718" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A718" s="7">
         <v>0</v>
       </c>
@@ -66236,7 +66297,7 @@
 V-FUEL  </v>
       </c>
     </row>
-    <row r="719" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A719" s="7">
         <v>0</v>
       </c>
@@ -66307,7 +66368,7 @@
 V-FUEL-MHOL  </v>
       </c>
     </row>
-    <row r="720" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A720" s="7">
         <v>0</v>
       </c>
@@ -66378,7 +66439,7 @@
 V-FUEL-PIPE  </v>
       </c>
     </row>
-    <row r="721" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A721" s="7">
         <v>0</v>
       </c>
@@ -66449,7 +66510,7 @@
 V-FUEL-TANK  </v>
       </c>
     </row>
-    <row r="722" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A722" s="7">
         <v>0</v>
       </c>
@@ -66520,7 +66581,7 @@
 V-FUEL-UGND  </v>
       </c>
     </row>
-    <row r="723" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A723" s="7">
         <v>0</v>
       </c>
@@ -66591,7 +66652,7 @@
 V-NGAS  </v>
       </c>
     </row>
-    <row r="724" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A724" s="7">
         <v>0</v>
       </c>
@@ -66662,7 +66723,7 @@
 V-NGAS-MHOL  </v>
       </c>
     </row>
-    <row r="725" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A725" s="7">
         <v>0</v>
       </c>
@@ -66733,7 +66794,7 @@
 V-NGAS-PIPE  </v>
       </c>
     </row>
-    <row r="726" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A726" s="7">
         <v>0</v>
       </c>
@@ -66804,7 +66865,7 @@
 V-NGAS-TANK  </v>
       </c>
     </row>
-    <row r="727" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A727" s="7">
         <v>0</v>
       </c>
@@ -66946,7 +67007,7 @@
 V-NODE  </v>
       </c>
     </row>
-    <row r="729" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A729" s="7">
         <v>0</v>
       </c>
@@ -67017,7 +67078,7 @@
 V-NODE-ABUT  </v>
       </c>
     </row>
-    <row r="730" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A730" s="7">
         <v>0</v>
       </c>
@@ -67088,7 +67149,7 @@
 V-NODE-ACTL  </v>
       </c>
     </row>
-    <row r="731" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A731" s="7">
         <v>0</v>
       </c>
@@ -67159,7 +67220,7 @@
 V-NODE-BLDG  </v>
       </c>
     </row>
-    <row r="732" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A732" s="7">
         <v>0</v>
       </c>
@@ -67230,7 +67291,7 @@
 V-NODE-BLIN  </v>
       </c>
     </row>
-    <row r="733" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A733" s="7">
         <v>0</v>
       </c>
@@ -67301,7 +67362,7 @@
 V-NODE-BRDG  </v>
       </c>
     </row>
-    <row r="734" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A734" s="7">
         <v>0</v>
       </c>
@@ -67372,7 +67433,7 @@
 V-NODE-BRKL  </v>
       </c>
     </row>
-    <row r="735" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A735" s="7">
         <v>0</v>
       </c>
@@ -67443,7 +67504,7 @@
 V-NODE-BROW  </v>
       </c>
     </row>
-    <row r="736" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A736" s="7">
         <v>0</v>
       </c>
@@ -67514,7 +67575,7 @@
 V-NODE-BRSH  </v>
       </c>
     </row>
-    <row r="737" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A737" s="7">
         <v>0</v>
       </c>
@@ -67585,7 +67646,7 @@
 V-NODE-CABL  </v>
       </c>
     </row>
-    <row r="738" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A738" s="7">
         <v>0</v>
       </c>
@@ -67656,7 +67717,7 @@
 V-NODE-CURB  </v>
       </c>
     </row>
-    <row r="739" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A739" s="7">
         <v>0</v>
       </c>
@@ -67727,7 +67788,7 @@
 V-NODE-DASP  </v>
       </c>
     </row>
-    <row r="740" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A740" s="7">
         <v>0</v>
       </c>
@@ -67798,7 +67859,7 @@
 V-NODE-DECK  </v>
       </c>
     </row>
-    <row r="741" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A741" s="7">
         <v>0</v>
       </c>
@@ -67869,7 +67930,7 @@
 V-NODE-DRIV  </v>
       </c>
     </row>
-    <row r="742" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A742" s="7">
         <v>0</v>
       </c>
@@ -67940,7 +68001,7 @@
 V-NODE-EASP  </v>
       </c>
     </row>
-    <row r="743" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A743" s="7">
         <v>0</v>
       </c>
@@ -68011,7 +68072,7 @@
 V-NODE-EXPJ  </v>
       </c>
     </row>
-    <row r="744" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A744" s="7">
         <v>0</v>
       </c>
@@ -68082,7 +68143,7 @@
 V-NODE-GRND  </v>
       </c>
     </row>
-    <row r="745" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A745" s="7">
         <v>0</v>
       </c>
@@ -68153,7 +68214,7 @@
 V-NODE-MHOL  </v>
       </c>
     </row>
-    <row r="746" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A746" s="7">
         <v>0</v>
       </c>
@@ -68224,7 +68285,7 @@
 V-NODE-MRKG  </v>
       </c>
     </row>
-    <row r="747" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A747" s="7">
         <v>0</v>
       </c>
@@ -68295,7 +68356,7 @@
 V-NODE-NGAS  </v>
       </c>
     </row>
-    <row r="748" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A748" s="7">
         <v>0</v>
       </c>
@@ -68366,7 +68427,7 @@
 V-NODE-PASP  </v>
       </c>
     </row>
-    <row r="749" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A749" s="7">
         <v>0</v>
       </c>
@@ -68437,7 +68498,7 @@
 V-NODE-PIPE  </v>
       </c>
     </row>
-    <row r="750" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A750" s="7">
         <v>0</v>
       </c>
@@ -68508,7 +68569,7 @@
 V-NODE-POLE  </v>
       </c>
     </row>
-    <row r="751" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A751" s="7">
         <v>0</v>
       </c>
@@ -68579,7 +68640,7 @@
 V-NODE-PVMT  </v>
       </c>
     </row>
-    <row r="752" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A752" s="7">
         <v>0</v>
       </c>
@@ -68650,7 +68711,7 @@
 V-NODE-SIGN  </v>
       </c>
     </row>
-    <row r="753" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A753" s="7">
         <v>0</v>
       </c>
@@ -68721,7 +68782,7 @@
 V-NODE-SSWR  </v>
       </c>
     </row>
-    <row r="754" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A754" s="7">
         <v>0</v>
       </c>
@@ -68792,7 +68853,7 @@
 V-NODE-STRM  </v>
       </c>
     </row>
-    <row r="755" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A755" s="7">
         <v>0</v>
       </c>
@@ -68863,7 +68924,7 @@
 V-NODE-SWLK  </v>
       </c>
     </row>
-    <row r="756" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A756" s="7">
         <v>0</v>
       </c>
@@ -68934,7 +68995,7 @@
 V-NODE-TREE  </v>
       </c>
     </row>
-    <row r="757" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757" s="7">
         <v>0</v>
       </c>
@@ -69005,7 +69066,7 @@
 V-NODE-TROW  </v>
       </c>
     </row>
-    <row r="758" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A758" s="7">
         <v>0</v>
       </c>
@@ -69147,7 +69208,7 @@
 V-POWR  </v>
       </c>
     </row>
-    <row r="760" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A760" s="7">
         <v>0</v>
       </c>
@@ -69218,7 +69279,7 @@
 V-POWR-FENC  </v>
       </c>
     </row>
-    <row r="761" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A761" s="7">
         <v>0</v>
       </c>
@@ -69289,7 +69350,7 @@
 V-POWR-INST  </v>
       </c>
     </row>
-    <row r="762" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A762" s="7">
         <v>0</v>
       </c>
@@ -69360,7 +69421,7 @@
 V-POWR-MHOL  </v>
       </c>
     </row>
-    <row r="763" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A763" s="7">
         <v>0</v>
       </c>
@@ -69431,7 +69492,7 @@
 V-POWR-OVHD  </v>
       </c>
     </row>
-    <row r="764" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A764" s="7">
         <v>0</v>
       </c>
@@ -69502,7 +69563,7 @@
 V-POWR-POLE  </v>
       </c>
     </row>
-    <row r="765" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A765" s="7">
         <v>0</v>
       </c>
@@ -69573,7 +69634,7 @@
 V-POWR-STRC  </v>
       </c>
     </row>
-    <row r="766" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A766" s="7">
         <v>0</v>
       </c>
@@ -69715,7 +69776,7 @@
 V-PRKG  </v>
       </c>
     </row>
-    <row r="768" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A768" s="7">
         <v>0</v>
       </c>
@@ -69786,7 +69847,7 @@
 V-PRKG-ASPH  </v>
       </c>
     </row>
-    <row r="769" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A769" s="7">
         <v>0</v>
       </c>
@@ -69857,7 +69918,7 @@
 V-PRKG-CNTR  </v>
       </c>
     </row>
-    <row r="770" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A770" s="7">
         <v>0</v>
       </c>
@@ -69928,7 +69989,7 @@
 V-PRKG-CONC  </v>
       </c>
     </row>
-    <row r="771" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A771" s="7">
         <v>0</v>
       </c>
@@ -69999,7 +70060,7 @@
 V-PRKG-CURB  </v>
       </c>
     </row>
-    <row r="772" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A772" s="7">
         <v>0</v>
       </c>
@@ -70070,7 +70131,7 @@
 V-PRKG-DRAN  </v>
       </c>
     </row>
-    <row r="773" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A773" s="7">
         <v>0</v>
       </c>
@@ -70141,7 +70202,7 @@
 V-PRKG-FLNE  </v>
       </c>
     </row>
-    <row r="774" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A774" s="7">
         <v>0</v>
       </c>
@@ -70212,7 +70273,7 @@
 V-PRKG-GRVL  </v>
       </c>
     </row>
-    <row r="775" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A775" s="7">
         <v>0</v>
       </c>
@@ -70283,7 +70344,7 @@
 V-PRKG-MRKG  </v>
       </c>
     </row>
-    <row r="776" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A776" s="7">
         <v>0</v>
       </c>
@@ -70354,7 +70415,7 @@
 V-PRKG-STRP  </v>
       </c>
     </row>
-    <row r="777" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A777" s="7">
         <v>0</v>
       </c>
@@ -70496,7 +70557,7 @@
 V-PROP  </v>
       </c>
     </row>
-    <row r="779" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A779" s="7">
         <v>0</v>
       </c>
@@ -70567,7 +70628,7 @@
 V-PROP-LINE  </v>
       </c>
     </row>
-    <row r="780" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A780" s="7">
         <v>0</v>
       </c>
@@ -70638,7 +70699,7 @@
 V-PROP-QTRS  </v>
       </c>
     </row>
-    <row r="781" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A781" s="7">
         <v>0</v>
       </c>
@@ -70709,7 +70770,7 @@
 V-PROP-RSRV  </v>
       </c>
     </row>
-    <row r="782" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A782" s="7">
         <v>0</v>
       </c>
@@ -70780,7 +70841,7 @@
 V-PROP-SBCK  </v>
       </c>
     </row>
-    <row r="783" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A783" s="7">
         <v>0</v>
       </c>
@@ -70851,7 +70912,7 @@
 V-PROP-SECT  </v>
       </c>
     </row>
-    <row r="784" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A784" s="7">
         <v>0</v>
       </c>
@@ -70922,7 +70983,7 @@
 V-PROP-SUBD  </v>
       </c>
     </row>
-    <row r="785" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A785" s="7">
         <v>0</v>
       </c>
@@ -70993,7 +71054,7 @@
 V-PROP-SXTS  </v>
       </c>
     </row>
-    <row r="786" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A786" s="7">
         <v>0</v>
       </c>
@@ -71064,7 +71125,7 @@
 V-PVMT  </v>
       </c>
     </row>
-    <row r="787" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A787" s="7">
         <v>0</v>
       </c>
@@ -71135,7 +71196,7 @@
 V-PVMT-ASPH  </v>
       </c>
     </row>
-    <row r="788" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A788" s="7">
         <v>0</v>
       </c>
@@ -71206,7 +71267,7 @@
 V-PVMT-CONC  </v>
       </c>
     </row>
-    <row r="789" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A789" s="7">
         <v>0</v>
       </c>
@@ -71277,7 +71338,7 @@
 V-PVMT-GRVL  </v>
       </c>
     </row>
-    <row r="790" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A790" s="7">
         <v>0</v>
       </c>
@@ -71348,7 +71409,7 @@
 V-RAIL  </v>
       </c>
     </row>
-    <row r="791" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A791" s="7">
         <v>0</v>
       </c>
@@ -71419,7 +71480,7 @@
 V-RAIL-CNTR  </v>
       </c>
     </row>
-    <row r="792" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A792" s="7">
         <v>0</v>
       </c>
@@ -71490,7 +71551,7 @@
 V-RAIL-EQPM  </v>
       </c>
     </row>
-    <row r="793" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A793" s="7">
         <v>0</v>
       </c>
@@ -71632,7 +71693,7 @@
 V-RIVR  </v>
       </c>
     </row>
-    <row r="795" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A795" s="7">
         <v>0</v>
       </c>
@@ -71703,7 +71764,7 @@
 V-RIVR-BOTM  </v>
       </c>
     </row>
-    <row r="796" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A796" s="7">
         <v>0</v>
       </c>
@@ -71774,7 +71835,7 @@
 V-RIVR-CNTR  </v>
       </c>
     </row>
-    <row r="797" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A797" s="7">
         <v>0</v>
       </c>
@@ -71845,7 +71906,7 @@
 V-RIVR-EDGE  </v>
       </c>
     </row>
-    <row r="798" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A798" s="7">
         <v>0</v>
       </c>
@@ -71987,7 +72048,7 @@
 V-ROAD  </v>
       </c>
     </row>
-    <row r="800" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A800" s="7">
         <v>0</v>
       </c>
@@ -72058,7 +72119,7 @@
 V-ROAD-ASPH  </v>
       </c>
     </row>
-    <row r="801" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A801" s="7">
         <v>0</v>
       </c>
@@ -72129,7 +72190,7 @@
 V-ROAD-CNTR  </v>
       </c>
     </row>
-    <row r="802" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A802" s="7">
         <v>0</v>
       </c>
@@ -72200,7 +72261,7 @@
 V-ROAD-CONC  </v>
       </c>
     </row>
-    <row r="803" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A803" s="7">
         <v>0</v>
       </c>
@@ -72271,7 +72332,7 @@
 V-ROAD-CURB  </v>
       </c>
     </row>
-    <row r="804" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A804" s="7">
         <v>0</v>
       </c>
@@ -72342,7 +72403,7 @@
 V-ROAD-FLNE  </v>
       </c>
     </row>
-    <row r="805" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A805" s="7">
         <v>0</v>
       </c>
@@ -72413,7 +72474,7 @@
 V-ROAD-GRVL  </v>
       </c>
     </row>
-    <row r="806" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A806" s="7">
         <v>0</v>
       </c>
@@ -72484,7 +72545,7 @@
 V-ROAD-MRKG  </v>
       </c>
     </row>
-    <row r="807" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A807" s="7">
         <v>0</v>
       </c>
@@ -72626,7 +72687,7 @@
 V-RRAP  </v>
       </c>
     </row>
-    <row r="809" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A809" s="7">
         <v>0</v>
       </c>
@@ -72697,7 +72758,7 @@
 V-RWAY  </v>
       </c>
     </row>
-    <row r="810" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A810" s="7">
         <v>0</v>
       </c>
@@ -72768,7 +72829,7 @@
 V-RWAY-CNTR  </v>
       </c>
     </row>
-    <row r="811" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A811" s="7">
         <v>0</v>
       </c>
@@ -72839,7 +72900,7 @@
 V-RWAY-CTLA  </v>
       </c>
     </row>
-    <row r="812" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A812" s="7">
         <v>0</v>
       </c>
@@ -72910,7 +72971,7 @@
 V-RWAY-LINE  </v>
       </c>
     </row>
-    <row r="813" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A813" s="7">
         <v>0</v>
       </c>
@@ -72981,7 +73042,7 @@
 V-RWAY-LMTA  </v>
       </c>
     </row>
-    <row r="814" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A814" s="7">
         <v>0</v>
       </c>
@@ -73052,7 +73113,7 @@
 V-RWAY-MRKR  </v>
       </c>
     </row>
-    <row r="815" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A815" s="7">
         <v>0</v>
       </c>
@@ -73194,7 +73255,7 @@
 V-SITE  </v>
       </c>
     </row>
-    <row r="817" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A817" s="7">
         <v>0</v>
       </c>
@@ -73265,7 +73326,7 @@
 V-SITE-EWAT  </v>
       </c>
     </row>
-    <row r="818" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818" s="7">
         <v>0</v>
       </c>
@@ -73336,7 +73397,7 @@
 V-SITE-FENC  </v>
       </c>
     </row>
-    <row r="819" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A819" s="7">
         <v>0</v>
       </c>
@@ -73407,7 +73468,7 @@
 V-SITE-ROCK  </v>
       </c>
     </row>
-    <row r="820" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A820" s="7">
         <v>0</v>
       </c>
@@ -73478,7 +73539,7 @@
 V-SITE-RTWL  </v>
       </c>
     </row>
-    <row r="821" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821" s="7">
         <v>0</v>
       </c>
@@ -73549,7 +73610,7 @@
 V-SITE-SIGN  </v>
       </c>
     </row>
-    <row r="822" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A822" s="7">
         <v>0</v>
       </c>
@@ -73691,7 +73752,7 @@
 V-SSWR  </v>
       </c>
     </row>
-    <row r="824" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824" s="7">
         <v>0</v>
       </c>
@@ -73762,7 +73823,7 @@
 V-SSWR-MHOL  </v>
       </c>
     </row>
-    <row r="825" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825" s="7">
         <v>0</v>
       </c>
@@ -73833,7 +73894,7 @@
 V-SSWR-PIPE  </v>
       </c>
     </row>
-    <row r="826" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826" s="7">
         <v>0</v>
       </c>
@@ -73904,7 +73965,7 @@
 V-SSWR-STRC  </v>
       </c>
     </row>
-    <row r="827" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A827" s="7">
         <v>0</v>
       </c>
@@ -73975,7 +74036,7 @@
 V-SSWR-UGND  </v>
       </c>
     </row>
-    <row r="828" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A828" s="7">
         <v>0</v>
       </c>
@@ -74046,7 +74107,7 @@
 V-STEM  </v>
       </c>
     </row>
-    <row r="829" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829" s="7">
         <v>0</v>
       </c>
@@ -74117,7 +74178,7 @@
 V-STEM-INST  </v>
       </c>
     </row>
-    <row r="830" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A830" s="7">
         <v>0</v>
       </c>
@@ -74188,7 +74249,7 @@
 V-STEM-MHOL  </v>
       </c>
     </row>
-    <row r="831" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A831" s="7">
         <v>0</v>
       </c>
@@ -74259,7 +74320,7 @@
 V-STEM-PIPE  </v>
       </c>
     </row>
-    <row r="832" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A832" s="7">
         <v>0</v>
       </c>
@@ -74330,7 +74391,7 @@
 V-STEM-STRC  </v>
       </c>
     </row>
-    <row r="833" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833" s="7">
         <v>0</v>
       </c>
@@ -74472,7 +74533,7 @@
 V-STRM  </v>
       </c>
     </row>
-    <row r="835" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835" s="7">
         <v>0</v>
       </c>
@@ -74543,7 +74604,7 @@
 V-STRM-DTCH  </v>
       </c>
     </row>
-    <row r="836" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836" s="7">
         <v>0</v>
       </c>
@@ -74614,7 +74675,7 @@
 V-STRM-MHOL  </v>
       </c>
     </row>
-    <row r="837" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837" s="7">
         <v>0</v>
       </c>
@@ -74685,7 +74746,7 @@
 V-STRM-PIPE  </v>
       </c>
     </row>
-    <row r="838" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="838" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A838" s="7">
         <v>0</v>
       </c>
@@ -74756,7 +74817,7 @@
 V-STRM-POND  </v>
       </c>
     </row>
-    <row r="839" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A839" s="7">
         <v>0</v>
       </c>
@@ -74827,7 +74888,7 @@
 V-STRM-STRC  </v>
       </c>
     </row>
-    <row r="840" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A840" s="7">
         <v>0</v>
       </c>
@@ -74969,7 +75030,7 @@
 V-SURV  </v>
       </c>
     </row>
-    <row r="842" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842" s="7">
         <v>0</v>
       </c>
@@ -75111,7 +75172,7 @@
 V-SWLK  </v>
       </c>
     </row>
-    <row r="844" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A844" s="7">
         <v>0</v>
       </c>
@@ -75182,7 +75243,7 @@
 V-SWLK-ASPH  </v>
       </c>
     </row>
-    <row r="845" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845" s="7">
         <v>0</v>
       </c>
@@ -75324,7 +75385,7 @@
 V-TOPO  </v>
       </c>
     </row>
-    <row r="847" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A847" s="7">
         <v>0</v>
       </c>
@@ -75395,7 +75456,7 @@
 V-TOPO-EWAT  </v>
       </c>
     </row>
-    <row r="848" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A848" s="7">
         <v>0</v>
       </c>
@@ -75466,7 +75527,7 @@
 V-TOPO-GRID  </v>
       </c>
     </row>
-    <row r="849" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849" s="7">
         <v>0</v>
       </c>
@@ -75537,7 +75598,7 @@
 V-TOPO-MAJR  </v>
       </c>
     </row>
-    <row r="850" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A850" s="7">
         <v>0</v>
       </c>
@@ -75608,7 +75669,7 @@
 V-TOPO-MINR  </v>
       </c>
     </row>
-    <row r="851" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A851" s="7">
         <v>0</v>
       </c>
@@ -75679,7 +75740,7 @@
 V-TOPO-SOUN  </v>
       </c>
     </row>
-    <row r="852" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="852" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A852" s="7">
         <v>0</v>
       </c>
@@ -75821,7 +75882,7 @@
 V-UNID  </v>
       </c>
     </row>
-    <row r="854" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854" s="7">
         <v>0</v>
       </c>
@@ -75892,7 +75953,7 @@
 V-UNID-CABL  </v>
       </c>
     </row>
-    <row r="855" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A855" s="7">
         <v>0</v>
       </c>
@@ -75963,7 +76024,7 @@
 V-UNID-PIPE  </v>
       </c>
     </row>
-    <row r="856" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A856" s="7">
         <v>0</v>
       </c>
@@ -76034,7 +76095,7 @@
 V-UNID-TANK  </v>
       </c>
     </row>
-    <row r="857" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A857" s="7">
         <v>0</v>
       </c>
@@ -76105,7 +76166,7 @@
 V-UNID-UTIL  </v>
       </c>
     </row>
-    <row r="858" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858" s="7">
         <v>0</v>
       </c>
@@ -76176,7 +76237,7 @@
 V-UNID-UTIL-OVHD  </v>
       </c>
     </row>
-    <row r="859" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A859" s="7">
         <v>0</v>
       </c>
@@ -76318,7 +76379,7 @@
 V-WATR  </v>
       </c>
     </row>
-    <row r="861" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861" s="7">
         <v>0</v>
       </c>
@@ -76389,7 +76450,7 @@
 V-WATR-INST  </v>
       </c>
     </row>
-    <row r="862" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862" s="7">
         <v>0</v>
       </c>
@@ -76460,7 +76521,7 @@
 V-WATR-MHOL  </v>
       </c>
     </row>
-    <row r="863" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A863" s="7">
         <v>0</v>
       </c>
@@ -76531,7 +76592,7 @@
 V-WATR-PIPE  </v>
       </c>
     </row>
-    <row r="864" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A864" s="7">
         <v>0</v>
       </c>
@@ -76602,7 +76663,7 @@
 V-WATR-STRC  </v>
       </c>
     </row>
-    <row r="865" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A865" s="7">
         <v>0</v>
       </c>
@@ -76674,7 +76735,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M865" xr:uid="{2CA60E93-22D8-4E5B-AC58-CD121D74306E}"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bDLe82qqSzJV1O68gjix3d5e8dLx7RYBtwcWA4KmNymteHqea+9k7d3AnVRJc77x4Gxt3FN1EqhcX9CTsR1rXA==" saltValue="vouAddI4TTuTvC8E1IVvMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A3:M865" xr:uid="{2CA60E93-22D8-4E5B-AC58-CD121D74306E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
@@ -76751,6 +76819,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="85273d68-90a1-4455-8abc-8dc013f26eed" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071D7322AB1F17A44BE7FE5C8D995D347" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a34332f796df4527adfd50cc06e73342">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256" xmlns:ns4="85273d68-90a1-4455-8abc-8dc013f26eed" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c194d0ced072f42b9bcad298aae9931c" ns3:_="" ns4:_="">
     <xsd:import namespace="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
@@ -77003,24 +77088,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E66BA-068D-48E6-8C46-D96E2B6CA4E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="85273d68-90a1-4455-8abc-8dc013f26eed"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="85273d68-90a1-4455-8abc-8dc013f26eed" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1556B-F96F-4768-A5C1-84E54B001EF8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17A2906D-5802-451E-9C96-391B04836A24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -77037,29 +77130,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1556B-F96F-4768-A5C1-84E54B001EF8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E66BA-068D-48E6-8C46-D96E2B6CA4E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="85273d68-90a1-4455-8abc-8dc013f26eed"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>